--- a/reports/Deliverable D01 (Level C)/Group/Planning-Template.xlsx
+++ b/reports/Deliverable D01 (Level C)/Group/Planning-Template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="d:\Courses\DT\25-26\Workspace-26\Scrapbook\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Javier\Downloads\Workspace-26\Scrapbook\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01042112-DBA6-485C-938E-1EDF0CFB59D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93F57BBF-E1E9-48C8-9A46-8F9C353399AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14856" xr2:uid="{683E09B8-1D94-4905-B116-9D998A46AAA3}"/>
+    <workbookView xWindow="10718" yWindow="0" windowWidth="10965" windowHeight="12863" activeTab="2" xr2:uid="{683E09B8-1D94-4905-B116-9D998A46AAA3}"/>
   </bookViews>
   <sheets>
     <sheet name="Copyright" sheetId="10" r:id="rId1"/>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="100">
   <si>
     <t xml:space="preserve">  Enter configuration data in these cells</t>
   </si>
@@ -335,6 +335,30 @@
   </si>
   <si>
     <t xml:space="preserve"> Data computed automatically.  Do not change them.</t>
+  </si>
+  <si>
+    <t>Realizar el chartering report.</t>
+  </si>
+  <si>
+    <t>Inicializar el repositorio en GitHub.</t>
+  </si>
+  <si>
+    <t>Instanciar el proyecto base "Hello-World" como "Acme-Starters-C"</t>
+  </si>
+  <si>
+    <t>Personalizar el proyecto con las tareas  que vienen descritas en la presetación S03.</t>
+  </si>
+  <si>
+    <t>T0005/D</t>
+  </si>
+  <si>
+    <t>Revisar tarea.</t>
+  </si>
+  <si>
+    <t>Realizar el primer reparto de tareas referidas al Requisito Cero.</t>
+  </si>
+  <si>
+    <t>Rellenar el formulario de identificación.</t>
   </si>
 </sst>
 </file>
@@ -1044,7 +1068,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -1361,12 +1385,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0BB59C7-21D2-4063-B60E-B9743CBEBCDD}">
   <dimension ref="B2:J12"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="16384" width="9.1328125" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B2" s="55" t="s">
         <v>78</v>
       </c>
@@ -1379,7 +1403,7 @@
       <c r="I2" s="55"/>
       <c r="J2" s="55"/>
     </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B4" s="53" t="s">
         <v>2</v>
       </c>
@@ -1392,7 +1416,7 @@
       <c r="I4" s="54"/>
       <c r="J4" s="54"/>
     </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B5" s="54"/>
       <c r="C5" s="54"/>
       <c r="D5" s="54"/>
@@ -1403,7 +1427,7 @@
       <c r="I5" s="54"/>
       <c r="J5" s="54"/>
     </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B6" s="54"/>
       <c r="C6" s="54"/>
       <c r="D6" s="54"/>
@@ -1414,7 +1438,7 @@
       <c r="I6" s="54"/>
       <c r="J6" s="54"/>
     </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B7" s="54"/>
       <c r="C7" s="54"/>
       <c r="D7" s="54"/>
@@ -1425,7 +1449,7 @@
       <c r="I7" s="54"/>
       <c r="J7" s="54"/>
     </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B8" s="54"/>
       <c r="C8" s="54"/>
       <c r="D8" s="54"/>
@@ -1436,7 +1460,7 @@
       <c r="I8" s="54"/>
       <c r="J8" s="54"/>
     </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B9" s="54"/>
       <c r="C9" s="54"/>
       <c r="D9" s="54"/>
@@ -1447,7 +1471,7 @@
       <c r="I9" s="54"/>
       <c r="J9" s="54"/>
     </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B10" s="54"/>
       <c r="C10" s="54"/>
       <c r="D10" s="54"/>
@@ -1458,7 +1482,7 @@
       <c r="I10" s="54"/>
       <c r="J10" s="54"/>
     </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B11" s="54"/>
       <c r="C11" s="54"/>
       <c r="D11" s="54"/>
@@ -1469,7 +1493,7 @@
       <c r="I11" s="54"/>
       <c r="J11" s="54"/>
     </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B12" s="54"/>
       <c r="C12" s="54"/>
       <c r="D12" s="54"/>
@@ -1493,9 +1517,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BB35E99-EEE5-419C-812A-054E20454F46}">
   <dimension ref="B2:J12"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B2" s="55" t="s">
         <v>4</v>
       </c>
@@ -1508,7 +1532,7 @@
       <c r="I2" s="55"/>
       <c r="J2" s="55"/>
     </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B3" s="2"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
@@ -1519,7 +1543,7 @@
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
     </row>
-    <row r="4" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B4" s="53" t="s">
         <v>3</v>
       </c>
@@ -1532,7 +1556,7 @@
       <c r="I4" s="53"/>
       <c r="J4" s="53"/>
     </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B5" s="53"/>
       <c r="C5" s="53"/>
       <c r="D5" s="53"/>
@@ -1543,7 +1567,7 @@
       <c r="I5" s="53"/>
       <c r="J5" s="53"/>
     </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B6" s="53"/>
       <c r="C6" s="53"/>
       <c r="D6" s="53"/>
@@ -1554,7 +1578,7 @@
       <c r="I6" s="53"/>
       <c r="J6" s="53"/>
     </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
@@ -1565,7 +1589,7 @@
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
     </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B8" s="39"/>
       <c r="C8" s="40" t="s">
         <v>79</v>
@@ -1578,7 +1602,7 @@
       <c r="I8" s="1"/>
       <c r="J8" s="1"/>
     </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B9" s="4"/>
       <c r="C9" s="56" t="s">
         <v>0</v>
@@ -1591,7 +1615,7 @@
       <c r="I9" s="56"/>
       <c r="J9" s="56"/>
     </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B10" s="49"/>
       <c r="C10" s="56" t="s">
         <v>90</v>
@@ -1604,7 +1628,7 @@
       <c r="I10" s="56"/>
       <c r="J10" s="56"/>
     </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B11" s="50"/>
       <c r="C11" s="48" t="s">
         <v>91</v>
@@ -1617,7 +1641,7 @@
       <c r="I11" s="48"/>
       <c r="J11" s="48"/>
     </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B12" s="3"/>
       <c r="C12" s="56" t="s">
         <v>1</v>
@@ -1644,14 +1668,14 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34CF3CD5-8D08-494F-856F-AF84E30F468A}">
-  <dimension ref="B2:P110"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="B2:P112"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="3" max="15" width="18.88671875" customWidth="1"/>
-    <col min="16" max="16" width="64.5546875" customWidth="1"/>
+    <col min="3" max="15" width="18.86328125" customWidth="1"/>
+    <col min="16" max="16" width="64.53125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:16" x14ac:dyDescent="0.45">
       <c r="C2" s="55" t="s">
         <v>5</v>
       </c>
@@ -1669,7 +1693,7 @@
       <c r="O2" s="55"/>
       <c r="P2" s="55"/>
     </row>
-    <row r="4" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C4" s="53" t="s">
         <v>75</v>
       </c>
@@ -1687,7 +1711,7 @@
       <c r="O4" s="53"/>
       <c r="P4" s="53"/>
     </row>
-    <row r="5" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:16" x14ac:dyDescent="0.45">
       <c r="C5" s="5"/>
       <c r="D5" s="5"/>
       <c r="E5" s="5"/>
@@ -1703,7 +1727,7 @@
       <c r="O5" s="5"/>
       <c r="P5" s="5"/>
     </row>
-    <row r="6" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:16" x14ac:dyDescent="0.45">
       <c r="C6" s="57" t="s">
         <v>68</v>
       </c>
@@ -1711,8 +1735,8 @@
         <v>69</v>
       </c>
       <c r="E6" s="35">
-        <f>SUM(N11:N110)</f>
-        <v>0</v>
+        <f>SUM(N12:N112)</f>
+        <v>277.5</v>
       </c>
       <c r="F6" s="5"/>
       <c r="G6" s="5"/>
@@ -1726,18 +1750,18 @@
       <c r="O6" s="5"/>
       <c r="P6" s="5"/>
     </row>
-    <row r="7" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:16" x14ac:dyDescent="0.45">
       <c r="C7" s="57"/>
       <c r="D7" s="11" t="s">
         <v>70</v>
       </c>
       <c r="E7" s="36">
-        <f>SUM(O11:O110)</f>
-        <v>0</v>
+        <f>SUM(O12:O112)</f>
+        <v>237.5</v>
       </c>
       <c r="J7" s="37"/>
     </row>
-    <row r="9" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B9" s="6"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
@@ -1760,7 +1784,7 @@
       <c r="O9" s="58"/>
       <c r="P9" s="7"/>
     </row>
-    <row r="10" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B10" s="8" t="s">
         <v>66</v>
       </c>
@@ -1807,224 +1831,342 @@
         <v>67</v>
       </c>
     </row>
-    <row r="11" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B11" s="41">
         <v>1</v>
       </c>
       <c r="C11" s="42" t="str">
         <f>IF(ISBLANK(D11), "", _xlfn.CONCAT("T", TEXT(B11, "0000"), "/", VLOOKUP(D11, Internal!$B$35:C$39, 2, FALSE), IF(OR(D11="QA", D11="Revision"), _xlfn.CONCAT("/", H11), "")))</f>
-        <v/>
-      </c>
-      <c r="D11" s="44"/>
-      <c r="E11" s="43"/>
-      <c r="F11" s="43"/>
-      <c r="G11" s="44"/>
+        <v>T0001/M</v>
+      </c>
+      <c r="D11" s="44" t="s">
+        <v>64</v>
+      </c>
+      <c r="E11" s="43" t="s">
+        <v>80</v>
+      </c>
+      <c r="F11" s="43" t="s">
+        <v>23</v>
+      </c>
+      <c r="G11" s="44" t="s">
+        <v>20</v>
+      </c>
       <c r="H11" s="43"/>
-      <c r="I11" s="46"/>
-      <c r="J11" s="46"/>
+      <c r="I11" s="46">
+        <v>46056.354166666664</v>
+      </c>
+      <c r="J11" s="46">
+        <v>46056.416666666664</v>
+      </c>
       <c r="K11" s="45" t="str">
         <f ca="1">IF(OR(I11="",J11=""),"",IF(AND(J11&lt;&gt;"",I11&gt;=NOW()),"Planned",IF(AND(J11&lt;&gt;"",J11&lt;NOW()),"Completed","Ongoing")))</f>
-        <v/>
-      </c>
-      <c r="L11" s="47"/>
-      <c r="M11" s="47"/>
-      <c r="N11" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L11" s="47">
+        <v>2</v>
+      </c>
+      <c r="M11" s="47">
+        <v>1.5</v>
+      </c>
+      <c r="N11" s="45">
         <f>IF(ISBLANK(L11), "", L11*VLOOKUP($F11,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O11" s="45" t="str">
+        <v>100</v>
+      </c>
+      <c r="O11" s="45">
         <f>IF(ISBLANK(M11), "", M11*VLOOKUP($F11,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P11" s="44"/>
-    </row>
-    <row r="12" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>75</v>
+      </c>
+      <c r="P11" s="44" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="12" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B12" s="41">
         <v>2</v>
       </c>
       <c r="C12" s="42" t="str">
         <f>IF(ISBLANK(D12), "", _xlfn.CONCAT("T", TEXT(B12, "0000"), "/", VLOOKUP(D12, Internal!$B$35:C$39, 2, FALSE), IF(OR(D12="QA", D12="Revision"), _xlfn.CONCAT("/", H12), "")))</f>
-        <v/>
-      </c>
-      <c r="D12" s="44"/>
-      <c r="E12" s="43"/>
-      <c r="F12" s="43"/>
-      <c r="G12" s="44"/>
+        <v>T0002/M</v>
+      </c>
+      <c r="D12" s="44" t="s">
+        <v>64</v>
+      </c>
+      <c r="E12" s="43" t="s">
+        <v>80</v>
+      </c>
+      <c r="F12" s="43" t="s">
+        <v>23</v>
+      </c>
+      <c r="G12" s="44" t="s">
+        <v>36</v>
+      </c>
       <c r="H12" s="43"/>
-      <c r="I12" s="46"/>
-      <c r="J12" s="46"/>
+      <c r="I12" s="46">
+        <v>46056.520833333336</v>
+      </c>
+      <c r="J12" s="46">
+        <v>46057.604166666664</v>
+      </c>
       <c r="K12" s="45" t="str">
-        <f t="shared" ref="K12:K75" ca="1" si="0">IF(OR(I12="",J12=""),"",IF(AND(J12&lt;&gt;"",I12&gt;=NOW()),"Planned",IF(AND(J12&lt;&gt;"",J12&lt;NOW()),"Completed","Ongoing")))</f>
-        <v/>
-      </c>
-      <c r="L12" s="47"/>
-      <c r="M12" s="47"/>
-      <c r="N12" s="45" t="str">
+        <f ca="1">IF(OR(I12="",J12=""),"",IF(AND(J12&lt;&gt;"",I12&gt;=NOW()),"Planned",IF(AND(J12&lt;&gt;"",J12&lt;NOW()),"Completed","Ongoing")))</f>
+        <v>Completed</v>
+      </c>
+      <c r="L12" s="47">
+        <v>3</v>
+      </c>
+      <c r="M12" s="47">
+        <v>4</v>
+      </c>
+      <c r="N12" s="45">
         <f>IF(ISBLANK(L12), "", L12*VLOOKUP($F12,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O12" s="45" t="str">
+        <v>150</v>
+      </c>
+      <c r="O12" s="45">
         <f>IF(ISBLANK(M12), "", M12*VLOOKUP($F12,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P12" s="44"/>
-    </row>
-    <row r="13" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>200</v>
+      </c>
+      <c r="P12" s="44" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="13" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B13" s="41">
         <v>3</v>
       </c>
       <c r="C13" s="42" t="str">
         <f>IF(ISBLANK(D13), "", _xlfn.CONCAT("T", TEXT(B13, "0000"), "/", VLOOKUP(D13, Internal!$B$35:C$39, 2, FALSE), IF(OR(D13="QA", D13="Revision"), _xlfn.CONCAT("/", H13), "")))</f>
-        <v/>
-      </c>
-      <c r="D13" s="44"/>
-      <c r="E13" s="43"/>
-      <c r="F13" s="43"/>
-      <c r="G13" s="44"/>
+        <v>T0003/M</v>
+      </c>
+      <c r="D13" s="44" t="s">
+        <v>64</v>
+      </c>
+      <c r="E13" s="43" t="s">
+        <v>80</v>
+      </c>
+      <c r="F13" s="43" t="s">
+        <v>23</v>
+      </c>
+      <c r="G13" s="44" t="s">
+        <v>34</v>
+      </c>
       <c r="H13" s="43"/>
-      <c r="I13" s="46"/>
-      <c r="J13" s="46"/>
+      <c r="I13" s="46">
+        <v>46056.416666666664</v>
+      </c>
+      <c r="J13" s="46">
+        <v>46056.427083333336</v>
+      </c>
       <c r="K13" s="45" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L13" s="47"/>
-      <c r="M13" s="47"/>
-      <c r="N13" s="45" t="str">
+        <f t="shared" ref="K13:K77" ca="1" si="0">IF(OR(I13="",J13=""),"",IF(AND(J13&lt;&gt;"",I13&gt;=NOW()),"Planned",IF(AND(J13&lt;&gt;"",J13&lt;NOW()),"Completed","Ongoing")))</f>
+        <v>Completed</v>
+      </c>
+      <c r="L13" s="47">
+        <v>0.25</v>
+      </c>
+      <c r="M13" s="47">
+        <v>0.25</v>
+      </c>
+      <c r="N13" s="45">
         <f>IF(ISBLANK(L13), "", L13*VLOOKUP($F13,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O13" s="45" t="str">
+        <v>12.5</v>
+      </c>
+      <c r="O13" s="45">
         <f>IF(ISBLANK(M13), "", M13*VLOOKUP($F13,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P13" s="44"/>
-    </row>
-    <row r="14" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>12.5</v>
+      </c>
+      <c r="P13" s="44" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="14" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B14" s="41">
         <v>4</v>
       </c>
       <c r="C14" s="42" t="str">
         <f>IF(ISBLANK(D14), "", _xlfn.CONCAT("T", TEXT(B14, "0000"), "/", VLOOKUP(D14, Internal!$B$35:C$39, 2, FALSE), IF(OR(D14="QA", D14="Revision"), _xlfn.CONCAT("/", H14), "")))</f>
-        <v/>
-      </c>
-      <c r="D14" s="44"/>
-      <c r="E14" s="43"/>
-      <c r="F14" s="43"/>
-      <c r="G14" s="44"/>
+        <v>T0004/M</v>
+      </c>
+      <c r="D14" s="44" t="s">
+        <v>64</v>
+      </c>
+      <c r="E14" s="43" t="s">
+        <v>80</v>
+      </c>
+      <c r="F14" s="43" t="s">
+        <v>23</v>
+      </c>
+      <c r="G14" s="44" t="s">
+        <v>32</v>
+      </c>
       <c r="H14" s="43"/>
-      <c r="I14" s="46"/>
-      <c r="J14" s="46"/>
+      <c r="I14" s="46">
+        <v>46056.427083333336</v>
+      </c>
+      <c r="J14" s="46">
+        <v>46056.4375</v>
+      </c>
       <c r="K14" s="45" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L14" s="47"/>
-      <c r="M14" s="47"/>
-      <c r="N14" s="45" t="str">
+        <f ca="1">IF(OR(I14="",J14=""),"",IF(AND(J14&lt;&gt;"",I14&gt;=NOW()),"Planned",IF(AND(J14&lt;&gt;"",J14&lt;NOW()),"Completed","Ongoing")))</f>
+        <v>Completed</v>
+      </c>
+      <c r="L14" s="47">
+        <v>0.25</v>
+      </c>
+      <c r="M14" s="47">
+        <v>0.25</v>
+      </c>
+      <c r="N14" s="45">
         <f>IF(ISBLANK(L14), "", L14*VLOOKUP($F14,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O14" s="45" t="str">
+        <v>12.5</v>
+      </c>
+      <c r="O14" s="45">
         <f>IF(ISBLANK(M14), "", M14*VLOOKUP($F14,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P14" s="44"/>
-    </row>
-    <row r="15" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>12.5</v>
+      </c>
+      <c r="P14" s="44" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="15" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B15" s="41">
         <v>5</v>
       </c>
       <c r="C15" s="42" t="str">
         <f>IF(ISBLANK(D15), "", _xlfn.CONCAT("T", TEXT(B15, "0000"), "/", VLOOKUP(D15, Internal!$B$35:C$39, 2, FALSE), IF(OR(D15="QA", D15="Revision"), _xlfn.CONCAT("/", H15), "")))</f>
-        <v/>
-      </c>
-      <c r="D15" s="44"/>
-      <c r="E15" s="43"/>
-      <c r="F15" s="43"/>
-      <c r="G15" s="44"/>
+        <v>T0005/D</v>
+      </c>
+      <c r="D15" s="44" t="s">
+        <v>62</v>
+      </c>
+      <c r="E15" s="43" t="s">
+        <v>80</v>
+      </c>
+      <c r="F15" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="G15" s="44" t="s">
+        <v>89</v>
+      </c>
       <c r="H15" s="43"/>
-      <c r="I15" s="46"/>
-      <c r="J15" s="46"/>
+      <c r="I15" s="46">
+        <v>46058.5</v>
+      </c>
+      <c r="J15" s="46">
+        <v>46058.520833333336</v>
+      </c>
       <c r="K15" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L15" s="47"/>
-      <c r="M15" s="47"/>
-      <c r="N15" s="45" t="str">
+        <v>Planned</v>
+      </c>
+      <c r="L15" s="47">
+        <v>0.5</v>
+      </c>
+      <c r="M15" s="47">
+        <v>0.5</v>
+      </c>
+      <c r="N15" s="45">
         <f>IF(ISBLANK(L15), "", L15*VLOOKUP($F15,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O15" s="45" t="str">
+        <v>12.5</v>
+      </c>
+      <c r="O15" s="45">
         <f>IF(ISBLANK(M15), "", M15*VLOOKUP($F15,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P15" s="44"/>
-    </row>
-    <row r="16" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>12.5</v>
+      </c>
+      <c r="P15" s="44" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="16" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B16" s="41">
         <v>6</v>
       </c>
       <c r="C16" s="42" t="str">
         <f>IF(ISBLANK(D16), "", _xlfn.CONCAT("T", TEXT(B16, "0000"), "/", VLOOKUP(D16, Internal!$B$35:C$39, 2, FALSE), IF(OR(D16="QA", D16="Revision"), _xlfn.CONCAT("/", H16), "")))</f>
-        <v/>
-      </c>
-      <c r="D16" s="44"/>
-      <c r="E16" s="43"/>
-      <c r="F16" s="43"/>
-      <c r="G16" s="44"/>
+        <v>T0006/D</v>
+      </c>
+      <c r="D16" s="44" t="s">
+        <v>62</v>
+      </c>
+      <c r="E16" s="43" t="s">
+        <v>80</v>
+      </c>
+      <c r="F16" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="G16" s="44" t="s">
+        <v>40</v>
+      </c>
       <c r="H16" s="43"/>
-      <c r="I16" s="46"/>
+      <c r="I16" s="46">
+        <v>46061.375</v>
+      </c>
       <c r="J16" s="46"/>
       <c r="K16" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
-      <c r="L16" s="47"/>
+      <c r="L16" s="47">
+        <v>3</v>
+      </c>
       <c r="M16" s="47"/>
-      <c r="N16" s="45" t="str">
+      <c r="N16" s="45">
         <f>IF(ISBLANK(L16), "", L16*VLOOKUP($F16,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
+        <v>75</v>
       </c>
       <c r="O16" s="45" t="str">
         <f>IF(ISBLANK(M16), "", M16*VLOOKUP($F16,Internal!$B$26:$C$32,2,FALSE))</f>
         <v/>
       </c>
-      <c r="P16" s="44"/>
-    </row>
-    <row r="17" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="P16" s="44" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="17" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B17" s="41">
         <v>7</v>
       </c>
       <c r="C17" s="42" t="str">
         <f>IF(ISBLANK(D17), "", _xlfn.CONCAT("T", TEXT(B17, "0000"), "/", VLOOKUP(D17, Internal!$B$35:C$39, 2, FALSE), IF(OR(D17="QA", D17="Revision"), _xlfn.CONCAT("/", H17), "")))</f>
-        <v/>
-      </c>
-      <c r="D17" s="44"/>
-      <c r="E17" s="43"/>
-      <c r="F17" s="43"/>
-      <c r="G17" s="44"/>
-      <c r="H17" s="43"/>
+        <v>T0007/R/T0005/D</v>
+      </c>
+      <c r="D17" s="44" t="s">
+        <v>61</v>
+      </c>
+      <c r="E17" s="43" t="s">
+        <v>82</v>
+      </c>
+      <c r="F17" s="43" t="s">
+        <v>26</v>
+      </c>
+      <c r="G17" s="44" t="s">
+        <v>87</v>
+      </c>
+      <c r="H17" s="43" t="s">
+        <v>96</v>
+      </c>
       <c r="I17" s="46"/>
       <c r="J17" s="46"/>
       <c r="K17" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
-      <c r="L17" s="47"/>
+      <c r="L17" s="47">
+        <v>0.5</v>
+      </c>
       <c r="M17" s="47"/>
-      <c r="N17" s="45" t="str">
+      <c r="N17" s="45">
         <f>IF(ISBLANK(L17), "", L17*VLOOKUP($F17,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
+        <v>15</v>
       </c>
       <c r="O17" s="45" t="str">
         <f>IF(ISBLANK(M17), "", M17*VLOOKUP($F17,Internal!$B$26:$C$32,2,FALSE))</f>
         <v/>
       </c>
-      <c r="P17" s="44"/>
-    </row>
-    <row r="18" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="P17" s="44" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="18" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B18" s="41">
         <v>8</v>
       </c>
@@ -2055,7 +2197,7 @@
       </c>
       <c r="P18" s="44"/>
     </row>
-    <row r="19" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B19" s="41">
         <v>9</v>
       </c>
@@ -2086,7 +2228,7 @@
       </c>
       <c r="P19" s="44"/>
     </row>
-    <row r="20" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B20" s="41">
         <v>10</v>
       </c>
@@ -2117,7 +2259,7 @@
       </c>
       <c r="P20" s="44"/>
     </row>
-    <row r="21" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B21" s="41">
         <v>11</v>
       </c>
@@ -2148,7 +2290,7 @@
       </c>
       <c r="P21" s="44"/>
     </row>
-    <row r="22" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B22" s="41">
         <v>12</v>
       </c>
@@ -2179,7 +2321,7 @@
       </c>
       <c r="P22" s="44"/>
     </row>
-    <row r="23" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B23" s="41">
         <v>13</v>
       </c>
@@ -2210,7 +2352,7 @@
       </c>
       <c r="P23" s="44"/>
     </row>
-    <row r="24" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B24" s="41">
         <v>14</v>
       </c>
@@ -2241,7 +2383,7 @@
       </c>
       <c r="P24" s="44"/>
     </row>
-    <row r="25" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B25" s="41">
         <v>15</v>
       </c>
@@ -2272,7 +2414,7 @@
       </c>
       <c r="P25" s="44"/>
     </row>
-    <row r="26" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B26" s="41">
         <v>16</v>
       </c>
@@ -2303,7 +2445,7 @@
       </c>
       <c r="P26" s="44"/>
     </row>
-    <row r="27" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B27" s="41">
         <v>17</v>
       </c>
@@ -2334,7 +2476,7 @@
       </c>
       <c r="P27" s="44"/>
     </row>
-    <row r="28" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B28" s="41">
         <v>18</v>
       </c>
@@ -2365,7 +2507,7 @@
       </c>
       <c r="P28" s="44"/>
     </row>
-    <row r="29" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B29" s="41">
         <v>19</v>
       </c>
@@ -2396,7 +2538,7 @@
       </c>
       <c r="P29" s="44"/>
     </row>
-    <row r="30" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B30" s="41">
         <v>20</v>
       </c>
@@ -2427,7 +2569,7 @@
       </c>
       <c r="P30" s="44"/>
     </row>
-    <row r="31" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B31" s="41">
         <v>21</v>
       </c>
@@ -2458,7 +2600,7 @@
       </c>
       <c r="P31" s="44"/>
     </row>
-    <row r="32" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B32" s="41">
         <v>22</v>
       </c>
@@ -2489,7 +2631,7 @@
       </c>
       <c r="P32" s="44"/>
     </row>
-    <row r="33" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B33" s="41">
         <v>23</v>
       </c>
@@ -2520,7 +2662,7 @@
       </c>
       <c r="P33" s="44"/>
     </row>
-    <row r="34" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B34" s="41">
         <v>24</v>
       </c>
@@ -2551,7 +2693,7 @@
       </c>
       <c r="P34" s="44"/>
     </row>
-    <row r="35" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B35" s="41">
         <v>25</v>
       </c>
@@ -2582,7 +2724,7 @@
       </c>
       <c r="P35" s="44"/>
     </row>
-    <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B36" s="41">
         <v>26</v>
       </c>
@@ -2613,7 +2755,7 @@
       </c>
       <c r="P36" s="44"/>
     </row>
-    <row r="37" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B37" s="41">
         <v>27</v>
       </c>
@@ -2644,7 +2786,7 @@
       </c>
       <c r="P37" s="44"/>
     </row>
-    <row r="38" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B38" s="41">
         <v>28</v>
       </c>
@@ -2675,7 +2817,7 @@
       </c>
       <c r="P38" s="44"/>
     </row>
-    <row r="39" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B39" s="41">
         <v>29</v>
       </c>
@@ -2706,7 +2848,7 @@
       </c>
       <c r="P39" s="44"/>
     </row>
-    <row r="40" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B40" s="41">
         <v>30</v>
       </c>
@@ -2737,7 +2879,7 @@
       </c>
       <c r="P40" s="44"/>
     </row>
-    <row r="41" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B41" s="41">
         <v>31</v>
       </c>
@@ -2768,7 +2910,7 @@
       </c>
       <c r="P41" s="44"/>
     </row>
-    <row r="42" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B42" s="41">
         <v>32</v>
       </c>
@@ -2799,7 +2941,7 @@
       </c>
       <c r="P42" s="44"/>
     </row>
-    <row r="43" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B43" s="41">
         <v>33</v>
       </c>
@@ -2830,7 +2972,7 @@
       </c>
       <c r="P43" s="44"/>
     </row>
-    <row r="44" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B44" s="41">
         <v>34</v>
       </c>
@@ -2861,7 +3003,7 @@
       </c>
       <c r="P44" s="44"/>
     </row>
-    <row r="45" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B45" s="41">
         <v>35</v>
       </c>
@@ -2892,7 +3034,7 @@
       </c>
       <c r="P45" s="44"/>
     </row>
-    <row r="46" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B46" s="41">
         <v>36</v>
       </c>
@@ -2923,7 +3065,7 @@
       </c>
       <c r="P46" s="44"/>
     </row>
-    <row r="47" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B47" s="41">
         <v>37</v>
       </c>
@@ -2954,7 +3096,7 @@
       </c>
       <c r="P47" s="44"/>
     </row>
-    <row r="48" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B48" s="41">
         <v>38</v>
       </c>
@@ -2985,7 +3127,7 @@
       </c>
       <c r="P48" s="44"/>
     </row>
-    <row r="49" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B49" s="41">
         <v>39</v>
       </c>
@@ -3016,7 +3158,7 @@
       </c>
       <c r="P49" s="44"/>
     </row>
-    <row r="50" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B50" s="41">
         <v>40</v>
       </c>
@@ -3047,7 +3189,7 @@
       </c>
       <c r="P50" s="44"/>
     </row>
-    <row r="51" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B51" s="41">
         <v>41</v>
       </c>
@@ -3078,7 +3220,7 @@
       </c>
       <c r="P51" s="44"/>
     </row>
-    <row r="52" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B52" s="41">
         <v>42</v>
       </c>
@@ -3109,7 +3251,7 @@
       </c>
       <c r="P52" s="44"/>
     </row>
-    <row r="53" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B53" s="41">
         <v>43</v>
       </c>
@@ -3140,7 +3282,7 @@
       </c>
       <c r="P53" s="44"/>
     </row>
-    <row r="54" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B54" s="41">
         <v>44</v>
       </c>
@@ -3171,7 +3313,7 @@
       </c>
       <c r="P54" s="44"/>
     </row>
-    <row r="55" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B55" s="41">
         <v>45</v>
       </c>
@@ -3202,7 +3344,7 @@
       </c>
       <c r="P55" s="44"/>
     </row>
-    <row r="56" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B56" s="41">
         <v>46</v>
       </c>
@@ -3233,7 +3375,7 @@
       </c>
       <c r="P56" s="44"/>
     </row>
-    <row r="57" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B57" s="41">
         <v>47</v>
       </c>
@@ -3264,7 +3406,7 @@
       </c>
       <c r="P57" s="44"/>
     </row>
-    <row r="58" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B58" s="41">
         <v>48</v>
       </c>
@@ -3295,7 +3437,7 @@
       </c>
       <c r="P58" s="44"/>
     </row>
-    <row r="59" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B59" s="41">
         <v>49</v>
       </c>
@@ -3326,7 +3468,7 @@
       </c>
       <c r="P59" s="44"/>
     </row>
-    <row r="60" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B60" s="41">
         <v>50</v>
       </c>
@@ -3357,7 +3499,7 @@
       </c>
       <c r="P60" s="44"/>
     </row>
-    <row r="61" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B61" s="41">
         <v>51</v>
       </c>
@@ -3388,7 +3530,7 @@
       </c>
       <c r="P61" s="44"/>
     </row>
-    <row r="62" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B62" s="41">
         <v>52</v>
       </c>
@@ -3419,7 +3561,7 @@
       </c>
       <c r="P62" s="44"/>
     </row>
-    <row r="63" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B63" s="41">
         <v>53</v>
       </c>
@@ -3450,7 +3592,7 @@
       </c>
       <c r="P63" s="44"/>
     </row>
-    <row r="64" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B64" s="41">
         <v>54</v>
       </c>
@@ -3481,7 +3623,7 @@
       </c>
       <c r="P64" s="44"/>
     </row>
-    <row r="65" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B65" s="41">
         <v>55</v>
       </c>
@@ -3512,7 +3654,7 @@
       </c>
       <c r="P65" s="44"/>
     </row>
-    <row r="66" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B66" s="41">
         <v>56</v>
       </c>
@@ -3543,7 +3685,7 @@
       </c>
       <c r="P66" s="44"/>
     </row>
-    <row r="67" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B67" s="41">
         <v>57</v>
       </c>
@@ -3574,7 +3716,7 @@
       </c>
       <c r="P67" s="44"/>
     </row>
-    <row r="68" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B68" s="41">
         <v>58</v>
       </c>
@@ -3605,7 +3747,7 @@
       </c>
       <c r="P68" s="44"/>
     </row>
-    <row r="69" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B69" s="41">
         <v>59</v>
       </c>
@@ -3636,7 +3778,7 @@
       </c>
       <c r="P69" s="44"/>
     </row>
-    <row r="70" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B70" s="41">
         <v>60</v>
       </c>
@@ -3667,7 +3809,7 @@
       </c>
       <c r="P70" s="44"/>
     </row>
-    <row r="71" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B71" s="41">
         <v>61</v>
       </c>
@@ -3698,7 +3840,7 @@
       </c>
       <c r="P71" s="44"/>
     </row>
-    <row r="72" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B72" s="41">
         <v>62</v>
       </c>
@@ -3729,7 +3871,7 @@
       </c>
       <c r="P72" s="44"/>
     </row>
-    <row r="73" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B73" s="41">
         <v>63</v>
       </c>
@@ -3760,7 +3902,7 @@
       </c>
       <c r="P73" s="44"/>
     </row>
-    <row r="74" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B74" s="41">
         <v>64</v>
       </c>
@@ -3791,7 +3933,7 @@
       </c>
       <c r="P74" s="44"/>
     </row>
-    <row r="75" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B75" s="41">
         <v>65</v>
       </c>
@@ -3822,7 +3964,7 @@
       </c>
       <c r="P75" s="44"/>
     </row>
-    <row r="76" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B76" s="41">
         <v>66</v>
       </c>
@@ -3838,7 +3980,7 @@
       <c r="I76" s="46"/>
       <c r="J76" s="46"/>
       <c r="K76" s="45" t="str">
-        <f t="shared" ref="K76:K110" ca="1" si="1">IF(OR(I76="",J76=""),"",IF(AND(J76&lt;&gt;"",I76&gt;=NOW()),"Planned",IF(AND(J76&lt;&gt;"",J76&lt;NOW()),"Completed","Ongoing")))</f>
+        <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
       <c r="L76" s="47"/>
@@ -3853,7 +3995,7 @@
       </c>
       <c r="P76" s="44"/>
     </row>
-    <row r="77" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B77" s="41">
         <v>67</v>
       </c>
@@ -3869,7 +4011,7 @@
       <c r="I77" s="46"/>
       <c r="J77" s="46"/>
       <c r="K77" s="45" t="str">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
       <c r="L77" s="47"/>
@@ -3884,7 +4026,7 @@
       </c>
       <c r="P77" s="44"/>
     </row>
-    <row r="78" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B78" s="41">
         <v>68</v>
       </c>
@@ -3900,7 +4042,7 @@
       <c r="I78" s="46"/>
       <c r="J78" s="46"/>
       <c r="K78" s="45" t="str">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" ref="K78:K112" ca="1" si="1">IF(OR(I78="",J78=""),"",IF(AND(J78&lt;&gt;"",I78&gt;=NOW()),"Planned",IF(AND(J78&lt;&gt;"",J78&lt;NOW()),"Completed","Ongoing")))</f>
         <v/>
       </c>
       <c r="L78" s="47"/>
@@ -3915,7 +4057,7 @@
       </c>
       <c r="P78" s="44"/>
     </row>
-    <row r="79" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B79" s="41">
         <v>69</v>
       </c>
@@ -3946,7 +4088,7 @@
       </c>
       <c r="P79" s="44"/>
     </row>
-    <row r="80" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B80" s="41">
         <v>70</v>
       </c>
@@ -3977,7 +4119,7 @@
       </c>
       <c r="P80" s="44"/>
     </row>
-    <row r="81" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B81" s="41">
         <v>71</v>
       </c>
@@ -4008,7 +4150,7 @@
       </c>
       <c r="P81" s="44"/>
     </row>
-    <row r="82" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B82" s="41">
         <v>72</v>
       </c>
@@ -4039,7 +4181,7 @@
       </c>
       <c r="P82" s="44"/>
     </row>
-    <row r="83" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B83" s="41">
         <v>73</v>
       </c>
@@ -4070,7 +4212,7 @@
       </c>
       <c r="P83" s="44"/>
     </row>
-    <row r="84" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B84" s="41">
         <v>74</v>
       </c>
@@ -4101,7 +4243,7 @@
       </c>
       <c r="P84" s="44"/>
     </row>
-    <row r="85" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B85" s="41">
         <v>75</v>
       </c>
@@ -4132,7 +4274,7 @@
       </c>
       <c r="P85" s="44"/>
     </row>
-    <row r="86" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B86" s="41">
         <v>76</v>
       </c>
@@ -4163,7 +4305,7 @@
       </c>
       <c r="P86" s="44"/>
     </row>
-    <row r="87" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B87" s="41">
         <v>77</v>
       </c>
@@ -4194,7 +4336,7 @@
       </c>
       <c r="P87" s="44"/>
     </row>
-    <row r="88" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B88" s="41">
         <v>78</v>
       </c>
@@ -4225,7 +4367,7 @@
       </c>
       <c r="P88" s="44"/>
     </row>
-    <row r="89" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B89" s="41">
         <v>79</v>
       </c>
@@ -4256,7 +4398,7 @@
       </c>
       <c r="P89" s="44"/>
     </row>
-    <row r="90" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B90" s="41">
         <v>80</v>
       </c>
@@ -4287,7 +4429,7 @@
       </c>
       <c r="P90" s="44"/>
     </row>
-    <row r="91" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B91" s="41">
         <v>81</v>
       </c>
@@ -4318,7 +4460,7 @@
       </c>
       <c r="P91" s="44"/>
     </row>
-    <row r="92" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B92" s="41">
         <v>82</v>
       </c>
@@ -4349,7 +4491,7 @@
       </c>
       <c r="P92" s="44"/>
     </row>
-    <row r="93" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B93" s="41">
         <v>83</v>
       </c>
@@ -4380,7 +4522,7 @@
       </c>
       <c r="P93" s="44"/>
     </row>
-    <row r="94" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B94" s="41">
         <v>84</v>
       </c>
@@ -4411,7 +4553,7 @@
       </c>
       <c r="P94" s="44"/>
     </row>
-    <row r="95" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B95" s="41">
         <v>85</v>
       </c>
@@ -4442,7 +4584,7 @@
       </c>
       <c r="P95" s="44"/>
     </row>
-    <row r="96" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B96" s="41">
         <v>86</v>
       </c>
@@ -4473,7 +4615,7 @@
       </c>
       <c r="P96" s="44"/>
     </row>
-    <row r="97" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B97" s="41">
         <v>87</v>
       </c>
@@ -4504,7 +4646,7 @@
       </c>
       <c r="P97" s="44"/>
     </row>
-    <row r="98" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B98" s="41">
         <v>88</v>
       </c>
@@ -4535,7 +4677,7 @@
       </c>
       <c r="P98" s="44"/>
     </row>
-    <row r="99" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B99" s="41">
         <v>89</v>
       </c>
@@ -4566,7 +4708,7 @@
       </c>
       <c r="P99" s="44"/>
     </row>
-    <row r="100" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B100" s="41">
         <v>90</v>
       </c>
@@ -4597,7 +4739,7 @@
       </c>
       <c r="P100" s="44"/>
     </row>
-    <row r="101" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B101" s="41">
         <v>91</v>
       </c>
@@ -4628,7 +4770,7 @@
       </c>
       <c r="P101" s="44"/>
     </row>
-    <row r="102" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B102" s="41">
         <v>92</v>
       </c>
@@ -4659,7 +4801,7 @@
       </c>
       <c r="P102" s="44"/>
     </row>
-    <row r="103" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B103" s="41">
         <v>93</v>
       </c>
@@ -4690,7 +4832,7 @@
       </c>
       <c r="P103" s="44"/>
     </row>
-    <row r="104" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B104" s="41">
         <v>94</v>
       </c>
@@ -4721,7 +4863,7 @@
       </c>
       <c r="P104" s="44"/>
     </row>
-    <row r="105" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B105" s="41">
         <v>95</v>
       </c>
@@ -4752,7 +4894,7 @@
       </c>
       <c r="P105" s="44"/>
     </row>
-    <row r="106" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B106" s="41">
         <v>96</v>
       </c>
@@ -4783,7 +4925,7 @@
       </c>
       <c r="P106" s="44"/>
     </row>
-    <row r="107" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B107" s="41">
         <v>97</v>
       </c>
@@ -4814,7 +4956,7 @@
       </c>
       <c r="P107" s="44"/>
     </row>
-    <row r="108" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="108" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B108" s="41">
         <v>98</v>
       </c>
@@ -4845,7 +4987,7 @@
       </c>
       <c r="P108" s="44"/>
     </row>
-    <row r="109" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="109" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B109" s="41">
         <v>99</v>
       </c>
@@ -4876,7 +5018,7 @@
       </c>
       <c r="P109" s="44"/>
     </row>
-    <row r="110" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B110" s="41">
         <v>100</v>
       </c>
@@ -4906,6 +5048,68 @@
         <v/>
       </c>
       <c r="P110" s="44"/>
+    </row>
+    <row r="111" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B111" s="41">
+        <v>101</v>
+      </c>
+      <c r="C111" s="42" t="str">
+        <f>IF(ISBLANK(D111), "", _xlfn.CONCAT("T", TEXT(B111, "0000"), "/", VLOOKUP(D111, Internal!$B$35:C$39, 2, FALSE), IF(OR(D111="QA", D111="Revision"), _xlfn.CONCAT("/", H111), "")))</f>
+        <v/>
+      </c>
+      <c r="D111" s="44"/>
+      <c r="E111" s="43"/>
+      <c r="F111" s="43"/>
+      <c r="G111" s="44"/>
+      <c r="H111" s="43"/>
+      <c r="I111" s="46"/>
+      <c r="J111" s="46"/>
+      <c r="K111" s="45" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="L111" s="47"/>
+      <c r="M111" s="47"/>
+      <c r="N111" s="45" t="str">
+        <f>IF(ISBLANK(L111), "", L111*VLOOKUP($F111,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v/>
+      </c>
+      <c r="O111" s="45" t="str">
+        <f>IF(ISBLANK(M111), "", M111*VLOOKUP($F111,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v/>
+      </c>
+      <c r="P111" s="44"/>
+    </row>
+    <row r="112" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B112" s="41">
+        <v>102</v>
+      </c>
+      <c r="C112" s="42" t="str">
+        <f>IF(ISBLANK(D112), "", _xlfn.CONCAT("T", TEXT(B112, "0000"), "/", VLOOKUP(D112, Internal!$B$35:C$39, 2, FALSE), IF(OR(D112="QA", D112="Revision"), _xlfn.CONCAT("/", H112), "")))</f>
+        <v/>
+      </c>
+      <c r="D112" s="44"/>
+      <c r="E112" s="43"/>
+      <c r="F112" s="43"/>
+      <c r="G112" s="44"/>
+      <c r="H112" s="43"/>
+      <c r="I112" s="46"/>
+      <c r="J112" s="46"/>
+      <c r="K112" s="45" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="L112" s="47"/>
+      <c r="M112" s="47"/>
+      <c r="N112" s="45" t="str">
+        <f>IF(ISBLANK(L112), "", L112*VLOOKUP($F112,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v/>
+      </c>
+      <c r="O112" s="45" t="str">
+        <f>IF(ISBLANK(M112), "", M112*VLOOKUP($F112,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v/>
+      </c>
+      <c r="P112" s="44"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -4917,32 +5121,32 @@
     <mergeCell ref="C4:P4"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
-  <conditionalFormatting sqref="H11:H110">
+  <conditionalFormatting sqref="H11:H112">
     <cfRule type="expression" dxfId="5" priority="2">
-      <formula>AND(H11&lt;&gt;"",COUNTIF($C$11:$C$110,H11)=0)</formula>
+      <formula>AND(H11&lt;&gt;"",COUNTIF($C$12:$C$112,H11)=0)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J11:J110">
+  <conditionalFormatting sqref="J11:J112">
     <cfRule type="expression" dxfId="4" priority="1">
       <formula>AND(I11&lt;&gt;"",J11&lt;&gt;"", I11&gt;J11)</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="9">
-    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Expected workload" prompt="Enter the expected workload in hours or fractions." sqref="L11:L110" xr:uid="{AADDA758-A288-4920-A868-A656B94EE475}">
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Expected workload" prompt="Enter the expected workload in hours or fractions." sqref="L11:L112" xr:uid="{AADDA758-A288-4920-A868-A656B94EE475}">
       <formula1>0</formula1>
       <formula2>1024</formula2>
     </dataValidation>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Description" prompt="Provide a succint description of the task.  If not possible, the provide a link to a document where is is described." sqref="P10" xr:uid="{D0BF2996-BBAB-402C-8777-D22DB1423D76}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Actual workload" prompt="Enter the actual workload in hours or fractions._x000a_" sqref="M11:M110" xr:uid="{FFAE3670-28C0-4D44-81DE-0074EF40B001}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Description" prompt="If actually necessary, then write a succint description and/or include a link to a document that provides further information." sqref="P11:P110 K11:K110" xr:uid="{4DDB20BC-C9D1-4AB5-9B81-3F9F25727EAD}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Costs" prompt="The costs are updated automatically.  Don't modify them manually" sqref="N11:O110" xr:uid="{3D1A9EDC-88F9-4796-ACC0-9C5DD1125EFE}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="ID" prompt="The IDs are updated automatically.  Don't modify them manually" sqref="C11:C110" xr:uid="{6C5AA884-EA5C-464F-AE09-58D1C86343FC}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="ORDER" prompt="Order numbers are internal data.  Do not change them._x000a_" sqref="B11:B110" xr:uid="{79B4C829-58F8-4180-8480-F4A0E1F5F1C5}"/>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Activity" prompt="Select the Activity to perfom.  Use &quot;Other&quot; only in truly exceptional cases." sqref="G11:G110" xr:uid="{402079F6-76CA-490B-9F74-CDFB1F7ED8BD}">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Actual workload" prompt="Enter the actual workload in hours or fractions._x000a_" sqref="M11:M112" xr:uid="{FFAE3670-28C0-4D44-81DE-0074EF40B001}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Description" prompt="If actually necessary, then write a succint description and/or include a link to a document that provides further information." sqref="K11:K112 P11:P112" xr:uid="{4DDB20BC-C9D1-4AB5-9B81-3F9F25727EAD}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Costs" prompt="The costs are updated automatically.  Don't modify them manually" sqref="N11:O112" xr:uid="{3D1A9EDC-88F9-4796-ACC0-9C5DD1125EFE}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="ID" prompt="The IDs are updated automatically.  Don't modify them manually" sqref="C11:C112" xr:uid="{6C5AA884-EA5C-464F-AE09-58D1C86343FC}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="ORDER" prompt="Order numbers are internal data.  Do not change them._x000a_" sqref="B11:B112" xr:uid="{79B4C829-58F8-4180-8480-F4A0E1F5F1C5}"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Activity" prompt="Select the Activity to perfom.  Use &quot;Other&quot; only in truly exceptional cases." sqref="G11:G112" xr:uid="{402079F6-76CA-490B-9F74-CDFB1F7ED8BD}">
       <formula1>INDIRECT(F11)</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Parent" prompt="Select the parent task if necessary.  Usually, only &quot;Quality Assurance&quot; and &quot;Revision&quot; tasks have parents." sqref="H11:H110" xr:uid="{D360DC77-273A-412B-AEBB-6D07121D9EA3}">
-      <formula1>$C$11:$C$110</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Parent" prompt="Select the parent task if necessary.  Usually, only &quot;Quality Assurance&quot; and &quot;Revision&quot; tasks have parents." sqref="H11:H112" xr:uid="{D360DC77-273A-412B-AEBB-6D07121D9EA3}">
+      <formula1>$C$12:$C$112</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4954,19 +5158,19 @@
           <x14:formula1>
             <xm:f>Internal!$B$26:$B$32</xm:f>
           </x14:formula1>
-          <xm:sqref>F11:F110</xm:sqref>
+          <xm:sqref>F11:F112</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Type" prompt="Indicate the type of task." xr:uid="{FB2BBB7B-03FF-45CB-8A89-AFA40F81FC94}">
           <x14:formula1>
             <xm:f>Internal!$B$35:$B$39</xm:f>
           </x14:formula1>
-          <xm:sqref>D11:D110</xm:sqref>
+          <xm:sqref>D11:D112</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Assignee" prompt="Select the workmate the task is assigned to." xr:uid="{9667150F-C763-44E5-A661-FFC8169264CA}">
           <x14:formula1>
             <xm:f>Internal!$B$9:$B$14</xm:f>
           </x14:formula1>
-          <xm:sqref>E11:E110</xm:sqref>
+          <xm:sqref>E11:E112</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Start moment" prompt="Indicate the moment when the assignee starts working on this task.  Use format yy/mm/dd hh:mm." xr:uid="{3E697798-8BF9-4850-9C0F-D14A9C11C1F7}">
           <x14:formula1>
@@ -4975,7 +5179,7 @@
           <x14:formula2>
             <xm:f>Internal!$C$23</xm:f>
           </x14:formula2>
-          <xm:sqref>I11:I110</xm:sqref>
+          <xm:sqref>I11:I112</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="End moment" prompt="Indicate the moment when the assignee finishes working on this task.  Use format yy/mm/dd hh:mm." xr:uid="{AA2B0FBE-439D-4BBE-9231-3859DD87C79A}">
           <x14:formula1>
@@ -4984,7 +5188,7 @@
           <x14:formula2>
             <xm:f>Internal!$C$23</xm:f>
           </x14:formula2>
-          <xm:sqref>J11:J110</xm:sqref>
+          <xm:sqref>J11:J112</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -4995,13 +5199,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F28A4DB1-CB48-4778-AC73-C91746932E53}">
   <dimension ref="B2:P110"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="3" max="15" width="18.88671875" customWidth="1"/>
-    <col min="16" max="16" width="64.5546875" customWidth="1"/>
+    <col min="3" max="15" width="18.86328125" customWidth="1"/>
+    <col min="16" max="16" width="64.53125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:16" x14ac:dyDescent="0.45">
       <c r="C2" s="55" t="s">
         <v>85</v>
       </c>
@@ -5019,7 +5223,7 @@
       <c r="O2" s="55"/>
       <c r="P2" s="55"/>
     </row>
-    <row r="4" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C4" s="53" t="s">
         <v>75</v>
       </c>
@@ -5037,7 +5241,7 @@
       <c r="O4" s="53"/>
       <c r="P4" s="53"/>
     </row>
-    <row r="5" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:16" x14ac:dyDescent="0.45">
       <c r="C5" s="5"/>
       <c r="D5" s="5"/>
       <c r="E5" s="5"/>
@@ -5053,7 +5257,7 @@
       <c r="O5" s="5"/>
       <c r="P5" s="5"/>
     </row>
-    <row r="6" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:16" x14ac:dyDescent="0.45">
       <c r="C6" s="57" t="s">
         <v>68</v>
       </c>
@@ -5076,7 +5280,7 @@
       <c r="O6" s="5"/>
       <c r="P6" s="5"/>
     </row>
-    <row r="7" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:16" x14ac:dyDescent="0.45">
       <c r="C7" s="57"/>
       <c r="D7" s="11" t="s">
         <v>70</v>
@@ -5087,7 +5291,7 @@
       </c>
       <c r="J7" s="37"/>
     </row>
-    <row r="9" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B9" s="6"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
@@ -5110,7 +5314,7 @@
       <c r="O9" s="58"/>
       <c r="P9" s="7"/>
     </row>
-    <row r="10" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B10" s="8" t="s">
         <v>66</v>
       </c>
@@ -5157,7 +5361,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="11" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B11" s="41">
         <v>1</v>
       </c>
@@ -5188,7 +5392,7 @@
       </c>
       <c r="P11" s="44"/>
     </row>
-    <row r="12" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B12" s="41">
         <v>2</v>
       </c>
@@ -5219,7 +5423,7 @@
       </c>
       <c r="P12" s="44"/>
     </row>
-    <row r="13" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B13" s="41">
         <v>3</v>
       </c>
@@ -5250,7 +5454,7 @@
       </c>
       <c r="P13" s="44"/>
     </row>
-    <row r="14" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B14" s="41">
         <v>4</v>
       </c>
@@ -5281,7 +5485,7 @@
       </c>
       <c r="P14" s="44"/>
     </row>
-    <row r="15" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B15" s="41">
         <v>5</v>
       </c>
@@ -5312,7 +5516,7 @@
       </c>
       <c r="P15" s="44"/>
     </row>
-    <row r="16" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B16" s="41">
         <v>6</v>
       </c>
@@ -5343,7 +5547,7 @@
       </c>
       <c r="P16" s="44"/>
     </row>
-    <row r="17" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B17" s="41">
         <v>7</v>
       </c>
@@ -5374,7 +5578,7 @@
       </c>
       <c r="P17" s="44"/>
     </row>
-    <row r="18" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B18" s="41">
         <v>8</v>
       </c>
@@ -5405,7 +5609,7 @@
       </c>
       <c r="P18" s="44"/>
     </row>
-    <row r="19" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B19" s="41">
         <v>9</v>
       </c>
@@ -5436,7 +5640,7 @@
       </c>
       <c r="P19" s="44"/>
     </row>
-    <row r="20" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B20" s="41">
         <v>10</v>
       </c>
@@ -5467,7 +5671,7 @@
       </c>
       <c r="P20" s="44"/>
     </row>
-    <row r="21" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B21" s="41">
         <v>11</v>
       </c>
@@ -5498,7 +5702,7 @@
       </c>
       <c r="P21" s="44"/>
     </row>
-    <row r="22" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B22" s="41">
         <v>12</v>
       </c>
@@ -5529,7 +5733,7 @@
       </c>
       <c r="P22" s="44"/>
     </row>
-    <row r="23" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B23" s="41">
         <v>13</v>
       </c>
@@ -5560,7 +5764,7 @@
       </c>
       <c r="P23" s="44"/>
     </row>
-    <row r="24" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B24" s="41">
         <v>14</v>
       </c>
@@ -5591,7 +5795,7 @@
       </c>
       <c r="P24" s="44"/>
     </row>
-    <row r="25" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B25" s="41">
         <v>15</v>
       </c>
@@ -5622,7 +5826,7 @@
       </c>
       <c r="P25" s="44"/>
     </row>
-    <row r="26" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B26" s="41">
         <v>16</v>
       </c>
@@ -5653,7 +5857,7 @@
       </c>
       <c r="P26" s="44"/>
     </row>
-    <row r="27" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B27" s="41">
         <v>17</v>
       </c>
@@ -5684,7 +5888,7 @@
       </c>
       <c r="P27" s="44"/>
     </row>
-    <row r="28" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B28" s="41">
         <v>18</v>
       </c>
@@ -5715,7 +5919,7 @@
       </c>
       <c r="P28" s="44"/>
     </row>
-    <row r="29" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B29" s="41">
         <v>19</v>
       </c>
@@ -5746,7 +5950,7 @@
       </c>
       <c r="P29" s="44"/>
     </row>
-    <row r="30" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B30" s="41">
         <v>20</v>
       </c>
@@ -5777,7 +5981,7 @@
       </c>
       <c r="P30" s="44"/>
     </row>
-    <row r="31" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B31" s="41">
         <v>21</v>
       </c>
@@ -5808,7 +6012,7 @@
       </c>
       <c r="P31" s="44"/>
     </row>
-    <row r="32" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B32" s="41">
         <v>22</v>
       </c>
@@ -5839,7 +6043,7 @@
       </c>
       <c r="P32" s="44"/>
     </row>
-    <row r="33" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B33" s="41">
         <v>23</v>
       </c>
@@ -5870,7 +6074,7 @@
       </c>
       <c r="P33" s="44"/>
     </row>
-    <row r="34" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B34" s="41">
         <v>24</v>
       </c>
@@ -5901,7 +6105,7 @@
       </c>
       <c r="P34" s="44"/>
     </row>
-    <row r="35" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B35" s="41">
         <v>25</v>
       </c>
@@ -5932,7 +6136,7 @@
       </c>
       <c r="P35" s="44"/>
     </row>
-    <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B36" s="41">
         <v>26</v>
       </c>
@@ -5963,7 +6167,7 @@
       </c>
       <c r="P36" s="44"/>
     </row>
-    <row r="37" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B37" s="41">
         <v>27</v>
       </c>
@@ -5994,7 +6198,7 @@
       </c>
       <c r="P37" s="44"/>
     </row>
-    <row r="38" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B38" s="41">
         <v>28</v>
       </c>
@@ -6025,7 +6229,7 @@
       </c>
       <c r="P38" s="44"/>
     </row>
-    <row r="39" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B39" s="41">
         <v>29</v>
       </c>
@@ -6056,7 +6260,7 @@
       </c>
       <c r="P39" s="44"/>
     </row>
-    <row r="40" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B40" s="41">
         <v>30</v>
       </c>
@@ -6087,7 +6291,7 @@
       </c>
       <c r="P40" s="44"/>
     </row>
-    <row r="41" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B41" s="41">
         <v>31</v>
       </c>
@@ -6118,7 +6322,7 @@
       </c>
       <c r="P41" s="44"/>
     </row>
-    <row r="42" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B42" s="41">
         <v>32</v>
       </c>
@@ -6149,7 +6353,7 @@
       </c>
       <c r="P42" s="44"/>
     </row>
-    <row r="43" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B43" s="41">
         <v>33</v>
       </c>
@@ -6180,7 +6384,7 @@
       </c>
       <c r="P43" s="44"/>
     </row>
-    <row r="44" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B44" s="41">
         <v>34</v>
       </c>
@@ -6211,7 +6415,7 @@
       </c>
       <c r="P44" s="44"/>
     </row>
-    <row r="45" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B45" s="41">
         <v>35</v>
       </c>
@@ -6242,7 +6446,7 @@
       </c>
       <c r="P45" s="44"/>
     </row>
-    <row r="46" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B46" s="41">
         <v>36</v>
       </c>
@@ -6273,7 +6477,7 @@
       </c>
       <c r="P46" s="44"/>
     </row>
-    <row r="47" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B47" s="41">
         <v>37</v>
       </c>
@@ -6304,7 +6508,7 @@
       </c>
       <c r="P47" s="44"/>
     </row>
-    <row r="48" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B48" s="41">
         <v>38</v>
       </c>
@@ -6335,7 +6539,7 @@
       </c>
       <c r="P48" s="44"/>
     </row>
-    <row r="49" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B49" s="41">
         <v>39</v>
       </c>
@@ -6366,7 +6570,7 @@
       </c>
       <c r="P49" s="44"/>
     </row>
-    <row r="50" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B50" s="41">
         <v>40</v>
       </c>
@@ -6397,7 +6601,7 @@
       </c>
       <c r="P50" s="44"/>
     </row>
-    <row r="51" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B51" s="41">
         <v>41</v>
       </c>
@@ -6428,7 +6632,7 @@
       </c>
       <c r="P51" s="44"/>
     </row>
-    <row r="52" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B52" s="41">
         <v>42</v>
       </c>
@@ -6459,7 +6663,7 @@
       </c>
       <c r="P52" s="44"/>
     </row>
-    <row r="53" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B53" s="41">
         <v>43</v>
       </c>
@@ -6490,7 +6694,7 @@
       </c>
       <c r="P53" s="44"/>
     </row>
-    <row r="54" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B54" s="41">
         <v>44</v>
       </c>
@@ -6521,7 +6725,7 @@
       </c>
       <c r="P54" s="44"/>
     </row>
-    <row r="55" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B55" s="41">
         <v>45</v>
       </c>
@@ -6552,7 +6756,7 @@
       </c>
       <c r="P55" s="44"/>
     </row>
-    <row r="56" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B56" s="41">
         <v>46</v>
       </c>
@@ -6583,7 +6787,7 @@
       </c>
       <c r="P56" s="44"/>
     </row>
-    <row r="57" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B57" s="41">
         <v>47</v>
       </c>
@@ -6614,7 +6818,7 @@
       </c>
       <c r="P57" s="44"/>
     </row>
-    <row r="58" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B58" s="41">
         <v>48</v>
       </c>
@@ -6645,7 +6849,7 @@
       </c>
       <c r="P58" s="44"/>
     </row>
-    <row r="59" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B59" s="41">
         <v>49</v>
       </c>
@@ -6676,7 +6880,7 @@
       </c>
       <c r="P59" s="44"/>
     </row>
-    <row r="60" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B60" s="41">
         <v>50</v>
       </c>
@@ -6707,7 +6911,7 @@
       </c>
       <c r="P60" s="44"/>
     </row>
-    <row r="61" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B61" s="41">
         <v>51</v>
       </c>
@@ -6738,7 +6942,7 @@
       </c>
       <c r="P61" s="44"/>
     </row>
-    <row r="62" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B62" s="41">
         <v>52</v>
       </c>
@@ -6769,7 +6973,7 @@
       </c>
       <c r="P62" s="44"/>
     </row>
-    <row r="63" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B63" s="41">
         <v>53</v>
       </c>
@@ -6800,7 +7004,7 @@
       </c>
       <c r="P63" s="44"/>
     </row>
-    <row r="64" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B64" s="41">
         <v>54</v>
       </c>
@@ -6831,7 +7035,7 @@
       </c>
       <c r="P64" s="44"/>
     </row>
-    <row r="65" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B65" s="41">
         <v>55</v>
       </c>
@@ -6862,7 +7066,7 @@
       </c>
       <c r="P65" s="44"/>
     </row>
-    <row r="66" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B66" s="41">
         <v>56</v>
       </c>
@@ -6893,7 +7097,7 @@
       </c>
       <c r="P66" s="44"/>
     </row>
-    <row r="67" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B67" s="41">
         <v>57</v>
       </c>
@@ -6924,7 +7128,7 @@
       </c>
       <c r="P67" s="44"/>
     </row>
-    <row r="68" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B68" s="41">
         <v>58</v>
       </c>
@@ -6955,7 +7159,7 @@
       </c>
       <c r="P68" s="44"/>
     </row>
-    <row r="69" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B69" s="41">
         <v>59</v>
       </c>
@@ -6986,7 +7190,7 @@
       </c>
       <c r="P69" s="44"/>
     </row>
-    <row r="70" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B70" s="41">
         <v>60</v>
       </c>
@@ -7017,7 +7221,7 @@
       </c>
       <c r="P70" s="44"/>
     </row>
-    <row r="71" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B71" s="41">
         <v>61</v>
       </c>
@@ -7048,7 +7252,7 @@
       </c>
       <c r="P71" s="44"/>
     </row>
-    <row r="72" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B72" s="41">
         <v>62</v>
       </c>
@@ -7079,7 +7283,7 @@
       </c>
       <c r="P72" s="44"/>
     </row>
-    <row r="73" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B73" s="41">
         <v>63</v>
       </c>
@@ -7110,7 +7314,7 @@
       </c>
       <c r="P73" s="44"/>
     </row>
-    <row r="74" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B74" s="41">
         <v>64</v>
       </c>
@@ -7141,7 +7345,7 @@
       </c>
       <c r="P74" s="44"/>
     </row>
-    <row r="75" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B75" s="41">
         <v>65</v>
       </c>
@@ -7172,7 +7376,7 @@
       </c>
       <c r="P75" s="44"/>
     </row>
-    <row r="76" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B76" s="41">
         <v>66</v>
       </c>
@@ -7203,7 +7407,7 @@
       </c>
       <c r="P76" s="44"/>
     </row>
-    <row r="77" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B77" s="41">
         <v>67</v>
       </c>
@@ -7234,7 +7438,7 @@
       </c>
       <c r="P77" s="44"/>
     </row>
-    <row r="78" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B78" s="41">
         <v>68</v>
       </c>
@@ -7265,7 +7469,7 @@
       </c>
       <c r="P78" s="44"/>
     </row>
-    <row r="79" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B79" s="41">
         <v>69</v>
       </c>
@@ -7296,7 +7500,7 @@
       </c>
       <c r="P79" s="44"/>
     </row>
-    <row r="80" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B80" s="41">
         <v>70</v>
       </c>
@@ -7327,7 +7531,7 @@
       </c>
       <c r="P80" s="44"/>
     </row>
-    <row r="81" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B81" s="41">
         <v>71</v>
       </c>
@@ -7358,7 +7562,7 @@
       </c>
       <c r="P81" s="44"/>
     </row>
-    <row r="82" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B82" s="41">
         <v>72</v>
       </c>
@@ -7389,7 +7593,7 @@
       </c>
       <c r="P82" s="44"/>
     </row>
-    <row r="83" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B83" s="41">
         <v>73</v>
       </c>
@@ -7420,7 +7624,7 @@
       </c>
       <c r="P83" s="44"/>
     </row>
-    <row r="84" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B84" s="41">
         <v>74</v>
       </c>
@@ -7451,7 +7655,7 @@
       </c>
       <c r="P84" s="44"/>
     </row>
-    <row r="85" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B85" s="41">
         <v>75</v>
       </c>
@@ -7482,7 +7686,7 @@
       </c>
       <c r="P85" s="44"/>
     </row>
-    <row r="86" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B86" s="41">
         <v>76</v>
       </c>
@@ -7513,7 +7717,7 @@
       </c>
       <c r="P86" s="44"/>
     </row>
-    <row r="87" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B87" s="41">
         <v>77</v>
       </c>
@@ -7544,7 +7748,7 @@
       </c>
       <c r="P87" s="44"/>
     </row>
-    <row r="88" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B88" s="41">
         <v>78</v>
       </c>
@@ -7575,7 +7779,7 @@
       </c>
       <c r="P88" s="44"/>
     </row>
-    <row r="89" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B89" s="41">
         <v>79</v>
       </c>
@@ -7606,7 +7810,7 @@
       </c>
       <c r="P89" s="44"/>
     </row>
-    <row r="90" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B90" s="41">
         <v>80</v>
       </c>
@@ -7637,7 +7841,7 @@
       </c>
       <c r="P90" s="44"/>
     </row>
-    <row r="91" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B91" s="41">
         <v>81</v>
       </c>
@@ -7668,7 +7872,7 @@
       </c>
       <c r="P91" s="44"/>
     </row>
-    <row r="92" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B92" s="41">
         <v>82</v>
       </c>
@@ -7699,7 +7903,7 @@
       </c>
       <c r="P92" s="44"/>
     </row>
-    <row r="93" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B93" s="41">
         <v>83</v>
       </c>
@@ -7730,7 +7934,7 @@
       </c>
       <c r="P93" s="44"/>
     </row>
-    <row r="94" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B94" s="41">
         <v>84</v>
       </c>
@@ -7761,7 +7965,7 @@
       </c>
       <c r="P94" s="44"/>
     </row>
-    <row r="95" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B95" s="41">
         <v>85</v>
       </c>
@@ -7792,7 +7996,7 @@
       </c>
       <c r="P95" s="44"/>
     </row>
-    <row r="96" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B96" s="41">
         <v>86</v>
       </c>
@@ -7823,7 +8027,7 @@
       </c>
       <c r="P96" s="44"/>
     </row>
-    <row r="97" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B97" s="41">
         <v>87</v>
       </c>
@@ -7854,7 +8058,7 @@
       </c>
       <c r="P97" s="44"/>
     </row>
-    <row r="98" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B98" s="41">
         <v>88</v>
       </c>
@@ -7885,7 +8089,7 @@
       </c>
       <c r="P98" s="44"/>
     </row>
-    <row r="99" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B99" s="41">
         <v>89</v>
       </c>
@@ -7916,7 +8120,7 @@
       </c>
       <c r="P99" s="44"/>
     </row>
-    <row r="100" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B100" s="41">
         <v>90</v>
       </c>
@@ -7947,7 +8151,7 @@
       </c>
       <c r="P100" s="44"/>
     </row>
-    <row r="101" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B101" s="41">
         <v>91</v>
       </c>
@@ -7978,7 +8182,7 @@
       </c>
       <c r="P101" s="44"/>
     </row>
-    <row r="102" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B102" s="41">
         <v>92</v>
       </c>
@@ -8009,7 +8213,7 @@
       </c>
       <c r="P102" s="44"/>
     </row>
-    <row r="103" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B103" s="41">
         <v>93</v>
       </c>
@@ -8040,7 +8244,7 @@
       </c>
       <c r="P103" s="44"/>
     </row>
-    <row r="104" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B104" s="41">
         <v>94</v>
       </c>
@@ -8071,7 +8275,7 @@
       </c>
       <c r="P104" s="44"/>
     </row>
-    <row r="105" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B105" s="41">
         <v>95</v>
       </c>
@@ -8102,7 +8306,7 @@
       </c>
       <c r="P105" s="44"/>
     </row>
-    <row r="106" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B106" s="41">
         <v>96</v>
       </c>
@@ -8133,7 +8337,7 @@
       </c>
       <c r="P106" s="44"/>
     </row>
-    <row r="107" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B107" s="41">
         <v>97</v>
       </c>
@@ -8164,7 +8368,7 @@
       </c>
       <c r="P107" s="44"/>
     </row>
-    <row r="108" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="108" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B108" s="41">
         <v>98</v>
       </c>
@@ -8195,7 +8399,7 @@
       </c>
       <c r="P108" s="44"/>
     </row>
-    <row r="109" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="109" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B109" s="41">
         <v>99</v>
       </c>
@@ -8226,7 +8430,7 @@
       </c>
       <c r="P109" s="44"/>
     </row>
-    <row r="110" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B110" s="41">
         <v>100</v>
       </c>
@@ -8344,13 +8548,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28A2F053-EB65-4682-A8B4-EF605DDDBF14}">
   <dimension ref="B2:P110"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="3" max="15" width="18.88671875" customWidth="1"/>
-    <col min="16" max="16" width="64.5546875" customWidth="1"/>
+    <col min="3" max="15" width="18.86328125" customWidth="1"/>
+    <col min="16" max="16" width="64.53125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:16" x14ac:dyDescent="0.45">
       <c r="C2" s="55" t="s">
         <v>86</v>
       </c>
@@ -8368,7 +8572,7 @@
       <c r="O2" s="55"/>
       <c r="P2" s="55"/>
     </row>
-    <row r="4" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C4" s="53" t="s">
         <v>75</v>
       </c>
@@ -8386,7 +8590,7 @@
       <c r="O4" s="53"/>
       <c r="P4" s="53"/>
     </row>
-    <row r="5" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:16" x14ac:dyDescent="0.45">
       <c r="C5" s="5"/>
       <c r="D5" s="5"/>
       <c r="E5" s="5"/>
@@ -8402,7 +8606,7 @@
       <c r="O5" s="5"/>
       <c r="P5" s="5"/>
     </row>
-    <row r="6" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:16" x14ac:dyDescent="0.45">
       <c r="C6" s="57" t="s">
         <v>68</v>
       </c>
@@ -8425,7 +8629,7 @@
       <c r="O6" s="5"/>
       <c r="P6" s="5"/>
     </row>
-    <row r="7" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:16" x14ac:dyDescent="0.45">
       <c r="C7" s="57"/>
       <c r="D7" s="11" t="s">
         <v>70</v>
@@ -8436,7 +8640,7 @@
       </c>
       <c r="J7" s="37"/>
     </row>
-    <row r="9" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B9" s="6"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
@@ -8459,7 +8663,7 @@
       <c r="O9" s="58"/>
       <c r="P9" s="7"/>
     </row>
-    <row r="10" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B10" s="8" t="s">
         <v>66</v>
       </c>
@@ -8506,7 +8710,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="11" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B11" s="41">
         <v>1</v>
       </c>
@@ -8537,7 +8741,7 @@
       </c>
       <c r="P11" s="44"/>
     </row>
-    <row r="12" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B12" s="41">
         <v>2</v>
       </c>
@@ -8568,7 +8772,7 @@
       </c>
       <c r="P12" s="44"/>
     </row>
-    <row r="13" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B13" s="41">
         <v>3</v>
       </c>
@@ -8599,7 +8803,7 @@
       </c>
       <c r="P13" s="44"/>
     </row>
-    <row r="14" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B14" s="41">
         <v>4</v>
       </c>
@@ -8630,7 +8834,7 @@
       </c>
       <c r="P14" s="44"/>
     </row>
-    <row r="15" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B15" s="41">
         <v>5</v>
       </c>
@@ -8661,7 +8865,7 @@
       </c>
       <c r="P15" s="44"/>
     </row>
-    <row r="16" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B16" s="41">
         <v>6</v>
       </c>
@@ -8692,7 +8896,7 @@
       </c>
       <c r="P16" s="44"/>
     </row>
-    <row r="17" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B17" s="41">
         <v>7</v>
       </c>
@@ -8723,7 +8927,7 @@
       </c>
       <c r="P17" s="44"/>
     </row>
-    <row r="18" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B18" s="41">
         <v>8</v>
       </c>
@@ -8754,7 +8958,7 @@
       </c>
       <c r="P18" s="44"/>
     </row>
-    <row r="19" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B19" s="41">
         <v>9</v>
       </c>
@@ -8785,7 +8989,7 @@
       </c>
       <c r="P19" s="44"/>
     </row>
-    <row r="20" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B20" s="41">
         <v>10</v>
       </c>
@@ -8816,7 +9020,7 @@
       </c>
       <c r="P20" s="44"/>
     </row>
-    <row r="21" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B21" s="41">
         <v>11</v>
       </c>
@@ -8847,7 +9051,7 @@
       </c>
       <c r="P21" s="44"/>
     </row>
-    <row r="22" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B22" s="41">
         <v>12</v>
       </c>
@@ -8878,7 +9082,7 @@
       </c>
       <c r="P22" s="44"/>
     </row>
-    <row r="23" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B23" s="41">
         <v>13</v>
       </c>
@@ -8909,7 +9113,7 @@
       </c>
       <c r="P23" s="44"/>
     </row>
-    <row r="24" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B24" s="41">
         <v>14</v>
       </c>
@@ -8940,7 +9144,7 @@
       </c>
       <c r="P24" s="44"/>
     </row>
-    <row r="25" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B25" s="41">
         <v>15</v>
       </c>
@@ -8971,7 +9175,7 @@
       </c>
       <c r="P25" s="44"/>
     </row>
-    <row r="26" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B26" s="41">
         <v>16</v>
       </c>
@@ -9002,7 +9206,7 @@
       </c>
       <c r="P26" s="44"/>
     </row>
-    <row r="27" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B27" s="41">
         <v>17</v>
       </c>
@@ -9033,7 +9237,7 @@
       </c>
       <c r="P27" s="44"/>
     </row>
-    <row r="28" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B28" s="41">
         <v>18</v>
       </c>
@@ -9064,7 +9268,7 @@
       </c>
       <c r="P28" s="44"/>
     </row>
-    <row r="29" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B29" s="41">
         <v>19</v>
       </c>
@@ -9095,7 +9299,7 @@
       </c>
       <c r="P29" s="44"/>
     </row>
-    <row r="30" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B30" s="41">
         <v>20</v>
       </c>
@@ -9126,7 +9330,7 @@
       </c>
       <c r="P30" s="44"/>
     </row>
-    <row r="31" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B31" s="41">
         <v>21</v>
       </c>
@@ -9157,7 +9361,7 @@
       </c>
       <c r="P31" s="44"/>
     </row>
-    <row r="32" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B32" s="41">
         <v>22</v>
       </c>
@@ -9188,7 +9392,7 @@
       </c>
       <c r="P32" s="44"/>
     </row>
-    <row r="33" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B33" s="41">
         <v>23</v>
       </c>
@@ -9219,7 +9423,7 @@
       </c>
       <c r="P33" s="44"/>
     </row>
-    <row r="34" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B34" s="41">
         <v>24</v>
       </c>
@@ -9250,7 +9454,7 @@
       </c>
       <c r="P34" s="44"/>
     </row>
-    <row r="35" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B35" s="41">
         <v>25</v>
       </c>
@@ -9281,7 +9485,7 @@
       </c>
       <c r="P35" s="44"/>
     </row>
-    <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B36" s="41">
         <v>26</v>
       </c>
@@ -9312,7 +9516,7 @@
       </c>
       <c r="P36" s="44"/>
     </row>
-    <row r="37" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B37" s="41">
         <v>27</v>
       </c>
@@ -9343,7 +9547,7 @@
       </c>
       <c r="P37" s="44"/>
     </row>
-    <row r="38" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B38" s="41">
         <v>28</v>
       </c>
@@ -9374,7 +9578,7 @@
       </c>
       <c r="P38" s="44"/>
     </row>
-    <row r="39" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B39" s="41">
         <v>29</v>
       </c>
@@ -9405,7 +9609,7 @@
       </c>
       <c r="P39" s="44"/>
     </row>
-    <row r="40" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B40" s="41">
         <v>30</v>
       </c>
@@ -9436,7 +9640,7 @@
       </c>
       <c r="P40" s="44"/>
     </row>
-    <row r="41" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B41" s="41">
         <v>31</v>
       </c>
@@ -9467,7 +9671,7 @@
       </c>
       <c r="P41" s="44"/>
     </row>
-    <row r="42" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B42" s="41">
         <v>32</v>
       </c>
@@ -9498,7 +9702,7 @@
       </c>
       <c r="P42" s="44"/>
     </row>
-    <row r="43" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B43" s="41">
         <v>33</v>
       </c>
@@ -9529,7 +9733,7 @@
       </c>
       <c r="P43" s="44"/>
     </row>
-    <row r="44" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B44" s="41">
         <v>34</v>
       </c>
@@ -9560,7 +9764,7 @@
       </c>
       <c r="P44" s="44"/>
     </row>
-    <row r="45" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B45" s="41">
         <v>35</v>
       </c>
@@ -9591,7 +9795,7 @@
       </c>
       <c r="P45" s="44"/>
     </row>
-    <row r="46" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B46" s="41">
         <v>36</v>
       </c>
@@ -9622,7 +9826,7 @@
       </c>
       <c r="P46" s="44"/>
     </row>
-    <row r="47" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B47" s="41">
         <v>37</v>
       </c>
@@ -9653,7 +9857,7 @@
       </c>
       <c r="P47" s="44"/>
     </row>
-    <row r="48" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B48" s="41">
         <v>38</v>
       </c>
@@ -9684,7 +9888,7 @@
       </c>
       <c r="P48" s="44"/>
     </row>
-    <row r="49" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B49" s="41">
         <v>39</v>
       </c>
@@ -9715,7 +9919,7 @@
       </c>
       <c r="P49" s="44"/>
     </row>
-    <row r="50" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B50" s="41">
         <v>40</v>
       </c>
@@ -9746,7 +9950,7 @@
       </c>
       <c r="P50" s="44"/>
     </row>
-    <row r="51" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B51" s="41">
         <v>41</v>
       </c>
@@ -9777,7 +9981,7 @@
       </c>
       <c r="P51" s="44"/>
     </row>
-    <row r="52" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B52" s="41">
         <v>42</v>
       </c>
@@ -9808,7 +10012,7 @@
       </c>
       <c r="P52" s="44"/>
     </row>
-    <row r="53" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B53" s="41">
         <v>43</v>
       </c>
@@ -9839,7 +10043,7 @@
       </c>
       <c r="P53" s="44"/>
     </row>
-    <row r="54" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B54" s="41">
         <v>44</v>
       </c>
@@ -9870,7 +10074,7 @@
       </c>
       <c r="P54" s="44"/>
     </row>
-    <row r="55" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B55" s="41">
         <v>45</v>
       </c>
@@ -9901,7 +10105,7 @@
       </c>
       <c r="P55" s="44"/>
     </row>
-    <row r="56" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B56" s="41">
         <v>46</v>
       </c>
@@ -9932,7 +10136,7 @@
       </c>
       <c r="P56" s="44"/>
     </row>
-    <row r="57" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B57" s="41">
         <v>47</v>
       </c>
@@ -9963,7 +10167,7 @@
       </c>
       <c r="P57" s="44"/>
     </row>
-    <row r="58" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B58" s="41">
         <v>48</v>
       </c>
@@ -9994,7 +10198,7 @@
       </c>
       <c r="P58" s="44"/>
     </row>
-    <row r="59" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B59" s="41">
         <v>49</v>
       </c>
@@ -10025,7 +10229,7 @@
       </c>
       <c r="P59" s="44"/>
     </row>
-    <row r="60" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B60" s="41">
         <v>50</v>
       </c>
@@ -10056,7 +10260,7 @@
       </c>
       <c r="P60" s="44"/>
     </row>
-    <row r="61" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B61" s="41">
         <v>51</v>
       </c>
@@ -10087,7 +10291,7 @@
       </c>
       <c r="P61" s="44"/>
     </row>
-    <row r="62" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B62" s="41">
         <v>52</v>
       </c>
@@ -10118,7 +10322,7 @@
       </c>
       <c r="P62" s="44"/>
     </row>
-    <row r="63" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B63" s="41">
         <v>53</v>
       </c>
@@ -10149,7 +10353,7 @@
       </c>
       <c r="P63" s="44"/>
     </row>
-    <row r="64" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B64" s="41">
         <v>54</v>
       </c>
@@ -10180,7 +10384,7 @@
       </c>
       <c r="P64" s="44"/>
     </row>
-    <row r="65" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B65" s="41">
         <v>55</v>
       </c>
@@ -10211,7 +10415,7 @@
       </c>
       <c r="P65" s="44"/>
     </row>
-    <row r="66" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B66" s="41">
         <v>56</v>
       </c>
@@ -10242,7 +10446,7 @@
       </c>
       <c r="P66" s="44"/>
     </row>
-    <row r="67" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B67" s="41">
         <v>57</v>
       </c>
@@ -10273,7 +10477,7 @@
       </c>
       <c r="P67" s="44"/>
     </row>
-    <row r="68" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B68" s="41">
         <v>58</v>
       </c>
@@ -10304,7 +10508,7 @@
       </c>
       <c r="P68" s="44"/>
     </row>
-    <row r="69" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B69" s="41">
         <v>59</v>
       </c>
@@ -10335,7 +10539,7 @@
       </c>
       <c r="P69" s="44"/>
     </row>
-    <row r="70" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B70" s="41">
         <v>60</v>
       </c>
@@ -10366,7 +10570,7 @@
       </c>
       <c r="P70" s="44"/>
     </row>
-    <row r="71" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B71" s="41">
         <v>61</v>
       </c>
@@ -10397,7 +10601,7 @@
       </c>
       <c r="P71" s="44"/>
     </row>
-    <row r="72" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B72" s="41">
         <v>62</v>
       </c>
@@ -10428,7 +10632,7 @@
       </c>
       <c r="P72" s="44"/>
     </row>
-    <row r="73" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B73" s="41">
         <v>63</v>
       </c>
@@ -10459,7 +10663,7 @@
       </c>
       <c r="P73" s="44"/>
     </row>
-    <row r="74" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B74" s="41">
         <v>64</v>
       </c>
@@ -10490,7 +10694,7 @@
       </c>
       <c r="P74" s="44"/>
     </row>
-    <row r="75" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B75" s="41">
         <v>65</v>
       </c>
@@ -10521,7 +10725,7 @@
       </c>
       <c r="P75" s="44"/>
     </row>
-    <row r="76" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B76" s="41">
         <v>66</v>
       </c>
@@ -10552,7 +10756,7 @@
       </c>
       <c r="P76" s="44"/>
     </row>
-    <row r="77" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B77" s="41">
         <v>67</v>
       </c>
@@ -10583,7 +10787,7 @@
       </c>
       <c r="P77" s="44"/>
     </row>
-    <row r="78" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B78" s="41">
         <v>68</v>
       </c>
@@ -10614,7 +10818,7 @@
       </c>
       <c r="P78" s="44"/>
     </row>
-    <row r="79" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B79" s="41">
         <v>69</v>
       </c>
@@ -10645,7 +10849,7 @@
       </c>
       <c r="P79" s="44"/>
     </row>
-    <row r="80" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B80" s="41">
         <v>70</v>
       </c>
@@ -10676,7 +10880,7 @@
       </c>
       <c r="P80" s="44"/>
     </row>
-    <row r="81" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B81" s="41">
         <v>71</v>
       </c>
@@ -10707,7 +10911,7 @@
       </c>
       <c r="P81" s="44"/>
     </row>
-    <row r="82" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B82" s="41">
         <v>72</v>
       </c>
@@ -10738,7 +10942,7 @@
       </c>
       <c r="P82" s="44"/>
     </row>
-    <row r="83" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B83" s="41">
         <v>73</v>
       </c>
@@ -10769,7 +10973,7 @@
       </c>
       <c r="P83" s="44"/>
     </row>
-    <row r="84" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B84" s="41">
         <v>74</v>
       </c>
@@ -10800,7 +11004,7 @@
       </c>
       <c r="P84" s="44"/>
     </row>
-    <row r="85" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B85" s="41">
         <v>75</v>
       </c>
@@ -10831,7 +11035,7 @@
       </c>
       <c r="P85" s="44"/>
     </row>
-    <row r="86" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B86" s="41">
         <v>76</v>
       </c>
@@ -10862,7 +11066,7 @@
       </c>
       <c r="P86" s="44"/>
     </row>
-    <row r="87" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B87" s="41">
         <v>77</v>
       </c>
@@ -10893,7 +11097,7 @@
       </c>
       <c r="P87" s="44"/>
     </row>
-    <row r="88" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B88" s="41">
         <v>78</v>
       </c>
@@ -10924,7 +11128,7 @@
       </c>
       <c r="P88" s="44"/>
     </row>
-    <row r="89" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B89" s="41">
         <v>79</v>
       </c>
@@ -10955,7 +11159,7 @@
       </c>
       <c r="P89" s="44"/>
     </row>
-    <row r="90" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B90" s="41">
         <v>80</v>
       </c>
@@ -10986,7 +11190,7 @@
       </c>
       <c r="P90" s="44"/>
     </row>
-    <row r="91" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B91" s="41">
         <v>81</v>
       </c>
@@ -11017,7 +11221,7 @@
       </c>
       <c r="P91" s="44"/>
     </row>
-    <row r="92" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B92" s="41">
         <v>82</v>
       </c>
@@ -11048,7 +11252,7 @@
       </c>
       <c r="P92" s="44"/>
     </row>
-    <row r="93" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B93" s="41">
         <v>83</v>
       </c>
@@ -11079,7 +11283,7 @@
       </c>
       <c r="P93" s="44"/>
     </row>
-    <row r="94" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B94" s="41">
         <v>84</v>
       </c>
@@ -11110,7 +11314,7 @@
       </c>
       <c r="P94" s="44"/>
     </row>
-    <row r="95" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B95" s="41">
         <v>85</v>
       </c>
@@ -11141,7 +11345,7 @@
       </c>
       <c r="P95" s="44"/>
     </row>
-    <row r="96" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B96" s="41">
         <v>86</v>
       </c>
@@ -11172,7 +11376,7 @@
       </c>
       <c r="P96" s="44"/>
     </row>
-    <row r="97" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B97" s="41">
         <v>87</v>
       </c>
@@ -11203,7 +11407,7 @@
       </c>
       <c r="P97" s="44"/>
     </row>
-    <row r="98" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B98" s="41">
         <v>88</v>
       </c>
@@ -11234,7 +11438,7 @@
       </c>
       <c r="P98" s="44"/>
     </row>
-    <row r="99" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B99" s="41">
         <v>89</v>
       </c>
@@ -11265,7 +11469,7 @@
       </c>
       <c r="P99" s="44"/>
     </row>
-    <row r="100" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B100" s="41">
         <v>90</v>
       </c>
@@ -11296,7 +11500,7 @@
       </c>
       <c r="P100" s="44"/>
     </row>
-    <row r="101" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B101" s="41">
         <v>91</v>
       </c>
@@ -11327,7 +11531,7 @@
       </c>
       <c r="P101" s="44"/>
     </row>
-    <row r="102" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B102" s="41">
         <v>92</v>
       </c>
@@ -11358,7 +11562,7 @@
       </c>
       <c r="P102" s="44"/>
     </row>
-    <row r="103" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B103" s="41">
         <v>93</v>
       </c>
@@ -11389,7 +11593,7 @@
       </c>
       <c r="P103" s="44"/>
     </row>
-    <row r="104" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B104" s="41">
         <v>94</v>
       </c>
@@ -11420,7 +11624,7 @@
       </c>
       <c r="P104" s="44"/>
     </row>
-    <row r="105" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B105" s="41">
         <v>95</v>
       </c>
@@ -11451,7 +11655,7 @@
       </c>
       <c r="P105" s="44"/>
     </row>
-    <row r="106" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B106" s="41">
         <v>96</v>
       </c>
@@ -11482,7 +11686,7 @@
       </c>
       <c r="P106" s="44"/>
     </row>
-    <row r="107" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B107" s="41">
         <v>97</v>
       </c>
@@ -11513,7 +11717,7 @@
       </c>
       <c r="P107" s="44"/>
     </row>
-    <row r="108" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="108" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B108" s="41">
         <v>98</v>
       </c>
@@ -11544,7 +11748,7 @@
       </c>
       <c r="P108" s="44"/>
     </row>
-    <row r="109" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="109" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B109" s="41">
         <v>99</v>
       </c>
@@ -11575,7 +11779,7 @@
       </c>
       <c r="P109" s="44"/>
     </row>
-    <row r="110" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B110" s="41">
         <v>100</v>
       </c>
@@ -11693,12 +11897,12 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6230FA8A-EA33-4C76-AA54-C885D607690C}">
   <dimension ref="B2:J39"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="10" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B2" s="55" t="s">
         <v>11</v>
       </c>
@@ -11711,7 +11915,7 @@
       <c r="I2" s="55"/>
       <c r="J2" s="55"/>
     </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B4" s="53" t="s">
         <v>13</v>
       </c>
@@ -11724,7 +11928,7 @@
       <c r="I4" s="53"/>
       <c r="J4" s="53"/>
     </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B5" s="53"/>
       <c r="C5" s="53"/>
       <c r="D5" s="53"/>
@@ -11735,7 +11939,7 @@
       <c r="I5" s="53"/>
       <c r="J5" s="53"/>
     </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B6" s="53"/>
       <c r="C6" s="53"/>
       <c r="D6" s="53"/>
@@ -11746,7 +11950,7 @@
       <c r="I6" s="53"/>
       <c r="J6" s="53"/>
     </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B7" s="5"/>
       <c r="C7" s="5"/>
       <c r="D7" s="5"/>
@@ -11757,7 +11961,7 @@
       <c r="I7" s="5"/>
       <c r="J7" s="5"/>
     </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B8" s="25" t="s">
         <v>12</v>
       </c>
@@ -11770,7 +11974,7 @@
       <c r="I8" s="12"/>
       <c r="J8" s="12"/>
     </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B9" s="13" t="s">
         <v>80</v>
       </c>
@@ -11783,7 +11987,7 @@
       <c r="I9" s="12"/>
       <c r="J9" s="12"/>
     </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B10" s="13" t="s">
         <v>81</v>
       </c>
@@ -11796,7 +12000,7 @@
       <c r="I10" s="12"/>
       <c r="J10" s="12"/>
     </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B11" s="13" t="s">
         <v>82</v>
       </c>
@@ -11809,7 +12013,7 @@
       <c r="I11" s="12"/>
       <c r="J11" s="12"/>
     </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B12" s="13" t="s">
         <v>83</v>
       </c>
@@ -11822,7 +12026,7 @@
       <c r="I12" s="12"/>
       <c r="J12" s="12"/>
     </row>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B13" s="13" t="s">
         <v>84</v>
       </c>
@@ -11835,7 +12039,7 @@
       <c r="I13" s="12"/>
       <c r="J13" s="12"/>
     </row>
-    <row r="14" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B14" s="14" t="s">
         <v>77</v>
       </c>
@@ -11848,7 +12052,7 @@
       <c r="I14" s="12"/>
       <c r="J14" s="12"/>
     </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B15" s="3"/>
       <c r="C15" s="12"/>
       <c r="D15" s="12"/>
@@ -11859,7 +12063,7 @@
       <c r="I15" s="12"/>
       <c r="J15" s="12"/>
     </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B16" s="26" t="s">
         <v>14</v>
       </c>
@@ -11872,7 +12076,7 @@
       <c r="I16" s="12"/>
       <c r="J16" s="12"/>
     </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B17" s="15" t="s">
         <v>15</v>
       </c>
@@ -11885,7 +12089,7 @@
       <c r="I17" s="12"/>
       <c r="J17" s="12"/>
     </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B18" s="15" t="s">
         <v>16</v>
       </c>
@@ -11898,7 +12102,7 @@
       <c r="I18" s="12"/>
       <c r="J18" s="12"/>
     </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B19" s="16" t="s">
         <v>17</v>
       </c>
@@ -11911,7 +12115,7 @@
       <c r="I19" s="12"/>
       <c r="J19" s="12"/>
     </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B20" s="3"/>
       <c r="C20" s="12"/>
       <c r="D20" s="12"/>
@@ -11922,7 +12126,7 @@
       <c r="I20" s="12"/>
       <c r="J20" s="12"/>
     </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B21" s="26" t="s">
         <v>54</v>
       </c>
@@ -11935,7 +12139,7 @@
       <c r="I21" s="12"/>
       <c r="J21" s="12"/>
     </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B22" s="17">
         <v>45658</v>
       </c>
@@ -11948,7 +12152,7 @@
       <c r="I22" s="12"/>
       <c r="J22" s="12"/>
     </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B23" s="18" t="s">
         <v>55</v>
       </c>
@@ -11961,7 +12165,7 @@
       <c r="I23" s="12"/>
       <c r="J23" s="12"/>
     </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B24" s="12"/>
       <c r="C24" s="12"/>
       <c r="D24" s="12"/>
@@ -11972,7 +12176,7 @@
       <c r="I24" s="12"/>
       <c r="J24" s="12"/>
     </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B25" s="27" t="s">
         <v>22</v>
       </c>
@@ -11989,7 +12193,7 @@
       <c r="I25" s="29"/>
       <c r="J25" s="30"/>
     </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B26" s="19" t="s">
         <v>29</v>
       </c>
@@ -12012,7 +12216,7 @@
       <c r="I26" s="12"/>
       <c r="J26" s="20"/>
     </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B27" s="19" t="s">
         <v>23</v>
       </c>
@@ -12039,7 +12243,7 @@
       </c>
       <c r="J27" s="20"/>
     </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B28" s="19" t="s">
         <v>24</v>
       </c>
@@ -12064,7 +12268,7 @@
       <c r="I28" s="12"/>
       <c r="J28" s="20"/>
     </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B29" s="19" t="s">
         <v>25</v>
       </c>
@@ -12091,7 +12295,7 @@
       </c>
       <c r="J29" s="20"/>
     </row>
-    <row r="30" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B30" s="19" t="s">
         <v>26</v>
       </c>
@@ -12118,7 +12322,7 @@
       </c>
       <c r="J30" s="20"/>
     </row>
-    <row r="31" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B31" s="21" t="s">
         <v>27</v>
       </c>
@@ -12147,7 +12351,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="32" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B32" s="22" t="s">
         <v>56</v>
       </c>
@@ -12164,7 +12368,7 @@
       <c r="I32" s="23"/>
       <c r="J32" s="24"/>
     </row>
-    <row r="33" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B33" s="12"/>
       <c r="C33" s="12"/>
       <c r="D33" s="12"/>
@@ -12175,7 +12379,7 @@
       <c r="I33" s="12"/>
       <c r="J33" s="12"/>
     </row>
-    <row r="34" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B34" s="33" t="s">
         <v>60</v>
       </c>
@@ -12190,7 +12394,7 @@
       <c r="I34" s="12"/>
       <c r="J34" s="12"/>
     </row>
-    <row r="35" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B35" s="21" t="s">
         <v>64</v>
       </c>
@@ -12205,7 +12409,7 @@
       <c r="I35" s="12"/>
       <c r="J35" s="12"/>
     </row>
-    <row r="36" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B36" s="21" t="s">
         <v>62</v>
       </c>
@@ -12220,7 +12424,7 @@
       <c r="I36" s="12"/>
       <c r="J36" s="12"/>
     </row>
-    <row r="37" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B37" s="21" t="s">
         <v>65</v>
       </c>
@@ -12235,7 +12439,7 @@
       <c r="I37" s="12"/>
       <c r="J37" s="12"/>
     </row>
-    <row r="38" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B38" s="21" t="s">
         <v>61</v>
       </c>
@@ -12250,7 +12454,7 @@
       <c r="I38" s="12"/>
       <c r="J38" s="12"/>
     </row>
-    <row r="39" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B39" s="32" t="s">
         <v>56</v>
       </c>

--- a/reports/Deliverable D01 (Level C)/Group/Planning-Template.xlsx
+++ b/reports/Deliverable D01 (Level C)/Group/Planning-Template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Javier\Downloads\Workspace-26\Scrapbook\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Javier\Downloads\Workspace-26\Projects\Acme-Starters-C\reports\Deliverable D01 (Level C)\Group\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93F57BBF-E1E9-48C8-9A46-8F9C353399AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0324068-7A2D-4E86-9EBA-51AE14C25813}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10718" yWindow="0" windowWidth="10965" windowHeight="12863" activeTab="2" xr2:uid="{683E09B8-1D94-4905-B116-9D998A46AAA3}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="2" xr2:uid="{683E09B8-1D94-4905-B116-9D998A46AAA3}"/>
   </bookViews>
   <sheets>
     <sheet name="Copyright" sheetId="10" r:id="rId1"/>
@@ -1757,7 +1757,7 @@
       </c>
       <c r="E7" s="36">
         <f>SUM(O12:O112)</f>
-        <v>237.5</v>
+        <v>287.5</v>
       </c>
       <c r="J7" s="37"/>
     </row>
@@ -2056,7 +2056,7 @@
       </c>
       <c r="K15" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Planned</v>
+        <v>Completed</v>
       </c>
       <c r="L15" s="47">
         <v>0.5</v>
@@ -2100,22 +2100,26 @@
       <c r="I16" s="46">
         <v>46061.375</v>
       </c>
-      <c r="J16" s="46"/>
+      <c r="J16" s="46">
+        <v>46061.59375</v>
+      </c>
       <c r="K16" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
+        <v>Completed</v>
       </c>
       <c r="L16" s="47">
         <v>3</v>
       </c>
-      <c r="M16" s="47"/>
+      <c r="M16" s="47">
+        <v>2</v>
+      </c>
       <c r="N16" s="45">
         <f>IF(ISBLANK(L16), "", L16*VLOOKUP($F16,Internal!$B$26:$C$32,2,FALSE))</f>
         <v>75</v>
       </c>
-      <c r="O16" s="45" t="str">
+      <c r="O16" s="45">
         <f>IF(ISBLANK(M16), "", M16*VLOOKUP($F16,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
+        <v>50</v>
       </c>
       <c r="P16" s="44" t="s">
         <v>95</v>

--- a/reports/Deliverable D01 (Level C)/Group/Planning-Template.xlsx
+++ b/reports/Deliverable D01 (Level C)/Group/Planning-Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Javier\Downloads\Workspace-26\Projects\Acme-Starters-C\reports\Deliverable D01 (Level C)\Group\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0324068-7A2D-4E86-9EBA-51AE14C25813}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3BBD17B-1F48-498D-8000-25F7CA5971AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="2" xr2:uid="{683E09B8-1D94-4905-B116-9D998A46AAA3}"/>
   </bookViews>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="102">
   <si>
     <t xml:space="preserve">  Enter configuration data in these cells</t>
   </si>
@@ -359,6 +359,12 @@
   </si>
   <si>
     <t>Rellenar el formulario de identificación.</t>
+  </si>
+  <si>
+    <t>Actualizar planificación.</t>
+  </si>
+  <si>
+    <t>Añadir apartados faltantes al chartering report.</t>
   </si>
 </sst>
 </file>
@@ -760,16 +766,6 @@
   <dxfs count="6">
     <dxf>
       <font>
-        <color rgb="FFFFFF00"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <strike val="0"/>
         <color rgb="FFFFFF00"/>
       </font>
@@ -813,6 +809,16 @@
     <dxf>
       <font>
         <strike val="0"/>
+        <color rgb="FFFFFF00"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FFFFFF00"/>
       </font>
       <fill>
@@ -1736,7 +1742,7 @@
       </c>
       <c r="E6" s="35">
         <f>SUM(N12:N112)</f>
-        <v>277.5</v>
+        <v>331.66666666666669</v>
       </c>
       <c r="F6" s="5"/>
       <c r="G6" s="5"/>
@@ -1757,7 +1763,7 @@
       </c>
       <c r="E7" s="36">
         <f>SUM(O12:O112)</f>
-        <v>287.5</v>
+        <v>361.66666666666669</v>
       </c>
       <c r="J7" s="37"/>
     </row>
@@ -2148,23 +2154,29 @@
       <c r="H17" s="43" t="s">
         <v>96</v>
       </c>
-      <c r="I17" s="46"/>
-      <c r="J17" s="46"/>
+      <c r="I17" s="46">
+        <v>46061.604166666664</v>
+      </c>
+      <c r="J17" s="46">
+        <v>46061.614583333336</v>
+      </c>
       <c r="K17" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
+        <v>Completed</v>
       </c>
       <c r="L17" s="47">
         <v>0.5</v>
       </c>
-      <c r="M17" s="47"/>
+      <c r="M17" s="47">
+        <v>0.25</v>
+      </c>
       <c r="N17" s="45">
         <f>IF(ISBLANK(L17), "", L17*VLOOKUP($F17,Internal!$B$26:$C$32,2,FALSE))</f>
         <v>15</v>
       </c>
-      <c r="O17" s="45" t="str">
+      <c r="O17" s="45">
         <f>IF(ISBLANK(M17), "", M17*VLOOKUP($F17,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
+        <v>7.5</v>
       </c>
       <c r="P17" s="44" t="s">
         <v>97</v>
@@ -2176,30 +2188,48 @@
       </c>
       <c r="C18" s="42" t="str">
         <f>IF(ISBLANK(D18), "", _xlfn.CONCAT("T", TEXT(B18, "0000"), "/", VLOOKUP(D18, Internal!$B$35:C$39, 2, FALSE), IF(OR(D18="QA", D18="Revision"), _xlfn.CONCAT("/", H18), "")))</f>
-        <v/>
-      </c>
-      <c r="D18" s="44"/>
-      <c r="E18" s="43"/>
-      <c r="F18" s="43"/>
-      <c r="G18" s="44"/>
+        <v>T0008/M</v>
+      </c>
+      <c r="D18" s="44" t="s">
+        <v>64</v>
+      </c>
+      <c r="E18" s="43" t="s">
+        <v>80</v>
+      </c>
+      <c r="F18" s="43" t="s">
+        <v>23</v>
+      </c>
+      <c r="G18" s="44" t="s">
+        <v>36</v>
+      </c>
       <c r="H18" s="43"/>
-      <c r="I18" s="46"/>
-      <c r="J18" s="46"/>
+      <c r="I18" s="46">
+        <v>46061.864583333336</v>
+      </c>
+      <c r="J18" s="46">
+        <v>46061.916666666664</v>
+      </c>
       <c r="K18" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L18" s="47"/>
-      <c r="M18" s="47"/>
-      <c r="N18" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L18" s="47">
+        <v>1</v>
+      </c>
+      <c r="M18" s="47">
+        <v>1.25</v>
+      </c>
+      <c r="N18" s="45">
         <f>IF(ISBLANK(L18), "", L18*VLOOKUP($F18,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O18" s="45" t="str">
+        <v>50</v>
+      </c>
+      <c r="O18" s="45">
         <f>IF(ISBLANK(M18), "", M18*VLOOKUP($F18,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P18" s="44"/>
+        <v>62.5</v>
+      </c>
+      <c r="P18" s="44" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="19" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B19" s="41">
@@ -2207,30 +2237,48 @@
       </c>
       <c r="C19" s="42" t="str">
         <f>IF(ISBLANK(D19), "", _xlfn.CONCAT("T", TEXT(B19, "0000"), "/", VLOOKUP(D19, Internal!$B$35:C$39, 2, FALSE), IF(OR(D19="QA", D19="Revision"), _xlfn.CONCAT("/", H19), "")))</f>
-        <v/>
-      </c>
-      <c r="D19" s="44"/>
-      <c r="E19" s="43"/>
-      <c r="F19" s="43"/>
-      <c r="G19" s="44"/>
+        <v>T0009/M</v>
+      </c>
+      <c r="D19" s="44" t="s">
+        <v>64</v>
+      </c>
+      <c r="E19" s="43" t="s">
+        <v>80</v>
+      </c>
+      <c r="F19" s="43" t="s">
+        <v>23</v>
+      </c>
+      <c r="G19" s="44" t="s">
+        <v>20</v>
+      </c>
       <c r="H19" s="43"/>
-      <c r="I19" s="46"/>
-      <c r="J19" s="46"/>
+      <c r="I19" s="46">
+        <v>46061.916666666664</v>
+      </c>
+      <c r="J19" s="46">
+        <v>46061.920138888891</v>
+      </c>
       <c r="K19" s="45" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L19" s="47"/>
-      <c r="M19" s="47"/>
-      <c r="N19" s="45" t="str">
+        <f t="shared" ref="K19" ca="1" si="1">IF(OR(I19="",J19=""),"",IF(AND(J19&lt;&gt;"",I19&gt;=NOW()),"Planned",IF(AND(J19&lt;&gt;"",J19&lt;NOW()),"Completed","Ongoing")))</f>
+        <v>Completed</v>
+      </c>
+      <c r="L19" s="47">
+        <v>8.3333333333333329E-2</v>
+      </c>
+      <c r="M19" s="47">
+        <v>8.3333333333333329E-2</v>
+      </c>
+      <c r="N19" s="45">
         <f>IF(ISBLANK(L19), "", L19*VLOOKUP($F19,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O19" s="45" t="str">
+        <v>4.1666666666666661</v>
+      </c>
+      <c r="O19" s="45">
         <f>IF(ISBLANK(M19), "", M19*VLOOKUP($F19,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P19" s="44"/>
+        <v>4.1666666666666661</v>
+      </c>
+      <c r="P19" s="44" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="20" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B20" s="41">
@@ -4046,7 +4094,7 @@
       <c r="I78" s="46"/>
       <c r="J78" s="46"/>
       <c r="K78" s="45" t="str">
-        <f t="shared" ref="K78:K112" ca="1" si="1">IF(OR(I78="",J78=""),"",IF(AND(J78&lt;&gt;"",I78&gt;=NOW()),"Planned",IF(AND(J78&lt;&gt;"",J78&lt;NOW()),"Completed","Ongoing")))</f>
+        <f t="shared" ref="K78:K112" ca="1" si="2">IF(OR(I78="",J78=""),"",IF(AND(J78&lt;&gt;"",I78&gt;=NOW()),"Planned",IF(AND(J78&lt;&gt;"",J78&lt;NOW()),"Completed","Ongoing")))</f>
         <v/>
       </c>
       <c r="L78" s="47"/>
@@ -4077,7 +4125,7 @@
       <c r="I79" s="46"/>
       <c r="J79" s="46"/>
       <c r="K79" s="45" t="str">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
       <c r="L79" s="47"/>
@@ -4108,7 +4156,7 @@
       <c r="I80" s="46"/>
       <c r="J80" s="46"/>
       <c r="K80" s="45" t="str">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
       <c r="L80" s="47"/>
@@ -4139,7 +4187,7 @@
       <c r="I81" s="46"/>
       <c r="J81" s="46"/>
       <c r="K81" s="45" t="str">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
       <c r="L81" s="47"/>
@@ -4170,7 +4218,7 @@
       <c r="I82" s="46"/>
       <c r="J82" s="46"/>
       <c r="K82" s="45" t="str">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
       <c r="L82" s="47"/>
@@ -4201,7 +4249,7 @@
       <c r="I83" s="46"/>
       <c r="J83" s="46"/>
       <c r="K83" s="45" t="str">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
       <c r="L83" s="47"/>
@@ -4232,7 +4280,7 @@
       <c r="I84" s="46"/>
       <c r="J84" s="46"/>
       <c r="K84" s="45" t="str">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
       <c r="L84" s="47"/>
@@ -4263,7 +4311,7 @@
       <c r="I85" s="46"/>
       <c r="J85" s="46"/>
       <c r="K85" s="45" t="str">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
       <c r="L85" s="47"/>
@@ -4294,7 +4342,7 @@
       <c r="I86" s="46"/>
       <c r="J86" s="46"/>
       <c r="K86" s="45" t="str">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
       <c r="L86" s="47"/>
@@ -4325,7 +4373,7 @@
       <c r="I87" s="46"/>
       <c r="J87" s="46"/>
       <c r="K87" s="45" t="str">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
       <c r="L87" s="47"/>
@@ -4356,7 +4404,7 @@
       <c r="I88" s="46"/>
       <c r="J88" s="46"/>
       <c r="K88" s="45" t="str">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
       <c r="L88" s="47"/>
@@ -4387,7 +4435,7 @@
       <c r="I89" s="46"/>
       <c r="J89" s="46"/>
       <c r="K89" s="45" t="str">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
       <c r="L89" s="47"/>
@@ -4418,7 +4466,7 @@
       <c r="I90" s="46"/>
       <c r="J90" s="46"/>
       <c r="K90" s="45" t="str">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
       <c r="L90" s="47"/>
@@ -4449,7 +4497,7 @@
       <c r="I91" s="46"/>
       <c r="J91" s="46"/>
       <c r="K91" s="45" t="str">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
       <c r="L91" s="47"/>
@@ -4480,7 +4528,7 @@
       <c r="I92" s="46"/>
       <c r="J92" s="46"/>
       <c r="K92" s="45" t="str">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
       <c r="L92" s="47"/>
@@ -4511,7 +4559,7 @@
       <c r="I93" s="46"/>
       <c r="J93" s="46"/>
       <c r="K93" s="45" t="str">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
       <c r="L93" s="47"/>
@@ -4542,7 +4590,7 @@
       <c r="I94" s="46"/>
       <c r="J94" s="46"/>
       <c r="K94" s="45" t="str">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
       <c r="L94" s="47"/>
@@ -4573,7 +4621,7 @@
       <c r="I95" s="46"/>
       <c r="J95" s="46"/>
       <c r="K95" s="45" t="str">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
       <c r="L95" s="47"/>
@@ -4604,7 +4652,7 @@
       <c r="I96" s="46"/>
       <c r="J96" s="46"/>
       <c r="K96" s="45" t="str">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
       <c r="L96" s="47"/>
@@ -4635,7 +4683,7 @@
       <c r="I97" s="46"/>
       <c r="J97" s="46"/>
       <c r="K97" s="45" t="str">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
       <c r="L97" s="47"/>
@@ -4666,7 +4714,7 @@
       <c r="I98" s="46"/>
       <c r="J98" s="46"/>
       <c r="K98" s="45" t="str">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
       <c r="L98" s="47"/>
@@ -4697,7 +4745,7 @@
       <c r="I99" s="46"/>
       <c r="J99" s="46"/>
       <c r="K99" s="45" t="str">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
       <c r="L99" s="47"/>
@@ -4728,7 +4776,7 @@
       <c r="I100" s="46"/>
       <c r="J100" s="46"/>
       <c r="K100" s="45" t="str">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
       <c r="L100" s="47"/>
@@ -4759,7 +4807,7 @@
       <c r="I101" s="46"/>
       <c r="J101" s="46"/>
       <c r="K101" s="45" t="str">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
       <c r="L101" s="47"/>
@@ -4790,7 +4838,7 @@
       <c r="I102" s="46"/>
       <c r="J102" s="46"/>
       <c r="K102" s="45" t="str">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
       <c r="L102" s="47"/>
@@ -4821,7 +4869,7 @@
       <c r="I103" s="46"/>
       <c r="J103" s="46"/>
       <c r="K103" s="45" t="str">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
       <c r="L103" s="47"/>
@@ -4852,7 +4900,7 @@
       <c r="I104" s="46"/>
       <c r="J104" s="46"/>
       <c r="K104" s="45" t="str">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
       <c r="L104" s="47"/>
@@ -4883,7 +4931,7 @@
       <c r="I105" s="46"/>
       <c r="J105" s="46"/>
       <c r="K105" s="45" t="str">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
       <c r="L105" s="47"/>
@@ -4914,7 +4962,7 @@
       <c r="I106" s="46"/>
       <c r="J106" s="46"/>
       <c r="K106" s="45" t="str">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
       <c r="L106" s="47"/>
@@ -4945,7 +4993,7 @@
       <c r="I107" s="46"/>
       <c r="J107" s="46"/>
       <c r="K107" s="45" t="str">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
       <c r="L107" s="47"/>
@@ -4976,7 +5024,7 @@
       <c r="I108" s="46"/>
       <c r="J108" s="46"/>
       <c r="K108" s="45" t="str">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
       <c r="L108" s="47"/>
@@ -5007,7 +5055,7 @@
       <c r="I109" s="46"/>
       <c r="J109" s="46"/>
       <c r="K109" s="45" t="str">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
       <c r="L109" s="47"/>
@@ -5038,7 +5086,7 @@
       <c r="I110" s="46"/>
       <c r="J110" s="46"/>
       <c r="K110" s="45" t="str">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
       <c r="L110" s="47"/>
@@ -5069,7 +5117,7 @@
       <c r="I111" s="46"/>
       <c r="J111" s="46"/>
       <c r="K111" s="45" t="str">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
       <c r="L111" s="47"/>
@@ -5100,7 +5148,7 @@
       <c r="I112" s="46"/>
       <c r="J112" s="46"/>
       <c r="K112" s="45" t="str">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
       <c r="L112" s="47"/>
@@ -5125,22 +5173,22 @@
     <mergeCell ref="C4:P4"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
+  <conditionalFormatting sqref="J11:J112">
+    <cfRule type="expression" dxfId="5" priority="1">
+      <formula>AND(I11&lt;&gt;"",J11&lt;&gt;"", I11&gt;J11)</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="H11:H112">
-    <cfRule type="expression" dxfId="5" priority="2">
+    <cfRule type="expression" dxfId="0" priority="3">
       <formula>AND(H11&lt;&gt;"",COUNTIF($C$12:$C$112,H11)=0)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J11:J112">
-    <cfRule type="expression" dxfId="4" priority="1">
-      <formula>AND(I11&lt;&gt;"",J11&lt;&gt;"", I11&gt;J11)</formula>
-    </cfRule>
-  </conditionalFormatting>
   <dataValidations count="9">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Description" prompt="Provide a succint description of the task.  If not possible, the provide a link to a document where is is described." sqref="P10" xr:uid="{D0BF2996-BBAB-402C-8777-D22DB1423D76}"/>
     <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Expected workload" prompt="Enter the expected workload in hours or fractions." sqref="L11:L112" xr:uid="{AADDA758-A288-4920-A868-A656B94EE475}">
       <formula1>0</formula1>
       <formula2>1024</formula2>
     </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Description" prompt="Provide a succint description of the task.  If not possible, the provide a link to a document where is is described." sqref="P10" xr:uid="{D0BF2996-BBAB-402C-8777-D22DB1423D76}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Actual workload" prompt="Enter the actual workload in hours or fractions._x000a_" sqref="M11:M112" xr:uid="{FFAE3670-28C0-4D44-81DE-0074EF40B001}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Description" prompt="If actually necessary, then write a succint description and/or include a link to a document that provides further information." sqref="K11:K112 P11:P112" xr:uid="{4DDB20BC-C9D1-4AB5-9B81-3F9F25727EAD}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Costs" prompt="The costs are updated automatically.  Don't modify them manually" sqref="N11:O112" xr:uid="{3D1A9EDC-88F9-4796-ACC0-9C5DD1125EFE}"/>
@@ -8475,12 +8523,12 @@
     <mergeCell ref="I9:J9"/>
   </mergeCells>
   <conditionalFormatting sqref="H11:H110">
-    <cfRule type="expression" dxfId="3" priority="2">
+    <cfRule type="expression" dxfId="4" priority="2">
       <formula>AND(H11&lt;&gt;"",COUNTIF($C$11:$C$110,H11)=0)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J11:J110">
-    <cfRule type="expression" dxfId="2" priority="1">
+    <cfRule type="expression" dxfId="3" priority="1">
       <formula>AND(I11&lt;&gt;"",J11&lt;&gt;"", I11&gt;J11)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11824,12 +11872,12 @@
     <mergeCell ref="I9:J9"/>
   </mergeCells>
   <conditionalFormatting sqref="H11:H110">
-    <cfRule type="expression" dxfId="1" priority="2">
+    <cfRule type="expression" dxfId="2" priority="2">
       <formula>AND(H11&lt;&gt;"",COUNTIF($C$11:$C$110,H11)=0)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J11:J110">
-    <cfRule type="expression" dxfId="0" priority="1">
+    <cfRule type="expression" dxfId="1" priority="1">
       <formula>AND(I11&lt;&gt;"",J11&lt;&gt;"", I11&gt;J11)</formula>
     </cfRule>
   </conditionalFormatting>

--- a/reports/Deliverable D01 (Level C)/Group/Planning-Template.xlsx
+++ b/reports/Deliverable D01 (Level C)/Group/Planning-Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Javier\Downloads\Workspace-26\Projects\Acme-Starters-C\reports\Deliverable D01 (Level C)\Group\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3BBD17B-1F48-498D-8000-25F7CA5971AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEFCDECD-5A75-4411-97CD-8F8FDD2B4F43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="2" xr2:uid="{683E09B8-1D94-4905-B116-9D998A46AAA3}"/>
   </bookViews>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="109">
   <si>
     <t xml:space="preserve">  Enter configuration data in these cells</t>
   </si>
@@ -366,6 +366,27 @@
   <si>
     <t>Añadir apartados faltantes al chartering report.</t>
   </si>
+  <si>
+    <t>Actulizar planificación.</t>
+  </si>
+  <si>
+    <t>Modificar chartering report.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Implementar requisito S1/1 sin validaciones personalizadas ni adicionales. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Implementar requisito S4/1 sin validaciones personalizadas ni adicionales. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Implementar requisito S5/1 sin validaciones personalizadas ni adicionales. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Implementar requisito S2/1 sin validaciones personalizadas ni adicionales. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Implementar requisito S3/1 sin validaciones personalizadas ni adicionales. </t>
+  </si>
 </sst>
 </file>
 
@@ -374,7 +395,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$EUR]\ #,##0.00"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -407,6 +428,14 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -631,7 +660,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -759,11 +788,24 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="6">
+    <dxf>
+      <font>
+        <color rgb="FFFFFF00"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <strike val="0"/>
@@ -809,16 +851,6 @@
     <dxf>
       <font>
         <strike val="0"/>
-        <color rgb="FFFFFF00"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FFFFFF00"/>
       </font>
       <fill>
@@ -1742,7 +1774,7 @@
       </c>
       <c r="E6" s="35">
         <f>SUM(N12:N112)</f>
-        <v>331.66666666666669</v>
+        <v>815</v>
       </c>
       <c r="F6" s="5"/>
       <c r="G6" s="5"/>
@@ -1763,7 +1795,7 @@
       </c>
       <c r="E7" s="36">
         <f>SUM(O12:O112)</f>
-        <v>361.66666666666669</v>
+        <v>370</v>
       </c>
       <c r="J7" s="37"/>
     </row>
@@ -2286,30 +2318,48 @@
       </c>
       <c r="C20" s="42" t="str">
         <f>IF(ISBLANK(D20), "", _xlfn.CONCAT("T", TEXT(B20, "0000"), "/", VLOOKUP(D20, Internal!$B$35:C$39, 2, FALSE), IF(OR(D20="QA", D20="Revision"), _xlfn.CONCAT("/", H20), "")))</f>
-        <v/>
-      </c>
-      <c r="D20" s="44"/>
-      <c r="E20" s="43"/>
-      <c r="F20" s="43"/>
-      <c r="G20" s="44"/>
+        <v>T0010/M</v>
+      </c>
+      <c r="D20" s="44" t="s">
+        <v>64</v>
+      </c>
+      <c r="E20" s="43" t="s">
+        <v>80</v>
+      </c>
+      <c r="F20" s="43" t="s">
+        <v>23</v>
+      </c>
+      <c r="G20" s="44" t="s">
+        <v>20</v>
+      </c>
       <c r="H20" s="43"/>
-      <c r="I20" s="46"/>
-      <c r="J20" s="46"/>
+      <c r="I20" s="46">
+        <v>46065.680555555555</v>
+      </c>
+      <c r="J20" s="46">
+        <v>46065.6875</v>
+      </c>
       <c r="K20" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L20" s="47"/>
-      <c r="M20" s="47"/>
-      <c r="N20" s="45" t="str">
+        <v>Ongoing</v>
+      </c>
+      <c r="L20" s="47">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="M20" s="47">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="N20" s="45">
         <f>IF(ISBLANK(L20), "", L20*VLOOKUP($F20,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O20" s="45" t="str">
+        <v>8.3333333333333321</v>
+      </c>
+      <c r="O20" s="45">
         <f>IF(ISBLANK(M20), "", M20*VLOOKUP($F20,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P20" s="44"/>
+        <v>8.3333333333333321</v>
+      </c>
+      <c r="P20" s="44" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="21" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B21" s="41">
@@ -2317,30 +2367,44 @@
       </c>
       <c r="C21" s="42" t="str">
         <f>IF(ISBLANK(D21), "", _xlfn.CONCAT("T", TEXT(B21, "0000"), "/", VLOOKUP(D21, Internal!$B$35:C$39, 2, FALSE), IF(OR(D21="QA", D21="Revision"), _xlfn.CONCAT("/", H21), "")))</f>
-        <v/>
-      </c>
-      <c r="D21" s="44"/>
-      <c r="E21" s="43"/>
-      <c r="F21" s="43"/>
-      <c r="G21" s="44"/>
+        <v>T0011/D</v>
+      </c>
+      <c r="D21" s="44" t="s">
+        <v>62</v>
+      </c>
+      <c r="E21" s="43" t="s">
+        <v>80</v>
+      </c>
+      <c r="F21" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="G21" s="44" t="s">
+        <v>41</v>
+      </c>
       <c r="H21" s="43"/>
-      <c r="I21" s="46"/>
+      <c r="I21" s="46">
+        <v>46065.708333333336</v>
+      </c>
       <c r="J21" s="46"/>
       <c r="K21" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
-      <c r="L21" s="47"/>
+      <c r="L21" s="47">
+        <v>3</v>
+      </c>
       <c r="M21" s="47"/>
-      <c r="N21" s="45" t="str">
+      <c r="N21" s="45">
         <f>IF(ISBLANK(L21), "", L21*VLOOKUP($F21,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
+        <v>75</v>
       </c>
       <c r="O21" s="45" t="str">
         <f>IF(ISBLANK(M21), "", M21*VLOOKUP($F21,Internal!$B$26:$C$32,2,FALSE))</f>
         <v/>
       </c>
-      <c r="P21" s="44"/>
+      <c r="P21" s="44" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="22" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B22" s="41">
@@ -2348,30 +2412,44 @@
       </c>
       <c r="C22" s="42" t="str">
         <f>IF(ISBLANK(D22), "", _xlfn.CONCAT("T", TEXT(B22, "0000"), "/", VLOOKUP(D22, Internal!$B$35:C$39, 2, FALSE), IF(OR(D22="QA", D22="Revision"), _xlfn.CONCAT("/", H22), "")))</f>
-        <v/>
-      </c>
-      <c r="D22" s="44"/>
-      <c r="E22" s="43"/>
-      <c r="F22" s="43"/>
-      <c r="G22" s="44"/>
+        <v>T0012/D</v>
+      </c>
+      <c r="D22" s="44" t="s">
+        <v>62</v>
+      </c>
+      <c r="E22" s="43" t="s">
+        <v>83</v>
+      </c>
+      <c r="F22" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="G22" s="44" t="s">
+        <v>41</v>
+      </c>
       <c r="H22" s="43"/>
-      <c r="I22" s="46"/>
+      <c r="I22" s="46">
+        <v>46065.708333333336</v>
+      </c>
       <c r="J22" s="46"/>
       <c r="K22" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
-      <c r="L22" s="47"/>
+      <c r="L22" s="47">
+        <v>3</v>
+      </c>
       <c r="M22" s="47"/>
-      <c r="N22" s="45" t="str">
+      <c r="N22" s="45">
         <f>IF(ISBLANK(L22), "", L22*VLOOKUP($F22,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
+        <v>75</v>
       </c>
       <c r="O22" s="45" t="str">
         <f>IF(ISBLANK(M22), "", M22*VLOOKUP($F22,Internal!$B$26:$C$32,2,FALSE))</f>
         <v/>
       </c>
-      <c r="P22" s="44"/>
+      <c r="P22" s="44" t="s">
+        <v>105</v>
+      </c>
     </row>
     <row r="23" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B23" s="41">
@@ -2379,30 +2457,44 @@
       </c>
       <c r="C23" s="42" t="str">
         <f>IF(ISBLANK(D23), "", _xlfn.CONCAT("T", TEXT(B23, "0000"), "/", VLOOKUP(D23, Internal!$B$35:C$39, 2, FALSE), IF(OR(D23="QA", D23="Revision"), _xlfn.CONCAT("/", H23), "")))</f>
-        <v/>
-      </c>
-      <c r="D23" s="44"/>
-      <c r="E23" s="43"/>
-      <c r="F23" s="43"/>
-      <c r="G23" s="44"/>
+        <v>T0013/D</v>
+      </c>
+      <c r="D23" s="44" t="s">
+        <v>62</v>
+      </c>
+      <c r="E23" s="43" t="s">
+        <v>84</v>
+      </c>
+      <c r="F23" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="G23" s="44" t="s">
+        <v>41</v>
+      </c>
       <c r="H23" s="43"/>
-      <c r="I23" s="46"/>
+      <c r="I23" s="46">
+        <v>46065.708333333336</v>
+      </c>
       <c r="J23" s="46"/>
       <c r="K23" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
-      <c r="L23" s="47"/>
+      <c r="L23" s="47">
+        <v>3</v>
+      </c>
       <c r="M23" s="47"/>
-      <c r="N23" s="45" t="str">
+      <c r="N23" s="45">
         <f>IF(ISBLANK(L23), "", L23*VLOOKUP($F23,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
+        <v>75</v>
       </c>
       <c r="O23" s="45" t="str">
         <f>IF(ISBLANK(M23), "", M23*VLOOKUP($F23,Internal!$B$26:$C$32,2,FALSE))</f>
         <v/>
       </c>
-      <c r="P23" s="44"/>
+      <c r="P23" s="44" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="24" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B24" s="41">
@@ -2410,30 +2502,44 @@
       </c>
       <c r="C24" s="42" t="str">
         <f>IF(ISBLANK(D24), "", _xlfn.CONCAT("T", TEXT(B24, "0000"), "/", VLOOKUP(D24, Internal!$B$35:C$39, 2, FALSE), IF(OR(D24="QA", D24="Revision"), _xlfn.CONCAT("/", H24), "")))</f>
-        <v/>
-      </c>
-      <c r="D24" s="44"/>
-      <c r="E24" s="43"/>
-      <c r="F24" s="43"/>
-      <c r="G24" s="44"/>
+        <v>T0014/D</v>
+      </c>
+      <c r="D24" s="44" t="s">
+        <v>62</v>
+      </c>
+      <c r="E24" s="43" t="s">
+        <v>81</v>
+      </c>
+      <c r="F24" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="G24" s="44" t="s">
+        <v>41</v>
+      </c>
       <c r="H24" s="43"/>
-      <c r="I24" s="46"/>
+      <c r="I24" s="46">
+        <v>46066.666666666664</v>
+      </c>
       <c r="J24" s="46"/>
       <c r="K24" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
-      <c r="L24" s="47"/>
+      <c r="L24" s="47">
+        <v>3</v>
+      </c>
       <c r="M24" s="47"/>
-      <c r="N24" s="45" t="str">
+      <c r="N24" s="45">
         <f>IF(ISBLANK(L24), "", L24*VLOOKUP($F24,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
+        <v>75</v>
       </c>
       <c r="O24" s="45" t="str">
         <f>IF(ISBLANK(M24), "", M24*VLOOKUP($F24,Internal!$B$26:$C$32,2,FALSE))</f>
         <v/>
       </c>
-      <c r="P24" s="44"/>
+      <c r="P24" s="44" t="s">
+        <v>107</v>
+      </c>
     </row>
     <row r="25" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B25" s="41">
@@ -2441,30 +2547,44 @@
       </c>
       <c r="C25" s="42" t="str">
         <f>IF(ISBLANK(D25), "", _xlfn.CONCAT("T", TEXT(B25, "0000"), "/", VLOOKUP(D25, Internal!$B$35:C$39, 2, FALSE), IF(OR(D25="QA", D25="Revision"), _xlfn.CONCAT("/", H25), "")))</f>
-        <v/>
-      </c>
-      <c r="D25" s="44"/>
-      <c r="E25" s="43"/>
-      <c r="F25" s="43"/>
-      <c r="G25" s="44"/>
+        <v>T0015/D</v>
+      </c>
+      <c r="D25" s="44" t="s">
+        <v>62</v>
+      </c>
+      <c r="E25" s="43" t="s">
+        <v>82</v>
+      </c>
+      <c r="F25" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="G25" s="44" t="s">
+        <v>41</v>
+      </c>
       <c r="H25" s="43"/>
-      <c r="I25" s="46"/>
+      <c r="I25" s="46">
+        <v>46067.416666666664</v>
+      </c>
       <c r="J25" s="46"/>
       <c r="K25" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
-      <c r="L25" s="47"/>
+      <c r="L25" s="47">
+        <v>3</v>
+      </c>
       <c r="M25" s="47"/>
-      <c r="N25" s="45" t="str">
+      <c r="N25" s="45">
         <f>IF(ISBLANK(L25), "", L25*VLOOKUP($F25,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
+        <v>75</v>
       </c>
       <c r="O25" s="45" t="str">
         <f>IF(ISBLANK(M25), "", M25*VLOOKUP($F25,Internal!$B$26:$C$32,2,FALSE))</f>
         <v/>
       </c>
-      <c r="P25" s="44"/>
+      <c r="P25" s="44" t="s">
+        <v>108</v>
+      </c>
     </row>
     <row r="26" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B26" s="41">
@@ -2472,30 +2592,44 @@
       </c>
       <c r="C26" s="42" t="str">
         <f>IF(ISBLANK(D26), "", _xlfn.CONCAT("T", TEXT(B26, "0000"), "/", VLOOKUP(D26, Internal!$B$35:C$39, 2, FALSE), IF(OR(D26="QA", D26="Revision"), _xlfn.CONCAT("/", H26), "")))</f>
-        <v/>
-      </c>
-      <c r="D26" s="44"/>
-      <c r="E26" s="43"/>
-      <c r="F26" s="43"/>
-      <c r="G26" s="44"/>
+        <v>T0016/M</v>
+      </c>
+      <c r="D26" s="44" t="s">
+        <v>64</v>
+      </c>
+      <c r="E26" s="43" t="s">
+        <v>80</v>
+      </c>
+      <c r="F26" s="43" t="s">
+        <v>23</v>
+      </c>
+      <c r="G26" s="44" t="s">
+        <v>36</v>
+      </c>
       <c r="H26" s="43"/>
-      <c r="I26" s="46"/>
+      <c r="I26" s="46">
+        <v>46067.666666666664</v>
+      </c>
       <c r="J26" s="46"/>
       <c r="K26" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
-      <c r="L26" s="47"/>
+      <c r="L26" s="47">
+        <v>2</v>
+      </c>
       <c r="M26" s="47"/>
-      <c r="N26" s="45" t="str">
+      <c r="N26" s="45">
         <f>IF(ISBLANK(L26), "", L26*VLOOKUP($F26,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
+        <v>100</v>
       </c>
       <c r="O26" s="45" t="str">
         <f>IF(ISBLANK(M26), "", M26*VLOOKUP($F26,Internal!$B$26:$C$32,2,FALSE))</f>
         <v/>
       </c>
-      <c r="P26" s="44"/>
+      <c r="P26" s="44" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="27" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B27" s="41">
@@ -2537,7 +2671,7 @@
         <v/>
       </c>
       <c r="D28" s="44"/>
-      <c r="E28" s="43"/>
+      <c r="E28" s="59"/>
       <c r="F28" s="43"/>
       <c r="G28" s="44"/>
       <c r="H28" s="43"/>
@@ -5173,14 +5307,14 @@
     <mergeCell ref="C4:P4"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
-  <conditionalFormatting sqref="J11:J112">
-    <cfRule type="expression" dxfId="5" priority="1">
-      <formula>AND(I11&lt;&gt;"",J11&lt;&gt;"", I11&gt;J11)</formula>
+  <conditionalFormatting sqref="H11:H112">
+    <cfRule type="expression" dxfId="5" priority="3">
+      <formula>AND(H11&lt;&gt;"",COUNTIF($C$12:$C$112,H11)=0)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H11:H112">
-    <cfRule type="expression" dxfId="0" priority="3">
-      <formula>AND(H11&lt;&gt;"",COUNTIF($C$12:$C$112,H11)=0)</formula>
+  <conditionalFormatting sqref="J11:J112">
+    <cfRule type="expression" dxfId="4" priority="1">
+      <formula>AND(I11&lt;&gt;"",J11&lt;&gt;"", I11&gt;J11)</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="9">
@@ -8523,12 +8657,12 @@
     <mergeCell ref="I9:J9"/>
   </mergeCells>
   <conditionalFormatting sqref="H11:H110">
-    <cfRule type="expression" dxfId="4" priority="2">
+    <cfRule type="expression" dxfId="3" priority="2">
       <formula>AND(H11&lt;&gt;"",COUNTIF($C$11:$C$110,H11)=0)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J11:J110">
-    <cfRule type="expression" dxfId="3" priority="1">
+    <cfRule type="expression" dxfId="2" priority="1">
       <formula>AND(I11&lt;&gt;"",J11&lt;&gt;"", I11&gt;J11)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11872,12 +12006,12 @@
     <mergeCell ref="I9:J9"/>
   </mergeCells>
   <conditionalFormatting sqref="H11:H110">
-    <cfRule type="expression" dxfId="2" priority="2">
+    <cfRule type="expression" dxfId="1" priority="2">
       <formula>AND(H11&lt;&gt;"",COUNTIF($C$11:$C$110,H11)=0)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J11:J110">
-    <cfRule type="expression" dxfId="1" priority="1">
+    <cfRule type="expression" dxfId="0" priority="1">
       <formula>AND(I11&lt;&gt;"",J11&lt;&gt;"", I11&gt;J11)</formula>
     </cfRule>
   </conditionalFormatting>

--- a/reports/Deliverable D01 (Level C)/Group/Planning-Template.xlsx
+++ b/reports/Deliverable D01 (Level C)/Group/Planning-Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Javier\Downloads\Workspace-26\Projects\Acme-Starters-C\reports\Deliverable D01 (Level C)\Group\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEFCDECD-5A75-4411-97CD-8F8FDD2B4F43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63FE3EB7-2DB7-4016-9261-F5AA9A177B76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="2" xr2:uid="{683E09B8-1D94-4905-B116-9D998A46AAA3}"/>
   </bookViews>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="111">
   <si>
     <t xml:space="preserve">  Enter configuration data in these cells</t>
   </si>
@@ -386,6 +386,12 @@
   </si>
   <si>
     <t xml:space="preserve">Implementar requisito S3/1 sin validaciones personalizadas ni adicionales. </t>
+  </si>
+  <si>
+    <t>Realizar re-planificación</t>
+  </si>
+  <si>
+    <t>Actualizar Acme-Framework a la versión 26.2.0</t>
   </si>
 </sst>
 </file>
@@ -770,6 +776,9 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -786,9 +795,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1429,118 +1435,118 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B2" s="55" t="s">
+      <c r="B2" s="56" t="s">
         <v>78</v>
       </c>
-      <c r="C2" s="55"/>
-      <c r="D2" s="55"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="55"/>
-      <c r="G2" s="55"/>
-      <c r="H2" s="55"/>
-      <c r="I2" s="55"/>
-      <c r="J2" s="55"/>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="56"/>
+      <c r="I2" s="56"/>
+      <c r="J2" s="56"/>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B4" s="53" t="s">
+      <c r="B4" s="54" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="54"/>
-      <c r="D4" s="54"/>
-      <c r="E4" s="54"/>
-      <c r="F4" s="54"/>
-      <c r="G4" s="54"/>
-      <c r="H4" s="54"/>
-      <c r="I4" s="54"/>
-      <c r="J4" s="54"/>
+      <c r="C4" s="55"/>
+      <c r="D4" s="55"/>
+      <c r="E4" s="55"/>
+      <c r="F4" s="55"/>
+      <c r="G4" s="55"/>
+      <c r="H4" s="55"/>
+      <c r="I4" s="55"/>
+      <c r="J4" s="55"/>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B5" s="54"/>
-      <c r="C5" s="54"/>
-      <c r="D5" s="54"/>
-      <c r="E5" s="54"/>
-      <c r="F5" s="54"/>
-      <c r="G5" s="54"/>
-      <c r="H5" s="54"/>
-      <c r="I5" s="54"/>
-      <c r="J5" s="54"/>
+      <c r="B5" s="55"/>
+      <c r="C5" s="55"/>
+      <c r="D5" s="55"/>
+      <c r="E5" s="55"/>
+      <c r="F5" s="55"/>
+      <c r="G5" s="55"/>
+      <c r="H5" s="55"/>
+      <c r="I5" s="55"/>
+      <c r="J5" s="55"/>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B6" s="54"/>
-      <c r="C6" s="54"/>
-      <c r="D6" s="54"/>
-      <c r="E6" s="54"/>
-      <c r="F6" s="54"/>
-      <c r="G6" s="54"/>
-      <c r="H6" s="54"/>
-      <c r="I6" s="54"/>
-      <c r="J6" s="54"/>
+      <c r="B6" s="55"/>
+      <c r="C6" s="55"/>
+      <c r="D6" s="55"/>
+      <c r="E6" s="55"/>
+      <c r="F6" s="55"/>
+      <c r="G6" s="55"/>
+      <c r="H6" s="55"/>
+      <c r="I6" s="55"/>
+      <c r="J6" s="55"/>
     </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B7" s="54"/>
-      <c r="C7" s="54"/>
-      <c r="D7" s="54"/>
-      <c r="E7" s="54"/>
-      <c r="F7" s="54"/>
-      <c r="G7" s="54"/>
-      <c r="H7" s="54"/>
-      <c r="I7" s="54"/>
-      <c r="J7" s="54"/>
+      <c r="B7" s="55"/>
+      <c r="C7" s="55"/>
+      <c r="D7" s="55"/>
+      <c r="E7" s="55"/>
+      <c r="F7" s="55"/>
+      <c r="G7" s="55"/>
+      <c r="H7" s="55"/>
+      <c r="I7" s="55"/>
+      <c r="J7" s="55"/>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B8" s="54"/>
-      <c r="C8" s="54"/>
-      <c r="D8" s="54"/>
-      <c r="E8" s="54"/>
-      <c r="F8" s="54"/>
-      <c r="G8" s="54"/>
-      <c r="H8" s="54"/>
-      <c r="I8" s="54"/>
-      <c r="J8" s="54"/>
+      <c r="B8" s="55"/>
+      <c r="C8" s="55"/>
+      <c r="D8" s="55"/>
+      <c r="E8" s="55"/>
+      <c r="F8" s="55"/>
+      <c r="G8" s="55"/>
+      <c r="H8" s="55"/>
+      <c r="I8" s="55"/>
+      <c r="J8" s="55"/>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B9" s="54"/>
-      <c r="C9" s="54"/>
-      <c r="D9" s="54"/>
-      <c r="E9" s="54"/>
-      <c r="F9" s="54"/>
-      <c r="G9" s="54"/>
-      <c r="H9" s="54"/>
-      <c r="I9" s="54"/>
-      <c r="J9" s="54"/>
+      <c r="B9" s="55"/>
+      <c r="C9" s="55"/>
+      <c r="D9" s="55"/>
+      <c r="E9" s="55"/>
+      <c r="F9" s="55"/>
+      <c r="G9" s="55"/>
+      <c r="H9" s="55"/>
+      <c r="I9" s="55"/>
+      <c r="J9" s="55"/>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B10" s="54"/>
-      <c r="C10" s="54"/>
-      <c r="D10" s="54"/>
-      <c r="E10" s="54"/>
-      <c r="F10" s="54"/>
-      <c r="G10" s="54"/>
-      <c r="H10" s="54"/>
-      <c r="I10" s="54"/>
-      <c r="J10" s="54"/>
+      <c r="B10" s="55"/>
+      <c r="C10" s="55"/>
+      <c r="D10" s="55"/>
+      <c r="E10" s="55"/>
+      <c r="F10" s="55"/>
+      <c r="G10" s="55"/>
+      <c r="H10" s="55"/>
+      <c r="I10" s="55"/>
+      <c r="J10" s="55"/>
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B11" s="54"/>
-      <c r="C11" s="54"/>
-      <c r="D11" s="54"/>
-      <c r="E11" s="54"/>
-      <c r="F11" s="54"/>
-      <c r="G11" s="54"/>
-      <c r="H11" s="54"/>
-      <c r="I11" s="54"/>
-      <c r="J11" s="54"/>
+      <c r="B11" s="55"/>
+      <c r="C11" s="55"/>
+      <c r="D11" s="55"/>
+      <c r="E11" s="55"/>
+      <c r="F11" s="55"/>
+      <c r="G11" s="55"/>
+      <c r="H11" s="55"/>
+      <c r="I11" s="55"/>
+      <c r="J11" s="55"/>
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B12" s="54"/>
-      <c r="C12" s="54"/>
-      <c r="D12" s="54"/>
-      <c r="E12" s="54"/>
-      <c r="F12" s="54"/>
-      <c r="G12" s="54"/>
-      <c r="H12" s="54"/>
-      <c r="I12" s="54"/>
-      <c r="J12" s="54"/>
+      <c r="B12" s="55"/>
+      <c r="C12" s="55"/>
+      <c r="D12" s="55"/>
+      <c r="E12" s="55"/>
+      <c r="F12" s="55"/>
+      <c r="G12" s="55"/>
+      <c r="H12" s="55"/>
+      <c r="I12" s="55"/>
+      <c r="J12" s="55"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1558,17 +1564,17 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="2" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B2" s="55" t="s">
+      <c r="B2" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="55"/>
-      <c r="D2" s="55"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="55"/>
-      <c r="G2" s="55"/>
-      <c r="H2" s="55"/>
-      <c r="I2" s="55"/>
-      <c r="J2" s="55"/>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="56"/>
+      <c r="I2" s="56"/>
+      <c r="J2" s="56"/>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B3" s="2"/>
@@ -1582,39 +1588,39 @@
       <c r="J3" s="1"/>
     </row>
     <row r="4" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B4" s="53" t="s">
+      <c r="B4" s="54" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="53"/>
-      <c r="D4" s="53"/>
-      <c r="E4" s="53"/>
-      <c r="F4" s="53"/>
-      <c r="G4" s="53"/>
-      <c r="H4" s="53"/>
-      <c r="I4" s="53"/>
-      <c r="J4" s="53"/>
+      <c r="C4" s="54"/>
+      <c r="D4" s="54"/>
+      <c r="E4" s="54"/>
+      <c r="F4" s="54"/>
+      <c r="G4" s="54"/>
+      <c r="H4" s="54"/>
+      <c r="I4" s="54"/>
+      <c r="J4" s="54"/>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B5" s="53"/>
-      <c r="C5" s="53"/>
-      <c r="D5" s="53"/>
-      <c r="E5" s="53"/>
-      <c r="F5" s="53"/>
-      <c r="G5" s="53"/>
-      <c r="H5" s="53"/>
-      <c r="I5" s="53"/>
-      <c r="J5" s="53"/>
+      <c r="B5" s="54"/>
+      <c r="C5" s="54"/>
+      <c r="D5" s="54"/>
+      <c r="E5" s="54"/>
+      <c r="F5" s="54"/>
+      <c r="G5" s="54"/>
+      <c r="H5" s="54"/>
+      <c r="I5" s="54"/>
+      <c r="J5" s="54"/>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B6" s="53"/>
-      <c r="C6" s="53"/>
-      <c r="D6" s="53"/>
-      <c r="E6" s="53"/>
-      <c r="F6" s="53"/>
-      <c r="G6" s="53"/>
-      <c r="H6" s="53"/>
-      <c r="I6" s="53"/>
-      <c r="J6" s="53"/>
+      <c r="B6" s="54"/>
+      <c r="C6" s="54"/>
+      <c r="D6" s="54"/>
+      <c r="E6" s="54"/>
+      <c r="F6" s="54"/>
+      <c r="G6" s="54"/>
+      <c r="H6" s="54"/>
+      <c r="I6" s="54"/>
+      <c r="J6" s="54"/>
     </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B7" s="1"/>
@@ -1642,29 +1648,29 @@
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B9" s="4"/>
-      <c r="C9" s="56" t="s">
+      <c r="C9" s="57" t="s">
         <v>0</v>
       </c>
-      <c r="D9" s="56"/>
-      <c r="E9" s="56"/>
-      <c r="F9" s="56"/>
-      <c r="G9" s="56"/>
-      <c r="H9" s="56"/>
-      <c r="I9" s="56"/>
-      <c r="J9" s="56"/>
+      <c r="D9" s="57"/>
+      <c r="E9" s="57"/>
+      <c r="F9" s="57"/>
+      <c r="G9" s="57"/>
+      <c r="H9" s="57"/>
+      <c r="I9" s="57"/>
+      <c r="J9" s="57"/>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B10" s="49"/>
-      <c r="C10" s="56" t="s">
+      <c r="C10" s="57" t="s">
         <v>90</v>
       </c>
-      <c r="D10" s="56"/>
-      <c r="E10" s="56"/>
-      <c r="F10" s="56"/>
-      <c r="G10" s="56"/>
-      <c r="H10" s="56"/>
-      <c r="I10" s="56"/>
-      <c r="J10" s="56"/>
+      <c r="D10" s="57"/>
+      <c r="E10" s="57"/>
+      <c r="F10" s="57"/>
+      <c r="G10" s="57"/>
+      <c r="H10" s="57"/>
+      <c r="I10" s="57"/>
+      <c r="J10" s="57"/>
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B11" s="50"/>
@@ -1681,16 +1687,16 @@
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B12" s="3"/>
-      <c r="C12" s="56" t="s">
+      <c r="C12" s="57" t="s">
         <v>1</v>
       </c>
-      <c r="D12" s="56"/>
-      <c r="E12" s="56"/>
-      <c r="F12" s="56"/>
-      <c r="G12" s="56"/>
-      <c r="H12" s="56"/>
-      <c r="I12" s="56"/>
-      <c r="J12" s="56"/>
+      <c r="D12" s="57"/>
+      <c r="E12" s="57"/>
+      <c r="F12" s="57"/>
+      <c r="G12" s="57"/>
+      <c r="H12" s="57"/>
+      <c r="I12" s="57"/>
+      <c r="J12" s="57"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -1714,40 +1720,40 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:16" x14ac:dyDescent="0.45">
-      <c r="C2" s="55" t="s">
+      <c r="C2" s="56" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="55"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="55"/>
-      <c r="G2" s="55"/>
-      <c r="H2" s="55"/>
-      <c r="I2" s="55"/>
-      <c r="J2" s="55"/>
-      <c r="K2" s="55"/>
-      <c r="L2" s="55"/>
-      <c r="M2" s="55"/>
-      <c r="N2" s="55"/>
-      <c r="O2" s="55"/>
-      <c r="P2" s="55"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="56"/>
+      <c r="I2" s="56"/>
+      <c r="J2" s="56"/>
+      <c r="K2" s="56"/>
+      <c r="L2" s="56"/>
+      <c r="M2" s="56"/>
+      <c r="N2" s="56"/>
+      <c r="O2" s="56"/>
+      <c r="P2" s="56"/>
     </row>
     <row r="4" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="C4" s="53" t="s">
+      <c r="C4" s="54" t="s">
         <v>75</v>
       </c>
-      <c r="D4" s="53"/>
-      <c r="E4" s="53"/>
-      <c r="F4" s="53"/>
-      <c r="G4" s="53"/>
-      <c r="H4" s="53"/>
-      <c r="I4" s="53"/>
-      <c r="J4" s="53"/>
-      <c r="K4" s="53"/>
-      <c r="L4" s="53"/>
-      <c r="M4" s="53"/>
-      <c r="N4" s="53"/>
-      <c r="O4" s="53"/>
-      <c r="P4" s="53"/>
+      <c r="D4" s="54"/>
+      <c r="E4" s="54"/>
+      <c r="F4" s="54"/>
+      <c r="G4" s="54"/>
+      <c r="H4" s="54"/>
+      <c r="I4" s="54"/>
+      <c r="J4" s="54"/>
+      <c r="K4" s="54"/>
+      <c r="L4" s="54"/>
+      <c r="M4" s="54"/>
+      <c r="N4" s="54"/>
+      <c r="O4" s="54"/>
+      <c r="P4" s="54"/>
     </row>
     <row r="5" spans="2:16" x14ac:dyDescent="0.45">
       <c r="C5" s="5"/>
@@ -1766,7 +1772,7 @@
       <c r="P5" s="5"/>
     </row>
     <row r="6" spans="2:16" x14ac:dyDescent="0.45">
-      <c r="C6" s="57" t="s">
+      <c r="C6" s="58" t="s">
         <v>68</v>
       </c>
       <c r="D6" s="10" t="s">
@@ -1774,7 +1780,7 @@
       </c>
       <c r="E6" s="35">
         <f>SUM(N12:N112)</f>
-        <v>815</v>
+        <v>831.66666666666674</v>
       </c>
       <c r="F6" s="5"/>
       <c r="G6" s="5"/>
@@ -1789,13 +1795,13 @@
       <c r="P6" s="5"/>
     </row>
     <row r="7" spans="2:16" x14ac:dyDescent="0.45">
-      <c r="C7" s="57"/>
+      <c r="C7" s="58"/>
       <c r="D7" s="11" t="s">
         <v>70</v>
       </c>
       <c r="E7" s="36">
         <f>SUM(O12:O112)</f>
-        <v>370</v>
+        <v>378.33333333333331</v>
       </c>
       <c r="J7" s="37"/>
     </row>
@@ -1807,19 +1813,19 @@
       <c r="F9" s="7"/>
       <c r="G9" s="7"/>
       <c r="H9" s="7"/>
-      <c r="I9" s="58" t="s">
+      <c r="I9" s="59" t="s">
         <v>51</v>
       </c>
-      <c r="J9" s="58"/>
+      <c r="J9" s="59"/>
       <c r="K9" s="7"/>
-      <c r="L9" s="58" t="s">
+      <c r="L9" s="59" t="s">
         <v>7</v>
       </c>
-      <c r="M9" s="58"/>
-      <c r="N9" s="58" t="s">
+      <c r="M9" s="59"/>
+      <c r="N9" s="59" t="s">
         <v>58</v>
       </c>
-      <c r="O9" s="58"/>
+      <c r="O9" s="59"/>
       <c r="P9" s="7"/>
     </row>
     <row r="10" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
@@ -2341,7 +2347,7 @@
       </c>
       <c r="K20" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Ongoing</v>
+        <v>Completed</v>
       </c>
       <c r="L20" s="47">
         <v>0.16666666666666666</v>
@@ -2637,30 +2643,48 @@
       </c>
       <c r="C27" s="42" t="str">
         <f>IF(ISBLANK(D27), "", _xlfn.CONCAT("T", TEXT(B27, "0000"), "/", VLOOKUP(D27, Internal!$B$35:C$39, 2, FALSE), IF(OR(D27="QA", D27="Revision"), _xlfn.CONCAT("/", H27), "")))</f>
-        <v/>
-      </c>
-      <c r="D27" s="44"/>
-      <c r="E27" s="43"/>
-      <c r="F27" s="43"/>
-      <c r="G27" s="44"/>
+        <v>T0017/M</v>
+      </c>
+      <c r="D27" s="44" t="s">
+        <v>64</v>
+      </c>
+      <c r="E27" s="43" t="s">
+        <v>80</v>
+      </c>
+      <c r="F27" s="43" t="s">
+        <v>23</v>
+      </c>
+      <c r="G27" s="44" t="s">
+        <v>33</v>
+      </c>
       <c r="H27" s="43"/>
-      <c r="I27" s="46"/>
-      <c r="J27" s="46"/>
+      <c r="I27" s="46">
+        <v>46066</v>
+      </c>
+      <c r="J27" s="46">
+        <v>46066.006944444445</v>
+      </c>
       <c r="K27" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L27" s="47"/>
-      <c r="M27" s="47"/>
-      <c r="N27" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L27" s="47">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="M27" s="47">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="N27" s="45">
         <f>IF(ISBLANK(L27), "", L27*VLOOKUP($F27,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O27" s="45" t="str">
+        <v>8.3333333333333321</v>
+      </c>
+      <c r="O27" s="45">
         <f>IF(ISBLANK(M27), "", M27*VLOOKUP($F27,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P27" s="44"/>
+        <v>8.3333333333333321</v>
+      </c>
+      <c r="P27" s="44" t="s">
+        <v>109</v>
+      </c>
     </row>
     <row r="28" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B28" s="41">
@@ -2668,30 +2692,44 @@
       </c>
       <c r="C28" s="42" t="str">
         <f>IF(ISBLANK(D28), "", _xlfn.CONCAT("T", TEXT(B28, "0000"), "/", VLOOKUP(D28, Internal!$B$35:C$39, 2, FALSE), IF(OR(D28="QA", D28="Revision"), _xlfn.CONCAT("/", H28), "")))</f>
-        <v/>
-      </c>
-      <c r="D28" s="44"/>
-      <c r="E28" s="59"/>
-      <c r="F28" s="43"/>
-      <c r="G28" s="44"/>
+        <v>T0018/D</v>
+      </c>
+      <c r="D28" s="44" t="s">
+        <v>62</v>
+      </c>
+      <c r="E28" s="53" t="s">
+        <v>80</v>
+      </c>
+      <c r="F28" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="G28" s="44" t="s">
+        <v>89</v>
+      </c>
       <c r="H28" s="43"/>
-      <c r="I28" s="46"/>
+      <c r="I28" s="46">
+        <v>46066.006944444445</v>
+      </c>
       <c r="J28" s="46"/>
       <c r="K28" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
-      <c r="L28" s="47"/>
+      <c r="L28" s="47">
+        <v>0.33333333333333331</v>
+      </c>
       <c r="M28" s="47"/>
-      <c r="N28" s="45" t="str">
+      <c r="N28" s="45">
         <f>IF(ISBLANK(L28), "", L28*VLOOKUP($F28,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
+        <v>8.3333333333333321</v>
       </c>
       <c r="O28" s="45" t="str">
         <f>IF(ISBLANK(M28), "", M28*VLOOKUP($F28,Internal!$B$26:$C$32,2,FALSE))</f>
         <v/>
       </c>
-      <c r="P28" s="44"/>
+      <c r="P28" s="44" t="s">
+        <v>110</v>
+      </c>
     </row>
     <row r="29" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B29" s="41">
@@ -5392,40 +5430,40 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:16" x14ac:dyDescent="0.45">
-      <c r="C2" s="55" t="s">
+      <c r="C2" s="56" t="s">
         <v>85</v>
       </c>
-      <c r="D2" s="55"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="55"/>
-      <c r="G2" s="55"/>
-      <c r="H2" s="55"/>
-      <c r="I2" s="55"/>
-      <c r="J2" s="55"/>
-      <c r="K2" s="55"/>
-      <c r="L2" s="55"/>
-      <c r="M2" s="55"/>
-      <c r="N2" s="55"/>
-      <c r="O2" s="55"/>
-      <c r="P2" s="55"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="56"/>
+      <c r="I2" s="56"/>
+      <c r="J2" s="56"/>
+      <c r="K2" s="56"/>
+      <c r="L2" s="56"/>
+      <c r="M2" s="56"/>
+      <c r="N2" s="56"/>
+      <c r="O2" s="56"/>
+      <c r="P2" s="56"/>
     </row>
     <row r="4" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="C4" s="53" t="s">
+      <c r="C4" s="54" t="s">
         <v>75</v>
       </c>
-      <c r="D4" s="53"/>
-      <c r="E4" s="53"/>
-      <c r="F4" s="53"/>
-      <c r="G4" s="53"/>
-      <c r="H4" s="53"/>
-      <c r="I4" s="53"/>
-      <c r="J4" s="53"/>
-      <c r="K4" s="53"/>
-      <c r="L4" s="53"/>
-      <c r="M4" s="53"/>
-      <c r="N4" s="53"/>
-      <c r="O4" s="53"/>
-      <c r="P4" s="53"/>
+      <c r="D4" s="54"/>
+      <c r="E4" s="54"/>
+      <c r="F4" s="54"/>
+      <c r="G4" s="54"/>
+      <c r="H4" s="54"/>
+      <c r="I4" s="54"/>
+      <c r="J4" s="54"/>
+      <c r="K4" s="54"/>
+      <c r="L4" s="54"/>
+      <c r="M4" s="54"/>
+      <c r="N4" s="54"/>
+      <c r="O4" s="54"/>
+      <c r="P4" s="54"/>
     </row>
     <row r="5" spans="2:16" x14ac:dyDescent="0.45">
       <c r="C5" s="5"/>
@@ -5444,7 +5482,7 @@
       <c r="P5" s="5"/>
     </row>
     <row r="6" spans="2:16" x14ac:dyDescent="0.45">
-      <c r="C6" s="57" t="s">
+      <c r="C6" s="58" t="s">
         <v>68</v>
       </c>
       <c r="D6" s="10" t="s">
@@ -5467,7 +5505,7 @@
       <c r="P6" s="5"/>
     </row>
     <row r="7" spans="2:16" x14ac:dyDescent="0.45">
-      <c r="C7" s="57"/>
+      <c r="C7" s="58"/>
       <c r="D7" s="11" t="s">
         <v>70</v>
       </c>
@@ -5485,19 +5523,19 @@
       <c r="F9" s="7"/>
       <c r="G9" s="7"/>
       <c r="H9" s="7"/>
-      <c r="I9" s="58" t="s">
+      <c r="I9" s="59" t="s">
         <v>51</v>
       </c>
-      <c r="J9" s="58"/>
+      <c r="J9" s="59"/>
       <c r="K9" s="7"/>
-      <c r="L9" s="58" t="s">
+      <c r="L9" s="59" t="s">
         <v>7</v>
       </c>
-      <c r="M9" s="58"/>
-      <c r="N9" s="58" t="s">
+      <c r="M9" s="59"/>
+      <c r="N9" s="59" t="s">
         <v>58</v>
       </c>
-      <c r="O9" s="58"/>
+      <c r="O9" s="59"/>
       <c r="P9" s="7"/>
     </row>
     <row r="10" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
@@ -8741,40 +8779,40 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:16" x14ac:dyDescent="0.45">
-      <c r="C2" s="55" t="s">
+      <c r="C2" s="56" t="s">
         <v>86</v>
       </c>
-      <c r="D2" s="55"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="55"/>
-      <c r="G2" s="55"/>
-      <c r="H2" s="55"/>
-      <c r="I2" s="55"/>
-      <c r="J2" s="55"/>
-      <c r="K2" s="55"/>
-      <c r="L2" s="55"/>
-      <c r="M2" s="55"/>
-      <c r="N2" s="55"/>
-      <c r="O2" s="55"/>
-      <c r="P2" s="55"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="56"/>
+      <c r="I2" s="56"/>
+      <c r="J2" s="56"/>
+      <c r="K2" s="56"/>
+      <c r="L2" s="56"/>
+      <c r="M2" s="56"/>
+      <c r="N2" s="56"/>
+      <c r="O2" s="56"/>
+      <c r="P2" s="56"/>
     </row>
     <row r="4" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="C4" s="53" t="s">
+      <c r="C4" s="54" t="s">
         <v>75</v>
       </c>
-      <c r="D4" s="53"/>
-      <c r="E4" s="53"/>
-      <c r="F4" s="53"/>
-      <c r="G4" s="53"/>
-      <c r="H4" s="53"/>
-      <c r="I4" s="53"/>
-      <c r="J4" s="53"/>
-      <c r="K4" s="53"/>
-      <c r="L4" s="53"/>
-      <c r="M4" s="53"/>
-      <c r="N4" s="53"/>
-      <c r="O4" s="53"/>
-      <c r="P4" s="53"/>
+      <c r="D4" s="54"/>
+      <c r="E4" s="54"/>
+      <c r="F4" s="54"/>
+      <c r="G4" s="54"/>
+      <c r="H4" s="54"/>
+      <c r="I4" s="54"/>
+      <c r="J4" s="54"/>
+      <c r="K4" s="54"/>
+      <c r="L4" s="54"/>
+      <c r="M4" s="54"/>
+      <c r="N4" s="54"/>
+      <c r="O4" s="54"/>
+      <c r="P4" s="54"/>
     </row>
     <row r="5" spans="2:16" x14ac:dyDescent="0.45">
       <c r="C5" s="5"/>
@@ -8793,7 +8831,7 @@
       <c r="P5" s="5"/>
     </row>
     <row r="6" spans="2:16" x14ac:dyDescent="0.45">
-      <c r="C6" s="57" t="s">
+      <c r="C6" s="58" t="s">
         <v>68</v>
       </c>
       <c r="D6" s="10" t="s">
@@ -8816,7 +8854,7 @@
       <c r="P6" s="5"/>
     </row>
     <row r="7" spans="2:16" x14ac:dyDescent="0.45">
-      <c r="C7" s="57"/>
+      <c r="C7" s="58"/>
       <c r="D7" s="11" t="s">
         <v>70</v>
       </c>
@@ -8834,19 +8872,19 @@
       <c r="F9" s="7"/>
       <c r="G9" s="7"/>
       <c r="H9" s="7"/>
-      <c r="I9" s="58" t="s">
+      <c r="I9" s="59" t="s">
         <v>51</v>
       </c>
-      <c r="J9" s="58"/>
+      <c r="J9" s="59"/>
       <c r="K9" s="7"/>
-      <c r="L9" s="58" t="s">
+      <c r="L9" s="59" t="s">
         <v>7</v>
       </c>
-      <c r="M9" s="58"/>
-      <c r="N9" s="58" t="s">
+      <c r="M9" s="59"/>
+      <c r="N9" s="59" t="s">
         <v>58</v>
       </c>
-      <c r="O9" s="58"/>
+      <c r="O9" s="59"/>
       <c r="P9" s="7"/>
     </row>
     <row r="10" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
@@ -12089,52 +12127,52 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B2" s="55" t="s">
+      <c r="B2" s="56" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="55"/>
-      <c r="D2" s="55"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="55"/>
-      <c r="G2" s="55"/>
-      <c r="H2" s="55"/>
-      <c r="I2" s="55"/>
-      <c r="J2" s="55"/>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="56"/>
+      <c r="I2" s="56"/>
+      <c r="J2" s="56"/>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B4" s="53" t="s">
+      <c r="B4" s="54" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="53"/>
-      <c r="D4" s="53"/>
-      <c r="E4" s="53"/>
-      <c r="F4" s="53"/>
-      <c r="G4" s="53"/>
-      <c r="H4" s="53"/>
-      <c r="I4" s="53"/>
-      <c r="J4" s="53"/>
+      <c r="C4" s="54"/>
+      <c r="D4" s="54"/>
+      <c r="E4" s="54"/>
+      <c r="F4" s="54"/>
+      <c r="G4" s="54"/>
+      <c r="H4" s="54"/>
+      <c r="I4" s="54"/>
+      <c r="J4" s="54"/>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B5" s="53"/>
-      <c r="C5" s="53"/>
-      <c r="D5" s="53"/>
-      <c r="E5" s="53"/>
-      <c r="F5" s="53"/>
-      <c r="G5" s="53"/>
-      <c r="H5" s="53"/>
-      <c r="I5" s="53"/>
-      <c r="J5" s="53"/>
+      <c r="B5" s="54"/>
+      <c r="C5" s="54"/>
+      <c r="D5" s="54"/>
+      <c r="E5" s="54"/>
+      <c r="F5" s="54"/>
+      <c r="G5" s="54"/>
+      <c r="H5" s="54"/>
+      <c r="I5" s="54"/>
+      <c r="J5" s="54"/>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B6" s="53"/>
-      <c r="C6" s="53"/>
-      <c r="D6" s="53"/>
-      <c r="E6" s="53"/>
-      <c r="F6" s="53"/>
-      <c r="G6" s="53"/>
-      <c r="H6" s="53"/>
-      <c r="I6" s="53"/>
-      <c r="J6" s="53"/>
+      <c r="B6" s="54"/>
+      <c r="C6" s="54"/>
+      <c r="D6" s="54"/>
+      <c r="E6" s="54"/>
+      <c r="F6" s="54"/>
+      <c r="G6" s="54"/>
+      <c r="H6" s="54"/>
+      <c r="I6" s="54"/>
+      <c r="J6" s="54"/>
     </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B7" s="5"/>

--- a/reports/Deliverable D01 (Level C)/Group/Planning-Template.xlsx
+++ b/reports/Deliverable D01 (Level C)/Group/Planning-Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Javier\Downloads\Workspace-26\Projects\Acme-Starters-C\reports\Deliverable D01 (Level C)\Group\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63FE3EB7-2DB7-4016-9261-F5AA9A177B76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1120C43-8129-4DDD-94CE-1E864276BC34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="2" xr2:uid="{683E09B8-1D94-4905-B116-9D998A46AAA3}"/>
   </bookViews>
@@ -1801,7 +1801,7 @@
       </c>
       <c r="E7" s="36">
         <f>SUM(O12:O112)</f>
-        <v>378.33333333333331</v>
+        <v>395</v>
       </c>
       <c r="J7" s="37"/>
     </row>
@@ -2710,22 +2710,26 @@
       <c r="I28" s="46">
         <v>46066.006944444445</v>
       </c>
-      <c r="J28" s="46"/>
+      <c r="J28" s="46">
+        <v>46066.034722222219</v>
+      </c>
       <c r="K28" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
+        <v>Ongoing</v>
       </c>
       <c r="L28" s="47">
         <v>0.33333333333333331</v>
       </c>
-      <c r="M28" s="47"/>
+      <c r="M28" s="47">
+        <v>0.66666666666666663</v>
+      </c>
       <c r="N28" s="45">
         <f>IF(ISBLANK(L28), "", L28*VLOOKUP($F28,Internal!$B$26:$C$32,2,FALSE))</f>
         <v>8.3333333333333321</v>
       </c>
-      <c r="O28" s="45" t="str">
+      <c r="O28" s="45">
         <f>IF(ISBLANK(M28), "", M28*VLOOKUP($F28,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
+        <v>16.666666666666664</v>
       </c>
       <c r="P28" s="44" t="s">
         <v>110</v>

--- a/reports/Deliverable D01 (Level C)/Group/Planning-Template.xlsx
+++ b/reports/Deliverable D01 (Level C)/Group/Planning-Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Javier\Downloads\Workspace-26\Projects\Acme-Starters-C\reports\Deliverable D01 (Level C)\Group\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1120C43-8129-4DDD-94CE-1E864276BC34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{104EF387-DBB9-48A9-9AE3-297D933BB532}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="2" xr2:uid="{683E09B8-1D94-4905-B116-9D998A46AAA3}"/>
   </bookViews>
@@ -1801,7 +1801,7 @@
       </c>
       <c r="E7" s="36">
         <f>SUM(O12:O112)</f>
-        <v>395</v>
+        <v>470</v>
       </c>
       <c r="J7" s="37"/>
     </row>
@@ -2391,22 +2391,26 @@
       <c r="I21" s="46">
         <v>46065.708333333336</v>
       </c>
-      <c r="J21" s="46"/>
+      <c r="J21" s="46">
+        <v>46067.578472222223</v>
+      </c>
       <c r="K21" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
+        <v>Completed</v>
       </c>
       <c r="L21" s="47">
         <v>3</v>
       </c>
-      <c r="M21" s="47"/>
+      <c r="M21" s="47">
+        <v>3</v>
+      </c>
       <c r="N21" s="45">
         <f>IF(ISBLANK(L21), "", L21*VLOOKUP($F21,Internal!$B$26:$C$32,2,FALSE))</f>
         <v>75</v>
       </c>
-      <c r="O21" s="45" t="str">
+      <c r="O21" s="45">
         <f>IF(ISBLANK(M21), "", M21*VLOOKUP($F21,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
+        <v>75</v>
       </c>
       <c r="P21" s="44" t="s">
         <v>104</v>
@@ -2715,7 +2719,7 @@
       </c>
       <c r="K28" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Ongoing</v>
+        <v>Completed</v>
       </c>
       <c r="L28" s="47">
         <v>0.33333333333333331</v>

--- a/reports/Deliverable D01 (Level C)/Group/Planning-Template.xlsx
+++ b/reports/Deliverable D01 (Level C)/Group/Planning-Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Javier\Downloads\Workspace-26\Projects\Acme-Starters-C\reports\Deliverable D01 (Level C)\Group\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{104EF387-DBB9-48A9-9AE3-297D933BB532}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B439684E-6F8F-47B6-9BE0-2C167E605147}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="2" xr2:uid="{683E09B8-1D94-4905-B116-9D998A46AAA3}"/>
   </bookViews>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="117">
   <si>
     <t xml:space="preserve">  Enter configuration data in these cells</t>
   </si>
@@ -393,6 +393,24 @@
   <si>
     <t>Actualizar Acme-Framework a la versión 26.2.0</t>
   </si>
+  <si>
+    <t>T0018/D</t>
+  </si>
+  <si>
+    <t>T0011/D</t>
+  </si>
+  <si>
+    <t>T0015/D</t>
+  </si>
+  <si>
+    <t>T0012/D</t>
+  </si>
+  <si>
+    <t>T0014/D</t>
+  </si>
+  <si>
+    <t>T0013/D</t>
+  </si>
 </sst>
 </file>
 
@@ -401,7 +419,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$EUR]\ #,##0.00"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -434,14 +452,6 @@
     </font>
     <font>
       <sz val="8"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -776,9 +786,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -795,6 +802,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1435,118 +1445,118 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B2" s="56" t="s">
+      <c r="B2" s="55" t="s">
         <v>78</v>
       </c>
-      <c r="C2" s="56"/>
-      <c r="D2" s="56"/>
-      <c r="E2" s="56"/>
-      <c r="F2" s="56"/>
-      <c r="G2" s="56"/>
-      <c r="H2" s="56"/>
-      <c r="I2" s="56"/>
-      <c r="J2" s="56"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
+      <c r="J2" s="55"/>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B4" s="54" t="s">
+      <c r="B4" s="53" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="55"/>
-      <c r="D4" s="55"/>
-      <c r="E4" s="55"/>
-      <c r="F4" s="55"/>
-      <c r="G4" s="55"/>
-      <c r="H4" s="55"/>
-      <c r="I4" s="55"/>
-      <c r="J4" s="55"/>
+      <c r="C4" s="54"/>
+      <c r="D4" s="54"/>
+      <c r="E4" s="54"/>
+      <c r="F4" s="54"/>
+      <c r="G4" s="54"/>
+      <c r="H4" s="54"/>
+      <c r="I4" s="54"/>
+      <c r="J4" s="54"/>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B5" s="55"/>
-      <c r="C5" s="55"/>
-      <c r="D5" s="55"/>
-      <c r="E5" s="55"/>
-      <c r="F5" s="55"/>
-      <c r="G5" s="55"/>
-      <c r="H5" s="55"/>
-      <c r="I5" s="55"/>
-      <c r="J5" s="55"/>
+      <c r="B5" s="54"/>
+      <c r="C5" s="54"/>
+      <c r="D5" s="54"/>
+      <c r="E5" s="54"/>
+      <c r="F5" s="54"/>
+      <c r="G5" s="54"/>
+      <c r="H5" s="54"/>
+      <c r="I5" s="54"/>
+      <c r="J5" s="54"/>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B6" s="55"/>
-      <c r="C6" s="55"/>
-      <c r="D6" s="55"/>
-      <c r="E6" s="55"/>
-      <c r="F6" s="55"/>
-      <c r="G6" s="55"/>
-      <c r="H6" s="55"/>
-      <c r="I6" s="55"/>
-      <c r="J6" s="55"/>
+      <c r="B6" s="54"/>
+      <c r="C6" s="54"/>
+      <c r="D6" s="54"/>
+      <c r="E6" s="54"/>
+      <c r="F6" s="54"/>
+      <c r="G6" s="54"/>
+      <c r="H6" s="54"/>
+      <c r="I6" s="54"/>
+      <c r="J6" s="54"/>
     </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B7" s="55"/>
-      <c r="C7" s="55"/>
-      <c r="D7" s="55"/>
-      <c r="E7" s="55"/>
-      <c r="F7" s="55"/>
-      <c r="G7" s="55"/>
-      <c r="H7" s="55"/>
-      <c r="I7" s="55"/>
-      <c r="J7" s="55"/>
+      <c r="B7" s="54"/>
+      <c r="C7" s="54"/>
+      <c r="D7" s="54"/>
+      <c r="E7" s="54"/>
+      <c r="F7" s="54"/>
+      <c r="G7" s="54"/>
+      <c r="H7" s="54"/>
+      <c r="I7" s="54"/>
+      <c r="J7" s="54"/>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B8" s="55"/>
-      <c r="C8" s="55"/>
-      <c r="D8" s="55"/>
-      <c r="E8" s="55"/>
-      <c r="F8" s="55"/>
-      <c r="G8" s="55"/>
-      <c r="H8" s="55"/>
-      <c r="I8" s="55"/>
-      <c r="J8" s="55"/>
+      <c r="B8" s="54"/>
+      <c r="C8" s="54"/>
+      <c r="D8" s="54"/>
+      <c r="E8" s="54"/>
+      <c r="F8" s="54"/>
+      <c r="G8" s="54"/>
+      <c r="H8" s="54"/>
+      <c r="I8" s="54"/>
+      <c r="J8" s="54"/>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B9" s="55"/>
-      <c r="C9" s="55"/>
-      <c r="D9" s="55"/>
-      <c r="E9" s="55"/>
-      <c r="F9" s="55"/>
-      <c r="G9" s="55"/>
-      <c r="H9" s="55"/>
-      <c r="I9" s="55"/>
-      <c r="J9" s="55"/>
+      <c r="B9" s="54"/>
+      <c r="C9" s="54"/>
+      <c r="D9" s="54"/>
+      <c r="E9" s="54"/>
+      <c r="F9" s="54"/>
+      <c r="G9" s="54"/>
+      <c r="H9" s="54"/>
+      <c r="I9" s="54"/>
+      <c r="J9" s="54"/>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B10" s="55"/>
-      <c r="C10" s="55"/>
-      <c r="D10" s="55"/>
-      <c r="E10" s="55"/>
-      <c r="F10" s="55"/>
-      <c r="G10" s="55"/>
-      <c r="H10" s="55"/>
-      <c r="I10" s="55"/>
-      <c r="J10" s="55"/>
+      <c r="B10" s="54"/>
+      <c r="C10" s="54"/>
+      <c r="D10" s="54"/>
+      <c r="E10" s="54"/>
+      <c r="F10" s="54"/>
+      <c r="G10" s="54"/>
+      <c r="H10" s="54"/>
+      <c r="I10" s="54"/>
+      <c r="J10" s="54"/>
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B11" s="55"/>
-      <c r="C11" s="55"/>
-      <c r="D11" s="55"/>
-      <c r="E11" s="55"/>
-      <c r="F11" s="55"/>
-      <c r="G11" s="55"/>
-      <c r="H11" s="55"/>
-      <c r="I11" s="55"/>
-      <c r="J11" s="55"/>
+      <c r="B11" s="54"/>
+      <c r="C11" s="54"/>
+      <c r="D11" s="54"/>
+      <c r="E11" s="54"/>
+      <c r="F11" s="54"/>
+      <c r="G11" s="54"/>
+      <c r="H11" s="54"/>
+      <c r="I11" s="54"/>
+      <c r="J11" s="54"/>
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B12" s="55"/>
-      <c r="C12" s="55"/>
-      <c r="D12" s="55"/>
-      <c r="E12" s="55"/>
-      <c r="F12" s="55"/>
-      <c r="G12" s="55"/>
-      <c r="H12" s="55"/>
-      <c r="I12" s="55"/>
-      <c r="J12" s="55"/>
+      <c r="B12" s="54"/>
+      <c r="C12" s="54"/>
+      <c r="D12" s="54"/>
+      <c r="E12" s="54"/>
+      <c r="F12" s="54"/>
+      <c r="G12" s="54"/>
+      <c r="H12" s="54"/>
+      <c r="I12" s="54"/>
+      <c r="J12" s="54"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1564,17 +1574,17 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="2" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B2" s="56" t="s">
+      <c r="B2" s="55" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="56"/>
-      <c r="D2" s="56"/>
-      <c r="E2" s="56"/>
-      <c r="F2" s="56"/>
-      <c r="G2" s="56"/>
-      <c r="H2" s="56"/>
-      <c r="I2" s="56"/>
-      <c r="J2" s="56"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
+      <c r="J2" s="55"/>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B3" s="2"/>
@@ -1588,39 +1598,39 @@
       <c r="J3" s="1"/>
     </row>
     <row r="4" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B4" s="54" t="s">
+      <c r="B4" s="53" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="54"/>
-      <c r="D4" s="54"/>
-      <c r="E4" s="54"/>
-      <c r="F4" s="54"/>
-      <c r="G4" s="54"/>
-      <c r="H4" s="54"/>
-      <c r="I4" s="54"/>
-      <c r="J4" s="54"/>
+      <c r="C4" s="53"/>
+      <c r="D4" s="53"/>
+      <c r="E4" s="53"/>
+      <c r="F4" s="53"/>
+      <c r="G4" s="53"/>
+      <c r="H4" s="53"/>
+      <c r="I4" s="53"/>
+      <c r="J4" s="53"/>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B5" s="54"/>
-      <c r="C5" s="54"/>
-      <c r="D5" s="54"/>
-      <c r="E5" s="54"/>
-      <c r="F5" s="54"/>
-      <c r="G5" s="54"/>
-      <c r="H5" s="54"/>
-      <c r="I5" s="54"/>
-      <c r="J5" s="54"/>
+      <c r="B5" s="53"/>
+      <c r="C5" s="53"/>
+      <c r="D5" s="53"/>
+      <c r="E5" s="53"/>
+      <c r="F5" s="53"/>
+      <c r="G5" s="53"/>
+      <c r="H5" s="53"/>
+      <c r="I5" s="53"/>
+      <c r="J5" s="53"/>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B6" s="54"/>
-      <c r="C6" s="54"/>
-      <c r="D6" s="54"/>
-      <c r="E6" s="54"/>
-      <c r="F6" s="54"/>
-      <c r="G6" s="54"/>
-      <c r="H6" s="54"/>
-      <c r="I6" s="54"/>
-      <c r="J6" s="54"/>
+      <c r="B6" s="53"/>
+      <c r="C6" s="53"/>
+      <c r="D6" s="53"/>
+      <c r="E6" s="53"/>
+      <c r="F6" s="53"/>
+      <c r="G6" s="53"/>
+      <c r="H6" s="53"/>
+      <c r="I6" s="53"/>
+      <c r="J6" s="53"/>
     </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B7" s="1"/>
@@ -1648,29 +1658,29 @@
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B9" s="4"/>
-      <c r="C9" s="57" t="s">
+      <c r="C9" s="56" t="s">
         <v>0</v>
       </c>
-      <c r="D9" s="57"/>
-      <c r="E9" s="57"/>
-      <c r="F9" s="57"/>
-      <c r="G9" s="57"/>
-      <c r="H9" s="57"/>
-      <c r="I9" s="57"/>
-      <c r="J9" s="57"/>
+      <c r="D9" s="56"/>
+      <c r="E9" s="56"/>
+      <c r="F9" s="56"/>
+      <c r="G9" s="56"/>
+      <c r="H9" s="56"/>
+      <c r="I9" s="56"/>
+      <c r="J9" s="56"/>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B10" s="49"/>
-      <c r="C10" s="57" t="s">
+      <c r="C10" s="56" t="s">
         <v>90</v>
       </c>
-      <c r="D10" s="57"/>
-      <c r="E10" s="57"/>
-      <c r="F10" s="57"/>
-      <c r="G10" s="57"/>
-      <c r="H10" s="57"/>
-      <c r="I10" s="57"/>
-      <c r="J10" s="57"/>
+      <c r="D10" s="56"/>
+      <c r="E10" s="56"/>
+      <c r="F10" s="56"/>
+      <c r="G10" s="56"/>
+      <c r="H10" s="56"/>
+      <c r="I10" s="56"/>
+      <c r="J10" s="56"/>
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B11" s="50"/>
@@ -1687,16 +1697,16 @@
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B12" s="3"/>
-      <c r="C12" s="57" t="s">
+      <c r="C12" s="56" t="s">
         <v>1</v>
       </c>
-      <c r="D12" s="57"/>
-      <c r="E12" s="57"/>
-      <c r="F12" s="57"/>
-      <c r="G12" s="57"/>
-      <c r="H12" s="57"/>
-      <c r="I12" s="57"/>
-      <c r="J12" s="57"/>
+      <c r="D12" s="56"/>
+      <c r="E12" s="56"/>
+      <c r="F12" s="56"/>
+      <c r="G12" s="56"/>
+      <c r="H12" s="56"/>
+      <c r="I12" s="56"/>
+      <c r="J12" s="56"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -1720,40 +1730,40 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:16" x14ac:dyDescent="0.45">
-      <c r="C2" s="56" t="s">
+      <c r="C2" s="55" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="56"/>
-      <c r="E2" s="56"/>
-      <c r="F2" s="56"/>
-      <c r="G2" s="56"/>
-      <c r="H2" s="56"/>
-      <c r="I2" s="56"/>
-      <c r="J2" s="56"/>
-      <c r="K2" s="56"/>
-      <c r="L2" s="56"/>
-      <c r="M2" s="56"/>
-      <c r="N2" s="56"/>
-      <c r="O2" s="56"/>
-      <c r="P2" s="56"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
+      <c r="J2" s="55"/>
+      <c r="K2" s="55"/>
+      <c r="L2" s="55"/>
+      <c r="M2" s="55"/>
+      <c r="N2" s="55"/>
+      <c r="O2" s="55"/>
+      <c r="P2" s="55"/>
     </row>
     <row r="4" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="C4" s="54" t="s">
+      <c r="C4" s="53" t="s">
         <v>75</v>
       </c>
-      <c r="D4" s="54"/>
-      <c r="E4" s="54"/>
-      <c r="F4" s="54"/>
-      <c r="G4" s="54"/>
-      <c r="H4" s="54"/>
-      <c r="I4" s="54"/>
-      <c r="J4" s="54"/>
-      <c r="K4" s="54"/>
-      <c r="L4" s="54"/>
-      <c r="M4" s="54"/>
-      <c r="N4" s="54"/>
-      <c r="O4" s="54"/>
-      <c r="P4" s="54"/>
+      <c r="D4" s="53"/>
+      <c r="E4" s="53"/>
+      <c r="F4" s="53"/>
+      <c r="G4" s="53"/>
+      <c r="H4" s="53"/>
+      <c r="I4" s="53"/>
+      <c r="J4" s="53"/>
+      <c r="K4" s="53"/>
+      <c r="L4" s="53"/>
+      <c r="M4" s="53"/>
+      <c r="N4" s="53"/>
+      <c r="O4" s="53"/>
+      <c r="P4" s="53"/>
     </row>
     <row r="5" spans="2:16" x14ac:dyDescent="0.45">
       <c r="C5" s="5"/>
@@ -1772,7 +1782,7 @@
       <c r="P5" s="5"/>
     </row>
     <row r="6" spans="2:16" x14ac:dyDescent="0.45">
-      <c r="C6" s="58" t="s">
+      <c r="C6" s="57" t="s">
         <v>68</v>
       </c>
       <c r="D6" s="10" t="s">
@@ -1780,7 +1790,7 @@
       </c>
       <c r="E6" s="35">
         <f>SUM(N12:N112)</f>
-        <v>831.66666666666674</v>
+        <v>870.00000000000011</v>
       </c>
       <c r="F6" s="5"/>
       <c r="G6" s="5"/>
@@ -1795,13 +1805,13 @@
       <c r="P6" s="5"/>
     </row>
     <row r="7" spans="2:16" x14ac:dyDescent="0.45">
-      <c r="C7" s="58"/>
+      <c r="C7" s="57"/>
       <c r="D7" s="11" t="s">
         <v>70</v>
       </c>
       <c r="E7" s="36">
         <f>SUM(O12:O112)</f>
-        <v>470</v>
+        <v>968.33333333333337</v>
       </c>
       <c r="J7" s="37"/>
     </row>
@@ -1813,19 +1823,19 @@
       <c r="F9" s="7"/>
       <c r="G9" s="7"/>
       <c r="H9" s="7"/>
-      <c r="I9" s="59" t="s">
+      <c r="I9" s="58" t="s">
         <v>51</v>
       </c>
-      <c r="J9" s="59"/>
+      <c r="J9" s="58"/>
       <c r="K9" s="7"/>
-      <c r="L9" s="59" t="s">
+      <c r="L9" s="58" t="s">
         <v>7</v>
       </c>
-      <c r="M9" s="59"/>
-      <c r="N9" s="59" t="s">
+      <c r="M9" s="58"/>
+      <c r="N9" s="58" t="s">
         <v>58</v>
       </c>
-      <c r="O9" s="59"/>
+      <c r="O9" s="58"/>
       <c r="P9" s="7"/>
     </row>
     <row r="10" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
@@ -2389,7 +2399,7 @@
       </c>
       <c r="H21" s="43"/>
       <c r="I21" s="46">
-        <v>46065.708333333336</v>
+        <v>46067.416666666664</v>
       </c>
       <c r="J21" s="46">
         <v>46067.578472222223</v>
@@ -2438,24 +2448,28 @@
       </c>
       <c r="H22" s="43"/>
       <c r="I22" s="46">
-        <v>46065.708333333336</v>
-      </c>
-      <c r="J22" s="46"/>
+        <v>46068.416666666664</v>
+      </c>
+      <c r="J22" s="46">
+        <v>46068.5625</v>
+      </c>
       <c r="K22" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
+        <v>Completed</v>
       </c>
       <c r="L22" s="47">
         <v>3</v>
       </c>
-      <c r="M22" s="47"/>
+      <c r="M22" s="47">
+        <v>3</v>
+      </c>
       <c r="N22" s="45">
         <f>IF(ISBLANK(L22), "", L22*VLOOKUP($F22,Internal!$B$26:$C$32,2,FALSE))</f>
         <v>75</v>
       </c>
-      <c r="O22" s="45" t="str">
+      <c r="O22" s="45">
         <f>IF(ISBLANK(M22), "", M22*VLOOKUP($F22,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
+        <v>75</v>
       </c>
       <c r="P22" s="44" t="s">
         <v>105</v>
@@ -2483,24 +2497,28 @@
       </c>
       <c r="H23" s="43"/>
       <c r="I23" s="46">
-        <v>46065.708333333336</v>
-      </c>
-      <c r="J23" s="46"/>
+        <v>46065.416666666664</v>
+      </c>
+      <c r="J23" s="46">
+        <v>46065.541666666664</v>
+      </c>
       <c r="K23" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
+        <v>Completed</v>
       </c>
       <c r="L23" s="47">
         <v>3</v>
       </c>
-      <c r="M23" s="47"/>
+      <c r="M23" s="47">
+        <v>3</v>
+      </c>
       <c r="N23" s="45">
         <f>IF(ISBLANK(L23), "", L23*VLOOKUP($F23,Internal!$B$26:$C$32,2,FALSE))</f>
         <v>75</v>
       </c>
-      <c r="O23" s="45" t="str">
+      <c r="O23" s="45">
         <f>IF(ISBLANK(M23), "", M23*VLOOKUP($F23,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
+        <v>75</v>
       </c>
       <c r="P23" s="44" t="s">
         <v>106</v>
@@ -2528,24 +2546,28 @@
       </c>
       <c r="H24" s="43"/>
       <c r="I24" s="46">
-        <v>46066.666666666664</v>
-      </c>
-      <c r="J24" s="46"/>
+        <v>46068.75</v>
+      </c>
+      <c r="J24" s="46">
+        <v>46068.885416666664</v>
+      </c>
       <c r="K24" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
+        <v>Completed</v>
       </c>
       <c r="L24" s="47">
         <v>3</v>
       </c>
-      <c r="M24" s="47"/>
+      <c r="M24" s="47">
+        <v>3</v>
+      </c>
       <c r="N24" s="45">
         <f>IF(ISBLANK(L24), "", L24*VLOOKUP($F24,Internal!$B$26:$C$32,2,FALSE))</f>
         <v>75</v>
       </c>
-      <c r="O24" s="45" t="str">
+      <c r="O24" s="45">
         <f>IF(ISBLANK(M24), "", M24*VLOOKUP($F24,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
+        <v>75</v>
       </c>
       <c r="P24" s="44" t="s">
         <v>107</v>
@@ -2573,24 +2595,28 @@
       </c>
       <c r="H25" s="43"/>
       <c r="I25" s="46">
-        <v>46067.416666666664</v>
-      </c>
-      <c r="J25" s="46"/>
+        <v>46068.416666666664</v>
+      </c>
+      <c r="J25" s="46">
+        <v>46068.572916666664</v>
+      </c>
       <c r="K25" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
+        <v>Completed</v>
       </c>
       <c r="L25" s="47">
         <v>3</v>
       </c>
-      <c r="M25" s="47"/>
+      <c r="M25" s="47">
+        <v>3</v>
+      </c>
       <c r="N25" s="45">
         <f>IF(ISBLANK(L25), "", L25*VLOOKUP($F25,Internal!$B$26:$C$32,2,FALSE))</f>
         <v>75</v>
       </c>
-      <c r="O25" s="45" t="str">
+      <c r="O25" s="45">
         <f>IF(ISBLANK(M25), "", M25*VLOOKUP($F25,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
+        <v>75</v>
       </c>
       <c r="P25" s="44" t="s">
         <v>108</v>
@@ -2618,24 +2644,28 @@
       </c>
       <c r="H26" s="43"/>
       <c r="I26" s="46">
-        <v>46067.666666666664</v>
-      </c>
-      <c r="J26" s="46"/>
+        <v>46068.75</v>
+      </c>
+      <c r="J26" s="46">
+        <v>46068.875</v>
+      </c>
       <c r="K26" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
+        <v>Completed</v>
       </c>
       <c r="L26" s="47">
         <v>2</v>
       </c>
-      <c r="M26" s="47"/>
+      <c r="M26" s="47">
+        <v>2.5</v>
+      </c>
       <c r="N26" s="45">
         <f>IF(ISBLANK(L26), "", L26*VLOOKUP($F26,Internal!$B$26:$C$32,2,FALSE))</f>
         <v>100</v>
       </c>
-      <c r="O26" s="45" t="str">
+      <c r="O26" s="45">
         <f>IF(ISBLANK(M26), "", M26*VLOOKUP($F26,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
+        <v>125</v>
       </c>
       <c r="P26" s="44" t="s">
         <v>103</v>
@@ -2701,7 +2731,7 @@
       <c r="D28" s="44" t="s">
         <v>62</v>
       </c>
-      <c r="E28" s="53" t="s">
+      <c r="E28" s="59" t="s">
         <v>80</v>
       </c>
       <c r="F28" s="43" t="s">
@@ -2745,30 +2775,48 @@
       </c>
       <c r="C29" s="42" t="str">
         <f>IF(ISBLANK(D29), "", _xlfn.CONCAT("T", TEXT(B29, "0000"), "/", VLOOKUP(D29, Internal!$B$35:C$39, 2, FALSE), IF(OR(D29="QA", D29="Revision"), _xlfn.CONCAT("/", H29), "")))</f>
-        <v/>
-      </c>
-      <c r="D29" s="44"/>
-      <c r="E29" s="43"/>
-      <c r="F29" s="43"/>
-      <c r="G29" s="44"/>
+        <v>T0019/M</v>
+      </c>
+      <c r="D29" s="44" t="s">
+        <v>64</v>
+      </c>
+      <c r="E29" s="43" t="s">
+        <v>80</v>
+      </c>
+      <c r="F29" s="43" t="s">
+        <v>23</v>
+      </c>
+      <c r="G29" s="44" t="s">
+        <v>20</v>
+      </c>
       <c r="H29" s="43"/>
-      <c r="I29" s="46"/>
-      <c r="J29" s="46"/>
+      <c r="I29" s="46">
+        <v>46069</v>
+      </c>
+      <c r="J29" s="46">
+        <v>46069.006944444445</v>
+      </c>
       <c r="K29" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L29" s="47"/>
-      <c r="M29" s="47"/>
-      <c r="N29" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L29" s="47">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="M29" s="47">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="N29" s="45">
         <f>IF(ISBLANK(L29), "", L29*VLOOKUP($F29,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O29" s="45" t="str">
+        <v>8.3333333333333321</v>
+      </c>
+      <c r="O29" s="45">
         <f>IF(ISBLANK(M29), "", M29*VLOOKUP($F29,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P29" s="44"/>
+        <v>8.3333333333333321</v>
+      </c>
+      <c r="P29" s="44" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="30" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B30" s="41">
@@ -2776,30 +2824,50 @@
       </c>
       <c r="C30" s="42" t="str">
         <f>IF(ISBLANK(D30), "", _xlfn.CONCAT("T", TEXT(B30, "0000"), "/", VLOOKUP(D30, Internal!$B$35:C$39, 2, FALSE), IF(OR(D30="QA", D30="Revision"), _xlfn.CONCAT("/", H30), "")))</f>
-        <v/>
-      </c>
-      <c r="D30" s="44"/>
-      <c r="E30" s="43"/>
-      <c r="F30" s="43"/>
-      <c r="G30" s="44"/>
-      <c r="H30" s="43"/>
-      <c r="I30" s="46"/>
-      <c r="J30" s="46"/>
+        <v>T0020/R/T0018/D</v>
+      </c>
+      <c r="D30" s="44" t="s">
+        <v>61</v>
+      </c>
+      <c r="E30" s="43" t="s">
+        <v>82</v>
+      </c>
+      <c r="F30" s="43" t="s">
+        <v>26</v>
+      </c>
+      <c r="G30" s="44" t="s">
+        <v>87</v>
+      </c>
+      <c r="H30" s="43" t="s">
+        <v>111</v>
+      </c>
+      <c r="I30" s="46">
+        <v>46066.5</v>
+      </c>
+      <c r="J30" s="46">
+        <v>46066.506944444445</v>
+      </c>
       <c r="K30" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L30" s="47"/>
-      <c r="M30" s="47"/>
-      <c r="N30" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L30" s="47">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="M30" s="47">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="N30" s="45">
         <f>IF(ISBLANK(L30), "", L30*VLOOKUP($F30,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O30" s="45" t="str">
+        <v>5</v>
+      </c>
+      <c r="O30" s="45">
         <f>IF(ISBLANK(M30), "", M30*VLOOKUP($F30,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P30" s="44"/>
+        <v>5</v>
+      </c>
+      <c r="P30" s="44" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="31" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B31" s="41">
@@ -2807,30 +2875,50 @@
       </c>
       <c r="C31" s="42" t="str">
         <f>IF(ISBLANK(D31), "", _xlfn.CONCAT("T", TEXT(B31, "0000"), "/", VLOOKUP(D31, Internal!$B$35:C$39, 2, FALSE), IF(OR(D31="QA", D31="Revision"), _xlfn.CONCAT("/", H31), "")))</f>
-        <v/>
-      </c>
-      <c r="D31" s="44"/>
-      <c r="E31" s="43"/>
-      <c r="F31" s="43"/>
-      <c r="G31" s="44"/>
-      <c r="H31" s="43"/>
-      <c r="I31" s="46"/>
-      <c r="J31" s="46"/>
+        <v>T0021/R/T0011/D</v>
+      </c>
+      <c r="D31" s="44" t="s">
+        <v>61</v>
+      </c>
+      <c r="E31" s="43" t="s">
+        <v>82</v>
+      </c>
+      <c r="F31" s="43" t="s">
+        <v>26</v>
+      </c>
+      <c r="G31" s="44" t="s">
+        <v>87</v>
+      </c>
+      <c r="H31" s="43" t="s">
+        <v>112</v>
+      </c>
+      <c r="I31" s="46">
+        <v>46067.708333333336</v>
+      </c>
+      <c r="J31" s="46">
+        <v>46067.75</v>
+      </c>
       <c r="K31" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L31" s="47"/>
-      <c r="M31" s="47"/>
-      <c r="N31" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L31" s="47">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="M31" s="47">
+        <v>1</v>
+      </c>
+      <c r="N31" s="45">
         <f>IF(ISBLANK(L31), "", L31*VLOOKUP($F31,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O31" s="45" t="str">
+        <v>5</v>
+      </c>
+      <c r="O31" s="45">
         <f>IF(ISBLANK(M31), "", M31*VLOOKUP($F31,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P31" s="44"/>
+        <v>30</v>
+      </c>
+      <c r="P31" s="44" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="32" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B32" s="41">
@@ -2838,30 +2926,50 @@
       </c>
       <c r="C32" s="42" t="str">
         <f>IF(ISBLANK(D32), "", _xlfn.CONCAT("T", TEXT(B32, "0000"), "/", VLOOKUP(D32, Internal!$B$35:C$39, 2, FALSE), IF(OR(D32="QA", D32="Revision"), _xlfn.CONCAT("/", H32), "")))</f>
-        <v/>
-      </c>
-      <c r="D32" s="44"/>
-      <c r="E32" s="43"/>
-      <c r="F32" s="43"/>
-      <c r="G32" s="44"/>
-      <c r="H32" s="43"/>
-      <c r="I32" s="46"/>
-      <c r="J32" s="46"/>
+        <v>T0022/R/T0015/D</v>
+      </c>
+      <c r="D32" s="44" t="s">
+        <v>61</v>
+      </c>
+      <c r="E32" s="43" t="s">
+        <v>83</v>
+      </c>
+      <c r="F32" s="43" t="s">
+        <v>26</v>
+      </c>
+      <c r="G32" s="44" t="s">
+        <v>87</v>
+      </c>
+      <c r="H32" s="43" t="s">
+        <v>113</v>
+      </c>
+      <c r="I32" s="46">
+        <v>46068.541666666664</v>
+      </c>
+      <c r="J32" s="46">
+        <v>46068.548611111109</v>
+      </c>
       <c r="K32" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L32" s="47"/>
-      <c r="M32" s="47"/>
-      <c r="N32" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L32" s="47">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="M32" s="47">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="N32" s="45">
         <f>IF(ISBLANK(L32), "", L32*VLOOKUP($F32,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O32" s="45" t="str">
+        <v>5</v>
+      </c>
+      <c r="O32" s="45">
         <f>IF(ISBLANK(M32), "", M32*VLOOKUP($F32,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P32" s="44"/>
+        <v>5</v>
+      </c>
+      <c r="P32" s="44" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="33" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B33" s="41">
@@ -2869,30 +2977,50 @@
       </c>
       <c r="C33" s="42" t="str">
         <f>IF(ISBLANK(D33), "", _xlfn.CONCAT("T", TEXT(B33, "0000"), "/", VLOOKUP(D33, Internal!$B$35:C$39, 2, FALSE), IF(OR(D33="QA", D33="Revision"), _xlfn.CONCAT("/", H33), "")))</f>
-        <v/>
-      </c>
-      <c r="D33" s="44"/>
-      <c r="E33" s="43"/>
-      <c r="F33" s="43"/>
-      <c r="G33" s="44"/>
-      <c r="H33" s="43"/>
-      <c r="I33" s="46"/>
-      <c r="J33" s="46"/>
+        <v>T0023/R/T0012/D</v>
+      </c>
+      <c r="D33" s="44" t="s">
+        <v>61</v>
+      </c>
+      <c r="E33" s="43" t="s">
+        <v>80</v>
+      </c>
+      <c r="F33" s="43" t="s">
+        <v>26</v>
+      </c>
+      <c r="G33" s="44" t="s">
+        <v>87</v>
+      </c>
+      <c r="H33" s="43" t="s">
+        <v>114</v>
+      </c>
+      <c r="I33" s="46">
+        <v>46068.743055555555</v>
+      </c>
+      <c r="J33" s="46">
+        <v>46068.75</v>
+      </c>
       <c r="K33" s="45" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L33" s="47"/>
-      <c r="M33" s="47"/>
-      <c r="N33" s="45" t="str">
+        <f ca="1">IF(OR(I33="",J33=""),"",IF(AND(J33&lt;&gt;"",I33&gt;=NOW()),"Planned",IF(AND(J33&lt;&gt;"",J33&lt;NOW()),"Completed","Ongoing")))</f>
+        <v>Completed</v>
+      </c>
+      <c r="L33" s="47">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="M33" s="47">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="N33" s="45">
         <f>IF(ISBLANK(L33), "", L33*VLOOKUP($F33,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O33" s="45" t="str">
+        <v>5</v>
+      </c>
+      <c r="O33" s="45">
         <f>IF(ISBLANK(M33), "", M33*VLOOKUP($F33,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P33" s="44"/>
+        <v>5</v>
+      </c>
+      <c r="P33" s="44" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="34" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B34" s="41">
@@ -2900,30 +3028,50 @@
       </c>
       <c r="C34" s="42" t="str">
         <f>IF(ISBLANK(D34), "", _xlfn.CONCAT("T", TEXT(B34, "0000"), "/", VLOOKUP(D34, Internal!$B$35:C$39, 2, FALSE), IF(OR(D34="QA", D34="Revision"), _xlfn.CONCAT("/", H34), "")))</f>
-        <v/>
-      </c>
-      <c r="D34" s="44"/>
-      <c r="E34" s="43"/>
-      <c r="F34" s="43"/>
-      <c r="G34" s="44"/>
-      <c r="H34" s="43"/>
-      <c r="I34" s="46"/>
-      <c r="J34" s="46"/>
+        <v>T0024/R/T0014/D</v>
+      </c>
+      <c r="D34" s="44" t="s">
+        <v>61</v>
+      </c>
+      <c r="E34" s="43" t="s">
+        <v>84</v>
+      </c>
+      <c r="F34" s="43" t="s">
+        <v>26</v>
+      </c>
+      <c r="G34" s="44" t="s">
+        <v>87</v>
+      </c>
+      <c r="H34" s="43" t="s">
+        <v>115</v>
+      </c>
+      <c r="I34" s="46">
+        <v>46068.895833333336</v>
+      </c>
+      <c r="J34" s="46">
+        <v>46068.916666666664</v>
+      </c>
       <c r="K34" s="45" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L34" s="47"/>
-      <c r="M34" s="47"/>
-      <c r="N34" s="45" t="str">
+        <f ca="1">IF(OR(I34="",J34=""),"",IF(AND(J34&lt;&gt;"",I34&gt;=NOW()),"Planned",IF(AND(J34&lt;&gt;"",J34&lt;NOW()),"Completed","Ongoing")))</f>
+        <v>Completed</v>
+      </c>
+      <c r="L34" s="47">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="M34" s="47">
+        <v>0.5</v>
+      </c>
+      <c r="N34" s="45">
         <f>IF(ISBLANK(L34), "", L34*VLOOKUP($F34,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O34" s="45" t="str">
+        <v>5</v>
+      </c>
+      <c r="O34" s="45">
         <f>IF(ISBLANK(M34), "", M34*VLOOKUP($F34,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P34" s="44"/>
+        <v>15</v>
+      </c>
+      <c r="P34" s="44" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="35" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B35" s="41">
@@ -2931,30 +3079,50 @@
       </c>
       <c r="C35" s="42" t="str">
         <f>IF(ISBLANK(D35), "", _xlfn.CONCAT("T", TEXT(B35, "0000"), "/", VLOOKUP(D35, Internal!$B$35:C$39, 2, FALSE), IF(OR(D35="QA", D35="Revision"), _xlfn.CONCAT("/", H35), "")))</f>
-        <v/>
-      </c>
-      <c r="D35" s="44"/>
-      <c r="E35" s="43"/>
-      <c r="F35" s="43"/>
-      <c r="G35" s="44"/>
-      <c r="H35" s="43"/>
-      <c r="I35" s="46"/>
-      <c r="J35" s="46"/>
+        <v>T0025/R/T0013/D</v>
+      </c>
+      <c r="D35" s="44" t="s">
+        <v>61</v>
+      </c>
+      <c r="E35" s="43" t="s">
+        <v>81</v>
+      </c>
+      <c r="F35" s="43" t="s">
+        <v>26</v>
+      </c>
+      <c r="G35" s="44" t="s">
+        <v>87</v>
+      </c>
+      <c r="H35" s="43" t="s">
+        <v>116</v>
+      </c>
+      <c r="I35" s="46">
+        <v>46069.395833333336</v>
+      </c>
+      <c r="J35" s="46">
+        <v>46069.402777777781</v>
+      </c>
       <c r="K35" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L35" s="47"/>
-      <c r="M35" s="47"/>
-      <c r="N35" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L35" s="47">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="M35" s="47">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="N35" s="45">
         <f>IF(ISBLANK(L35), "", L35*VLOOKUP($F35,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O35" s="45" t="str">
+        <v>5</v>
+      </c>
+      <c r="O35" s="45">
         <f>IF(ISBLANK(M35), "", M35*VLOOKUP($F35,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P35" s="44"/>
+        <v>5</v>
+      </c>
+      <c r="P35" s="44" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="36" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B36" s="41">
@@ -5358,7 +5526,7 @@
       <formula>AND(H11&lt;&gt;"",COUNTIF($C$12:$C$112,H11)=0)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J11:J112">
+  <conditionalFormatting sqref="J11:J32 J34:J112">
     <cfRule type="expression" dxfId="4" priority="1">
       <formula>AND(I11&lt;&gt;"",J11&lt;&gt;"", I11&gt;J11)</formula>
     </cfRule>
@@ -5411,7 +5579,7 @@
           <x14:formula2>
             <xm:f>Internal!$C$23</xm:f>
           </x14:formula2>
-          <xm:sqref>I11:I112</xm:sqref>
+          <xm:sqref>J33 I11:I112</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="End moment" prompt="Indicate the moment when the assignee finishes working on this task.  Use format yy/mm/dd hh:mm." xr:uid="{AA2B0FBE-439D-4BBE-9231-3859DD87C79A}">
           <x14:formula1>
@@ -5420,7 +5588,7 @@
           <x14:formula2>
             <xm:f>Internal!$C$23</xm:f>
           </x14:formula2>
-          <xm:sqref>J11:J112</xm:sqref>
+          <xm:sqref>J34:J112 J11:J32</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -5438,40 +5606,40 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:16" x14ac:dyDescent="0.45">
-      <c r="C2" s="56" t="s">
+      <c r="C2" s="55" t="s">
         <v>85</v>
       </c>
-      <c r="D2" s="56"/>
-      <c r="E2" s="56"/>
-      <c r="F2" s="56"/>
-      <c r="G2" s="56"/>
-      <c r="H2" s="56"/>
-      <c r="I2" s="56"/>
-      <c r="J2" s="56"/>
-      <c r="K2" s="56"/>
-      <c r="L2" s="56"/>
-      <c r="M2" s="56"/>
-      <c r="N2" s="56"/>
-      <c r="O2" s="56"/>
-      <c r="P2" s="56"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
+      <c r="J2" s="55"/>
+      <c r="K2" s="55"/>
+      <c r="L2" s="55"/>
+      <c r="M2" s="55"/>
+      <c r="N2" s="55"/>
+      <c r="O2" s="55"/>
+      <c r="P2" s="55"/>
     </row>
     <row r="4" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="C4" s="54" t="s">
+      <c r="C4" s="53" t="s">
         <v>75</v>
       </c>
-      <c r="D4" s="54"/>
-      <c r="E4" s="54"/>
-      <c r="F4" s="54"/>
-      <c r="G4" s="54"/>
-      <c r="H4" s="54"/>
-      <c r="I4" s="54"/>
-      <c r="J4" s="54"/>
-      <c r="K4" s="54"/>
-      <c r="L4" s="54"/>
-      <c r="M4" s="54"/>
-      <c r="N4" s="54"/>
-      <c r="O4" s="54"/>
-      <c r="P4" s="54"/>
+      <c r="D4" s="53"/>
+      <c r="E4" s="53"/>
+      <c r="F4" s="53"/>
+      <c r="G4" s="53"/>
+      <c r="H4" s="53"/>
+      <c r="I4" s="53"/>
+      <c r="J4" s="53"/>
+      <c r="K4" s="53"/>
+      <c r="L4" s="53"/>
+      <c r="M4" s="53"/>
+      <c r="N4" s="53"/>
+      <c r="O4" s="53"/>
+      <c r="P4" s="53"/>
     </row>
     <row r="5" spans="2:16" x14ac:dyDescent="0.45">
       <c r="C5" s="5"/>
@@ -5490,7 +5658,7 @@
       <c r="P5" s="5"/>
     </row>
     <row r="6" spans="2:16" x14ac:dyDescent="0.45">
-      <c r="C6" s="58" t="s">
+      <c r="C6" s="57" t="s">
         <v>68</v>
       </c>
       <c r="D6" s="10" t="s">
@@ -5513,7 +5681,7 @@
       <c r="P6" s="5"/>
     </row>
     <row r="7" spans="2:16" x14ac:dyDescent="0.45">
-      <c r="C7" s="58"/>
+      <c r="C7" s="57"/>
       <c r="D7" s="11" t="s">
         <v>70</v>
       </c>
@@ -5531,19 +5699,19 @@
       <c r="F9" s="7"/>
       <c r="G9" s="7"/>
       <c r="H9" s="7"/>
-      <c r="I9" s="59" t="s">
+      <c r="I9" s="58" t="s">
         <v>51</v>
       </c>
-      <c r="J9" s="59"/>
+      <c r="J9" s="58"/>
       <c r="K9" s="7"/>
-      <c r="L9" s="59" t="s">
+      <c r="L9" s="58" t="s">
         <v>7</v>
       </c>
-      <c r="M9" s="59"/>
-      <c r="N9" s="59" t="s">
+      <c r="M9" s="58"/>
+      <c r="N9" s="58" t="s">
         <v>58</v>
       </c>
-      <c r="O9" s="59"/>
+      <c r="O9" s="58"/>
       <c r="P9" s="7"/>
     </row>
     <row r="10" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
@@ -8787,40 +8955,40 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:16" x14ac:dyDescent="0.45">
-      <c r="C2" s="56" t="s">
+      <c r="C2" s="55" t="s">
         <v>86</v>
       </c>
-      <c r="D2" s="56"/>
-      <c r="E2" s="56"/>
-      <c r="F2" s="56"/>
-      <c r="G2" s="56"/>
-      <c r="H2" s="56"/>
-      <c r="I2" s="56"/>
-      <c r="J2" s="56"/>
-      <c r="K2" s="56"/>
-      <c r="L2" s="56"/>
-      <c r="M2" s="56"/>
-      <c r="N2" s="56"/>
-      <c r="O2" s="56"/>
-      <c r="P2" s="56"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
+      <c r="J2" s="55"/>
+      <c r="K2" s="55"/>
+      <c r="L2" s="55"/>
+      <c r="M2" s="55"/>
+      <c r="N2" s="55"/>
+      <c r="O2" s="55"/>
+      <c r="P2" s="55"/>
     </row>
     <row r="4" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="C4" s="54" t="s">
+      <c r="C4" s="53" t="s">
         <v>75</v>
       </c>
-      <c r="D4" s="54"/>
-      <c r="E4" s="54"/>
-      <c r="F4" s="54"/>
-      <c r="G4" s="54"/>
-      <c r="H4" s="54"/>
-      <c r="I4" s="54"/>
-      <c r="J4" s="54"/>
-      <c r="K4" s="54"/>
-      <c r="L4" s="54"/>
-      <c r="M4" s="54"/>
-      <c r="N4" s="54"/>
-      <c r="O4" s="54"/>
-      <c r="P4" s="54"/>
+      <c r="D4" s="53"/>
+      <c r="E4" s="53"/>
+      <c r="F4" s="53"/>
+      <c r="G4" s="53"/>
+      <c r="H4" s="53"/>
+      <c r="I4" s="53"/>
+      <c r="J4" s="53"/>
+      <c r="K4" s="53"/>
+      <c r="L4" s="53"/>
+      <c r="M4" s="53"/>
+      <c r="N4" s="53"/>
+      <c r="O4" s="53"/>
+      <c r="P4" s="53"/>
     </row>
     <row r="5" spans="2:16" x14ac:dyDescent="0.45">
       <c r="C5" s="5"/>
@@ -8839,7 +9007,7 @@
       <c r="P5" s="5"/>
     </row>
     <row r="6" spans="2:16" x14ac:dyDescent="0.45">
-      <c r="C6" s="58" t="s">
+      <c r="C6" s="57" t="s">
         <v>68</v>
       </c>
       <c r="D6" s="10" t="s">
@@ -8862,7 +9030,7 @@
       <c r="P6" s="5"/>
     </row>
     <row r="7" spans="2:16" x14ac:dyDescent="0.45">
-      <c r="C7" s="58"/>
+      <c r="C7" s="57"/>
       <c r="D7" s="11" t="s">
         <v>70</v>
       </c>
@@ -8880,19 +9048,19 @@
       <c r="F9" s="7"/>
       <c r="G9" s="7"/>
       <c r="H9" s="7"/>
-      <c r="I9" s="59" t="s">
+      <c r="I9" s="58" t="s">
         <v>51</v>
       </c>
-      <c r="J9" s="59"/>
+      <c r="J9" s="58"/>
       <c r="K9" s="7"/>
-      <c r="L9" s="59" t="s">
+      <c r="L9" s="58" t="s">
         <v>7</v>
       </c>
-      <c r="M9" s="59"/>
-      <c r="N9" s="59" t="s">
+      <c r="M9" s="58"/>
+      <c r="N9" s="58" t="s">
         <v>58</v>
       </c>
-      <c r="O9" s="59"/>
+      <c r="O9" s="58"/>
       <c r="P9" s="7"/>
     </row>
     <row r="10" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
@@ -12135,52 +12303,52 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B2" s="56" t="s">
+      <c r="B2" s="55" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="56"/>
-      <c r="D2" s="56"/>
-      <c r="E2" s="56"/>
-      <c r="F2" s="56"/>
-      <c r="G2" s="56"/>
-      <c r="H2" s="56"/>
-      <c r="I2" s="56"/>
-      <c r="J2" s="56"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
+      <c r="J2" s="55"/>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B4" s="54" t="s">
+      <c r="B4" s="53" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="54"/>
-      <c r="D4" s="54"/>
-      <c r="E4" s="54"/>
-      <c r="F4" s="54"/>
-      <c r="G4" s="54"/>
-      <c r="H4" s="54"/>
-      <c r="I4" s="54"/>
-      <c r="J4" s="54"/>
+      <c r="C4" s="53"/>
+      <c r="D4" s="53"/>
+      <c r="E4" s="53"/>
+      <c r="F4" s="53"/>
+      <c r="G4" s="53"/>
+      <c r="H4" s="53"/>
+      <c r="I4" s="53"/>
+      <c r="J4" s="53"/>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B5" s="54"/>
-      <c r="C5" s="54"/>
-      <c r="D5" s="54"/>
-      <c r="E5" s="54"/>
-      <c r="F5" s="54"/>
-      <c r="G5" s="54"/>
-      <c r="H5" s="54"/>
-      <c r="I5" s="54"/>
-      <c r="J5" s="54"/>
+      <c r="B5" s="53"/>
+      <c r="C5" s="53"/>
+      <c r="D5" s="53"/>
+      <c r="E5" s="53"/>
+      <c r="F5" s="53"/>
+      <c r="G5" s="53"/>
+      <c r="H5" s="53"/>
+      <c r="I5" s="53"/>
+      <c r="J5" s="53"/>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B6" s="54"/>
-      <c r="C6" s="54"/>
-      <c r="D6" s="54"/>
-      <c r="E6" s="54"/>
-      <c r="F6" s="54"/>
-      <c r="G6" s="54"/>
-      <c r="H6" s="54"/>
-      <c r="I6" s="54"/>
-      <c r="J6" s="54"/>
+      <c r="B6" s="53"/>
+      <c r="C6" s="53"/>
+      <c r="D6" s="53"/>
+      <c r="E6" s="53"/>
+      <c r="F6" s="53"/>
+      <c r="G6" s="53"/>
+      <c r="H6" s="53"/>
+      <c r="I6" s="53"/>
+      <c r="J6" s="53"/>
     </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B7" s="5"/>

--- a/reports/Deliverable D01 (Level C)/Group/Planning-Template.xlsx
+++ b/reports/Deliverable D01 (Level C)/Group/Planning-Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Javier\Downloads\Workspace-26\Projects\Acme-Starters-C\reports\Deliverable D01 (Level C)\Group\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B439684E-6F8F-47B6-9BE0-2C167E605147}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30EC09D0-6CBE-4047-AC84-39D229261495}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="2" xr2:uid="{683E09B8-1D94-4905-B116-9D998A46AAA3}"/>
   </bookViews>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="131">
   <si>
     <t xml:space="preserve">  Enter configuration data in these cells</t>
   </si>
@@ -411,6 +411,48 @@
   <si>
     <t>T0013/D</t>
   </si>
+  <si>
+    <t>Crear datos de prueba para crear 2 cuentas de administrador.</t>
+  </si>
+  <si>
+    <t>Implementar restricciones esbozadas en el archivo 'Model-CG.ufx'</t>
+  </si>
+  <si>
+    <t>T0028/D</t>
+  </si>
+  <si>
+    <t>T0027/D</t>
+  </si>
+  <si>
+    <t>T0029/D</t>
+  </si>
+  <si>
+    <t>T0033/D</t>
+  </si>
+  <si>
+    <t>T0032/D</t>
+  </si>
+  <si>
+    <t>T0031/D</t>
+  </si>
+  <si>
+    <t>T0030/D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Implementar requisito S1/1 con validaciones personalizadas y adicionales. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Implementar requisito S2/1 con validaciones personalizadas y adicionales. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Implementar requisito S3/1 con validaciones personalizadas y adicionales. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Implementar requisito S4/1 con validaciones personalizadas y adicionales. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Implementar requisito S5/1 con validaciones personalizadas y adicionales. </t>
+  </si>
 </sst>
 </file>
 
@@ -676,7 +718,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -802,9 +844,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1790,7 +1829,7 @@
       </c>
       <c r="E6" s="35">
         <f>SUM(N12:N112)</f>
-        <v>870.00000000000011</v>
+        <v>1398.3333333333335</v>
       </c>
       <c r="F6" s="5"/>
       <c r="G6" s="5"/>
@@ -1811,7 +1850,7 @@
       </c>
       <c r="E7" s="36">
         <f>SUM(O12:O112)</f>
-        <v>968.33333333333337</v>
+        <v>980.83333333333337</v>
       </c>
       <c r="J7" s="37"/>
     </row>
@@ -2731,7 +2770,7 @@
       <c r="D28" s="44" t="s">
         <v>62</v>
       </c>
-      <c r="E28" s="59" t="s">
+      <c r="E28" s="43" t="s">
         <v>80</v>
       </c>
       <c r="F28" s="43" t="s">
@@ -3130,30 +3169,48 @@
       </c>
       <c r="C36" s="42" t="str">
         <f>IF(ISBLANK(D36), "", _xlfn.CONCAT("T", TEXT(B36, "0000"), "/", VLOOKUP(D36, Internal!$B$35:C$39, 2, FALSE), IF(OR(D36="QA", D36="Revision"), _xlfn.CONCAT("/", H36), "")))</f>
-        <v/>
-      </c>
-      <c r="D36" s="44"/>
-      <c r="E36" s="43"/>
-      <c r="F36" s="43"/>
-      <c r="G36" s="44"/>
+        <v>T0026/M</v>
+      </c>
+      <c r="D36" s="44" t="s">
+        <v>64</v>
+      </c>
+      <c r="E36" s="43" t="s">
+        <v>80</v>
+      </c>
+      <c r="F36" s="43" t="s">
+        <v>23</v>
+      </c>
+      <c r="G36" s="44" t="s">
+        <v>20</v>
+      </c>
       <c r="H36" s="43"/>
-      <c r="I36" s="46"/>
-      <c r="J36" s="46"/>
+      <c r="I36" s="46">
+        <v>46072.694444444445</v>
+      </c>
+      <c r="J36" s="46">
+        <v>46072.704861111109</v>
+      </c>
       <c r="K36" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L36" s="47"/>
-      <c r="M36" s="47"/>
-      <c r="N36" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L36" s="47">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="M36" s="47">
+        <v>0.25</v>
+      </c>
+      <c r="N36" s="45">
         <f>IF(ISBLANK(L36), "", L36*VLOOKUP($F36,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O36" s="45" t="str">
+        <v>8.3333333333333321</v>
+      </c>
+      <c r="O36" s="45">
         <f>IF(ISBLANK(M36), "", M36*VLOOKUP($F36,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P36" s="44"/>
+        <v>12.5</v>
+      </c>
+      <c r="P36" s="44" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="37" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B37" s="41">
@@ -3161,30 +3218,44 @@
       </c>
       <c r="C37" s="42" t="str">
         <f>IF(ISBLANK(D37), "", _xlfn.CONCAT("T", TEXT(B37, "0000"), "/", VLOOKUP(D37, Internal!$B$35:C$39, 2, FALSE), IF(OR(D37="QA", D37="Revision"), _xlfn.CONCAT("/", H37), "")))</f>
-        <v/>
-      </c>
-      <c r="D37" s="44"/>
-      <c r="E37" s="43"/>
-      <c r="F37" s="43"/>
-      <c r="G37" s="44"/>
+        <v>T0027/D</v>
+      </c>
+      <c r="D37" s="44" t="s">
+        <v>62</v>
+      </c>
+      <c r="E37" s="43" t="s">
+        <v>82</v>
+      </c>
+      <c r="F37" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="G37" s="44" t="s">
+        <v>41</v>
+      </c>
       <c r="H37" s="43"/>
-      <c r="I37" s="46"/>
+      <c r="I37" s="46">
+        <v>46072.708333333336</v>
+      </c>
       <c r="J37" s="46"/>
       <c r="K37" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
-      <c r="L37" s="47"/>
+      <c r="L37" s="47">
+        <v>1</v>
+      </c>
       <c r="M37" s="47"/>
-      <c r="N37" s="45" t="str">
+      <c r="N37" s="45">
         <f>IF(ISBLANK(L37), "", L37*VLOOKUP($F37,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
+        <v>25</v>
       </c>
       <c r="O37" s="45" t="str">
         <f>IF(ISBLANK(M37), "", M37*VLOOKUP($F37,Internal!$B$26:$C$32,2,FALSE))</f>
         <v/>
       </c>
-      <c r="P37" s="44"/>
+      <c r="P37" s="44" t="s">
+        <v>117</v>
+      </c>
     </row>
     <row r="38" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B38" s="41">
@@ -3192,30 +3263,44 @@
       </c>
       <c r="C38" s="42" t="str">
         <f>IF(ISBLANK(D38), "", _xlfn.CONCAT("T", TEXT(B38, "0000"), "/", VLOOKUP(D38, Internal!$B$35:C$39, 2, FALSE), IF(OR(D38="QA", D38="Revision"), _xlfn.CONCAT("/", H38), "")))</f>
-        <v/>
-      </c>
-      <c r="D38" s="44"/>
-      <c r="E38" s="43"/>
-      <c r="F38" s="43"/>
-      <c r="G38" s="44"/>
+        <v>T0028/D</v>
+      </c>
+      <c r="D38" s="44" t="s">
+        <v>62</v>
+      </c>
+      <c r="E38" s="43" t="s">
+        <v>84</v>
+      </c>
+      <c r="F38" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="G38" s="44" t="s">
+        <v>41</v>
+      </c>
       <c r="H38" s="43"/>
-      <c r="I38" s="46"/>
+      <c r="I38" s="46">
+        <v>46073.708333333336</v>
+      </c>
       <c r="J38" s="46"/>
       <c r="K38" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
-      <c r="L38" s="47"/>
+      <c r="L38" s="47">
+        <v>2</v>
+      </c>
       <c r="M38" s="47"/>
-      <c r="N38" s="45" t="str">
+      <c r="N38" s="45">
         <f>IF(ISBLANK(L38), "", L38*VLOOKUP($F38,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
+        <v>50</v>
       </c>
       <c r="O38" s="45" t="str">
         <f>IF(ISBLANK(M38), "", M38*VLOOKUP($F38,Internal!$B$26:$C$32,2,FALSE))</f>
         <v/>
       </c>
-      <c r="P38" s="44"/>
+      <c r="P38" s="44" t="s">
+        <v>118</v>
+      </c>
     </row>
     <row r="39" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B39" s="41">
@@ -3223,30 +3308,44 @@
       </c>
       <c r="C39" s="42" t="str">
         <f>IF(ISBLANK(D39), "", _xlfn.CONCAT("T", TEXT(B39, "0000"), "/", VLOOKUP(D39, Internal!$B$35:C$39, 2, FALSE), IF(OR(D39="QA", D39="Revision"), _xlfn.CONCAT("/", H39), "")))</f>
-        <v/>
-      </c>
-      <c r="D39" s="44"/>
-      <c r="E39" s="43"/>
-      <c r="F39" s="43"/>
-      <c r="G39" s="44"/>
+        <v>T0029/D</v>
+      </c>
+      <c r="D39" s="44" t="s">
+        <v>62</v>
+      </c>
+      <c r="E39" s="43" t="s">
+        <v>80</v>
+      </c>
+      <c r="F39" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="G39" s="44" t="s">
+        <v>41</v>
+      </c>
       <c r="H39" s="43"/>
-      <c r="I39" s="46"/>
+      <c r="I39" s="46">
+        <v>46074.708333333336</v>
+      </c>
       <c r="J39" s="46"/>
       <c r="K39" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
-      <c r="L39" s="47"/>
+      <c r="L39" s="47">
+        <v>3</v>
+      </c>
       <c r="M39" s="47"/>
-      <c r="N39" s="45" t="str">
+      <c r="N39" s="45">
         <f>IF(ISBLANK(L39), "", L39*VLOOKUP($F39,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
+        <v>75</v>
       </c>
       <c r="O39" s="45" t="str">
         <f>IF(ISBLANK(M39), "", M39*VLOOKUP($F39,Internal!$B$26:$C$32,2,FALSE))</f>
         <v/>
       </c>
-      <c r="P39" s="44"/>
+      <c r="P39" s="44" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="40" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B40" s="41">
@@ -3254,30 +3353,44 @@
       </c>
       <c r="C40" s="42" t="str">
         <f>IF(ISBLANK(D40), "", _xlfn.CONCAT("T", TEXT(B40, "0000"), "/", VLOOKUP(D40, Internal!$B$35:C$39, 2, FALSE), IF(OR(D40="QA", D40="Revision"), _xlfn.CONCAT("/", H40), "")))</f>
-        <v/>
-      </c>
-      <c r="D40" s="44"/>
-      <c r="E40" s="43"/>
-      <c r="F40" s="43"/>
-      <c r="G40" s="44"/>
+        <v>T0030/D</v>
+      </c>
+      <c r="D40" s="44" t="s">
+        <v>62</v>
+      </c>
+      <c r="E40" s="43" t="s">
+        <v>81</v>
+      </c>
+      <c r="F40" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="G40" s="44" t="s">
+        <v>41</v>
+      </c>
       <c r="H40" s="43"/>
-      <c r="I40" s="46"/>
+      <c r="I40" s="46">
+        <v>46075.708333333336</v>
+      </c>
       <c r="J40" s="46"/>
       <c r="K40" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
-      <c r="L40" s="47"/>
+      <c r="L40" s="47">
+        <v>3</v>
+      </c>
       <c r="M40" s="47"/>
-      <c r="N40" s="45" t="str">
+      <c r="N40" s="45">
         <f>IF(ISBLANK(L40), "", L40*VLOOKUP($F40,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
+        <v>75</v>
       </c>
       <c r="O40" s="45" t="str">
         <f>IF(ISBLANK(M40), "", M40*VLOOKUP($F40,Internal!$B$26:$C$32,2,FALSE))</f>
         <v/>
       </c>
-      <c r="P40" s="44"/>
+      <c r="P40" s="44" t="s">
+        <v>127</v>
+      </c>
     </row>
     <row r="41" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B41" s="41">
@@ -3285,30 +3398,44 @@
       </c>
       <c r="C41" s="42" t="str">
         <f>IF(ISBLANK(D41), "", _xlfn.CONCAT("T", TEXT(B41, "0000"), "/", VLOOKUP(D41, Internal!$B$35:C$39, 2, FALSE), IF(OR(D41="QA", D41="Revision"), _xlfn.CONCAT("/", H41), "")))</f>
-        <v/>
-      </c>
-      <c r="D41" s="44"/>
-      <c r="E41" s="43"/>
-      <c r="F41" s="43"/>
-      <c r="G41" s="44"/>
+        <v>T0031/D</v>
+      </c>
+      <c r="D41" s="44" t="s">
+        <v>62</v>
+      </c>
+      <c r="E41" s="43" t="s">
+        <v>82</v>
+      </c>
+      <c r="F41" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="G41" s="44" t="s">
+        <v>41</v>
+      </c>
       <c r="H41" s="43"/>
-      <c r="I41" s="46"/>
+      <c r="I41" s="46">
+        <v>46076.708333333336</v>
+      </c>
       <c r="J41" s="46"/>
       <c r="K41" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
-      <c r="L41" s="47"/>
+      <c r="L41" s="47">
+        <v>3</v>
+      </c>
       <c r="M41" s="47"/>
-      <c r="N41" s="45" t="str">
+      <c r="N41" s="45">
         <f>IF(ISBLANK(L41), "", L41*VLOOKUP($F41,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
+        <v>75</v>
       </c>
       <c r="O41" s="45" t="str">
         <f>IF(ISBLANK(M41), "", M41*VLOOKUP($F41,Internal!$B$26:$C$32,2,FALSE))</f>
         <v/>
       </c>
-      <c r="P41" s="44"/>
+      <c r="P41" s="44" t="s">
+        <v>128</v>
+      </c>
     </row>
     <row r="42" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B42" s="41">
@@ -3316,30 +3443,44 @@
       </c>
       <c r="C42" s="42" t="str">
         <f>IF(ISBLANK(D42), "", _xlfn.CONCAT("T", TEXT(B42, "0000"), "/", VLOOKUP(D42, Internal!$B$35:C$39, 2, FALSE), IF(OR(D42="QA", D42="Revision"), _xlfn.CONCAT("/", H42), "")))</f>
-        <v/>
-      </c>
-      <c r="D42" s="44"/>
-      <c r="E42" s="43"/>
-      <c r="F42" s="43"/>
-      <c r="G42" s="44"/>
+        <v>T0032/D</v>
+      </c>
+      <c r="D42" s="44" t="s">
+        <v>62</v>
+      </c>
+      <c r="E42" s="43" t="s">
+        <v>83</v>
+      </c>
+      <c r="F42" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="G42" s="44" t="s">
+        <v>41</v>
+      </c>
       <c r="H42" s="43"/>
-      <c r="I42" s="46"/>
+      <c r="I42" s="46">
+        <v>46077.708333333336</v>
+      </c>
       <c r="J42" s="46"/>
       <c r="K42" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
-      <c r="L42" s="47"/>
+      <c r="L42" s="47">
+        <v>3</v>
+      </c>
       <c r="M42" s="47"/>
-      <c r="N42" s="45" t="str">
+      <c r="N42" s="45">
         <f>IF(ISBLANK(L42), "", L42*VLOOKUP($F42,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
+        <v>75</v>
       </c>
       <c r="O42" s="45" t="str">
         <f>IF(ISBLANK(M42), "", M42*VLOOKUP($F42,Internal!$B$26:$C$32,2,FALSE))</f>
         <v/>
       </c>
-      <c r="P42" s="44"/>
+      <c r="P42" s="44" t="s">
+        <v>129</v>
+      </c>
     </row>
     <row r="43" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B43" s="41">
@@ -3347,30 +3488,44 @@
       </c>
       <c r="C43" s="42" t="str">
         <f>IF(ISBLANK(D43), "", _xlfn.CONCAT("T", TEXT(B43, "0000"), "/", VLOOKUP(D43, Internal!$B$35:C$39, 2, FALSE), IF(OR(D43="QA", D43="Revision"), _xlfn.CONCAT("/", H43), "")))</f>
-        <v/>
-      </c>
-      <c r="D43" s="44"/>
-      <c r="E43" s="43"/>
-      <c r="F43" s="43"/>
-      <c r="G43" s="44"/>
+        <v>T0033/D</v>
+      </c>
+      <c r="D43" s="44" t="s">
+        <v>62</v>
+      </c>
+      <c r="E43" s="43" t="s">
+        <v>84</v>
+      </c>
+      <c r="F43" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="G43" s="44" t="s">
+        <v>41</v>
+      </c>
       <c r="H43" s="43"/>
-      <c r="I43" s="46"/>
+      <c r="I43" s="46">
+        <v>46078.708333333336</v>
+      </c>
       <c r="J43" s="46"/>
       <c r="K43" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
-      <c r="L43" s="47"/>
+      <c r="L43" s="47">
+        <v>3</v>
+      </c>
       <c r="M43" s="47"/>
-      <c r="N43" s="45" t="str">
+      <c r="N43" s="45">
         <f>IF(ISBLANK(L43), "", L43*VLOOKUP($F43,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
+        <v>75</v>
       </c>
       <c r="O43" s="45" t="str">
         <f>IF(ISBLANK(M43), "", M43*VLOOKUP($F43,Internal!$B$26:$C$32,2,FALSE))</f>
         <v/>
       </c>
-      <c r="P43" s="44"/>
+      <c r="P43" s="44" t="s">
+        <v>130</v>
+      </c>
     </row>
     <row r="44" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B44" s="41">
@@ -3378,30 +3533,44 @@
       </c>
       <c r="C44" s="42" t="str">
         <f>IF(ISBLANK(D44), "", _xlfn.CONCAT("T", TEXT(B44, "0000"), "/", VLOOKUP(D44, Internal!$B$35:C$39, 2, FALSE), IF(OR(D44="QA", D44="Revision"), _xlfn.CONCAT("/", H44), "")))</f>
-        <v/>
-      </c>
-      <c r="D44" s="44"/>
-      <c r="E44" s="43"/>
-      <c r="F44" s="43"/>
-      <c r="G44" s="44"/>
-      <c r="H44" s="43"/>
+        <v>T0034/R/T0027/D</v>
+      </c>
+      <c r="D44" s="44" t="s">
+        <v>61</v>
+      </c>
+      <c r="E44" s="43" t="s">
+        <v>83</v>
+      </c>
+      <c r="F44" s="43" t="s">
+        <v>26</v>
+      </c>
+      <c r="G44" s="44" t="s">
+        <v>87</v>
+      </c>
+      <c r="H44" s="43" t="s">
+        <v>120</v>
+      </c>
       <c r="I44" s="46"/>
       <c r="J44" s="46"/>
       <c r="K44" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
-      <c r="L44" s="47"/>
+      <c r="L44" s="47">
+        <v>0.5</v>
+      </c>
       <c r="M44" s="47"/>
-      <c r="N44" s="45" t="str">
+      <c r="N44" s="45">
         <f>IF(ISBLANK(L44), "", L44*VLOOKUP($F44,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
+        <v>15</v>
       </c>
       <c r="O44" s="45" t="str">
         <f>IF(ISBLANK(M44), "", M44*VLOOKUP($F44,Internal!$B$26:$C$32,2,FALSE))</f>
         <v/>
       </c>
-      <c r="P44" s="44"/>
+      <c r="P44" s="44" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="45" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B45" s="41">
@@ -3409,30 +3578,44 @@
       </c>
       <c r="C45" s="42" t="str">
         <f>IF(ISBLANK(D45), "", _xlfn.CONCAT("T", TEXT(B45, "0000"), "/", VLOOKUP(D45, Internal!$B$35:C$39, 2, FALSE), IF(OR(D45="QA", D45="Revision"), _xlfn.CONCAT("/", H45), "")))</f>
-        <v/>
-      </c>
-      <c r="D45" s="44"/>
-      <c r="E45" s="43"/>
-      <c r="F45" s="43"/>
-      <c r="G45" s="44"/>
-      <c r="H45" s="43"/>
+        <v>T0035/R/T0028/D</v>
+      </c>
+      <c r="D45" s="44" t="s">
+        <v>61</v>
+      </c>
+      <c r="E45" s="43" t="s">
+        <v>80</v>
+      </c>
+      <c r="F45" s="43" t="s">
+        <v>26</v>
+      </c>
+      <c r="G45" s="44" t="s">
+        <v>87</v>
+      </c>
+      <c r="H45" s="43" t="s">
+        <v>119</v>
+      </c>
       <c r="I45" s="46"/>
       <c r="J45" s="46"/>
       <c r="K45" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
-      <c r="L45" s="47"/>
+      <c r="L45" s="47">
+        <v>0.16666666666666666</v>
+      </c>
       <c r="M45" s="47"/>
-      <c r="N45" s="45" t="str">
+      <c r="N45" s="45">
         <f>IF(ISBLANK(L45), "", L45*VLOOKUP($F45,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="O45" s="45" t="str">
         <f>IF(ISBLANK(M45), "", M45*VLOOKUP($F45,Internal!$B$26:$C$32,2,FALSE))</f>
         <v/>
       </c>
-      <c r="P45" s="44"/>
+      <c r="P45" s="44" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="46" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B46" s="41">
@@ -3440,30 +3623,44 @@
       </c>
       <c r="C46" s="42" t="str">
         <f>IF(ISBLANK(D46), "", _xlfn.CONCAT("T", TEXT(B46, "0000"), "/", VLOOKUP(D46, Internal!$B$35:C$39, 2, FALSE), IF(OR(D46="QA", D46="Revision"), _xlfn.CONCAT("/", H46), "")))</f>
-        <v/>
-      </c>
-      <c r="D46" s="44"/>
-      <c r="E46" s="43"/>
-      <c r="F46" s="43"/>
-      <c r="G46" s="44"/>
-      <c r="H46" s="43"/>
+        <v>T0036/R/T0033/D</v>
+      </c>
+      <c r="D46" s="44" t="s">
+        <v>61</v>
+      </c>
+      <c r="E46" s="43" t="s">
+        <v>80</v>
+      </c>
+      <c r="F46" s="43" t="s">
+        <v>26</v>
+      </c>
+      <c r="G46" s="44" t="s">
+        <v>87</v>
+      </c>
+      <c r="H46" s="43" t="s">
+        <v>122</v>
+      </c>
       <c r="I46" s="46"/>
       <c r="J46" s="46"/>
       <c r="K46" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
-      <c r="L46" s="47"/>
+      <c r="L46" s="47">
+        <v>0.33333333333333331</v>
+      </c>
       <c r="M46" s="47"/>
-      <c r="N46" s="45" t="str">
+      <c r="N46" s="45">
         <f>IF(ISBLANK(L46), "", L46*VLOOKUP($F46,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="O46" s="45" t="str">
         <f>IF(ISBLANK(M46), "", M46*VLOOKUP($F46,Internal!$B$26:$C$32,2,FALSE))</f>
         <v/>
       </c>
-      <c r="P46" s="44"/>
+      <c r="P46" s="44" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="47" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B47" s="41">
@@ -3471,30 +3668,44 @@
       </c>
       <c r="C47" s="42" t="str">
         <f>IF(ISBLANK(D47), "", _xlfn.CONCAT("T", TEXT(B47, "0000"), "/", VLOOKUP(D47, Internal!$B$35:C$39, 2, FALSE), IF(OR(D47="QA", D47="Revision"), _xlfn.CONCAT("/", H47), "")))</f>
-        <v/>
-      </c>
-      <c r="D47" s="44"/>
-      <c r="E47" s="43"/>
-      <c r="F47" s="43"/>
-      <c r="G47" s="44"/>
-      <c r="H47" s="43"/>
+        <v>T0037/R/T0032/D</v>
+      </c>
+      <c r="D47" s="44" t="s">
+        <v>61</v>
+      </c>
+      <c r="E47" s="43" t="s">
+        <v>81</v>
+      </c>
+      <c r="F47" s="43" t="s">
+        <v>26</v>
+      </c>
+      <c r="G47" s="44" t="s">
+        <v>87</v>
+      </c>
+      <c r="H47" s="43" t="s">
+        <v>123</v>
+      </c>
       <c r="I47" s="46"/>
       <c r="J47" s="46"/>
       <c r="K47" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
-      <c r="L47" s="47"/>
+      <c r="L47" s="47">
+        <v>0.33333333333333331</v>
+      </c>
       <c r="M47" s="47"/>
-      <c r="N47" s="45" t="str">
+      <c r="N47" s="45">
         <f>IF(ISBLANK(L47), "", L47*VLOOKUP($F47,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="O47" s="45" t="str">
         <f>IF(ISBLANK(M47), "", M47*VLOOKUP($F47,Internal!$B$26:$C$32,2,FALSE))</f>
         <v/>
       </c>
-      <c r="P47" s="44"/>
+      <c r="P47" s="44" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="48" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B48" s="41">
@@ -3502,30 +3713,44 @@
       </c>
       <c r="C48" s="42" t="str">
         <f>IF(ISBLANK(D48), "", _xlfn.CONCAT("T", TEXT(B48, "0000"), "/", VLOOKUP(D48, Internal!$B$35:C$39, 2, FALSE), IF(OR(D48="QA", D48="Revision"), _xlfn.CONCAT("/", H48), "")))</f>
-        <v/>
-      </c>
-      <c r="D48" s="44"/>
-      <c r="E48" s="43"/>
-      <c r="F48" s="43"/>
-      <c r="G48" s="44"/>
-      <c r="H48" s="43"/>
+        <v>T0038/R/T0029/D</v>
+      </c>
+      <c r="D48" s="44" t="s">
+        <v>61</v>
+      </c>
+      <c r="E48" s="43" t="s">
+        <v>82</v>
+      </c>
+      <c r="F48" s="43" t="s">
+        <v>26</v>
+      </c>
+      <c r="G48" s="44" t="s">
+        <v>87</v>
+      </c>
+      <c r="H48" s="43" t="s">
+        <v>121</v>
+      </c>
       <c r="I48" s="46"/>
       <c r="J48" s="46"/>
       <c r="K48" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
-      <c r="L48" s="47"/>
+      <c r="L48" s="47">
+        <v>0.33333333333333331</v>
+      </c>
       <c r="M48" s="47"/>
-      <c r="N48" s="45" t="str">
+      <c r="N48" s="45">
         <f>IF(ISBLANK(L48), "", L48*VLOOKUP($F48,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="O48" s="45" t="str">
         <f>IF(ISBLANK(M48), "", M48*VLOOKUP($F48,Internal!$B$26:$C$32,2,FALSE))</f>
         <v/>
       </c>
-      <c r="P48" s="44"/>
+      <c r="P48" s="44" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="49" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B49" s="41">
@@ -3533,30 +3758,44 @@
       </c>
       <c r="C49" s="42" t="str">
         <f>IF(ISBLANK(D49), "", _xlfn.CONCAT("T", TEXT(B49, "0000"), "/", VLOOKUP(D49, Internal!$B$35:C$39, 2, FALSE), IF(OR(D49="QA", D49="Revision"), _xlfn.CONCAT("/", H49), "")))</f>
-        <v/>
-      </c>
-      <c r="D49" s="44"/>
-      <c r="E49" s="43"/>
-      <c r="F49" s="43"/>
-      <c r="G49" s="44"/>
-      <c r="H49" s="43"/>
+        <v>T0039/R/T0031/D</v>
+      </c>
+      <c r="D49" s="44" t="s">
+        <v>61</v>
+      </c>
+      <c r="E49" s="43" t="s">
+        <v>83</v>
+      </c>
+      <c r="F49" s="43" t="s">
+        <v>26</v>
+      </c>
+      <c r="G49" s="44" t="s">
+        <v>87</v>
+      </c>
+      <c r="H49" s="43" t="s">
+        <v>124</v>
+      </c>
       <c r="I49" s="46"/>
       <c r="J49" s="46"/>
       <c r="K49" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
-      <c r="L49" s="47"/>
+      <c r="L49" s="47">
+        <v>0.33333333333333331</v>
+      </c>
       <c r="M49" s="47"/>
-      <c r="N49" s="45" t="str">
+      <c r="N49" s="45">
         <f>IF(ISBLANK(L49), "", L49*VLOOKUP($F49,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="O49" s="45" t="str">
         <f>IF(ISBLANK(M49), "", M49*VLOOKUP($F49,Internal!$B$26:$C$32,2,FALSE))</f>
         <v/>
       </c>
-      <c r="P49" s="44"/>
+      <c r="P49" s="44" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="50" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B50" s="41">
@@ -3564,30 +3803,44 @@
       </c>
       <c r="C50" s="42" t="str">
         <f>IF(ISBLANK(D50), "", _xlfn.CONCAT("T", TEXT(B50, "0000"), "/", VLOOKUP(D50, Internal!$B$35:C$39, 2, FALSE), IF(OR(D50="QA", D50="Revision"), _xlfn.CONCAT("/", H50), "")))</f>
-        <v/>
-      </c>
-      <c r="D50" s="44"/>
-      <c r="E50" s="43"/>
-      <c r="F50" s="43"/>
-      <c r="G50" s="44"/>
-      <c r="H50" s="43"/>
+        <v>T0040/R/T0030/D</v>
+      </c>
+      <c r="D50" s="44" t="s">
+        <v>61</v>
+      </c>
+      <c r="E50" s="43" t="s">
+        <v>84</v>
+      </c>
+      <c r="F50" s="43" t="s">
+        <v>26</v>
+      </c>
+      <c r="G50" s="44" t="s">
+        <v>87</v>
+      </c>
+      <c r="H50" s="43" t="s">
+        <v>125</v>
+      </c>
       <c r="I50" s="46"/>
       <c r="J50" s="46"/>
       <c r="K50" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
-      <c r="L50" s="47"/>
+      <c r="L50" s="47">
+        <v>0.33333333333333331</v>
+      </c>
       <c r="M50" s="47"/>
-      <c r="N50" s="45" t="str">
+      <c r="N50" s="45">
         <f>IF(ISBLANK(L50), "", L50*VLOOKUP($F50,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="O50" s="45" t="str">
         <f>IF(ISBLANK(M50), "", M50*VLOOKUP($F50,Internal!$B$26:$C$32,2,FALSE))</f>
         <v/>
       </c>
-      <c r="P50" s="44"/>
+      <c r="P50" s="44" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="51" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B51" s="41">
@@ -5526,7 +5779,7 @@
       <formula>AND(H11&lt;&gt;"",COUNTIF($C$12:$C$112,H11)=0)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J11:J32 J34:J112">
+  <conditionalFormatting sqref="J11:J32 J34:J35 J37:J112">
     <cfRule type="expression" dxfId="4" priority="1">
       <formula>AND(I11&lt;&gt;"",J11&lt;&gt;"", I11&gt;J11)</formula>
     </cfRule>
@@ -5579,7 +5832,7 @@
           <x14:formula2>
             <xm:f>Internal!$C$23</xm:f>
           </x14:formula2>
-          <xm:sqref>J33 I11:I112</xm:sqref>
+          <xm:sqref>J33 I11:I112 J36</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="End moment" prompt="Indicate the moment when the assignee finishes working on this task.  Use format yy/mm/dd hh:mm." xr:uid="{AA2B0FBE-439D-4BBE-9231-3859DD87C79A}">
           <x14:formula1>
@@ -5588,7 +5841,7 @@
           <x14:formula2>
             <xm:f>Internal!$C$23</xm:f>
           </x14:formula2>
-          <xm:sqref>J34:J112 J11:J32</xm:sqref>
+          <xm:sqref>J11:J32 J34:J35 J37:J112</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/reports/Deliverable D01 (Level C)/Group/Planning-Template.xlsx
+++ b/reports/Deliverable D01 (Level C)/Group/Planning-Template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Javier\Downloads\Workspace-26\Projects\Acme-Starters-C\reports\Deliverable D01 (Level C)\Group\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uses0-my.sharepoint.com/personal/laucubsan_alum_us_es/Documents/DP2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30EC09D0-6CBE-4047-AC84-39D229261495}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="597" documentId="13_ncr:1_{30EC09D0-6CBE-4047-AC84-39D229261495}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8E2C692B-7C5B-43AB-AD58-363B5594A7B2}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="2" xr2:uid="{683E09B8-1D94-4905-B116-9D998A46AAA3}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="2" activeTab="2" xr2:uid="{683E09B8-1D94-4905-B116-9D998A46AAA3}"/>
   </bookViews>
   <sheets>
     <sheet name="Copyright" sheetId="10" r:id="rId1"/>
@@ -32,7 +32,7 @@
     <definedName name="Student">Internal!$D$26:$G$26</definedName>
     <definedName name="Tester">Internal!$D$30:$I$30</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -53,12 +53,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="131">
-  <si>
-    <t xml:space="preserve">  Enter configuration data in these cells</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Internal data.  Do not change them.</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="617" uniqueCount="177">
+  <si>
+    <t>Copyright</t>
   </si>
   <si>
     <t># Planning-Template.xlsx
@@ -70,19 +67,79 @@
 they accept any liabilities with respect to them.</t>
   </si>
   <si>
+    <t>Abstract</t>
+  </si>
+  <si>
     <t>This spreadsheet is intended to facilitate planning on the tasks of your project.  Please, share it in your workgroup and closely follow the methodology taught.</t>
   </si>
   <si>
-    <t>Abstract</t>
+    <t xml:space="preserve">  Help comments</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Enter configuration data in these cells</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Warning and error messages.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Data computed automatically.  Do not change them.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Internal data.  Do not change them.</t>
   </si>
   <si>
     <t>Deliverable D01</t>
   </si>
   <si>
+    <t>Use this form to document the tasks that you perform in your projects.  Please, review the colour code in the "Abstract" sheet.  In the exceptional case that you need to perform more tasks than expected, add them at the end.</t>
+  </si>
+  <si>
+    <t>Costs</t>
+  </si>
+  <si>
+    <t>Expected:</t>
+  </si>
+  <si>
+    <t>Actual:</t>
+  </si>
+  <si>
+    <t>Execution period</t>
+  </si>
+  <si>
+    <t>Workload (in hours)</t>
+  </si>
+  <si>
+    <t>Costs (in EUR)</t>
+  </si>
+  <si>
+    <t>ORDER</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
     <t>Assignee</t>
   </si>
   <si>
-    <t>Workload (in hours)</t>
+    <t>Role</t>
+  </si>
+  <si>
+    <t>Activity</t>
+  </si>
+  <si>
+    <t>Parent</t>
+  </si>
+  <si>
+    <t>Start moment</t>
+  </si>
+  <si>
+    <t>End moment</t>
+  </si>
+  <si>
+    <t>Status</t>
   </si>
   <si>
     <t>Expected</t>
@@ -91,16 +148,349 @@
     <t>Actual</t>
   </si>
   <si>
-    <t>Status</t>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Management</t>
+  </si>
+  <si>
+    <t>Student 1</t>
+  </si>
+  <si>
+    <t>Manager</t>
+  </si>
+  <si>
+    <t>Make plans</t>
+  </si>
+  <si>
+    <t>Realizar el primer reparto de tareas referidas al Requisito Cero.</t>
+  </si>
+  <si>
+    <t>Write report</t>
+  </si>
+  <si>
+    <t>Realizar el chartering report.</t>
+  </si>
+  <si>
+    <t>Initialise repository</t>
+  </si>
+  <si>
+    <t>Inicializar el repositorio en GitHub.</t>
+  </si>
+  <si>
+    <t>Other (Describe)</t>
+  </si>
+  <si>
+    <t>Rellenar el formulario de identificación.</t>
+  </si>
+  <si>
+    <t>Development</t>
+  </si>
+  <si>
+    <t>Developer</t>
+  </si>
+  <si>
+    <t>Create dev. config.</t>
+  </si>
+  <si>
+    <t>Instanciar el proyecto base "Hello-World" como "Acme-Starters-C"</t>
+  </si>
+  <si>
+    <t>Customise the starter</t>
+  </si>
+  <si>
+    <t>Personalizar el proyecto con las tareas  que vienen descritas en la presetación S03.</t>
+  </si>
+  <si>
+    <t>Revision</t>
+  </si>
+  <si>
+    <t>Student 3</t>
+  </si>
+  <si>
+    <t>Tester</t>
+  </si>
+  <si>
+    <t>Check task</t>
+  </si>
+  <si>
+    <t>T0005/D</t>
+  </si>
+  <si>
+    <t>Revisar tarea.</t>
+  </si>
+  <si>
+    <t>Añadir apartados faltantes al chartering report.</t>
+  </si>
+  <si>
+    <t>Actualizar planificación.</t>
+  </si>
+  <si>
+    <t>Actulizar planificación.</t>
+  </si>
+  <si>
+    <t>Implement feature</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Implementar requisito S1/1 sin validaciones personalizadas ni adicionales. </t>
+  </si>
+  <si>
+    <t>Student 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Implementar requisito S4/1 sin validaciones personalizadas ni adicionales. </t>
+  </si>
+  <si>
+    <t>Student 5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Implementar requisito S5/1 sin validaciones personalizadas ni adicionales. </t>
+  </si>
+  <si>
+    <t>Student 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Implementar requisito S2/1 sin validaciones personalizadas ni adicionales. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Implementar requisito S3/1 sin validaciones personalizadas ni adicionales. </t>
+  </si>
+  <si>
+    <t>Modificar chartering report.</t>
+  </si>
+  <si>
+    <t>Make re-plannings</t>
+  </si>
+  <si>
+    <t>Realizar re-planificación</t>
+  </si>
+  <si>
+    <t>Actualizar Acme-Framework a la versión 26.2.0</t>
+  </si>
+  <si>
+    <t>T0018/D</t>
+  </si>
+  <si>
+    <t>T0011/D</t>
+  </si>
+  <si>
+    <t>T0015/D</t>
+  </si>
+  <si>
+    <t>T0012/D</t>
+  </si>
+  <si>
+    <t>T0014/D</t>
+  </si>
+  <si>
+    <t>T0013/D</t>
+  </si>
+  <si>
+    <t>Crear datos de prueba para crear 2 cuentas de administrador.</t>
+  </si>
+  <si>
+    <t>Implementar restricciones esbozadas en el archivo 'Model-CG.ufx'</t>
+  </si>
+  <si>
+    <t>Implementar requisito S1/1 al completo.</t>
+  </si>
+  <si>
+    <t>Implementar requisito S2/1 al completo.</t>
+  </si>
+  <si>
+    <t>Implementar requisito S3/1 al completo.</t>
+  </si>
+  <si>
+    <t>Implementar requisito S4/1 al completo.</t>
+  </si>
+  <si>
+    <t>Implementar requisito S5/1 al completo.</t>
+  </si>
+  <si>
+    <t>T0027/D</t>
+  </si>
+  <si>
+    <t>T0028/D</t>
+  </si>
+  <si>
+    <t>T0033/D</t>
+  </si>
+  <si>
+    <t>T0032/D</t>
+  </si>
+  <si>
+    <t>T0029/D</t>
+  </si>
+  <si>
+    <t>T0031/D</t>
+  </si>
+  <si>
+    <t>T0030/D</t>
+  </si>
+  <si>
+    <t>Modificar tipo Moment por Date en todas las entidades.</t>
+  </si>
+  <si>
+    <t>T0041/D</t>
+  </si>
+  <si>
+    <t>Crear sample y errata data para las entidades del requisito S1/1</t>
+  </si>
+  <si>
+    <t>Crear  sample y errata data para las entidades del requisito S2/1</t>
+  </si>
+  <si>
+    <t>Crear  sample y errata data para las entidades del requisito S3/1</t>
+  </si>
+  <si>
+    <t>Crear  sample y errata data para las entidades del requisito S4/1</t>
+  </si>
+  <si>
+    <t>Completed</t>
+  </si>
+  <si>
+    <t>Crear  sample y errata data para las entidades del requisito S5/1</t>
+  </si>
+  <si>
+    <t>T0047/D</t>
+  </si>
+  <si>
+    <t>T0046/D</t>
+  </si>
+  <si>
+    <t>T0043/D</t>
+  </si>
+  <si>
+    <t>T0045/D</t>
+  </si>
+  <si>
+    <t>T0044/D</t>
+  </si>
+  <si>
+    <t>Actualizar  Acme-Framework a la versión 26.3.0</t>
+  </si>
+  <si>
+    <t>T0053/D</t>
+  </si>
+  <si>
+    <t>Implementar requisito S1/2</t>
+  </si>
+  <si>
+    <t>Implementar requisito S2/2</t>
+  </si>
+  <si>
+    <t>Implementar requisito S3/2</t>
+  </si>
+  <si>
+    <t>Implementar requisito S4/2</t>
+  </si>
+  <si>
+    <t>Implementar requisito S5/2</t>
+  </si>
+  <si>
+    <t>T0059/D</t>
+  </si>
+  <si>
+    <t>T0058/D</t>
+  </si>
+  <si>
+    <t>T0055/D</t>
+  </si>
+  <si>
+    <t>T0057/D</t>
+  </si>
+  <si>
+    <t>T0056/D</t>
+  </si>
+  <si>
+    <t>Implementar requisito S1/3</t>
+  </si>
+  <si>
+    <t>Implementar requisito S2/3</t>
+  </si>
+  <si>
+    <t>Implementar requisito S3/3</t>
+  </si>
+  <si>
+    <t>Implementar requisito S4/3</t>
+  </si>
+  <si>
+    <t>Implementar requisito S5/3</t>
+  </si>
+  <si>
+    <t>T0069/D</t>
+  </si>
+  <si>
+    <t>T0068/D</t>
+  </si>
+  <si>
+    <t>T0065/D</t>
+  </si>
+  <si>
+    <t>T0067/D</t>
+  </si>
+  <si>
+    <t>T0066/D</t>
+  </si>
+  <si>
+    <t>Implementar requisito S1/4</t>
+  </si>
+  <si>
+    <t>Implementar requisito S2/4</t>
+  </si>
+  <si>
+    <t>Implementar requisito S3/4</t>
+  </si>
+  <si>
+    <t>Implementar requisito S4/4</t>
+  </si>
+  <si>
+    <t>Implementar requisito S5/4</t>
+  </si>
+  <si>
+    <t>T0079/D</t>
+  </si>
+  <si>
+    <t>T0078/D</t>
+  </si>
+  <si>
+    <t>T0075/D</t>
+  </si>
+  <si>
+    <t>T0077/D</t>
+  </si>
+  <si>
+    <t>T0076/D</t>
+  </si>
+  <si>
+    <t>Other</t>
+  </si>
+  <si>
+    <t>Operator</t>
+  </si>
+  <si>
+    <t>Package deliverable</t>
+  </si>
+  <si>
+    <t>Realizar entrega del proyecto versión C</t>
+  </si>
+  <si>
+    <t>Deliverable D02</t>
+  </si>
+  <si>
+    <t>Deliverable D03</t>
   </si>
   <si>
     <t>Internal data</t>
   </si>
   <si>
+    <t>This sheet contains internal data that are used elsewhere to perform some checks and computations.  Please, do not modify it al all.</t>
+  </si>
+  <si>
     <t>Prospective assignees</t>
   </si>
   <si>
-    <t>This sheet contains internal data that are used elsewhere to perform some checks and computations.  Please, do not modify it al all.</t>
+    <t>ALL</t>
   </si>
   <si>
     <t>Statuses</t>
@@ -115,63 +505,39 @@
     <t>Finished</t>
   </si>
   <si>
-    <t>Parent</t>
-  </si>
-  <si>
-    <t>ID</t>
-  </si>
-  <si>
-    <t>Make plans</t>
-  </si>
-  <si>
-    <t>Role</t>
+    <t>Moments</t>
+  </si>
+  <si>
+    <t>2100/31/12  23:59:59</t>
   </si>
   <si>
     <t>Roles</t>
   </si>
   <si>
-    <t>Manager</t>
+    <t>Cost</t>
+  </si>
+  <si>
+    <t>Tasks…</t>
+  </si>
+  <si>
+    <t>Student</t>
+  </si>
+  <si>
+    <t>Attend lecture</t>
+  </si>
+  <si>
+    <t>Study and train</t>
+  </si>
+  <si>
+    <t>Attend work meeting</t>
+  </si>
+  <si>
+    <t>Supervise task</t>
   </si>
   <si>
     <t>Analyst</t>
   </si>
   <si>
-    <t>Developer</t>
-  </si>
-  <si>
-    <t>Tester</t>
-  </si>
-  <si>
-    <t>Operator</t>
-  </si>
-  <si>
-    <t>Tasks…</t>
-  </si>
-  <si>
-    <t>Student</t>
-  </si>
-  <si>
-    <t>Attend lecture</t>
-  </si>
-  <si>
-    <t>Study and train</t>
-  </si>
-  <si>
-    <t>Other (Describe)</t>
-  </si>
-  <si>
-    <t>Make re-plannings</t>
-  </si>
-  <si>
-    <t>Initialise repository</t>
-  </si>
-  <si>
-    <t>Supervise task</t>
-  </si>
-  <si>
-    <t>Write report</t>
-  </si>
-  <si>
     <t>Elicit requirements</t>
   </si>
   <si>
@@ -181,12 +547,6 @@
     <t>Create domain model</t>
   </si>
   <si>
-    <t>Customise the starter</t>
-  </si>
-  <si>
-    <t>Implement feature</t>
-  </si>
-  <si>
     <t>Test feature informally</t>
   </si>
   <si>
@@ -199,7 +559,7 @@
     <t>Test performance formally</t>
   </si>
   <si>
-    <t>Package deliverable</t>
+    <t>Prepare dep. platf.</t>
   </si>
   <si>
     <t>Upload deliverable</t>
@@ -211,247 +571,25 @@
     <t>Keep application running</t>
   </si>
   <si>
-    <t>Attend work meeting</t>
-  </si>
-  <si>
-    <t>Execution period</t>
-  </si>
-  <si>
-    <t>Start moment</t>
-  </si>
-  <si>
-    <t>End moment</t>
-  </si>
-  <si>
-    <t>Moments</t>
-  </si>
-  <si>
-    <t>2100/31/12  23:59:59</t>
-  </si>
-  <si>
-    <t>Other</t>
-  </si>
-  <si>
-    <t>Cost</t>
-  </si>
-  <si>
-    <t>Costs (in EUR)</t>
-  </si>
-  <si>
-    <t>Type</t>
-  </si>
-  <si>
     <t>Task types</t>
   </si>
   <si>
-    <t>Revision</t>
-  </si>
-  <si>
-    <t>Development</t>
-  </si>
-  <si>
     <t>Key</t>
   </si>
   <si>
-    <t>Management</t>
+    <t>M</t>
+  </si>
+  <si>
+    <t>D</t>
   </si>
   <si>
     <t>QA</t>
   </si>
   <si>
-    <t>ORDER</t>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>Costs</t>
-  </si>
-  <si>
-    <t>Expected:</t>
-  </si>
-  <si>
-    <t>Actual:</t>
-  </si>
-  <si>
     <t>R</t>
   </si>
   <si>
-    <t>D</t>
-  </si>
-  <si>
     <t>O</t>
-  </si>
-  <si>
-    <t>M</t>
-  </si>
-  <si>
-    <t>Use this form to document the tasks that you perform in your projects.  Please, review the colour code in the "Abstract" sheet.  In the exceptional case that you need to perform more tasks than expected, add them at the end.</t>
-  </si>
-  <si>
-    <t>Activity</t>
-  </si>
-  <si>
-    <t>ALL</t>
-  </si>
-  <si>
-    <t>Copyright</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Help comments</t>
-  </si>
-  <si>
-    <t>Student 1</t>
-  </si>
-  <si>
-    <t>Student 2</t>
-  </si>
-  <si>
-    <t>Student 3</t>
-  </si>
-  <si>
-    <t>Student 4</t>
-  </si>
-  <si>
-    <t>Student 5</t>
-  </si>
-  <si>
-    <t>Deliverable D02</t>
-  </si>
-  <si>
-    <t>Deliverable D03</t>
-  </si>
-  <si>
-    <t>Check task</t>
-  </si>
-  <si>
-    <t>Prepare dep. platf.</t>
-  </si>
-  <si>
-    <t>Create dev. config.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Warning and error messages.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Data computed automatically.  Do not change them.</t>
-  </si>
-  <si>
-    <t>Realizar el chartering report.</t>
-  </si>
-  <si>
-    <t>Inicializar el repositorio en GitHub.</t>
-  </si>
-  <si>
-    <t>Instanciar el proyecto base "Hello-World" como "Acme-Starters-C"</t>
-  </si>
-  <si>
-    <t>Personalizar el proyecto con las tareas  que vienen descritas en la presetación S03.</t>
-  </si>
-  <si>
-    <t>T0005/D</t>
-  </si>
-  <si>
-    <t>Revisar tarea.</t>
-  </si>
-  <si>
-    <t>Realizar el primer reparto de tareas referidas al Requisito Cero.</t>
-  </si>
-  <si>
-    <t>Rellenar el formulario de identificación.</t>
-  </si>
-  <si>
-    <t>Actualizar planificación.</t>
-  </si>
-  <si>
-    <t>Añadir apartados faltantes al chartering report.</t>
-  </si>
-  <si>
-    <t>Actulizar planificación.</t>
-  </si>
-  <si>
-    <t>Modificar chartering report.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Implementar requisito S1/1 sin validaciones personalizadas ni adicionales. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Implementar requisito S4/1 sin validaciones personalizadas ni adicionales. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Implementar requisito S5/1 sin validaciones personalizadas ni adicionales. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Implementar requisito S2/1 sin validaciones personalizadas ni adicionales. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Implementar requisito S3/1 sin validaciones personalizadas ni adicionales. </t>
-  </si>
-  <si>
-    <t>Realizar re-planificación</t>
-  </si>
-  <si>
-    <t>Actualizar Acme-Framework a la versión 26.2.0</t>
-  </si>
-  <si>
-    <t>T0018/D</t>
-  </si>
-  <si>
-    <t>T0011/D</t>
-  </si>
-  <si>
-    <t>T0015/D</t>
-  </si>
-  <si>
-    <t>T0012/D</t>
-  </si>
-  <si>
-    <t>T0014/D</t>
-  </si>
-  <si>
-    <t>T0013/D</t>
-  </si>
-  <si>
-    <t>Crear datos de prueba para crear 2 cuentas de administrador.</t>
-  </si>
-  <si>
-    <t>Implementar restricciones esbozadas en el archivo 'Model-CG.ufx'</t>
-  </si>
-  <si>
-    <t>T0028/D</t>
-  </si>
-  <si>
-    <t>T0027/D</t>
-  </si>
-  <si>
-    <t>T0029/D</t>
-  </si>
-  <si>
-    <t>T0033/D</t>
-  </si>
-  <si>
-    <t>T0032/D</t>
-  </si>
-  <si>
-    <t>T0031/D</t>
-  </si>
-  <si>
-    <t>T0030/D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Implementar requisito S1/1 con validaciones personalizadas y adicionales. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Implementar requisito S2/1 con validaciones personalizadas y adicionales. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Implementar requisito S3/1 con validaciones personalizadas y adicionales. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Implementar requisito S4/1 con validaciones personalizadas y adicionales. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Implementar requisito S5/1 con validaciones personalizadas y adicionales. </t>
   </si>
 </sst>
 </file>
@@ -718,7 +856,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -828,23 +966,24 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="2" fontId="2" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1158,6 +1297,10 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1484,118 +1627,118 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B2" s="55" t="s">
-        <v>78</v>
-      </c>
-      <c r="C2" s="55"/>
-      <c r="D2" s="55"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="55"/>
-      <c r="G2" s="55"/>
-      <c r="H2" s="55"/>
-      <c r="I2" s="55"/>
-      <c r="J2" s="55"/>
+      <c r="B2" s="56" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="56"/>
+      <c r="I2" s="56"/>
+      <c r="J2" s="56"/>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B4" s="53" t="s">
-        <v>2</v>
-      </c>
-      <c r="C4" s="54"/>
-      <c r="D4" s="54"/>
-      <c r="E4" s="54"/>
-      <c r="F4" s="54"/>
-      <c r="G4" s="54"/>
-      <c r="H4" s="54"/>
-      <c r="I4" s="54"/>
-      <c r="J4" s="54"/>
+      <c r="B4" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="58"/>
+      <c r="D4" s="58"/>
+      <c r="E4" s="58"/>
+      <c r="F4" s="58"/>
+      <c r="G4" s="58"/>
+      <c r="H4" s="58"/>
+      <c r="I4" s="58"/>
+      <c r="J4" s="58"/>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B5" s="54"/>
-      <c r="C5" s="54"/>
-      <c r="D5" s="54"/>
-      <c r="E5" s="54"/>
-      <c r="F5" s="54"/>
-      <c r="G5" s="54"/>
-      <c r="H5" s="54"/>
-      <c r="I5" s="54"/>
-      <c r="J5" s="54"/>
+      <c r="B5" s="58"/>
+      <c r="C5" s="58"/>
+      <c r="D5" s="58"/>
+      <c r="E5" s="58"/>
+      <c r="F5" s="58"/>
+      <c r="G5" s="58"/>
+      <c r="H5" s="58"/>
+      <c r="I5" s="58"/>
+      <c r="J5" s="58"/>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B6" s="54"/>
-      <c r="C6" s="54"/>
-      <c r="D6" s="54"/>
-      <c r="E6" s="54"/>
-      <c r="F6" s="54"/>
-      <c r="G6" s="54"/>
-      <c r="H6" s="54"/>
-      <c r="I6" s="54"/>
-      <c r="J6" s="54"/>
+      <c r="B6" s="58"/>
+      <c r="C6" s="58"/>
+      <c r="D6" s="58"/>
+      <c r="E6" s="58"/>
+      <c r="F6" s="58"/>
+      <c r="G6" s="58"/>
+      <c r="H6" s="58"/>
+      <c r="I6" s="58"/>
+      <c r="J6" s="58"/>
     </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B7" s="54"/>
-      <c r="C7" s="54"/>
-      <c r="D7" s="54"/>
-      <c r="E7" s="54"/>
-      <c r="F7" s="54"/>
-      <c r="G7" s="54"/>
-      <c r="H7" s="54"/>
-      <c r="I7" s="54"/>
-      <c r="J7" s="54"/>
+      <c r="B7" s="58"/>
+      <c r="C7" s="58"/>
+      <c r="D7" s="58"/>
+      <c r="E7" s="58"/>
+      <c r="F7" s="58"/>
+      <c r="G7" s="58"/>
+      <c r="H7" s="58"/>
+      <c r="I7" s="58"/>
+      <c r="J7" s="58"/>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B8" s="54"/>
-      <c r="C8" s="54"/>
-      <c r="D8" s="54"/>
-      <c r="E8" s="54"/>
-      <c r="F8" s="54"/>
-      <c r="G8" s="54"/>
-      <c r="H8" s="54"/>
-      <c r="I8" s="54"/>
-      <c r="J8" s="54"/>
+      <c r="B8" s="58"/>
+      <c r="C8" s="58"/>
+      <c r="D8" s="58"/>
+      <c r="E8" s="58"/>
+      <c r="F8" s="58"/>
+      <c r="G8" s="58"/>
+      <c r="H8" s="58"/>
+      <c r="I8" s="58"/>
+      <c r="J8" s="58"/>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B9" s="54"/>
-      <c r="C9" s="54"/>
-      <c r="D9" s="54"/>
-      <c r="E9" s="54"/>
-      <c r="F9" s="54"/>
-      <c r="G9" s="54"/>
-      <c r="H9" s="54"/>
-      <c r="I9" s="54"/>
-      <c r="J9" s="54"/>
+      <c r="B9" s="58"/>
+      <c r="C9" s="58"/>
+      <c r="D9" s="58"/>
+      <c r="E9" s="58"/>
+      <c r="F9" s="58"/>
+      <c r="G9" s="58"/>
+      <c r="H9" s="58"/>
+      <c r="I9" s="58"/>
+      <c r="J9" s="58"/>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B10" s="54"/>
-      <c r="C10" s="54"/>
-      <c r="D10" s="54"/>
-      <c r="E10" s="54"/>
-      <c r="F10" s="54"/>
-      <c r="G10" s="54"/>
-      <c r="H10" s="54"/>
-      <c r="I10" s="54"/>
-      <c r="J10" s="54"/>
+      <c r="B10" s="58"/>
+      <c r="C10" s="58"/>
+      <c r="D10" s="58"/>
+      <c r="E10" s="58"/>
+      <c r="F10" s="58"/>
+      <c r="G10" s="58"/>
+      <c r="H10" s="58"/>
+      <c r="I10" s="58"/>
+      <c r="J10" s="58"/>
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B11" s="54"/>
-      <c r="C11" s="54"/>
-      <c r="D11" s="54"/>
-      <c r="E11" s="54"/>
-      <c r="F11" s="54"/>
-      <c r="G11" s="54"/>
-      <c r="H11" s="54"/>
-      <c r="I11" s="54"/>
-      <c r="J11" s="54"/>
+      <c r="B11" s="58"/>
+      <c r="C11" s="58"/>
+      <c r="D11" s="58"/>
+      <c r="E11" s="58"/>
+      <c r="F11" s="58"/>
+      <c r="G11" s="58"/>
+      <c r="H11" s="58"/>
+      <c r="I11" s="58"/>
+      <c r="J11" s="58"/>
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B12" s="54"/>
-      <c r="C12" s="54"/>
-      <c r="D12" s="54"/>
-      <c r="E12" s="54"/>
-      <c r="F12" s="54"/>
-      <c r="G12" s="54"/>
-      <c r="H12" s="54"/>
-      <c r="I12" s="54"/>
-      <c r="J12" s="54"/>
+      <c r="B12" s="58"/>
+      <c r="C12" s="58"/>
+      <c r="D12" s="58"/>
+      <c r="E12" s="58"/>
+      <c r="F12" s="58"/>
+      <c r="G12" s="58"/>
+      <c r="H12" s="58"/>
+      <c r="I12" s="58"/>
+      <c r="J12" s="58"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1610,20 +1753,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BB35E99-EEE5-419C-812A-054E20454F46}">
   <dimension ref="B2:J12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="2" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B2" s="55" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" s="55"/>
-      <c r="D2" s="55"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="55"/>
-      <c r="G2" s="55"/>
-      <c r="H2" s="55"/>
-      <c r="I2" s="55"/>
-      <c r="J2" s="55"/>
+      <c r="B2" s="56" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="56"/>
+      <c r="I2" s="56"/>
+      <c r="J2" s="56"/>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B3" s="2"/>
@@ -1637,39 +1780,39 @@
       <c r="J3" s="1"/>
     </row>
     <row r="4" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B4" s="53" t="s">
+      <c r="B4" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="53"/>
-      <c r="D4" s="53"/>
-      <c r="E4" s="53"/>
-      <c r="F4" s="53"/>
-      <c r="G4" s="53"/>
-      <c r="H4" s="53"/>
-      <c r="I4" s="53"/>
-      <c r="J4" s="53"/>
+      <c r="C4" s="57"/>
+      <c r="D4" s="57"/>
+      <c r="E4" s="57"/>
+      <c r="F4" s="57"/>
+      <c r="G4" s="57"/>
+      <c r="H4" s="57"/>
+      <c r="I4" s="57"/>
+      <c r="J4" s="57"/>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B5" s="53"/>
-      <c r="C5" s="53"/>
-      <c r="D5" s="53"/>
-      <c r="E5" s="53"/>
-      <c r="F5" s="53"/>
-      <c r="G5" s="53"/>
-      <c r="H5" s="53"/>
-      <c r="I5" s="53"/>
-      <c r="J5" s="53"/>
+      <c r="B5" s="57"/>
+      <c r="C5" s="57"/>
+      <c r="D5" s="57"/>
+      <c r="E5" s="57"/>
+      <c r="F5" s="57"/>
+      <c r="G5" s="57"/>
+      <c r="H5" s="57"/>
+      <c r="I5" s="57"/>
+      <c r="J5" s="57"/>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B6" s="53"/>
-      <c r="C6" s="53"/>
-      <c r="D6" s="53"/>
-      <c r="E6" s="53"/>
-      <c r="F6" s="53"/>
-      <c r="G6" s="53"/>
-      <c r="H6" s="53"/>
-      <c r="I6" s="53"/>
-      <c r="J6" s="53"/>
+      <c r="B6" s="57"/>
+      <c r="C6" s="57"/>
+      <c r="D6" s="57"/>
+      <c r="E6" s="57"/>
+      <c r="F6" s="57"/>
+      <c r="G6" s="57"/>
+      <c r="H6" s="57"/>
+      <c r="I6" s="57"/>
+      <c r="J6" s="57"/>
     </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B7" s="1"/>
@@ -1685,7 +1828,7 @@
     <row r="8" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B8" s="39"/>
       <c r="C8" s="40" t="s">
-        <v>79</v>
+        <v>4</v>
       </c>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
@@ -1697,34 +1840,34 @@
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B9" s="4"/>
-      <c r="C9" s="56" t="s">
-        <v>0</v>
-      </c>
-      <c r="D9" s="56"/>
-      <c r="E9" s="56"/>
-      <c r="F9" s="56"/>
-      <c r="G9" s="56"/>
-      <c r="H9" s="56"/>
-      <c r="I9" s="56"/>
-      <c r="J9" s="56"/>
+      <c r="C9" s="59" t="s">
+        <v>5</v>
+      </c>
+      <c r="D9" s="59"/>
+      <c r="E9" s="59"/>
+      <c r="F9" s="59"/>
+      <c r="G9" s="59"/>
+      <c r="H9" s="59"/>
+      <c r="I9" s="59"/>
+      <c r="J9" s="59"/>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B10" s="49"/>
-      <c r="C10" s="56" t="s">
-        <v>90</v>
-      </c>
-      <c r="D10" s="56"/>
-      <c r="E10" s="56"/>
-      <c r="F10" s="56"/>
-      <c r="G10" s="56"/>
-      <c r="H10" s="56"/>
-      <c r="I10" s="56"/>
-      <c r="J10" s="56"/>
+      <c r="C10" s="59" t="s">
+        <v>6</v>
+      </c>
+      <c r="D10" s="59"/>
+      <c r="E10" s="59"/>
+      <c r="F10" s="59"/>
+      <c r="G10" s="59"/>
+      <c r="H10" s="59"/>
+      <c r="I10" s="59"/>
+      <c r="J10" s="59"/>
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B11" s="50"/>
       <c r="C11" s="48" t="s">
-        <v>91</v>
+        <v>7</v>
       </c>
       <c r="D11" s="48"/>
       <c r="E11" s="48"/>
@@ -1736,16 +1879,16 @@
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B12" s="3"/>
-      <c r="C12" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="D12" s="56"/>
-      <c r="E12" s="56"/>
-      <c r="F12" s="56"/>
-      <c r="G12" s="56"/>
-      <c r="H12" s="56"/>
-      <c r="I12" s="56"/>
-      <c r="J12" s="56"/>
+      <c r="C12" s="59" t="s">
+        <v>8</v>
+      </c>
+      <c r="D12" s="59"/>
+      <c r="E12" s="59"/>
+      <c r="F12" s="59"/>
+      <c r="G12" s="59"/>
+      <c r="H12" s="59"/>
+      <c r="I12" s="59"/>
+      <c r="J12" s="59"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -1761,48 +1904,48 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34CF3CD5-8D08-494F-856F-AF84E30F468A}">
-  <dimension ref="B2:P112"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="B2:P113"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="3" max="15" width="18.86328125" customWidth="1"/>
-    <col min="16" max="16" width="64.53125" customWidth="1"/>
+    <col min="16" max="16" width="64.59765625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:16" x14ac:dyDescent="0.45">
-      <c r="C2" s="55" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" s="55"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="55"/>
-      <c r="G2" s="55"/>
-      <c r="H2" s="55"/>
-      <c r="I2" s="55"/>
-      <c r="J2" s="55"/>
-      <c r="K2" s="55"/>
-      <c r="L2" s="55"/>
-      <c r="M2" s="55"/>
-      <c r="N2" s="55"/>
-      <c r="O2" s="55"/>
-      <c r="P2" s="55"/>
+      <c r="C2" s="56" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="56"/>
+      <c r="I2" s="56"/>
+      <c r="J2" s="56"/>
+      <c r="K2" s="56"/>
+      <c r="L2" s="56"/>
+      <c r="M2" s="56"/>
+      <c r="N2" s="56"/>
+      <c r="O2" s="56"/>
+      <c r="P2" s="56"/>
     </row>
     <row r="4" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="C4" s="53" t="s">
-        <v>75</v>
-      </c>
-      <c r="D4" s="53"/>
-      <c r="E4" s="53"/>
-      <c r="F4" s="53"/>
-      <c r="G4" s="53"/>
-      <c r="H4" s="53"/>
-      <c r="I4" s="53"/>
-      <c r="J4" s="53"/>
-      <c r="K4" s="53"/>
-      <c r="L4" s="53"/>
-      <c r="M4" s="53"/>
-      <c r="N4" s="53"/>
-      <c r="O4" s="53"/>
-      <c r="P4" s="53"/>
+      <c r="C4" s="57" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="57"/>
+      <c r="E4" s="57"/>
+      <c r="F4" s="57"/>
+      <c r="G4" s="57"/>
+      <c r="H4" s="57"/>
+      <c r="I4" s="57"/>
+      <c r="J4" s="57"/>
+      <c r="K4" s="57"/>
+      <c r="L4" s="57"/>
+      <c r="M4" s="57"/>
+      <c r="N4" s="57"/>
+      <c r="O4" s="57"/>
+      <c r="P4" s="57"/>
     </row>
     <row r="5" spans="2:16" x14ac:dyDescent="0.45">
       <c r="C5" s="5"/>
@@ -1821,15 +1964,15 @@
       <c r="P5" s="5"/>
     </row>
     <row r="6" spans="2:16" x14ac:dyDescent="0.45">
-      <c r="C6" s="57" t="s">
-        <v>68</v>
+      <c r="C6" s="54" t="s">
+        <v>11</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>69</v>
+        <v>12</v>
       </c>
       <c r="E6" s="35">
-        <f>SUM(N12:N112)</f>
-        <v>1398.3333333333335</v>
+        <f>SUM(N12:N113)</f>
+        <v>3411.0666666666671</v>
       </c>
       <c r="F6" s="5"/>
       <c r="G6" s="5"/>
@@ -1844,13 +1987,13 @@
       <c r="P6" s="5"/>
     </row>
     <row r="7" spans="2:16" x14ac:dyDescent="0.45">
-      <c r="C7" s="57"/>
+      <c r="C7" s="54"/>
       <c r="D7" s="11" t="s">
-        <v>70</v>
+        <v>13</v>
       </c>
       <c r="E7" s="36">
-        <f>SUM(O12:O112)</f>
-        <v>980.83333333333337</v>
+        <f>SUM(O12:O113)</f>
+        <v>4130.333333333333</v>
       </c>
       <c r="J7" s="37"/>
     </row>
@@ -1862,66 +2005,66 @@
       <c r="F9" s="7"/>
       <c r="G9" s="7"/>
       <c r="H9" s="7"/>
-      <c r="I9" s="58" t="s">
-        <v>51</v>
-      </c>
-      <c r="J9" s="58"/>
+      <c r="I9" s="55" t="s">
+        <v>14</v>
+      </c>
+      <c r="J9" s="55"/>
       <c r="K9" s="7"/>
-      <c r="L9" s="58" t="s">
-        <v>7</v>
-      </c>
-      <c r="M9" s="58"/>
-      <c r="N9" s="58" t="s">
-        <v>58</v>
-      </c>
-      <c r="O9" s="58"/>
+      <c r="L9" s="55" t="s">
+        <v>15</v>
+      </c>
+      <c r="M9" s="55"/>
+      <c r="N9" s="55" t="s">
+        <v>16</v>
+      </c>
+      <c r="O9" s="55"/>
       <c r="P9" s="7"/>
     </row>
     <row r="10" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B10" s="8" t="s">
-        <v>66</v>
+        <v>17</v>
       </c>
       <c r="C10" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D10" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="D10" s="9" t="s">
-        <v>59</v>
-      </c>
       <c r="E10" s="9" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="F10" s="9" t="s">
         <v>21</v>
       </c>
       <c r="G10" s="9" t="s">
-        <v>76</v>
+        <v>22</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I10" s="38" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="J10" s="38" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="K10" s="9" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="L10" s="38" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="M10" s="38" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="N10" s="38" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="O10" s="38" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="P10" s="9" t="s">
-        <v>67</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
@@ -1933,16 +2076,16 @@
         <v>T0001/M</v>
       </c>
       <c r="D11" s="44" t="s">
-        <v>64</v>
+        <v>30</v>
       </c>
       <c r="E11" s="43" t="s">
-        <v>80</v>
+        <v>31</v>
       </c>
       <c r="F11" s="43" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="G11" s="44" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="H11" s="43"/>
       <c r="I11" s="46">
@@ -1970,7 +2113,7 @@
         <v>75</v>
       </c>
       <c r="P11" s="44" t="s">
-        <v>98</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
@@ -1982,16 +2125,16 @@
         <v>T0002/M</v>
       </c>
       <c r="D12" s="44" t="s">
-        <v>64</v>
+        <v>30</v>
       </c>
       <c r="E12" s="43" t="s">
-        <v>80</v>
+        <v>31</v>
       </c>
       <c r="F12" s="43" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="G12" s="44" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H12" s="43"/>
       <c r="I12" s="46">
@@ -2019,7 +2162,7 @@
         <v>200</v>
       </c>
       <c r="P12" s="44" t="s">
-        <v>92</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
@@ -2031,16 +2174,16 @@
         <v>T0003/M</v>
       </c>
       <c r="D13" s="44" t="s">
-        <v>64</v>
+        <v>30</v>
       </c>
       <c r="E13" s="43" t="s">
-        <v>80</v>
+        <v>31</v>
       </c>
       <c r="F13" s="43" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="G13" s="44" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="H13" s="43"/>
       <c r="I13" s="46">
@@ -2068,7 +2211,7 @@
         <v>12.5</v>
       </c>
       <c r="P13" s="44" t="s">
-        <v>93</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
@@ -2080,16 +2223,16 @@
         <v>T0004/M</v>
       </c>
       <c r="D14" s="44" t="s">
-        <v>64</v>
+        <v>30</v>
       </c>
       <c r="E14" s="43" t="s">
-        <v>80</v>
+        <v>31</v>
       </c>
       <c r="F14" s="43" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="G14" s="44" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="H14" s="43"/>
       <c r="I14" s="46">
@@ -2117,7 +2260,7 @@
         <v>12.5</v>
       </c>
       <c r="P14" s="44" t="s">
-        <v>99</v>
+        <v>40</v>
       </c>
     </row>
     <row r="15" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
@@ -2129,16 +2272,16 @@
         <v>T0005/D</v>
       </c>
       <c r="D15" s="44" t="s">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="E15" s="43" t="s">
-        <v>80</v>
+        <v>31</v>
       </c>
       <c r="F15" s="43" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="G15" s="44" t="s">
-        <v>89</v>
+        <v>43</v>
       </c>
       <c r="H15" s="43"/>
       <c r="I15" s="46">
@@ -2166,7 +2309,7 @@
         <v>12.5</v>
       </c>
       <c r="P15" s="44" t="s">
-        <v>94</v>
+        <v>44</v>
       </c>
     </row>
     <row r="16" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
@@ -2178,16 +2321,16 @@
         <v>T0006/D</v>
       </c>
       <c r="D16" s="44" t="s">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="E16" s="43" t="s">
-        <v>80</v>
+        <v>31</v>
       </c>
       <c r="F16" s="43" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="G16" s="44" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="H16" s="43"/>
       <c r="I16" s="46">
@@ -2215,7 +2358,7 @@
         <v>50</v>
       </c>
       <c r="P16" s="44" t="s">
-        <v>95</v>
+        <v>46</v>
       </c>
     </row>
     <row r="17" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
@@ -2227,19 +2370,19 @@
         <v>T0007/R/T0005/D</v>
       </c>
       <c r="D17" s="44" t="s">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="E17" s="43" t="s">
-        <v>82</v>
+        <v>48</v>
       </c>
       <c r="F17" s="43" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="G17" s="44" t="s">
-        <v>87</v>
+        <v>50</v>
       </c>
       <c r="H17" s="43" t="s">
-        <v>96</v>
+        <v>51</v>
       </c>
       <c r="I17" s="46">
         <v>46061.604166666664</v>
@@ -2266,7 +2409,7 @@
         <v>7.5</v>
       </c>
       <c r="P17" s="44" t="s">
-        <v>97</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
@@ -2278,16 +2421,16 @@
         <v>T0008/M</v>
       </c>
       <c r="D18" s="44" t="s">
-        <v>64</v>
+        <v>30</v>
       </c>
       <c r="E18" s="43" t="s">
-        <v>80</v>
+        <v>31</v>
       </c>
       <c r="F18" s="43" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="G18" s="44" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H18" s="43"/>
       <c r="I18" s="46">
@@ -2315,7 +2458,7 @@
         <v>62.5</v>
       </c>
       <c r="P18" s="44" t="s">
-        <v>101</v>
+        <v>53</v>
       </c>
     </row>
     <row r="19" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
@@ -2327,16 +2470,16 @@
         <v>T0009/M</v>
       </c>
       <c r="D19" s="44" t="s">
-        <v>64</v>
+        <v>30</v>
       </c>
       <c r="E19" s="43" t="s">
-        <v>80</v>
+        <v>31</v>
       </c>
       <c r="F19" s="43" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="G19" s="44" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="H19" s="43"/>
       <c r="I19" s="46">
@@ -2364,7 +2507,7 @@
         <v>4.1666666666666661</v>
       </c>
       <c r="P19" s="44" t="s">
-        <v>100</v>
+        <v>54</v>
       </c>
     </row>
     <row r="20" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
@@ -2376,16 +2519,16 @@
         <v>T0010/M</v>
       </c>
       <c r="D20" s="44" t="s">
-        <v>64</v>
+        <v>30</v>
       </c>
       <c r="E20" s="43" t="s">
-        <v>80</v>
+        <v>31</v>
       </c>
       <c r="F20" s="43" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="G20" s="44" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="H20" s="43"/>
       <c r="I20" s="46">
@@ -2413,7 +2556,7 @@
         <v>8.3333333333333321</v>
       </c>
       <c r="P20" s="44" t="s">
-        <v>102</v>
+        <v>55</v>
       </c>
     </row>
     <row r="21" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
@@ -2425,16 +2568,16 @@
         <v>T0011/D</v>
       </c>
       <c r="D21" s="44" t="s">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="E21" s="43" t="s">
-        <v>80</v>
+        <v>31</v>
       </c>
       <c r="F21" s="43" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="G21" s="44" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="H21" s="43"/>
       <c r="I21" s="46">
@@ -2462,7 +2605,7 @@
         <v>75</v>
       </c>
       <c r="P21" s="44" t="s">
-        <v>104</v>
+        <v>57</v>
       </c>
     </row>
     <row r="22" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
@@ -2474,16 +2617,16 @@
         <v>T0012/D</v>
       </c>
       <c r="D22" s="44" t="s">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="E22" s="43" t="s">
-        <v>83</v>
+        <v>58</v>
       </c>
       <c r="F22" s="43" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="G22" s="44" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="H22" s="43"/>
       <c r="I22" s="46">
@@ -2511,7 +2654,7 @@
         <v>75</v>
       </c>
       <c r="P22" s="44" t="s">
-        <v>105</v>
+        <v>59</v>
       </c>
     </row>
     <row r="23" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
@@ -2523,16 +2666,16 @@
         <v>T0013/D</v>
       </c>
       <c r="D23" s="44" t="s">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="E23" s="43" t="s">
-        <v>84</v>
+        <v>60</v>
       </c>
       <c r="F23" s="43" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="G23" s="44" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="H23" s="43"/>
       <c r="I23" s="46">
@@ -2560,7 +2703,7 @@
         <v>75</v>
       </c>
       <c r="P23" s="44" t="s">
-        <v>106</v>
+        <v>61</v>
       </c>
     </row>
     <row r="24" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
@@ -2572,16 +2715,16 @@
         <v>T0014/D</v>
       </c>
       <c r="D24" s="44" t="s">
+        <v>41</v>
+      </c>
+      <c r="E24" s="43" t="s">
         <v>62</v>
       </c>
-      <c r="E24" s="43" t="s">
-        <v>81</v>
-      </c>
       <c r="F24" s="43" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="G24" s="44" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="H24" s="43"/>
       <c r="I24" s="46">
@@ -2609,7 +2752,7 @@
         <v>75</v>
       </c>
       <c r="P24" s="44" t="s">
-        <v>107</v>
+        <v>63</v>
       </c>
     </row>
     <row r="25" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
@@ -2621,16 +2764,16 @@
         <v>T0015/D</v>
       </c>
       <c r="D25" s="44" t="s">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="E25" s="43" t="s">
-        <v>82</v>
+        <v>48</v>
       </c>
       <c r="F25" s="43" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="G25" s="44" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="H25" s="43"/>
       <c r="I25" s="46">
@@ -2658,7 +2801,7 @@
         <v>75</v>
       </c>
       <c r="P25" s="44" t="s">
-        <v>108</v>
+        <v>64</v>
       </c>
     </row>
     <row r="26" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
@@ -2670,16 +2813,16 @@
         <v>T0016/M</v>
       </c>
       <c r="D26" s="44" t="s">
-        <v>64</v>
+        <v>30</v>
       </c>
       <c r="E26" s="43" t="s">
-        <v>80</v>
+        <v>31</v>
       </c>
       <c r="F26" s="43" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="G26" s="44" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H26" s="43"/>
       <c r="I26" s="46">
@@ -2707,7 +2850,7 @@
         <v>125</v>
       </c>
       <c r="P26" s="44" t="s">
-        <v>103</v>
+        <v>65</v>
       </c>
     </row>
     <row r="27" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
@@ -2719,16 +2862,16 @@
         <v>T0017/M</v>
       </c>
       <c r="D27" s="44" t="s">
-        <v>64</v>
+        <v>30</v>
       </c>
       <c r="E27" s="43" t="s">
-        <v>80</v>
+        <v>31</v>
       </c>
       <c r="F27" s="43" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="G27" s="44" t="s">
-        <v>33</v>
+        <v>66</v>
       </c>
       <c r="H27" s="43"/>
       <c r="I27" s="46">
@@ -2756,7 +2899,7 @@
         <v>8.3333333333333321</v>
       </c>
       <c r="P27" s="44" t="s">
-        <v>109</v>
+        <v>67</v>
       </c>
     </row>
     <row r="28" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
@@ -2768,16 +2911,16 @@
         <v>T0018/D</v>
       </c>
       <c r="D28" s="44" t="s">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="E28" s="43" t="s">
-        <v>80</v>
+        <v>31</v>
       </c>
       <c r="F28" s="43" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="G28" s="44" t="s">
-        <v>89</v>
+        <v>43</v>
       </c>
       <c r="H28" s="43"/>
       <c r="I28" s="46">
@@ -2805,7 +2948,7 @@
         <v>16.666666666666664</v>
       </c>
       <c r="P28" s="44" t="s">
-        <v>110</v>
+        <v>68</v>
       </c>
     </row>
     <row r="29" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
@@ -2817,16 +2960,16 @@
         <v>T0019/M</v>
       </c>
       <c r="D29" s="44" t="s">
-        <v>64</v>
+        <v>30</v>
       </c>
       <c r="E29" s="43" t="s">
-        <v>80</v>
+        <v>31</v>
       </c>
       <c r="F29" s="43" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="G29" s="44" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="H29" s="43"/>
       <c r="I29" s="46">
@@ -2854,7 +2997,7 @@
         <v>8.3333333333333321</v>
       </c>
       <c r="P29" s="44" t="s">
-        <v>102</v>
+        <v>55</v>
       </c>
     </row>
     <row r="30" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
@@ -2866,19 +3009,19 @@
         <v>T0020/R/T0018/D</v>
       </c>
       <c r="D30" s="44" t="s">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="E30" s="43" t="s">
-        <v>82</v>
+        <v>48</v>
       </c>
       <c r="F30" s="43" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="G30" s="44" t="s">
-        <v>87</v>
+        <v>50</v>
       </c>
       <c r="H30" s="43" t="s">
-        <v>111</v>
+        <v>69</v>
       </c>
       <c r="I30" s="46">
         <v>46066.5</v>
@@ -2905,7 +3048,7 @@
         <v>5</v>
       </c>
       <c r="P30" s="44" t="s">
-        <v>97</v>
+        <v>52</v>
       </c>
     </row>
     <row r="31" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
@@ -2917,19 +3060,19 @@
         <v>T0021/R/T0011/D</v>
       </c>
       <c r="D31" s="44" t="s">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="E31" s="43" t="s">
-        <v>82</v>
+        <v>48</v>
       </c>
       <c r="F31" s="43" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="G31" s="44" t="s">
-        <v>87</v>
+        <v>50</v>
       </c>
       <c r="H31" s="43" t="s">
-        <v>112</v>
+        <v>70</v>
       </c>
       <c r="I31" s="46">
         <v>46067.708333333336</v>
@@ -2956,7 +3099,7 @@
         <v>30</v>
       </c>
       <c r="P31" s="44" t="s">
-        <v>97</v>
+        <v>52</v>
       </c>
     </row>
     <row r="32" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
@@ -2968,19 +3111,19 @@
         <v>T0022/R/T0015/D</v>
       </c>
       <c r="D32" s="44" t="s">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="E32" s="43" t="s">
-        <v>83</v>
+        <v>58</v>
       </c>
       <c r="F32" s="43" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="G32" s="44" t="s">
-        <v>87</v>
+        <v>50</v>
       </c>
       <c r="H32" s="43" t="s">
-        <v>113</v>
+        <v>71</v>
       </c>
       <c r="I32" s="46">
         <v>46068.541666666664</v>
@@ -3007,7 +3150,7 @@
         <v>5</v>
       </c>
       <c r="P32" s="44" t="s">
-        <v>97</v>
+        <v>52</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
@@ -3019,19 +3162,19 @@
         <v>T0023/R/T0012/D</v>
       </c>
       <c r="D33" s="44" t="s">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="E33" s="43" t="s">
-        <v>80</v>
+        <v>31</v>
       </c>
       <c r="F33" s="43" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="G33" s="44" t="s">
-        <v>87</v>
+        <v>50</v>
       </c>
       <c r="H33" s="43" t="s">
-        <v>114</v>
+        <v>72</v>
       </c>
       <c r="I33" s="46">
         <v>46068.743055555555</v>
@@ -3058,7 +3201,7 @@
         <v>5</v>
       </c>
       <c r="P33" s="44" t="s">
-        <v>97</v>
+        <v>52</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
@@ -3070,19 +3213,19 @@
         <v>T0024/R/T0014/D</v>
       </c>
       <c r="D34" s="44" t="s">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="E34" s="43" t="s">
-        <v>84</v>
+        <v>60</v>
       </c>
       <c r="F34" s="43" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="G34" s="44" t="s">
-        <v>87</v>
+        <v>50</v>
       </c>
       <c r="H34" s="43" t="s">
-        <v>115</v>
+        <v>73</v>
       </c>
       <c r="I34" s="46">
         <v>46068.895833333336</v>
@@ -3109,7 +3252,7 @@
         <v>15</v>
       </c>
       <c r="P34" s="44" t="s">
-        <v>97</v>
+        <v>52</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
@@ -3121,19 +3264,19 @@
         <v>T0025/R/T0013/D</v>
       </c>
       <c r="D35" s="44" t="s">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="E35" s="43" t="s">
-        <v>81</v>
+        <v>62</v>
       </c>
       <c r="F35" s="43" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="G35" s="44" t="s">
-        <v>87</v>
+        <v>50</v>
       </c>
       <c r="H35" s="43" t="s">
-        <v>116</v>
+        <v>74</v>
       </c>
       <c r="I35" s="46">
         <v>46069.395833333336</v>
@@ -3160,7 +3303,7 @@
         <v>5</v>
       </c>
       <c r="P35" s="44" t="s">
-        <v>97</v>
+        <v>52</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
@@ -3172,16 +3315,16 @@
         <v>T0026/M</v>
       </c>
       <c r="D36" s="44" t="s">
-        <v>64</v>
+        <v>30</v>
       </c>
       <c r="E36" s="43" t="s">
-        <v>80</v>
+        <v>31</v>
       </c>
       <c r="F36" s="43" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="G36" s="44" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="H36" s="43"/>
       <c r="I36" s="46">
@@ -3209,7 +3352,7 @@
         <v>12.5</v>
       </c>
       <c r="P36" s="44" t="s">
-        <v>100</v>
+        <v>54</v>
       </c>
     </row>
     <row r="37" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
@@ -3221,40 +3364,44 @@
         <v>T0027/D</v>
       </c>
       <c r="D37" s="44" t="s">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="E37" s="43" t="s">
-        <v>82</v>
+        <v>48</v>
       </c>
       <c r="F37" s="43" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="G37" s="44" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="H37" s="43"/>
       <c r="I37" s="46">
-        <v>46072.708333333336</v>
-      </c>
-      <c r="J37" s="46"/>
+        <v>46075.75</v>
+      </c>
+      <c r="J37" s="46">
+        <v>46076.416666666664</v>
+      </c>
       <c r="K37" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
+        <v>Completed</v>
       </c>
       <c r="L37" s="47">
         <v>1</v>
       </c>
-      <c r="M37" s="47"/>
+      <c r="M37" s="47">
+        <v>2.5</v>
+      </c>
       <c r="N37" s="45">
         <f>IF(ISBLANK(L37), "", L37*VLOOKUP($F37,Internal!$B$26:$C$32,2,FALSE))</f>
         <v>25</v>
       </c>
-      <c r="O37" s="45" t="str">
+      <c r="O37" s="45">
         <f>IF(ISBLANK(M37), "", M37*VLOOKUP($F37,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
+        <v>62.5</v>
       </c>
       <c r="P37" s="44" t="s">
-        <v>117</v>
+        <v>75</v>
       </c>
     </row>
     <row r="38" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
@@ -3266,40 +3413,44 @@
         <v>T0028/D</v>
       </c>
       <c r="D38" s="44" t="s">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="E38" s="43" t="s">
-        <v>84</v>
+        <v>60</v>
       </c>
       <c r="F38" s="43" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="G38" s="44" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="H38" s="43"/>
       <c r="I38" s="46">
         <v>46073.708333333336</v>
       </c>
-      <c r="J38" s="46"/>
+      <c r="J38" s="46">
+        <v>46076.354166666664</v>
+      </c>
       <c r="K38" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
+        <v>Completed</v>
       </c>
       <c r="L38" s="47">
         <v>2</v>
       </c>
-      <c r="M38" s="47"/>
+      <c r="M38" s="47">
+        <v>2</v>
+      </c>
       <c r="N38" s="45">
         <f>IF(ISBLANK(L38), "", L38*VLOOKUP($F38,Internal!$B$26:$C$32,2,FALSE))</f>
         <v>50</v>
       </c>
-      <c r="O38" s="45" t="str">
+      <c r="O38" s="45">
         <f>IF(ISBLANK(M38), "", M38*VLOOKUP($F38,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
+        <v>50</v>
       </c>
       <c r="P38" s="44" t="s">
-        <v>118</v>
+        <v>76</v>
       </c>
     </row>
     <row r="39" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
@@ -3311,40 +3462,44 @@
         <v>T0029/D</v>
       </c>
       <c r="D39" s="44" t="s">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="E39" s="43" t="s">
-        <v>80</v>
+        <v>31</v>
       </c>
       <c r="F39" s="43" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="G39" s="44" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="H39" s="43"/>
       <c r="I39" s="46">
-        <v>46074.708333333336</v>
-      </c>
-      <c r="J39" s="46"/>
+        <v>46074.416666666664</v>
+      </c>
+      <c r="J39" s="46">
+        <v>46074.677083333336</v>
+      </c>
       <c r="K39" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
+        <v>Completed</v>
       </c>
       <c r="L39" s="47">
-        <v>3</v>
-      </c>
-      <c r="M39" s="47"/>
+        <v>5</v>
+      </c>
+      <c r="M39" s="47">
+        <v>6</v>
+      </c>
       <c r="N39" s="45">
         <f>IF(ISBLANK(L39), "", L39*VLOOKUP($F39,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v>75</v>
-      </c>
-      <c r="O39" s="45" t="str">
+        <v>125</v>
+      </c>
+      <c r="O39" s="45">
         <f>IF(ISBLANK(M39), "", M39*VLOOKUP($F39,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
+        <v>150</v>
       </c>
       <c r="P39" s="44" t="s">
-        <v>126</v>
+        <v>77</v>
       </c>
     </row>
     <row r="40" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
@@ -3356,40 +3511,44 @@
         <v>T0030/D</v>
       </c>
       <c r="D40" s="44" t="s">
+        <v>41</v>
+      </c>
+      <c r="E40" s="43" t="s">
         <v>62</v>
       </c>
-      <c r="E40" s="43" t="s">
-        <v>81</v>
-      </c>
       <c r="F40" s="43" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="G40" s="44" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="H40" s="43"/>
       <c r="I40" s="46">
         <v>46075.708333333336</v>
       </c>
-      <c r="J40" s="46"/>
+      <c r="J40" s="46">
+        <v>46075.833333333336</v>
+      </c>
       <c r="K40" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
+        <v>Completed</v>
       </c>
       <c r="L40" s="47">
-        <v>3</v>
-      </c>
-      <c r="M40" s="47"/>
+        <v>5</v>
+      </c>
+      <c r="M40" s="47">
+        <v>6</v>
+      </c>
       <c r="N40" s="45">
         <f>IF(ISBLANK(L40), "", L40*VLOOKUP($F40,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v>75</v>
-      </c>
-      <c r="O40" s="45" t="str">
+        <v>125</v>
+      </c>
+      <c r="O40" s="45">
         <f>IF(ISBLANK(M40), "", M40*VLOOKUP($F40,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
+        <v>150</v>
       </c>
       <c r="P40" s="44" t="s">
-        <v>127</v>
+        <v>78</v>
       </c>
     </row>
     <row r="41" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
@@ -3401,40 +3560,44 @@
         <v>T0031/D</v>
       </c>
       <c r="D41" s="44" t="s">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="E41" s="43" t="s">
-        <v>82</v>
+        <v>48</v>
       </c>
       <c r="F41" s="43" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="G41" s="44" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="H41" s="43"/>
       <c r="I41" s="46">
-        <v>46076.708333333336</v>
-      </c>
-      <c r="J41" s="46"/>
+        <v>46075.708333333336</v>
+      </c>
+      <c r="J41" s="46">
+        <v>46075.833333333336</v>
+      </c>
       <c r="K41" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
+        <v>Completed</v>
       </c>
       <c r="L41" s="47">
-        <v>3</v>
-      </c>
-      <c r="M41" s="47"/>
+        <v>5</v>
+      </c>
+      <c r="M41" s="47">
+        <v>6</v>
+      </c>
       <c r="N41" s="45">
         <f>IF(ISBLANK(L41), "", L41*VLOOKUP($F41,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v>75</v>
-      </c>
-      <c r="O41" s="45" t="str">
+        <v>125</v>
+      </c>
+      <c r="O41" s="45">
         <f>IF(ISBLANK(M41), "", M41*VLOOKUP($F41,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
+        <v>150</v>
       </c>
       <c r="P41" s="44" t="s">
-        <v>128</v>
+        <v>79</v>
       </c>
     </row>
     <row r="42" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
@@ -3446,40 +3609,44 @@
         <v>T0032/D</v>
       </c>
       <c r="D42" s="44" t="s">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="E42" s="43" t="s">
-        <v>83</v>
+        <v>58</v>
       </c>
       <c r="F42" s="43" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="G42" s="44" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="H42" s="43"/>
       <c r="I42" s="46">
-        <v>46077.708333333336</v>
-      </c>
-      <c r="J42" s="46"/>
+        <v>46075.708333333336</v>
+      </c>
+      <c r="J42" s="46">
+        <v>46075.833333333336</v>
+      </c>
       <c r="K42" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
+        <v>Completed</v>
       </c>
       <c r="L42" s="47">
-        <v>3</v>
-      </c>
-      <c r="M42" s="47"/>
+        <v>5</v>
+      </c>
+      <c r="M42" s="47">
+        <v>6</v>
+      </c>
       <c r="N42" s="45">
         <f>IF(ISBLANK(L42), "", L42*VLOOKUP($F42,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v>75</v>
-      </c>
-      <c r="O42" s="45" t="str">
+        <v>125</v>
+      </c>
+      <c r="O42" s="45">
         <f>IF(ISBLANK(M42), "", M42*VLOOKUP($F42,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
+        <v>150</v>
       </c>
       <c r="P42" s="44" t="s">
-        <v>129</v>
+        <v>80</v>
       </c>
     </row>
     <row r="43" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
@@ -3491,40 +3658,44 @@
         <v>T0033/D</v>
       </c>
       <c r="D43" s="44" t="s">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="E43" s="43" t="s">
-        <v>84</v>
+        <v>60</v>
       </c>
       <c r="F43" s="43" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="G43" s="44" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="H43" s="43"/>
       <c r="I43" s="46">
-        <v>46078.708333333336</v>
-      </c>
-      <c r="J43" s="46"/>
+        <v>46075.708333333336</v>
+      </c>
+      <c r="J43" s="46">
+        <v>46075.833333333336</v>
+      </c>
       <c r="K43" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
+        <v>Completed</v>
       </c>
       <c r="L43" s="47">
-        <v>3</v>
-      </c>
-      <c r="M43" s="47"/>
+        <v>5</v>
+      </c>
+      <c r="M43" s="47">
+        <v>6</v>
+      </c>
       <c r="N43" s="45">
         <f>IF(ISBLANK(L43), "", L43*VLOOKUP($F43,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v>75</v>
-      </c>
-      <c r="O43" s="45" t="str">
+        <v>125</v>
+      </c>
+      <c r="O43" s="45">
         <f>IF(ISBLANK(M43), "", M43*VLOOKUP($F43,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
+        <v>150</v>
       </c>
       <c r="P43" s="44" t="s">
-        <v>130</v>
+        <v>81</v>
       </c>
     </row>
     <row r="44" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
@@ -3536,40 +3707,46 @@
         <v>T0034/R/T0027/D</v>
       </c>
       <c r="D44" s="44" t="s">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="E44" s="43" t="s">
-        <v>83</v>
+        <v>58</v>
       </c>
       <c r="F44" s="43" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="G44" s="44" t="s">
-        <v>87</v>
+        <v>50</v>
       </c>
       <c r="H44" s="43" t="s">
-        <v>120</v>
-      </c>
-      <c r="I44" s="46"/>
-      <c r="J44" s="46"/>
+        <v>82</v>
+      </c>
+      <c r="I44" s="46">
+        <v>46076.420138888891</v>
+      </c>
+      <c r="J44" s="46">
+        <v>46076.423611111109</v>
+      </c>
       <c r="K44" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
+        <v>Completed</v>
       </c>
       <c r="L44" s="47">
-        <v>0.5</v>
-      </c>
-      <c r="M44" s="47"/>
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="M44" s="47">
+        <v>8.3333333333333329E-2</v>
+      </c>
       <c r="N44" s="45">
         <f>IF(ISBLANK(L44), "", L44*VLOOKUP($F44,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v>15</v>
-      </c>
-      <c r="O44" s="45" t="str">
+        <v>5</v>
+      </c>
+      <c r="O44" s="45">
         <f>IF(ISBLANK(M44), "", M44*VLOOKUP($F44,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
+        <v>2.5</v>
       </c>
       <c r="P44" s="44" t="s">
-        <v>97</v>
+        <v>52</v>
       </c>
     </row>
     <row r="45" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
@@ -3581,40 +3758,46 @@
         <v>T0035/R/T0028/D</v>
       </c>
       <c r="D45" s="44" t="s">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="E45" s="43" t="s">
-        <v>80</v>
+        <v>31</v>
       </c>
       <c r="F45" s="43" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="G45" s="44" t="s">
-        <v>87</v>
+        <v>50</v>
       </c>
       <c r="H45" s="43" t="s">
-        <v>119</v>
-      </c>
-      <c r="I45" s="46"/>
-      <c r="J45" s="46"/>
+        <v>83</v>
+      </c>
+      <c r="I45" s="46">
+        <v>46075.791666666664</v>
+      </c>
+      <c r="J45" s="46">
+        <v>46075.798611111109</v>
+      </c>
       <c r="K45" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
+        <v>Completed</v>
       </c>
       <c r="L45" s="47">
         <v>0.16666666666666666</v>
       </c>
-      <c r="M45" s="47"/>
+      <c r="M45" s="47">
+        <v>0.16666666666666666</v>
+      </c>
       <c r="N45" s="45">
         <f>IF(ISBLANK(L45), "", L45*VLOOKUP($F45,Internal!$B$26:$C$32,2,FALSE))</f>
         <v>5</v>
       </c>
-      <c r="O45" s="45" t="str">
+      <c r="O45" s="45">
         <f>IF(ISBLANK(M45), "", M45*VLOOKUP($F45,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="P45" s="44" t="s">
-        <v>97</v>
+        <v>52</v>
       </c>
     </row>
     <row r="46" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
@@ -3626,40 +3809,46 @@
         <v>T0036/R/T0033/D</v>
       </c>
       <c r="D46" s="44" t="s">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="E46" s="43" t="s">
-        <v>80</v>
+        <v>31</v>
       </c>
       <c r="F46" s="43" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="G46" s="44" t="s">
-        <v>87</v>
+        <v>50</v>
       </c>
       <c r="H46" s="43" t="s">
-        <v>122</v>
-      </c>
-      <c r="I46" s="46"/>
-      <c r="J46" s="46"/>
+        <v>84</v>
+      </c>
+      <c r="I46" s="46">
+        <v>46075.833333333336</v>
+      </c>
+      <c r="J46" s="46">
+        <v>46075.840277777781</v>
+      </c>
       <c r="K46" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
+        <v>Completed</v>
       </c>
       <c r="L46" s="47">
         <v>0.33333333333333331</v>
       </c>
-      <c r="M46" s="47"/>
+      <c r="M46" s="47">
+        <v>0.16666666666666666</v>
+      </c>
       <c r="N46" s="45">
         <f>IF(ISBLANK(L46), "", L46*VLOOKUP($F46,Internal!$B$26:$C$32,2,FALSE))</f>
         <v>10</v>
       </c>
-      <c r="O46" s="45" t="str">
+      <c r="O46" s="45">
         <f>IF(ISBLANK(M46), "", M46*VLOOKUP($F46,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="P46" s="44" t="s">
-        <v>97</v>
+        <v>52</v>
       </c>
     </row>
     <row r="47" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
@@ -3671,40 +3860,46 @@
         <v>T0037/R/T0032/D</v>
       </c>
       <c r="D47" s="44" t="s">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="E47" s="43" t="s">
-        <v>81</v>
+        <v>62</v>
       </c>
       <c r="F47" s="43" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="G47" s="44" t="s">
-        <v>87</v>
+        <v>50</v>
       </c>
       <c r="H47" s="43" t="s">
-        <v>123</v>
-      </c>
-      <c r="I47" s="46"/>
-      <c r="J47" s="46"/>
+        <v>85</v>
+      </c>
+      <c r="I47" s="46">
+        <v>46075.833333333336</v>
+      </c>
+      <c r="J47" s="46">
+        <v>46075.840277777781</v>
+      </c>
       <c r="K47" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
+        <v>Completed</v>
       </c>
       <c r="L47" s="47">
         <v>0.33333333333333331</v>
       </c>
-      <c r="M47" s="47"/>
+      <c r="M47" s="47">
+        <v>0.16666666666666666</v>
+      </c>
       <c r="N47" s="45">
         <f>IF(ISBLANK(L47), "", L47*VLOOKUP($F47,Internal!$B$26:$C$32,2,FALSE))</f>
         <v>10</v>
       </c>
-      <c r="O47" s="45" t="str">
+      <c r="O47" s="45">
         <f>IF(ISBLANK(M47), "", M47*VLOOKUP($F47,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="P47" s="44" t="s">
-        <v>97</v>
+        <v>52</v>
       </c>
     </row>
     <row r="48" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
@@ -3716,40 +3911,46 @@
         <v>T0038/R/T0029/D</v>
       </c>
       <c r="D48" s="44" t="s">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="E48" s="43" t="s">
-        <v>82</v>
+        <v>48</v>
       </c>
       <c r="F48" s="43" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="G48" s="44" t="s">
-        <v>87</v>
+        <v>50</v>
       </c>
       <c r="H48" s="43" t="s">
-        <v>121</v>
-      </c>
-      <c r="I48" s="46"/>
-      <c r="J48" s="46"/>
+        <v>86</v>
+      </c>
+      <c r="I48" s="46">
+        <v>46075.833333333336</v>
+      </c>
+      <c r="J48" s="46">
+        <v>46075.840277777781</v>
+      </c>
       <c r="K48" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
+        <v>Completed</v>
       </c>
       <c r="L48" s="47">
         <v>0.33333333333333331</v>
       </c>
-      <c r="M48" s="47"/>
+      <c r="M48" s="47">
+        <v>0.16666666666666666</v>
+      </c>
       <c r="N48" s="45">
         <f>IF(ISBLANK(L48), "", L48*VLOOKUP($F48,Internal!$B$26:$C$32,2,FALSE))</f>
         <v>10</v>
       </c>
-      <c r="O48" s="45" t="str">
+      <c r="O48" s="45">
         <f>IF(ISBLANK(M48), "", M48*VLOOKUP($F48,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="P48" s="44" t="s">
-        <v>97</v>
+        <v>52</v>
       </c>
     </row>
     <row r="49" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
@@ -3761,40 +3962,46 @@
         <v>T0039/R/T0031/D</v>
       </c>
       <c r="D49" s="44" t="s">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="E49" s="43" t="s">
-        <v>83</v>
+        <v>58</v>
       </c>
       <c r="F49" s="43" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="G49" s="44" t="s">
+        <v>50</v>
+      </c>
+      <c r="H49" s="43" t="s">
         <v>87</v>
       </c>
-      <c r="H49" s="43" t="s">
-        <v>124</v>
-      </c>
-      <c r="I49" s="46"/>
-      <c r="J49" s="46"/>
+      <c r="I49" s="46">
+        <v>46075.833333333336</v>
+      </c>
+      <c r="J49" s="46">
+        <v>46075.840277777781</v>
+      </c>
       <c r="K49" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
+        <v>Completed</v>
       </c>
       <c r="L49" s="47">
         <v>0.33333333333333331</v>
       </c>
-      <c r="M49" s="47"/>
+      <c r="M49" s="47">
+        <v>0.16666666666666666</v>
+      </c>
       <c r="N49" s="45">
         <f>IF(ISBLANK(L49), "", L49*VLOOKUP($F49,Internal!$B$26:$C$32,2,FALSE))</f>
         <v>10</v>
       </c>
-      <c r="O49" s="45" t="str">
+      <c r="O49" s="45">
         <f>IF(ISBLANK(M49), "", M49*VLOOKUP($F49,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="P49" s="44" t="s">
-        <v>97</v>
+        <v>52</v>
       </c>
     </row>
     <row r="50" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
@@ -3806,40 +4013,46 @@
         <v>T0040/R/T0030/D</v>
       </c>
       <c r="D50" s="44" t="s">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="E50" s="43" t="s">
-        <v>84</v>
+        <v>60</v>
       </c>
       <c r="F50" s="43" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="G50" s="44" t="s">
-        <v>87</v>
+        <v>50</v>
       </c>
       <c r="H50" s="43" t="s">
-        <v>125</v>
-      </c>
-      <c r="I50" s="46"/>
-      <c r="J50" s="46"/>
+        <v>88</v>
+      </c>
+      <c r="I50" s="46">
+        <v>46076.833333333336</v>
+      </c>
+      <c r="J50" s="46">
+        <v>46075.840277777781</v>
+      </c>
       <c r="K50" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
+        <v>Completed</v>
       </c>
       <c r="L50" s="47">
         <v>0.33333333333333331</v>
       </c>
-      <c r="M50" s="47"/>
+      <c r="M50" s="47">
+        <v>0.16666666666666666</v>
+      </c>
       <c r="N50" s="45">
         <f>IF(ISBLANK(L50), "", L50*VLOOKUP($F50,Internal!$B$26:$C$32,2,FALSE))</f>
         <v>10</v>
       </c>
-      <c r="O50" s="45" t="str">
+      <c r="O50" s="45">
         <f>IF(ISBLANK(M50), "", M50*VLOOKUP($F50,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="P50" s="44" t="s">
-        <v>97</v>
+        <v>52</v>
       </c>
     </row>
     <row r="51" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
@@ -3848,30 +4061,48 @@
       </c>
       <c r="C51" s="42" t="str">
         <f>IF(ISBLANK(D51), "", _xlfn.CONCAT("T", TEXT(B51, "0000"), "/", VLOOKUP(D51, Internal!$B$35:C$39, 2, FALSE), IF(OR(D51="QA", D51="Revision"), _xlfn.CONCAT("/", H51), "")))</f>
-        <v/>
-      </c>
-      <c r="D51" s="44"/>
-      <c r="E51" s="43"/>
-      <c r="F51" s="43"/>
-      <c r="G51" s="44"/>
+        <v>T0041/D</v>
+      </c>
+      <c r="D51" s="44" t="s">
+        <v>41</v>
+      </c>
+      <c r="E51" s="43" t="s">
+        <v>48</v>
+      </c>
+      <c r="F51" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="G51" s="44" t="s">
+        <v>56</v>
+      </c>
       <c r="H51" s="43"/>
-      <c r="I51" s="46"/>
-      <c r="J51" s="46"/>
+      <c r="I51" s="46">
+        <v>46076.368055555555</v>
+      </c>
+      <c r="J51" s="46">
+        <v>46076.375</v>
+      </c>
       <c r="K51" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L51" s="47"/>
-      <c r="M51" s="47"/>
-      <c r="N51" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L51" s="47">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="M51" s="47">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="N51" s="45">
         <f>IF(ISBLANK(L51), "", L51*VLOOKUP($F51,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O51" s="45" t="str">
+        <v>4.1666666666666661</v>
+      </c>
+      <c r="O51" s="45">
         <f>IF(ISBLANK(M51), "", M51*VLOOKUP($F51,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P51" s="44"/>
+        <v>4.1666666666666661</v>
+      </c>
+      <c r="P51" s="44" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="52" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B52" s="41">
@@ -3879,30 +4110,50 @@
       </c>
       <c r="C52" s="42" t="str">
         <f>IF(ISBLANK(D52), "", _xlfn.CONCAT("T", TEXT(B52, "0000"), "/", VLOOKUP(D52, Internal!$B$35:C$39, 2, FALSE), IF(OR(D52="QA", D52="Revision"), _xlfn.CONCAT("/", H52), "")))</f>
-        <v/>
-      </c>
-      <c r="D52" s="44"/>
-      <c r="E52" s="43"/>
-      <c r="F52" s="43"/>
-      <c r="G52" s="44"/>
-      <c r="H52" s="43"/>
-      <c r="I52" s="46"/>
-      <c r="J52" s="46"/>
+        <v>T0042/R/T0041/D</v>
+      </c>
+      <c r="D52" s="44" t="s">
+        <v>47</v>
+      </c>
+      <c r="E52" s="43" t="s">
+        <v>58</v>
+      </c>
+      <c r="F52" s="43" t="s">
+        <v>49</v>
+      </c>
+      <c r="G52" s="44" t="s">
+        <v>50</v>
+      </c>
+      <c r="H52" s="43" t="s">
+        <v>90</v>
+      </c>
+      <c r="I52" s="46">
+        <v>46076.375</v>
+      </c>
+      <c r="J52" s="46">
+        <v>46076.381944444445</v>
+      </c>
       <c r="K52" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L52" s="47"/>
-      <c r="M52" s="47"/>
-      <c r="N52" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L52" s="47">
+        <v>8.3333333333333329E-2</v>
+      </c>
+      <c r="M52" s="47">
+        <v>8.3333333333333329E-2</v>
+      </c>
+      <c r="N52" s="45">
         <f>IF(ISBLANK(L52), "", L52*VLOOKUP($F52,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O52" s="45" t="str">
+        <v>2.5</v>
+      </c>
+      <c r="O52" s="45">
         <f>IF(ISBLANK(M52), "", M52*VLOOKUP($F52,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P52" s="44"/>
+        <v>2.5</v>
+      </c>
+      <c r="P52" s="44" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="53" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B53" s="41">
@@ -3910,154 +4161,243 @@
       </c>
       <c r="C53" s="42" t="str">
         <f>IF(ISBLANK(D53), "", _xlfn.CONCAT("T", TEXT(B53, "0000"), "/", VLOOKUP(D53, Internal!$B$35:C$39, 2, FALSE), IF(OR(D53="QA", D53="Revision"), _xlfn.CONCAT("/", H53), "")))</f>
-        <v/>
-      </c>
-      <c r="D53" s="44"/>
-      <c r="E53" s="43"/>
-      <c r="F53" s="43"/>
-      <c r="G53" s="44"/>
+        <v>T0043/D</v>
+      </c>
+      <c r="D53" s="44" t="s">
+        <v>41</v>
+      </c>
+      <c r="E53" s="43" t="s">
+        <v>31</v>
+      </c>
+      <c r="F53" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="G53" s="44" t="s">
+        <v>56</v>
+      </c>
       <c r="H53" s="43"/>
-      <c r="I53" s="46"/>
-      <c r="J53" s="46"/>
+      <c r="I53" s="46">
+        <v>46080.791666666664</v>
+      </c>
+      <c r="J53" s="46">
+        <v>46081</v>
+      </c>
       <c r="K53" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L53" s="47"/>
-      <c r="M53" s="47"/>
-      <c r="N53" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L53" s="47">
+        <v>3</v>
+      </c>
+      <c r="M53" s="47">
+        <v>5</v>
+      </c>
+      <c r="N53" s="45">
         <f>IF(ISBLANK(L53), "", L53*VLOOKUP($F53,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O53" s="45" t="str">
+        <v>75</v>
+      </c>
+      <c r="O53" s="45">
         <f>IF(ISBLANK(M53), "", M53*VLOOKUP($F53,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P53" s="44"/>
-    </row>
-    <row r="54" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+        <v>125</v>
+      </c>
+      <c r="P53" s="44" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="54" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B54" s="41">
         <v>44</v>
       </c>
       <c r="C54" s="42" t="str">
         <f>IF(ISBLANK(D54), "", _xlfn.CONCAT("T", TEXT(B54, "0000"), "/", VLOOKUP(D54, Internal!$B$35:C$39, 2, FALSE), IF(OR(D54="QA", D54="Revision"), _xlfn.CONCAT("/", H54), "")))</f>
-        <v/>
-      </c>
-      <c r="D54" s="44"/>
-      <c r="E54" s="43"/>
-      <c r="F54" s="43"/>
-      <c r="G54" s="44"/>
+        <v>T0044/D</v>
+      </c>
+      <c r="D54" s="44" t="s">
+        <v>41</v>
+      </c>
+      <c r="E54" s="43" t="s">
+        <v>62</v>
+      </c>
+      <c r="F54" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="G54" s="44" t="s">
+        <v>56</v>
+      </c>
       <c r="H54" s="43"/>
-      <c r="I54" s="46"/>
-      <c r="J54" s="46"/>
+      <c r="I54" s="46">
+        <v>46082.791666666664</v>
+      </c>
+      <c r="J54" s="46">
+        <v>46095.75</v>
+      </c>
       <c r="K54" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L54" s="47"/>
-      <c r="M54" s="47"/>
-      <c r="N54" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L54" s="53">
+        <v>3</v>
+      </c>
+      <c r="M54" s="47">
+        <v>3</v>
+      </c>
+      <c r="N54" s="45">
         <f>IF(ISBLANK(L54), "", L54*VLOOKUP($F54,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O54" s="45" t="str">
+        <v>75</v>
+      </c>
+      <c r="O54" s="45">
         <f>IF(ISBLANK(M54), "", M54*VLOOKUP($F54,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P54" s="44"/>
-    </row>
-    <row r="55" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+        <v>75</v>
+      </c>
+      <c r="P54" s="44" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="55" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B55" s="41">
         <v>45</v>
       </c>
       <c r="C55" s="42" t="str">
         <f>IF(ISBLANK(D55), "", _xlfn.CONCAT("T", TEXT(B55, "0000"), "/", VLOOKUP(D55, Internal!$B$35:C$39, 2, FALSE), IF(OR(D55="QA", D55="Revision"), _xlfn.CONCAT("/", H55), "")))</f>
-        <v/>
-      </c>
-      <c r="D55" s="44"/>
-      <c r="E55" s="43"/>
-      <c r="F55" s="43"/>
-      <c r="G55" s="44"/>
+        <v>T0045/D</v>
+      </c>
+      <c r="D55" s="44" t="s">
+        <v>41</v>
+      </c>
+      <c r="E55" s="43" t="s">
+        <v>48</v>
+      </c>
+      <c r="F55" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="G55" s="44" t="s">
+        <v>56</v>
+      </c>
       <c r="H55" s="43"/>
-      <c r="I55" s="46"/>
-      <c r="J55" s="46"/>
+      <c r="I55" s="46">
+        <v>46082.6875</v>
+      </c>
+      <c r="J55" s="46">
+        <v>46091.791666666664</v>
+      </c>
       <c r="K55" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L55" s="47"/>
-      <c r="M55" s="47"/>
-      <c r="N55" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L55" s="47">
+        <v>3</v>
+      </c>
+      <c r="M55" s="47">
+        <v>5</v>
+      </c>
+      <c r="N55" s="45">
         <f>IF(ISBLANK(L55), "", L55*VLOOKUP($F55,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O55" s="45" t="str">
+        <v>75</v>
+      </c>
+      <c r="O55" s="45">
         <f>IF(ISBLANK(M55), "", M55*VLOOKUP($F55,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P55" s="44"/>
-    </row>
-    <row r="56" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+        <v>125</v>
+      </c>
+      <c r="P55" s="44" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="56" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B56" s="41">
         <v>46</v>
       </c>
       <c r="C56" s="42" t="str">
         <f>IF(ISBLANK(D56), "", _xlfn.CONCAT("T", TEXT(B56, "0000"), "/", VLOOKUP(D56, Internal!$B$35:C$39, 2, FALSE), IF(OR(D56="QA", D56="Revision"), _xlfn.CONCAT("/", H56), "")))</f>
-        <v/>
-      </c>
-      <c r="D56" s="44"/>
-      <c r="E56" s="43"/>
-      <c r="F56" s="43"/>
-      <c r="G56" s="44"/>
+        <v>T0046/D</v>
+      </c>
+      <c r="D56" s="44" t="s">
+        <v>41</v>
+      </c>
+      <c r="E56" s="43" t="s">
+        <v>58</v>
+      </c>
+      <c r="F56" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="G56" s="44" t="s">
+        <v>56</v>
+      </c>
       <c r="H56" s="43"/>
-      <c r="I56" s="46"/>
-      <c r="J56" s="46"/>
+      <c r="I56" s="46">
+        <v>46082.666666666664</v>
+      </c>
+      <c r="J56" s="46">
+        <v>46095.583333333336</v>
+      </c>
       <c r="K56" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L56" s="47"/>
-      <c r="M56" s="47"/>
-      <c r="N56" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L56" s="47">
+        <v>3</v>
+      </c>
+      <c r="M56" s="47">
+        <v>5</v>
+      </c>
+      <c r="N56" s="45">
         <f>IF(ISBLANK(L56), "", L56*VLOOKUP($F56,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O56" s="45" t="str">
+        <v>75</v>
+      </c>
+      <c r="O56" s="45">
         <f>IF(ISBLANK(M56), "", M56*VLOOKUP($F56,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P56" s="44"/>
-    </row>
-    <row r="57" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+        <v>125</v>
+      </c>
+      <c r="P56" s="44" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="57" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B57" s="41">
         <v>47</v>
       </c>
       <c r="C57" s="42" t="str">
         <f>IF(ISBLANK(D57), "", _xlfn.CONCAT("T", TEXT(B57, "0000"), "/", VLOOKUP(D57, Internal!$B$35:C$39, 2, FALSE), IF(OR(D57="QA", D57="Revision"), _xlfn.CONCAT("/", H57), "")))</f>
-        <v/>
-      </c>
-      <c r="D57" s="44"/>
-      <c r="E57" s="43"/>
-      <c r="F57" s="43"/>
-      <c r="G57" s="44"/>
+        <v>T0047/D</v>
+      </c>
+      <c r="D57" s="44" t="s">
+        <v>41</v>
+      </c>
+      <c r="E57" s="43" t="s">
+        <v>60</v>
+      </c>
+      <c r="F57" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="G57" s="44" t="s">
+        <v>56</v>
+      </c>
       <c r="H57" s="43"/>
-      <c r="I57" s="46"/>
-      <c r="J57" s="46"/>
-      <c r="K57" s="45" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L57" s="47"/>
-      <c r="M57" s="47"/>
-      <c r="N57" s="45" t="str">
+      <c r="I57" s="46">
+        <v>46086.479166666664</v>
+      </c>
+      <c r="J57" s="46">
+        <v>46097.395833333336</v>
+      </c>
+      <c r="K57" s="45" t="s">
+        <v>95</v>
+      </c>
+      <c r="L57" s="47">
+        <v>3</v>
+      </c>
+      <c r="M57" s="47">
+        <v>5</v>
+      </c>
+      <c r="N57" s="45">
         <f>IF(ISBLANK(L57), "", L57*VLOOKUP($F57,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O57" s="45" t="str">
+        <v>75</v>
+      </c>
+      <c r="O57" s="45">
         <f>IF(ISBLANK(M57), "", M57*VLOOKUP($F57,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P57" s="44"/>
+        <v>125</v>
+      </c>
+      <c r="P57" s="44" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="58" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B58" s="41">
@@ -4065,247 +4405,403 @@
       </c>
       <c r="C58" s="42" t="str">
         <f>IF(ISBLANK(D58), "", _xlfn.CONCAT("T", TEXT(B58, "0000"), "/", VLOOKUP(D58, Internal!$B$35:C$39, 2, FALSE), IF(OR(D58="QA", D58="Revision"), _xlfn.CONCAT("/", H58), "")))</f>
-        <v/>
-      </c>
-      <c r="D58" s="44"/>
-      <c r="E58" s="43"/>
-      <c r="F58" s="43"/>
-      <c r="G58" s="44"/>
-      <c r="H58" s="43"/>
-      <c r="I58" s="46"/>
-      <c r="J58" s="46"/>
+        <v>T0048/R/T0047/D</v>
+      </c>
+      <c r="D58" s="44" t="s">
+        <v>47</v>
+      </c>
+      <c r="E58" s="43" t="s">
+        <v>31</v>
+      </c>
+      <c r="F58" s="43" t="s">
+        <v>49</v>
+      </c>
+      <c r="G58" s="44" t="s">
+        <v>50</v>
+      </c>
+      <c r="H58" s="43" t="s">
+        <v>97</v>
+      </c>
+      <c r="I58" s="46">
+        <v>46086.743055555555</v>
+      </c>
+      <c r="J58" s="46">
+        <v>46086.753472222219</v>
+      </c>
       <c r="K58" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L58" s="47"/>
-      <c r="M58" s="47"/>
-      <c r="N58" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L58" s="47">
+        <v>8.3333333333333329E-2</v>
+      </c>
+      <c r="M58" s="47">
+        <v>0.25</v>
+      </c>
+      <c r="N58" s="45">
         <f>IF(ISBLANK(L58), "", L58*VLOOKUP($F58,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O58" s="45" t="str">
+        <v>2.5</v>
+      </c>
+      <c r="O58" s="45">
         <f>IF(ISBLANK(M58), "", M58*VLOOKUP($F58,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P58" s="44"/>
-    </row>
-    <row r="59" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+        <v>7.5</v>
+      </c>
+      <c r="P58" s="44" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="59" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B59" s="41">
         <v>49</v>
       </c>
       <c r="C59" s="42" t="str">
         <f>IF(ISBLANK(D59), "", _xlfn.CONCAT("T", TEXT(B59, "0000"), "/", VLOOKUP(D59, Internal!$B$35:C$39, 2, FALSE), IF(OR(D59="QA", D59="Revision"), _xlfn.CONCAT("/", H59), "")))</f>
-        <v/>
-      </c>
-      <c r="D59" s="44"/>
-      <c r="E59" s="43"/>
-      <c r="F59" s="43"/>
-      <c r="G59" s="44"/>
-      <c r="H59" s="43"/>
-      <c r="I59" s="46"/>
-      <c r="J59" s="46"/>
+        <v>T0049/R/T0046/D</v>
+      </c>
+      <c r="D59" s="44" t="s">
+        <v>47</v>
+      </c>
+      <c r="E59" s="43" t="s">
+        <v>62</v>
+      </c>
+      <c r="F59" s="43" t="s">
+        <v>49</v>
+      </c>
+      <c r="G59" s="44" t="s">
+        <v>50</v>
+      </c>
+      <c r="H59" s="43" t="s">
+        <v>98</v>
+      </c>
+      <c r="I59" s="46">
+        <v>46083.75</v>
+      </c>
+      <c r="J59" s="46">
+        <v>46083.756944444445</v>
+      </c>
       <c r="K59" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L59" s="47"/>
-      <c r="M59" s="47"/>
-      <c r="N59" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L59" s="47">
+        <v>0.08</v>
+      </c>
+      <c r="M59" s="47">
+        <v>0.08</v>
+      </c>
+      <c r="N59" s="45">
         <f>IF(ISBLANK(L59), "", L59*VLOOKUP($F59,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O59" s="45" t="str">
+        <v>2.4</v>
+      </c>
+      <c r="O59" s="45">
         <f>IF(ISBLANK(M59), "", M59*VLOOKUP($F59,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P59" s="44"/>
-    </row>
-    <row r="60" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+        <v>2.4</v>
+      </c>
+      <c r="P59" s="44" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="60" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B60" s="41">
         <v>50</v>
       </c>
       <c r="C60" s="42" t="str">
         <f>IF(ISBLANK(D60), "", _xlfn.CONCAT("T", TEXT(B60, "0000"), "/", VLOOKUP(D60, Internal!$B$35:C$39, 2, FALSE), IF(OR(D60="QA", D60="Revision"), _xlfn.CONCAT("/", H60), "")))</f>
-        <v/>
-      </c>
-      <c r="D60" s="44"/>
-      <c r="E60" s="43"/>
-      <c r="F60" s="43"/>
-      <c r="G60" s="44"/>
-      <c r="H60" s="43"/>
-      <c r="I60" s="46"/>
-      <c r="J60" s="46"/>
+        <v>T0050/R/T0043/D</v>
+      </c>
+      <c r="D60" s="44" t="s">
+        <v>47</v>
+      </c>
+      <c r="E60" s="43" t="s">
+        <v>48</v>
+      </c>
+      <c r="F60" s="43" t="s">
+        <v>49</v>
+      </c>
+      <c r="G60" s="44" t="s">
+        <v>50</v>
+      </c>
+      <c r="H60" s="43" t="s">
+        <v>99</v>
+      </c>
+      <c r="I60" s="46">
+        <v>46082.75</v>
+      </c>
+      <c r="J60" s="46">
+        <v>46082.754166666666</v>
+      </c>
       <c r="K60" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L60" s="47"/>
-      <c r="M60" s="47"/>
-      <c r="N60" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L60" s="47">
+        <v>8.3333333333333329E-2</v>
+      </c>
+      <c r="M60" s="47">
+        <v>8.3333333333333329E-2</v>
+      </c>
+      <c r="N60" s="45">
         <f>IF(ISBLANK(L60), "", L60*VLOOKUP($F60,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O60" s="45" t="str">
+        <v>2.5</v>
+      </c>
+      <c r="O60" s="45">
         <f>IF(ISBLANK(M60), "", M60*VLOOKUP($F60,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P60" s="44"/>
-    </row>
-    <row r="61" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+        <v>2.5</v>
+      </c>
+      <c r="P60" s="44" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="61" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B61" s="41">
         <v>51</v>
       </c>
       <c r="C61" s="42" t="str">
         <f>IF(ISBLANK(D61), "", _xlfn.CONCAT("T", TEXT(B61, "0000"), "/", VLOOKUP(D61, Internal!$B$35:C$39, 2, FALSE), IF(OR(D61="QA", D61="Revision"), _xlfn.CONCAT("/", H61), "")))</f>
-        <v/>
-      </c>
-      <c r="D61" s="44"/>
-      <c r="E61" s="43"/>
-      <c r="F61" s="43"/>
-      <c r="G61" s="44"/>
-      <c r="H61" s="43"/>
-      <c r="I61" s="46"/>
-      <c r="J61" s="46"/>
+        <v>T0051/R/T0045/D</v>
+      </c>
+      <c r="D61" s="44" t="s">
+        <v>47</v>
+      </c>
+      <c r="E61" s="43" t="s">
+        <v>58</v>
+      </c>
+      <c r="F61" s="43" t="s">
+        <v>49</v>
+      </c>
+      <c r="G61" s="44" t="s">
+        <v>50</v>
+      </c>
+      <c r="H61" s="43" t="s">
+        <v>100</v>
+      </c>
+      <c r="I61" s="46">
+        <v>46083.75</v>
+      </c>
+      <c r="J61" s="46">
+        <v>46083.756944444445</v>
+      </c>
       <c r="K61" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L61" s="47"/>
-      <c r="M61" s="47"/>
-      <c r="N61" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L61" s="47">
+        <v>0.08</v>
+      </c>
+      <c r="M61" s="47">
+        <v>0.08</v>
+      </c>
+      <c r="N61" s="45">
         <f>IF(ISBLANK(L61), "", L61*VLOOKUP($F61,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O61" s="45" t="str">
+        <v>2.4</v>
+      </c>
+      <c r="O61" s="45">
         <f>IF(ISBLANK(M61), "", M61*VLOOKUP($F61,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P61" s="44"/>
-    </row>
-    <row r="62" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+        <v>2.4</v>
+      </c>
+      <c r="P61" s="44" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="62" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B62" s="41">
         <v>52</v>
       </c>
       <c r="C62" s="42" t="str">
         <f>IF(ISBLANK(D62), "", _xlfn.CONCAT("T", TEXT(B62, "0000"), "/", VLOOKUP(D62, Internal!$B$35:C$39, 2, FALSE), IF(OR(D62="QA", D62="Revision"), _xlfn.CONCAT("/", H62), "")))</f>
-        <v/>
-      </c>
-      <c r="D62" s="44"/>
-      <c r="E62" s="43"/>
-      <c r="F62" s="43"/>
-      <c r="G62" s="44"/>
-      <c r="H62" s="43"/>
-      <c r="I62" s="46"/>
-      <c r="J62" s="46"/>
+        <v>T0052/R/T0044/D</v>
+      </c>
+      <c r="D62" s="44" t="s">
+        <v>47</v>
+      </c>
+      <c r="E62" s="43" t="s">
+        <v>60</v>
+      </c>
+      <c r="F62" s="43" t="s">
+        <v>49</v>
+      </c>
+      <c r="G62" s="44" t="s">
+        <v>50</v>
+      </c>
+      <c r="H62" s="43" t="s">
+        <v>101</v>
+      </c>
+      <c r="I62" s="46">
+        <v>46086.444444444445</v>
+      </c>
+      <c r="J62" s="46">
+        <v>46086.465277777781</v>
+      </c>
       <c r="K62" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L62" s="47"/>
-      <c r="M62" s="47"/>
-      <c r="N62" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L62" s="47">
+        <v>1</v>
+      </c>
+      <c r="M62" s="47">
+        <v>0.5</v>
+      </c>
+      <c r="N62" s="45">
         <f>IF(ISBLANK(L62), "", L62*VLOOKUP($F62,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O62" s="45" t="str">
+        <v>30</v>
+      </c>
+      <c r="O62" s="45">
         <f>IF(ISBLANK(M62), "", M62*VLOOKUP($F62,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P62" s="44"/>
-    </row>
-    <row r="63" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+        <v>15</v>
+      </c>
+      <c r="P62" s="44" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="63" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B63" s="41">
         <v>53</v>
       </c>
       <c r="C63" s="42" t="str">
         <f>IF(ISBLANK(D63), "", _xlfn.CONCAT("T", TEXT(B63, "0000"), "/", VLOOKUP(D63, Internal!$B$35:C$39, 2, FALSE), IF(OR(D63="QA", D63="Revision"), _xlfn.CONCAT("/", H63), "")))</f>
-        <v/>
-      </c>
-      <c r="D63" s="44"/>
-      <c r="E63" s="43"/>
-      <c r="F63" s="43"/>
-      <c r="G63" s="44"/>
+        <v>T0053/D</v>
+      </c>
+      <c r="D63" s="44" t="s">
+        <v>41</v>
+      </c>
+      <c r="E63" s="43" t="s">
+        <v>31</v>
+      </c>
+      <c r="F63" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="G63" s="44" t="s">
+        <v>43</v>
+      </c>
       <c r="H63" s="43"/>
-      <c r="I63" s="46"/>
-      <c r="J63" s="46"/>
+      <c r="I63" s="46">
+        <v>46086.520833333336</v>
+      </c>
+      <c r="J63" s="46">
+        <v>46086.548611111109</v>
+      </c>
       <c r="K63" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L63" s="47"/>
-      <c r="M63" s="47"/>
-      <c r="N63" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L63" s="47">
+        <v>0.5</v>
+      </c>
+      <c r="M63" s="47">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="N63" s="45">
         <f>IF(ISBLANK(L63), "", L63*VLOOKUP($F63,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O63" s="45" t="str">
+        <v>12.5</v>
+      </c>
+      <c r="O63" s="45">
         <f>IF(ISBLANK(M63), "", M63*VLOOKUP($F63,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P63" s="44"/>
-    </row>
-    <row r="64" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+        <v>16.666666666666664</v>
+      </c>
+      <c r="P63" s="44" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="64" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B64" s="41">
         <v>54</v>
       </c>
       <c r="C64" s="42" t="str">
         <f>IF(ISBLANK(D64), "", _xlfn.CONCAT("T", TEXT(B64, "0000"), "/", VLOOKUP(D64, Internal!$B$35:C$39, 2, FALSE), IF(OR(D64="QA", D64="Revision"), _xlfn.CONCAT("/", H64), "")))</f>
-        <v/>
-      </c>
-      <c r="D64" s="44"/>
-      <c r="E64" s="43"/>
-      <c r="F64" s="43"/>
-      <c r="G64" s="44"/>
-      <c r="H64" s="43"/>
-      <c r="I64" s="46"/>
-      <c r="J64" s="46"/>
+        <v>T0054/R/T0053/D</v>
+      </c>
+      <c r="D64" s="44" t="s">
+        <v>47</v>
+      </c>
+      <c r="E64" s="43" t="s">
+        <v>48</v>
+      </c>
+      <c r="F64" s="43" t="s">
+        <v>49</v>
+      </c>
+      <c r="G64" s="44" t="s">
+        <v>50</v>
+      </c>
+      <c r="H64" s="43" t="s">
+        <v>103</v>
+      </c>
+      <c r="I64" s="46">
+        <v>46086.552083333336</v>
+      </c>
+      <c r="J64" s="46">
+        <v>46086.555555555555</v>
+      </c>
       <c r="K64" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L64" s="47"/>
-      <c r="M64" s="47"/>
-      <c r="N64" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L64" s="47">
+        <v>8.3333333333333329E-2</v>
+      </c>
+      <c r="M64" s="47">
+        <v>8.3333333333333329E-2</v>
+      </c>
+      <c r="N64" s="45">
         <f>IF(ISBLANK(L64), "", L64*VLOOKUP($F64,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O64" s="45" t="str">
+        <v>2.5</v>
+      </c>
+      <c r="O64" s="45">
         <f>IF(ISBLANK(M64), "", M64*VLOOKUP($F64,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P64" s="44"/>
-    </row>
-    <row r="65" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+        <v>2.5</v>
+      </c>
+      <c r="P64" s="44" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B65" s="41">
         <v>55</v>
       </c>
       <c r="C65" s="42" t="str">
         <f>IF(ISBLANK(D65), "", _xlfn.CONCAT("T", TEXT(B65, "0000"), "/", VLOOKUP(D65, Internal!$B$35:C$39, 2, FALSE), IF(OR(D65="QA", D65="Revision"), _xlfn.CONCAT("/", H65), "")))</f>
-        <v/>
-      </c>
-      <c r="D65" s="44"/>
-      <c r="E65" s="43"/>
-      <c r="F65" s="43"/>
-      <c r="G65" s="44"/>
+        <v>T0055/D</v>
+      </c>
+      <c r="D65" s="44" t="s">
+        <v>41</v>
+      </c>
+      <c r="E65" s="43" t="s">
+        <v>31</v>
+      </c>
+      <c r="F65" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="G65" s="44" t="s">
+        <v>56</v>
+      </c>
       <c r="H65" s="43"/>
-      <c r="I65" s="46"/>
-      <c r="J65" s="46"/>
+      <c r="I65" s="46">
+        <v>46088.8125</v>
+      </c>
+      <c r="J65" s="46">
+        <v>46088.993055555555</v>
+      </c>
       <c r="K65" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L65" s="47"/>
-      <c r="M65" s="47"/>
-      <c r="N65" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L65" s="47">
+        <v>3</v>
+      </c>
+      <c r="M65" s="47">
+        <v>3.5</v>
+      </c>
+      <c r="N65" s="45">
         <f>IF(ISBLANK(L65), "", L65*VLOOKUP($F65,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O65" s="45" t="str">
+        <v>75</v>
+      </c>
+      <c r="O65" s="45">
         <f>IF(ISBLANK(M65), "", M65*VLOOKUP($F65,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P65" s="44"/>
+        <v>87.5</v>
+      </c>
+      <c r="P65" s="44" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="66" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B66" s="41">
@@ -4313,30 +4809,48 @@
       </c>
       <c r="C66" s="42" t="str">
         <f>IF(ISBLANK(D66), "", _xlfn.CONCAT("T", TEXT(B66, "0000"), "/", VLOOKUP(D66, Internal!$B$35:C$39, 2, FALSE), IF(OR(D66="QA", D66="Revision"), _xlfn.CONCAT("/", H66), "")))</f>
-        <v/>
-      </c>
-      <c r="D66" s="44"/>
-      <c r="E66" s="43"/>
-      <c r="F66" s="43"/>
-      <c r="G66" s="44"/>
+        <v>T0056/D</v>
+      </c>
+      <c r="D66" s="44" t="s">
+        <v>41</v>
+      </c>
+      <c r="E66" s="43" t="s">
+        <v>62</v>
+      </c>
+      <c r="F66" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="G66" s="44" t="s">
+        <v>56</v>
+      </c>
       <c r="H66" s="43"/>
-      <c r="I66" s="46"/>
-      <c r="J66" s="46"/>
+      <c r="I66" s="46">
+        <v>46089.770833333336</v>
+      </c>
+      <c r="J66" s="46">
+        <v>46096.666666666664</v>
+      </c>
       <c r="K66" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L66" s="47"/>
-      <c r="M66" s="47"/>
-      <c r="N66" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L66" s="47">
+        <v>3</v>
+      </c>
+      <c r="M66" s="47">
+        <v>3</v>
+      </c>
+      <c r="N66" s="45">
         <f>IF(ISBLANK(L66), "", L66*VLOOKUP($F66,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O66" s="45" t="str">
+        <v>75</v>
+      </c>
+      <c r="O66" s="45">
         <f>IF(ISBLANK(M66), "", M66*VLOOKUP($F66,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P66" s="44"/>
+        <v>75</v>
+      </c>
+      <c r="P66" s="44" t="s">
+        <v>105</v>
+      </c>
     </row>
     <row r="67" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B67" s="41">
@@ -4344,30 +4858,48 @@
       </c>
       <c r="C67" s="42" t="str">
         <f>IF(ISBLANK(D67), "", _xlfn.CONCAT("T", TEXT(B67, "0000"), "/", VLOOKUP(D67, Internal!$B$35:C$39, 2, FALSE), IF(OR(D67="QA", D67="Revision"), _xlfn.CONCAT("/", H67), "")))</f>
-        <v/>
-      </c>
-      <c r="D67" s="44"/>
-      <c r="E67" s="43"/>
-      <c r="F67" s="43"/>
-      <c r="G67" s="44"/>
+        <v>T0057/D</v>
+      </c>
+      <c r="D67" s="44" t="s">
+        <v>41</v>
+      </c>
+      <c r="E67" s="43" t="s">
+        <v>48</v>
+      </c>
+      <c r="F67" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="G67" s="44" t="s">
+        <v>56</v>
+      </c>
       <c r="H67" s="43"/>
-      <c r="I67" s="46"/>
-      <c r="J67" s="46"/>
+      <c r="I67" s="46">
+        <v>46089.5</v>
+      </c>
+      <c r="J67" s="46">
+        <v>46094.723611111112</v>
+      </c>
       <c r="K67" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L67" s="47"/>
-      <c r="M67" s="47"/>
-      <c r="N67" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L67" s="47">
+        <v>3</v>
+      </c>
+      <c r="M67" s="47">
+        <v>4</v>
+      </c>
+      <c r="N67" s="45">
         <f>IF(ISBLANK(L67), "", L67*VLOOKUP($F67,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O67" s="45" t="str">
+        <v>75</v>
+      </c>
+      <c r="O67" s="45">
         <f>IF(ISBLANK(M67), "", M67*VLOOKUP($F67,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P67" s="44"/>
+        <v>100</v>
+      </c>
+      <c r="P67" s="44" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="68" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B68" s="41">
@@ -4375,30 +4907,48 @@
       </c>
       <c r="C68" s="42" t="str">
         <f>IF(ISBLANK(D68), "", _xlfn.CONCAT("T", TEXT(B68, "0000"), "/", VLOOKUP(D68, Internal!$B$35:C$39, 2, FALSE), IF(OR(D68="QA", D68="Revision"), _xlfn.CONCAT("/", H68), "")))</f>
-        <v/>
-      </c>
-      <c r="D68" s="44"/>
-      <c r="E68" s="43"/>
-      <c r="F68" s="43"/>
-      <c r="G68" s="44"/>
+        <v>T0058/D</v>
+      </c>
+      <c r="D68" s="44" t="s">
+        <v>41</v>
+      </c>
+      <c r="E68" s="43" t="s">
+        <v>58</v>
+      </c>
+      <c r="F68" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="G68" s="44" t="s">
+        <v>56</v>
+      </c>
       <c r="H68" s="43"/>
-      <c r="I68" s="46"/>
-      <c r="J68" s="46"/>
+      <c r="I68" s="46">
+        <v>46089.5</v>
+      </c>
+      <c r="J68" s="46">
+        <v>46095.698611111111</v>
+      </c>
       <c r="K68" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L68" s="47"/>
-      <c r="M68" s="47"/>
-      <c r="N68" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L68" s="47">
+        <v>3</v>
+      </c>
+      <c r="M68" s="47">
+        <v>4</v>
+      </c>
+      <c r="N68" s="45">
         <f>IF(ISBLANK(L68), "", L68*VLOOKUP($F68,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O68" s="45" t="str">
+        <v>75</v>
+      </c>
+      <c r="O68" s="45">
         <f>IF(ISBLANK(M68), "", M68*VLOOKUP($F68,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P68" s="44"/>
+        <v>100</v>
+      </c>
+      <c r="P68" s="44" t="s">
+        <v>107</v>
+      </c>
     </row>
     <row r="69" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B69" s="41">
@@ -4406,30 +4956,48 @@
       </c>
       <c r="C69" s="42" t="str">
         <f>IF(ISBLANK(D69), "", _xlfn.CONCAT("T", TEXT(B69, "0000"), "/", VLOOKUP(D69, Internal!$B$35:C$39, 2, FALSE), IF(OR(D69="QA", D69="Revision"), _xlfn.CONCAT("/", H69), "")))</f>
-        <v/>
-      </c>
-      <c r="D69" s="44"/>
-      <c r="E69" s="43"/>
-      <c r="F69" s="43"/>
-      <c r="G69" s="44"/>
+        <v>T0059/D</v>
+      </c>
+      <c r="D69" s="44" t="s">
+        <v>41</v>
+      </c>
+      <c r="E69" s="43" t="s">
+        <v>60</v>
+      </c>
+      <c r="F69" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="G69" s="44" t="s">
+        <v>56</v>
+      </c>
       <c r="H69" s="43"/>
-      <c r="I69" s="46"/>
-      <c r="J69" s="46"/>
+      <c r="I69" s="46">
+        <v>46097.493055555555</v>
+      </c>
+      <c r="J69" s="46">
+        <v>46099.625</v>
+      </c>
       <c r="K69" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L69" s="47"/>
-      <c r="M69" s="47"/>
-      <c r="N69" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L69" s="47">
+        <v>3</v>
+      </c>
+      <c r="M69" s="47">
+        <v>4</v>
+      </c>
+      <c r="N69" s="45">
         <f>IF(ISBLANK(L69), "", L69*VLOOKUP($F69,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O69" s="45" t="str">
+        <v>75</v>
+      </c>
+      <c r="O69" s="45">
         <f>IF(ISBLANK(M69), "", M69*VLOOKUP($F69,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P69" s="44"/>
+        <v>100</v>
+      </c>
+      <c r="P69" s="44" t="s">
+        <v>108</v>
+      </c>
     </row>
     <row r="70" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B70" s="41">
@@ -4437,30 +5005,50 @@
       </c>
       <c r="C70" s="42" t="str">
         <f>IF(ISBLANK(D70), "", _xlfn.CONCAT("T", TEXT(B70, "0000"), "/", VLOOKUP(D70, Internal!$B$35:C$39, 2, FALSE), IF(OR(D70="QA", D70="Revision"), _xlfn.CONCAT("/", H70), "")))</f>
-        <v/>
-      </c>
-      <c r="D70" s="44"/>
-      <c r="E70" s="43"/>
-      <c r="F70" s="43"/>
-      <c r="G70" s="44"/>
-      <c r="H70" s="43"/>
-      <c r="I70" s="46"/>
-      <c r="J70" s="46"/>
+        <v>T0060/R/T0059/D</v>
+      </c>
+      <c r="D70" s="44" t="s">
+        <v>47</v>
+      </c>
+      <c r="E70" s="43" t="s">
+        <v>31</v>
+      </c>
+      <c r="F70" s="43" t="s">
+        <v>49</v>
+      </c>
+      <c r="G70" s="44" t="s">
+        <v>50</v>
+      </c>
+      <c r="H70" s="43" t="s">
+        <v>109</v>
+      </c>
+      <c r="I70" s="46">
+        <v>46097.75</v>
+      </c>
+      <c r="J70" s="46">
+        <v>46097.753472222219</v>
+      </c>
       <c r="K70" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L70" s="47"/>
-      <c r="M70" s="47"/>
-      <c r="N70" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L70" s="47">
+        <v>8.3333333333333329E-2</v>
+      </c>
+      <c r="M70" s="47">
+        <v>8.3333333333333329E-2</v>
+      </c>
+      <c r="N70" s="45">
         <f>IF(ISBLANK(L70), "", L70*VLOOKUP($F70,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O70" s="45" t="str">
+        <v>2.5</v>
+      </c>
+      <c r="O70" s="45">
         <f>IF(ISBLANK(M70), "", M70*VLOOKUP($F70,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P70" s="44"/>
+        <v>2.5</v>
+      </c>
+      <c r="P70" s="44" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="71" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B71" s="41">
@@ -4468,30 +5056,50 @@
       </c>
       <c r="C71" s="42" t="str">
         <f>IF(ISBLANK(D71), "", _xlfn.CONCAT("T", TEXT(B71, "0000"), "/", VLOOKUP(D71, Internal!$B$35:C$39, 2, FALSE), IF(OR(D71="QA", D71="Revision"), _xlfn.CONCAT("/", H71), "")))</f>
-        <v/>
-      </c>
-      <c r="D71" s="44"/>
-      <c r="E71" s="43"/>
-      <c r="F71" s="43"/>
-      <c r="G71" s="44"/>
-      <c r="H71" s="43"/>
-      <c r="I71" s="46"/>
-      <c r="J71" s="46"/>
+        <v>T0061/R/T0058/D</v>
+      </c>
+      <c r="D71" s="44" t="s">
+        <v>47</v>
+      </c>
+      <c r="E71" s="43" t="s">
+        <v>62</v>
+      </c>
+      <c r="F71" s="43" t="s">
+        <v>49</v>
+      </c>
+      <c r="G71" s="44" t="s">
+        <v>50</v>
+      </c>
+      <c r="H71" s="43" t="s">
+        <v>110</v>
+      </c>
+      <c r="I71" s="46">
+        <v>46095.5</v>
+      </c>
+      <c r="J71" s="46">
+        <v>46095.506944444445</v>
+      </c>
       <c r="K71" s="45" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L71" s="47"/>
-      <c r="M71" s="47"/>
-      <c r="N71" s="45" t="str">
+        <f ca="1">IF(OR(I71="",J71=""),"",IF(AND(J71&lt;&gt;"",I71&gt;=NOW()),"Planned",IF(AND(J71&lt;&gt;"",J71&lt;NOW()),"Completed","Ongoing")))</f>
+        <v>Completed</v>
+      </c>
+      <c r="L71" s="47">
+        <v>0.08</v>
+      </c>
+      <c r="M71" s="47">
+        <v>0.08</v>
+      </c>
+      <c r="N71" s="45">
         <f>IF(ISBLANK(L71), "", L71*VLOOKUP($F71,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O71" s="45" t="str">
+        <v>2.4</v>
+      </c>
+      <c r="O71" s="45">
         <f>IF(ISBLANK(M71), "", M71*VLOOKUP($F71,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P71" s="44"/>
+        <v>2.4</v>
+      </c>
+      <c r="P71" s="44" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="72" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B72" s="41">
@@ -4499,154 +5107,250 @@
       </c>
       <c r="C72" s="42" t="str">
         <f>IF(ISBLANK(D72), "", _xlfn.CONCAT("T", TEXT(B72, "0000"), "/", VLOOKUP(D72, Internal!$B$35:C$39, 2, FALSE), IF(OR(D72="QA", D72="Revision"), _xlfn.CONCAT("/", H72), "")))</f>
-        <v/>
-      </c>
-      <c r="D72" s="44"/>
-      <c r="E72" s="43"/>
-      <c r="F72" s="43"/>
-      <c r="G72" s="44"/>
-      <c r="H72" s="43"/>
-      <c r="I72" s="46"/>
-      <c r="J72" s="46"/>
+        <v>T0062/R/T0055/D</v>
+      </c>
+      <c r="D72" s="44" t="s">
+        <v>47</v>
+      </c>
+      <c r="E72" s="43" t="s">
+        <v>48</v>
+      </c>
+      <c r="F72" s="43" t="s">
+        <v>49</v>
+      </c>
+      <c r="G72" s="44" t="s">
+        <v>50</v>
+      </c>
+      <c r="H72" s="43" t="s">
+        <v>111</v>
+      </c>
+      <c r="I72" s="46">
+        <v>46094.486111111109</v>
+      </c>
+      <c r="J72" s="46">
+        <v>46094.493055555555</v>
+      </c>
       <c r="K72" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L72" s="47"/>
-      <c r="M72" s="47"/>
-      <c r="N72" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L72" s="47">
+        <v>8.3333333333333329E-2</v>
+      </c>
+      <c r="M72" s="47">
+        <v>8.3333333333333329E-2</v>
+      </c>
+      <c r="N72" s="45">
         <f>IF(ISBLANK(L72), "", L72*VLOOKUP($F72,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O72" s="45" t="str">
+        <v>2.5</v>
+      </c>
+      <c r="O72" s="45">
         <f>IF(ISBLANK(M72), "", M72*VLOOKUP($F72,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P72" s="44"/>
-    </row>
-    <row r="73" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+        <v>2.5</v>
+      </c>
+      <c r="P72" s="44" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="73" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B73" s="41">
         <v>63</v>
       </c>
       <c r="C73" s="42" t="str">
         <f>IF(ISBLANK(D73), "", _xlfn.CONCAT("T", TEXT(B73, "0000"), "/", VLOOKUP(D73, Internal!$B$35:C$39, 2, FALSE), IF(OR(D73="QA", D73="Revision"), _xlfn.CONCAT("/", H73), "")))</f>
-        <v/>
-      </c>
-      <c r="D73" s="44"/>
-      <c r="E73" s="43"/>
-      <c r="F73" s="43"/>
-      <c r="G73" s="44"/>
-      <c r="H73" s="43"/>
-      <c r="I73" s="46"/>
-      <c r="J73" s="46"/>
+        <v>T0063/R/T0057/D</v>
+      </c>
+      <c r="D73" s="44" t="s">
+        <v>47</v>
+      </c>
+      <c r="E73" s="43" t="s">
+        <v>58</v>
+      </c>
+      <c r="F73" s="43" t="s">
+        <v>49</v>
+      </c>
+      <c r="G73" s="44" t="s">
+        <v>50</v>
+      </c>
+      <c r="H73" s="43" t="s">
+        <v>112</v>
+      </c>
+      <c r="I73" s="46">
+        <v>46094.444444444445</v>
+      </c>
+      <c r="J73" s="46">
+        <v>46094.451388888891</v>
+      </c>
       <c r="K73" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L73" s="47"/>
-      <c r="M73" s="47"/>
-      <c r="N73" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L73" s="47">
+        <v>0.08</v>
+      </c>
+      <c r="M73" s="47">
+        <v>0.08</v>
+      </c>
+      <c r="N73" s="45">
         <f>IF(ISBLANK(L73), "", L73*VLOOKUP($F73,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O73" s="45" t="str">
+        <v>2.4</v>
+      </c>
+      <c r="O73" s="45">
         <f>IF(ISBLANK(M73), "", M73*VLOOKUP($F73,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P73" s="44"/>
-    </row>
-    <row r="74" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+        <v>2.4</v>
+      </c>
+      <c r="P73" s="44" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="74" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B74" s="41">
         <v>64</v>
       </c>
       <c r="C74" s="42" t="str">
         <f>IF(ISBLANK(D74), "", _xlfn.CONCAT("T", TEXT(B74, "0000"), "/", VLOOKUP(D74, Internal!$B$35:C$39, 2, FALSE), IF(OR(D74="QA", D74="Revision"), _xlfn.CONCAT("/", H74), "")))</f>
-        <v/>
-      </c>
-      <c r="D74" s="44"/>
-      <c r="E74" s="43"/>
-      <c r="F74" s="43"/>
-      <c r="G74" s="44"/>
-      <c r="H74" s="43"/>
-      <c r="I74" s="46"/>
-      <c r="J74" s="46"/>
+        <v>T0064/R/T0056/D</v>
+      </c>
+      <c r="D74" s="44" t="s">
+        <v>47</v>
+      </c>
+      <c r="E74" s="43" t="s">
+        <v>60</v>
+      </c>
+      <c r="F74" s="43" t="s">
+        <v>49</v>
+      </c>
+      <c r="G74" s="44" t="s">
+        <v>50</v>
+      </c>
+      <c r="H74" s="43" t="s">
+        <v>113</v>
+      </c>
+      <c r="I74" s="46">
+        <v>46096.888888888891</v>
+      </c>
+      <c r="J74" s="46">
+        <v>46096.909722222219</v>
+      </c>
       <c r="K74" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L74" s="47"/>
-      <c r="M74" s="47"/>
-      <c r="N74" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L74" s="47">
+        <v>0.33</v>
+      </c>
+      <c r="M74" s="47">
+        <v>0.5</v>
+      </c>
+      <c r="N74" s="45">
         <f>IF(ISBLANK(L74), "", L74*VLOOKUP($F74,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O74" s="45" t="str">
+        <v>9.9</v>
+      </c>
+      <c r="O74" s="45">
         <f>IF(ISBLANK(M74), "", M74*VLOOKUP($F74,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P74" s="44"/>
-    </row>
-    <row r="75" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+        <v>15</v>
+      </c>
+      <c r="P74" s="44" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="75" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B75" s="41">
         <v>65</v>
       </c>
       <c r="C75" s="42" t="str">
         <f>IF(ISBLANK(D75), "", _xlfn.CONCAT("T", TEXT(B75, "0000"), "/", VLOOKUP(D75, Internal!$B$35:C$39, 2, FALSE), IF(OR(D75="QA", D75="Revision"), _xlfn.CONCAT("/", H75), "")))</f>
-        <v/>
-      </c>
-      <c r="D75" s="44"/>
-      <c r="E75" s="43"/>
-      <c r="F75" s="43"/>
-      <c r="G75" s="44"/>
+        <v>T0065/D</v>
+      </c>
+      <c r="D75" s="44" t="s">
+        <v>41</v>
+      </c>
+      <c r="E75" s="43" t="s">
+        <v>31</v>
+      </c>
+      <c r="F75" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="G75" s="44" t="s">
+        <v>56</v>
+      </c>
       <c r="H75" s="43"/>
-      <c r="I75" s="46"/>
-      <c r="J75" s="46"/>
+      <c r="I75" s="46">
+        <v>46096.461805555555</v>
+      </c>
+      <c r="J75" s="46">
+        <v>46096.583333333336</v>
+      </c>
       <c r="K75" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L75" s="47"/>
-      <c r="M75" s="47"/>
-      <c r="N75" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L75" s="47">
+        <v>3</v>
+      </c>
+      <c r="M75" s="47">
+        <v>2</v>
+      </c>
+      <c r="N75" s="45">
         <f>IF(ISBLANK(L75), "", L75*VLOOKUP($F75,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O75" s="45" t="str">
+        <v>75</v>
+      </c>
+      <c r="O75" s="45">
         <f>IF(ISBLANK(M75), "", M75*VLOOKUP($F75,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P75" s="44"/>
-    </row>
-    <row r="76" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+        <v>50</v>
+      </c>
+      <c r="P75" s="44" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="76" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B76" s="41">
         <v>66</v>
       </c>
       <c r="C76" s="42" t="str">
         <f>IF(ISBLANK(D76), "", _xlfn.CONCAT("T", TEXT(B76, "0000"), "/", VLOOKUP(D76, Internal!$B$35:C$39, 2, FALSE), IF(OR(D76="QA", D76="Revision"), _xlfn.CONCAT("/", H76), "")))</f>
-        <v/>
-      </c>
-      <c r="D76" s="44"/>
-      <c r="E76" s="43"/>
-      <c r="F76" s="43"/>
-      <c r="G76" s="44"/>
+        <v>T0066/D</v>
+      </c>
+      <c r="D76" s="44" t="s">
+        <v>41</v>
+      </c>
+      <c r="E76" s="43" t="s">
+        <v>62</v>
+      </c>
+      <c r="F76" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="G76" s="44" t="s">
+        <v>56</v>
+      </c>
       <c r="H76" s="43"/>
-      <c r="I76" s="46"/>
-      <c r="J76" s="46"/>
+      <c r="I76" s="46">
+        <v>46096.666666666664</v>
+      </c>
+      <c r="J76" s="46">
+        <v>46096.777777777781</v>
+      </c>
       <c r="K76" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L76" s="47"/>
-      <c r="M76" s="47"/>
-      <c r="N76" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L76" s="47">
+        <v>3</v>
+      </c>
+      <c r="M76" s="47">
+        <v>3</v>
+      </c>
+      <c r="N76" s="45">
         <f>IF(ISBLANK(L76), "", L76*VLOOKUP($F76,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O76" s="45" t="str">
+        <v>75</v>
+      </c>
+      <c r="O76" s="45">
         <f>IF(ISBLANK(M76), "", M76*VLOOKUP($F76,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P76" s="44"/>
+        <v>75</v>
+      </c>
+      <c r="P76" s="44" t="s">
+        <v>115</v>
+      </c>
     </row>
     <row r="77" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B77" s="41">
@@ -4654,30 +5358,48 @@
       </c>
       <c r="C77" s="42" t="str">
         <f>IF(ISBLANK(D77), "", _xlfn.CONCAT("T", TEXT(B77, "0000"), "/", VLOOKUP(D77, Internal!$B$35:C$39, 2, FALSE), IF(OR(D77="QA", D77="Revision"), _xlfn.CONCAT("/", H77), "")))</f>
-        <v/>
-      </c>
-      <c r="D77" s="44"/>
-      <c r="E77" s="43"/>
-      <c r="F77" s="43"/>
-      <c r="G77" s="44"/>
+        <v>T0067/D</v>
+      </c>
+      <c r="D77" s="44" t="s">
+        <v>41</v>
+      </c>
+      <c r="E77" s="43" t="s">
+        <v>48</v>
+      </c>
+      <c r="F77" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="G77" s="44" t="s">
+        <v>56</v>
+      </c>
       <c r="H77" s="43"/>
-      <c r="I77" s="46"/>
-      <c r="J77" s="46"/>
+      <c r="I77" s="46">
+        <v>46094.6875</v>
+      </c>
+      <c r="J77" s="46">
+        <v>46094.78125</v>
+      </c>
       <c r="K77" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L77" s="47"/>
-      <c r="M77" s="47"/>
-      <c r="N77" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L77" s="47">
+        <v>3</v>
+      </c>
+      <c r="M77" s="47">
+        <v>2</v>
+      </c>
+      <c r="N77" s="45">
         <f>IF(ISBLANK(L77), "", L77*VLOOKUP($F77,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O77" s="45" t="str">
+        <v>75</v>
+      </c>
+      <c r="O77" s="45">
         <f>IF(ISBLANK(M77), "", M77*VLOOKUP($F77,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P77" s="44"/>
+        <v>50</v>
+      </c>
+      <c r="P77" s="44" t="s">
+        <v>116</v>
+      </c>
     </row>
     <row r="78" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B78" s="41">
@@ -4685,30 +5407,48 @@
       </c>
       <c r="C78" s="42" t="str">
         <f>IF(ISBLANK(D78), "", _xlfn.CONCAT("T", TEXT(B78, "0000"), "/", VLOOKUP(D78, Internal!$B$35:C$39, 2, FALSE), IF(OR(D78="QA", D78="Revision"), _xlfn.CONCAT("/", H78), "")))</f>
-        <v/>
-      </c>
-      <c r="D78" s="44"/>
-      <c r="E78" s="43"/>
-      <c r="F78" s="43"/>
-      <c r="G78" s="44"/>
+        <v>T0068/D</v>
+      </c>
+      <c r="D78" s="44" t="s">
+        <v>41</v>
+      </c>
+      <c r="E78" s="43" t="s">
+        <v>58</v>
+      </c>
+      <c r="F78" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="G78" s="44" t="s">
+        <v>56</v>
+      </c>
       <c r="H78" s="43"/>
-      <c r="I78" s="46"/>
-      <c r="J78" s="46"/>
+      <c r="I78" s="46">
+        <v>46095.8125</v>
+      </c>
+      <c r="J78" s="46">
+        <v>46095.854166666664</v>
+      </c>
       <c r="K78" s="45" t="str">
-        <f t="shared" ref="K78:K112" ca="1" si="2">IF(OR(I78="",J78=""),"",IF(AND(J78&lt;&gt;"",I78&gt;=NOW()),"Planned",IF(AND(J78&lt;&gt;"",J78&lt;NOW()),"Completed","Ongoing")))</f>
-        <v/>
-      </c>
-      <c r="L78" s="47"/>
-      <c r="M78" s="47"/>
-      <c r="N78" s="45" t="str">
+        <f t="shared" ref="K78:K113" ca="1" si="2">IF(OR(I78="",J78=""),"",IF(AND(J78&lt;&gt;"",I78&gt;=NOW()),"Planned",IF(AND(J78&lt;&gt;"",J78&lt;NOW()),"Completed","Ongoing")))</f>
+        <v>Completed</v>
+      </c>
+      <c r="L78" s="47">
+        <v>3</v>
+      </c>
+      <c r="M78" s="47">
+        <v>1</v>
+      </c>
+      <c r="N78" s="45">
         <f>IF(ISBLANK(L78), "", L78*VLOOKUP($F78,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O78" s="45" t="str">
+        <v>75</v>
+      </c>
+      <c r="O78" s="45">
         <f>IF(ISBLANK(M78), "", M78*VLOOKUP($F78,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P78" s="44"/>
+        <v>25</v>
+      </c>
+      <c r="P78" s="44" t="s">
+        <v>117</v>
+      </c>
     </row>
     <row r="79" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B79" s="41">
@@ -4716,30 +5456,48 @@
       </c>
       <c r="C79" s="42" t="str">
         <f>IF(ISBLANK(D79), "", _xlfn.CONCAT("T", TEXT(B79, "0000"), "/", VLOOKUP(D79, Internal!$B$35:C$39, 2, FALSE), IF(OR(D79="QA", D79="Revision"), _xlfn.CONCAT("/", H79), "")))</f>
-        <v/>
-      </c>
-      <c r="D79" s="44"/>
-      <c r="E79" s="43"/>
-      <c r="F79" s="43"/>
-      <c r="G79" s="44"/>
+        <v>T0069/D</v>
+      </c>
+      <c r="D79" s="44" t="s">
+        <v>41</v>
+      </c>
+      <c r="E79" s="43" t="s">
+        <v>60</v>
+      </c>
+      <c r="F79" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="G79" s="44" t="s">
+        <v>56</v>
+      </c>
       <c r="H79" s="43"/>
-      <c r="I79" s="46"/>
-      <c r="J79" s="46"/>
+      <c r="I79" s="46">
+        <v>46098.486111111109</v>
+      </c>
+      <c r="J79" s="46">
+        <v>46099.736111111109</v>
+      </c>
       <c r="K79" s="45" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-      <c r="L79" s="47"/>
-      <c r="M79" s="47"/>
-      <c r="N79" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L79" s="47">
+        <v>3</v>
+      </c>
+      <c r="M79" s="47">
+        <v>1</v>
+      </c>
+      <c r="N79" s="45">
         <f>IF(ISBLANK(L79), "", L79*VLOOKUP($F79,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O79" s="45" t="str">
+        <v>75</v>
+      </c>
+      <c r="O79" s="45">
         <f>IF(ISBLANK(M79), "", M79*VLOOKUP($F79,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P79" s="44"/>
+        <v>25</v>
+      </c>
+      <c r="P79" s="44" t="s">
+        <v>118</v>
+      </c>
     </row>
     <row r="80" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B80" s="41">
@@ -4747,30 +5505,50 @@
       </c>
       <c r="C80" s="42" t="str">
         <f>IF(ISBLANK(D80), "", _xlfn.CONCAT("T", TEXT(B80, "0000"), "/", VLOOKUP(D80, Internal!$B$35:C$39, 2, FALSE), IF(OR(D80="QA", D80="Revision"), _xlfn.CONCAT("/", H80), "")))</f>
-        <v/>
-      </c>
-      <c r="D80" s="44"/>
-      <c r="E80" s="43"/>
-      <c r="F80" s="43"/>
-      <c r="G80" s="44"/>
-      <c r="H80" s="43"/>
-      <c r="I80" s="46"/>
-      <c r="J80" s="46"/>
+        <v>T0070/R/T0069/D</v>
+      </c>
+      <c r="D80" s="44" t="s">
+        <v>47</v>
+      </c>
+      <c r="E80" s="43" t="s">
+        <v>31</v>
+      </c>
+      <c r="F80" s="43" t="s">
+        <v>49</v>
+      </c>
+      <c r="G80" s="44" t="s">
+        <v>50</v>
+      </c>
+      <c r="H80" s="43" t="s">
+        <v>119</v>
+      </c>
+      <c r="I80" s="46">
+        <v>46099.625</v>
+      </c>
+      <c r="J80" s="46">
+        <v>46099.628472222219</v>
+      </c>
       <c r="K80" s="45" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-      <c r="L80" s="47"/>
-      <c r="M80" s="47"/>
-      <c r="N80" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L80" s="47">
+        <v>8.3333333333333329E-2</v>
+      </c>
+      <c r="M80" s="47">
+        <v>8.3333333333333329E-2</v>
+      </c>
+      <c r="N80" s="45">
         <f>IF(ISBLANK(L80), "", L80*VLOOKUP($F80,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O80" s="45" t="str">
+        <v>2.5</v>
+      </c>
+      <c r="O80" s="45">
         <f>IF(ISBLANK(M80), "", M80*VLOOKUP($F80,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P80" s="44"/>
+        <v>2.5</v>
+      </c>
+      <c r="P80" s="44" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="81" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B81" s="41">
@@ -4778,30 +5556,50 @@
       </c>
       <c r="C81" s="42" t="str">
         <f>IF(ISBLANK(D81), "", _xlfn.CONCAT("T", TEXT(B81, "0000"), "/", VLOOKUP(D81, Internal!$B$35:C$39, 2, FALSE), IF(OR(D81="QA", D81="Revision"), _xlfn.CONCAT("/", H81), "")))</f>
-        <v/>
-      </c>
-      <c r="D81" s="44"/>
-      <c r="E81" s="43"/>
-      <c r="F81" s="43"/>
-      <c r="G81" s="44"/>
-      <c r="H81" s="43"/>
-      <c r="I81" s="46"/>
-      <c r="J81" s="46"/>
+        <v>T0071/R/T0068/D</v>
+      </c>
+      <c r="D81" s="44" t="s">
+        <v>47</v>
+      </c>
+      <c r="E81" s="43" t="s">
+        <v>62</v>
+      </c>
+      <c r="F81" s="43" t="s">
+        <v>49</v>
+      </c>
+      <c r="G81" s="44" t="s">
+        <v>50</v>
+      </c>
+      <c r="H81" s="43" t="s">
+        <v>120</v>
+      </c>
+      <c r="I81" s="46">
+        <v>46095.861111111109</v>
+      </c>
+      <c r="J81" s="46">
+        <v>46095.864583333336</v>
+      </c>
       <c r="K81" s="45" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-      <c r="L81" s="47"/>
-      <c r="M81" s="47"/>
-      <c r="N81" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L81" s="47">
+        <v>0.08</v>
+      </c>
+      <c r="M81" s="47">
+        <v>0.08</v>
+      </c>
+      <c r="N81" s="45">
         <f>IF(ISBLANK(L81), "", L81*VLOOKUP($F81,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O81" s="45" t="str">
+        <v>2.4</v>
+      </c>
+      <c r="O81" s="45">
         <f>IF(ISBLANK(M81), "", M81*VLOOKUP($F81,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P81" s="44"/>
+        <v>2.4</v>
+      </c>
+      <c r="P81" s="44" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="82" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B82" s="41">
@@ -4809,30 +5607,50 @@
       </c>
       <c r="C82" s="42" t="str">
         <f>IF(ISBLANK(D82), "", _xlfn.CONCAT("T", TEXT(B82, "0000"), "/", VLOOKUP(D82, Internal!$B$35:C$39, 2, FALSE), IF(OR(D82="QA", D82="Revision"), _xlfn.CONCAT("/", H82), "")))</f>
-        <v/>
-      </c>
-      <c r="D82" s="44"/>
-      <c r="E82" s="43"/>
-      <c r="F82" s="43"/>
-      <c r="G82" s="44"/>
-      <c r="H82" s="43"/>
-      <c r="I82" s="46"/>
-      <c r="J82" s="46"/>
+        <v>T0072/R/T0065/D</v>
+      </c>
+      <c r="D82" s="44" t="s">
+        <v>47</v>
+      </c>
+      <c r="E82" s="43" t="s">
+        <v>48</v>
+      </c>
+      <c r="F82" s="43" t="s">
+        <v>49</v>
+      </c>
+      <c r="G82" s="44" t="s">
+        <v>50</v>
+      </c>
+      <c r="H82" s="43" t="s">
+        <v>121</v>
+      </c>
+      <c r="I82" s="46">
+        <v>46096.694444444445</v>
+      </c>
+      <c r="J82" s="46">
+        <v>46096.701388888891</v>
+      </c>
       <c r="K82" s="45" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-      <c r="L82" s="47"/>
-      <c r="M82" s="47"/>
-      <c r="N82" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L82" s="47">
+        <v>8.3333333333333329E-2</v>
+      </c>
+      <c r="M82" s="47">
+        <v>8.3333333333333329E-2</v>
+      </c>
+      <c r="N82" s="45">
         <f>IF(ISBLANK(L82), "", L82*VLOOKUP($F82,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O82" s="45" t="str">
+        <v>2.5</v>
+      </c>
+      <c r="O82" s="45">
         <f>IF(ISBLANK(M82), "", M82*VLOOKUP($F82,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P82" s="44"/>
+        <v>2.5</v>
+      </c>
+      <c r="P82" s="44" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="83" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B83" s="41">
@@ -4840,30 +5658,50 @@
       </c>
       <c r="C83" s="42" t="str">
         <f>IF(ISBLANK(D83), "", _xlfn.CONCAT("T", TEXT(B83, "0000"), "/", VLOOKUP(D83, Internal!$B$35:C$39, 2, FALSE), IF(OR(D83="QA", D83="Revision"), _xlfn.CONCAT("/", H83), "")))</f>
-        <v/>
-      </c>
-      <c r="D83" s="44"/>
-      <c r="E83" s="43"/>
-      <c r="F83" s="43"/>
-      <c r="G83" s="44"/>
-      <c r="H83" s="43"/>
-      <c r="I83" s="46"/>
-      <c r="J83" s="46"/>
+        <v>T0073/R/T0067/D</v>
+      </c>
+      <c r="D83" s="44" t="s">
+        <v>47</v>
+      </c>
+      <c r="E83" s="43" t="s">
+        <v>58</v>
+      </c>
+      <c r="F83" s="43" t="s">
+        <v>49</v>
+      </c>
+      <c r="G83" s="44" t="s">
+        <v>50</v>
+      </c>
+      <c r="H83" s="43" t="s">
+        <v>122</v>
+      </c>
+      <c r="I83" s="46">
+        <v>46096.694444444445</v>
+      </c>
+      <c r="J83" s="46">
+        <v>46096.701388888891</v>
+      </c>
       <c r="K83" s="45" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-      <c r="L83" s="47"/>
-      <c r="M83" s="47"/>
-      <c r="N83" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L83" s="47">
+        <v>0.08</v>
+      </c>
+      <c r="M83" s="47">
+        <v>0.08</v>
+      </c>
+      <c r="N83" s="45">
         <f>IF(ISBLANK(L83), "", L83*VLOOKUP($F83,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O83" s="45" t="str">
+        <v>2.4</v>
+      </c>
+      <c r="O83" s="45">
         <f>IF(ISBLANK(M83), "", M83*VLOOKUP($F83,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P83" s="44"/>
+        <v>2.4</v>
+      </c>
+      <c r="P83" s="44" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="84" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B84" s="41">
@@ -4871,30 +5709,50 @@
       </c>
       <c r="C84" s="42" t="str">
         <f>IF(ISBLANK(D84), "", _xlfn.CONCAT("T", TEXT(B84, "0000"), "/", VLOOKUP(D84, Internal!$B$35:C$39, 2, FALSE), IF(OR(D84="QA", D84="Revision"), _xlfn.CONCAT("/", H84), "")))</f>
-        <v/>
-      </c>
-      <c r="D84" s="44"/>
-      <c r="E84" s="43"/>
-      <c r="F84" s="43"/>
-      <c r="G84" s="44"/>
-      <c r="H84" s="43"/>
-      <c r="I84" s="46"/>
-      <c r="J84" s="46"/>
+        <v>T0074/R/T0066/D</v>
+      </c>
+      <c r="D84" s="44" t="s">
+        <v>47</v>
+      </c>
+      <c r="E84" s="43" t="s">
+        <v>60</v>
+      </c>
+      <c r="F84" s="43" t="s">
+        <v>49</v>
+      </c>
+      <c r="G84" s="44" t="s">
+        <v>50</v>
+      </c>
+      <c r="H84" s="43" t="s">
+        <v>123</v>
+      </c>
+      <c r="I84" s="46">
+        <v>46097.475694444445</v>
+      </c>
+      <c r="J84" s="46">
+        <v>46097.486111111109</v>
+      </c>
       <c r="K84" s="45" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-      <c r="L84" s="47"/>
-      <c r="M84" s="47"/>
-      <c r="N84" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L84" s="47">
+        <v>0.5</v>
+      </c>
+      <c r="M84" s="47">
+        <v>0.25</v>
+      </c>
+      <c r="N84" s="45">
         <f>IF(ISBLANK(L84), "", L84*VLOOKUP($F84,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O84" s="45" t="str">
+        <v>15</v>
+      </c>
+      <c r="O84" s="45">
         <f>IF(ISBLANK(M84), "", M84*VLOOKUP($F84,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P84" s="44"/>
+        <v>7.5</v>
+      </c>
+      <c r="P84" s="44" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="85" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B85" s="41">
@@ -4902,30 +5760,48 @@
       </c>
       <c r="C85" s="42" t="str">
         <f>IF(ISBLANK(D85), "", _xlfn.CONCAT("T", TEXT(B85, "0000"), "/", VLOOKUP(D85, Internal!$B$35:C$39, 2, FALSE), IF(OR(D85="QA", D85="Revision"), _xlfn.CONCAT("/", H85), "")))</f>
-        <v/>
-      </c>
-      <c r="D85" s="44"/>
-      <c r="E85" s="43"/>
-      <c r="F85" s="43"/>
-      <c r="G85" s="44"/>
+        <v>T0075/D</v>
+      </c>
+      <c r="D85" s="44" t="s">
+        <v>41</v>
+      </c>
+      <c r="E85" s="43" t="s">
+        <v>31</v>
+      </c>
+      <c r="F85" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="G85" s="44" t="s">
+        <v>56</v>
+      </c>
       <c r="H85" s="43"/>
-      <c r="I85" s="46"/>
-      <c r="J85" s="46"/>
+      <c r="I85" s="46">
+        <v>46095.583333333336</v>
+      </c>
+      <c r="J85" s="46">
+        <v>46096.041666666664</v>
+      </c>
       <c r="K85" s="45" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-      <c r="L85" s="47"/>
-      <c r="M85" s="47"/>
-      <c r="N85" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L85" s="47">
+        <v>4</v>
+      </c>
+      <c r="M85" s="47">
+        <v>10</v>
+      </c>
+      <c r="N85" s="45">
         <f>IF(ISBLANK(L85), "", L85*VLOOKUP($F85,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O85" s="45" t="str">
+        <v>100</v>
+      </c>
+      <c r="O85" s="45">
         <f>IF(ISBLANK(M85), "", M85*VLOOKUP($F85,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P85" s="44"/>
+        <v>250</v>
+      </c>
+      <c r="P85" s="44" t="s">
+        <v>124</v>
+      </c>
     </row>
     <row r="86" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B86" s="41">
@@ -4933,30 +5809,48 @@
       </c>
       <c r="C86" s="42" t="str">
         <f>IF(ISBLANK(D86), "", _xlfn.CONCAT("T", TEXT(B86, "0000"), "/", VLOOKUP(D86, Internal!$B$35:C$39, 2, FALSE), IF(OR(D86="QA", D86="Revision"), _xlfn.CONCAT("/", H86), "")))</f>
-        <v/>
-      </c>
-      <c r="D86" s="44"/>
-      <c r="E86" s="43"/>
-      <c r="F86" s="43"/>
-      <c r="G86" s="44"/>
+        <v>T0076/D</v>
+      </c>
+      <c r="D86" s="44" t="s">
+        <v>41</v>
+      </c>
+      <c r="E86" s="43" t="s">
+        <v>62</v>
+      </c>
+      <c r="F86" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="G86" s="44" t="s">
+        <v>56</v>
+      </c>
       <c r="H86" s="43"/>
-      <c r="I86" s="46"/>
-      <c r="J86" s="46"/>
+      <c r="I86" s="46">
+        <v>46096.791666666664</v>
+      </c>
+      <c r="J86" s="46">
+        <v>46100.75</v>
+      </c>
       <c r="K86" s="45" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-      <c r="L86" s="47"/>
-      <c r="M86" s="47"/>
-      <c r="N86" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L86" s="47">
+        <v>4</v>
+      </c>
+      <c r="M86" s="47">
+        <v>4</v>
+      </c>
+      <c r="N86" s="45">
         <f>IF(ISBLANK(L86), "", L86*VLOOKUP($F86,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O86" s="45" t="str">
+        <v>100</v>
+      </c>
+      <c r="O86" s="45">
         <f>IF(ISBLANK(M86), "", M86*VLOOKUP($F86,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P86" s="44"/>
+        <v>100</v>
+      </c>
+      <c r="P86" s="44" t="s">
+        <v>125</v>
+      </c>
     </row>
     <row r="87" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B87" s="41">
@@ -4964,30 +5858,48 @@
       </c>
       <c r="C87" s="42" t="str">
         <f>IF(ISBLANK(D87), "", _xlfn.CONCAT("T", TEXT(B87, "0000"), "/", VLOOKUP(D87, Internal!$B$35:C$39, 2, FALSE), IF(OR(D87="QA", D87="Revision"), _xlfn.CONCAT("/", H87), "")))</f>
-        <v/>
-      </c>
-      <c r="D87" s="44"/>
-      <c r="E87" s="43"/>
-      <c r="F87" s="43"/>
-      <c r="G87" s="44"/>
+        <v>T0077/D</v>
+      </c>
+      <c r="D87" s="44" t="s">
+        <v>41</v>
+      </c>
+      <c r="E87" s="43" t="s">
+        <v>48</v>
+      </c>
+      <c r="F87" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="G87" s="44" t="s">
+        <v>56</v>
+      </c>
       <c r="H87" s="43"/>
-      <c r="I87" s="46"/>
-      <c r="J87" s="46"/>
+      <c r="I87" s="46">
+        <v>46094.8125</v>
+      </c>
+      <c r="J87" s="46">
+        <v>46098.729166666664</v>
+      </c>
       <c r="K87" s="45" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-      <c r="L87" s="47"/>
-      <c r="M87" s="47"/>
-      <c r="N87" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L87" s="47">
+        <v>4</v>
+      </c>
+      <c r="M87" s="47">
+        <v>10</v>
+      </c>
+      <c r="N87" s="45">
         <f>IF(ISBLANK(L87), "", L87*VLOOKUP($F87,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O87" s="45" t="str">
+        <v>100</v>
+      </c>
+      <c r="O87" s="45">
         <f>IF(ISBLANK(M87), "", M87*VLOOKUP($F87,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P87" s="44"/>
+        <v>250</v>
+      </c>
+      <c r="P87" s="44" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="88" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B88" s="41">
@@ -4995,30 +5907,48 @@
       </c>
       <c r="C88" s="42" t="str">
         <f>IF(ISBLANK(D88), "", _xlfn.CONCAT("T", TEXT(B88, "0000"), "/", VLOOKUP(D88, Internal!$B$35:C$39, 2, FALSE), IF(OR(D88="QA", D88="Revision"), _xlfn.CONCAT("/", H88), "")))</f>
-        <v/>
-      </c>
-      <c r="D88" s="44"/>
-      <c r="E88" s="43"/>
-      <c r="F88" s="43"/>
-      <c r="G88" s="44"/>
+        <v>T0078/D</v>
+      </c>
+      <c r="D88" s="44" t="s">
+        <v>41</v>
+      </c>
+      <c r="E88" s="43" t="s">
+        <v>58</v>
+      </c>
+      <c r="F88" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="G88" s="44" t="s">
+        <v>56</v>
+      </c>
       <c r="H88" s="43"/>
-      <c r="I88" s="46"/>
-      <c r="J88" s="46"/>
+      <c r="I88" s="46">
+        <v>46096.625</v>
+      </c>
+      <c r="J88" s="46">
+        <v>46096.804861111108</v>
+      </c>
       <c r="K88" s="45" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-      <c r="L88" s="47"/>
-      <c r="M88" s="47"/>
-      <c r="N88" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L88" s="47">
+        <v>4</v>
+      </c>
+      <c r="M88" s="47">
+        <v>4.5</v>
+      </c>
+      <c r="N88" s="45">
         <f>IF(ISBLANK(L88), "", L88*VLOOKUP($F88,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O88" s="45" t="str">
+        <v>100</v>
+      </c>
+      <c r="O88" s="45">
         <f>IF(ISBLANK(M88), "", M88*VLOOKUP($F88,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P88" s="44"/>
+        <v>112.5</v>
+      </c>
+      <c r="P88" s="44" t="s">
+        <v>127</v>
+      </c>
     </row>
     <row r="89" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B89" s="41">
@@ -5026,30 +5956,48 @@
       </c>
       <c r="C89" s="42" t="str">
         <f>IF(ISBLANK(D89), "", _xlfn.CONCAT("T", TEXT(B89, "0000"), "/", VLOOKUP(D89, Internal!$B$35:C$39, 2, FALSE), IF(OR(D89="QA", D89="Revision"), _xlfn.CONCAT("/", H89), "")))</f>
-        <v/>
-      </c>
-      <c r="D89" s="44"/>
-      <c r="E89" s="43"/>
-      <c r="F89" s="43"/>
-      <c r="G89" s="44"/>
+        <v>T0079/D</v>
+      </c>
+      <c r="D89" s="44" t="s">
+        <v>41</v>
+      </c>
+      <c r="E89" s="43" t="s">
+        <v>60</v>
+      </c>
+      <c r="F89" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="G89" s="44" t="s">
+        <v>56</v>
+      </c>
       <c r="H89" s="43"/>
-      <c r="I89" s="46"/>
-      <c r="J89" s="46"/>
+      <c r="I89" s="46">
+        <v>46099.777777777781</v>
+      </c>
+      <c r="J89" s="46">
+        <v>46100.784722222219</v>
+      </c>
       <c r="K89" s="45" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-      <c r="L89" s="47"/>
-      <c r="M89" s="47"/>
-      <c r="N89" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L89" s="47">
+        <v>4</v>
+      </c>
+      <c r="M89" s="47">
+        <v>5</v>
+      </c>
+      <c r="N89" s="45">
         <f>IF(ISBLANK(L89), "", L89*VLOOKUP($F89,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O89" s="45" t="str">
+        <v>100</v>
+      </c>
+      <c r="O89" s="45">
         <f>IF(ISBLANK(M89), "", M89*VLOOKUP($F89,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P89" s="44"/>
+        <v>125</v>
+      </c>
+      <c r="P89" s="44" t="s">
+        <v>128</v>
+      </c>
     </row>
     <row r="90" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B90" s="41">
@@ -5057,30 +6005,50 @@
       </c>
       <c r="C90" s="42" t="str">
         <f>IF(ISBLANK(D90), "", _xlfn.CONCAT("T", TEXT(B90, "0000"), "/", VLOOKUP(D90, Internal!$B$35:C$39, 2, FALSE), IF(OR(D90="QA", D90="Revision"), _xlfn.CONCAT("/", H90), "")))</f>
-        <v/>
-      </c>
-      <c r="D90" s="44"/>
-      <c r="E90" s="43"/>
-      <c r="F90" s="43"/>
-      <c r="G90" s="44"/>
-      <c r="H90" s="43"/>
-      <c r="I90" s="46"/>
-      <c r="J90" s="46"/>
+        <v>T0080/R/T0079/D</v>
+      </c>
+      <c r="D90" s="44" t="s">
+        <v>47</v>
+      </c>
+      <c r="E90" s="43" t="s">
+        <v>31</v>
+      </c>
+      <c r="F90" s="43" t="s">
+        <v>49</v>
+      </c>
+      <c r="G90" s="44" t="s">
+        <v>50</v>
+      </c>
+      <c r="H90" s="43" t="s">
+        <v>129</v>
+      </c>
+      <c r="I90" s="46">
+        <v>46100.743055555555</v>
+      </c>
+      <c r="J90" s="46">
+        <v>46100.75</v>
+      </c>
       <c r="K90" s="45" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-      <c r="L90" s="47"/>
-      <c r="M90" s="47"/>
-      <c r="N90" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L90" s="47">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="M90" s="47">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="N90" s="45">
         <f>IF(ISBLANK(L90), "", L90*VLOOKUP($F90,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O90" s="45" t="str">
+        <v>5</v>
+      </c>
+      <c r="O90" s="45">
         <f>IF(ISBLANK(M90), "", M90*VLOOKUP($F90,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P90" s="44"/>
+        <v>5</v>
+      </c>
+      <c r="P90" s="44" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="91" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B91" s="41">
@@ -5088,30 +6056,50 @@
       </c>
       <c r="C91" s="42" t="str">
         <f>IF(ISBLANK(D91), "", _xlfn.CONCAT("T", TEXT(B91, "0000"), "/", VLOOKUP(D91, Internal!$B$35:C$39, 2, FALSE), IF(OR(D91="QA", D91="Revision"), _xlfn.CONCAT("/", H91), "")))</f>
-        <v/>
-      </c>
-      <c r="D91" s="44"/>
-      <c r="E91" s="43"/>
-      <c r="F91" s="43"/>
-      <c r="G91" s="44"/>
-      <c r="H91" s="43"/>
-      <c r="I91" s="46"/>
-      <c r="J91" s="46"/>
+        <v>T0081/R/T0078/D</v>
+      </c>
+      <c r="D91" s="44" t="s">
+        <v>47</v>
+      </c>
+      <c r="E91" s="43" t="s">
+        <v>62</v>
+      </c>
+      <c r="F91" s="43" t="s">
+        <v>49</v>
+      </c>
+      <c r="G91" s="44" t="s">
+        <v>50</v>
+      </c>
+      <c r="H91" s="43" t="s">
+        <v>130</v>
+      </c>
+      <c r="I91" s="46">
+        <v>46099.75</v>
+      </c>
+      <c r="J91" s="46">
+        <v>46099.756944444445</v>
+      </c>
       <c r="K91" s="45" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-      <c r="L91" s="47"/>
-      <c r="M91" s="47"/>
-      <c r="N91" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L91" s="47">
+        <v>0.17</v>
+      </c>
+      <c r="M91" s="47">
+        <v>0.17</v>
+      </c>
+      <c r="N91" s="45">
         <f>IF(ISBLANK(L91), "", L91*VLOOKUP($F91,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O91" s="45" t="str">
+        <v>5.1000000000000005</v>
+      </c>
+      <c r="O91" s="45">
         <f>IF(ISBLANK(M91), "", M91*VLOOKUP($F91,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P91" s="44"/>
+        <v>5.1000000000000005</v>
+      </c>
+      <c r="P91" s="44" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="92" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B92" s="41">
@@ -5119,30 +6107,50 @@
       </c>
       <c r="C92" s="42" t="str">
         <f>IF(ISBLANK(D92), "", _xlfn.CONCAT("T", TEXT(B92, "0000"), "/", VLOOKUP(D92, Internal!$B$35:C$39, 2, FALSE), IF(OR(D92="QA", D92="Revision"), _xlfn.CONCAT("/", H92), "")))</f>
-        <v/>
-      </c>
-      <c r="D92" s="44"/>
-      <c r="E92" s="43"/>
-      <c r="F92" s="43"/>
-      <c r="G92" s="44"/>
-      <c r="H92" s="43"/>
-      <c r="I92" s="46"/>
-      <c r="J92" s="46"/>
+        <v>T0082/R/T0075/D</v>
+      </c>
+      <c r="D92" s="44" t="s">
+        <v>47</v>
+      </c>
+      <c r="E92" s="43" t="s">
+        <v>48</v>
+      </c>
+      <c r="F92" s="43" t="s">
+        <v>49</v>
+      </c>
+      <c r="G92" s="44" t="s">
+        <v>50</v>
+      </c>
+      <c r="H92" s="43" t="s">
+        <v>131</v>
+      </c>
+      <c r="I92" s="46">
+        <v>46100.444444444445</v>
+      </c>
+      <c r="J92" s="46">
+        <v>46100.451388888891</v>
+      </c>
       <c r="K92" s="45" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-      <c r="L92" s="47"/>
-      <c r="M92" s="47"/>
-      <c r="N92" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L92" s="47">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="M92" s="47">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="N92" s="45">
         <f>IF(ISBLANK(L92), "", L92*VLOOKUP($F92,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O92" s="45" t="str">
+        <v>5</v>
+      </c>
+      <c r="O92" s="45">
         <f>IF(ISBLANK(M92), "", M92*VLOOKUP($F92,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P92" s="44"/>
+        <v>5</v>
+      </c>
+      <c r="P92" s="44" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="93" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B93" s="41">
@@ -5150,30 +6158,50 @@
       </c>
       <c r="C93" s="42" t="str">
         <f>IF(ISBLANK(D93), "", _xlfn.CONCAT("T", TEXT(B93, "0000"), "/", VLOOKUP(D93, Internal!$B$35:C$39, 2, FALSE), IF(OR(D93="QA", D93="Revision"), _xlfn.CONCAT("/", H93), "")))</f>
-        <v/>
-      </c>
-      <c r="D93" s="44"/>
-      <c r="E93" s="43"/>
-      <c r="F93" s="43"/>
-      <c r="G93" s="44"/>
-      <c r="H93" s="43"/>
-      <c r="I93" s="46"/>
-      <c r="J93" s="46"/>
+        <v>T0083/R/T0077/D</v>
+      </c>
+      <c r="D93" s="44" t="s">
+        <v>47</v>
+      </c>
+      <c r="E93" s="43" t="s">
+        <v>58</v>
+      </c>
+      <c r="F93" s="43" t="s">
+        <v>49</v>
+      </c>
+      <c r="G93" s="44" t="s">
+        <v>50</v>
+      </c>
+      <c r="H93" s="43" t="s">
+        <v>132</v>
+      </c>
+      <c r="I93" s="46">
+        <v>46100.416666666664</v>
+      </c>
+      <c r="J93" s="46">
+        <v>46100.423611111109</v>
+      </c>
       <c r="K93" s="45" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-      <c r="L93" s="47"/>
-      <c r="M93" s="47"/>
-      <c r="N93" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L93" s="47">
+        <v>0.17</v>
+      </c>
+      <c r="M93" s="47">
+        <v>0.17</v>
+      </c>
+      <c r="N93" s="45">
         <f>IF(ISBLANK(L93), "", L93*VLOOKUP($F93,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O93" s="45" t="str">
+        <v>5.1000000000000005</v>
+      </c>
+      <c r="O93" s="45">
         <f>IF(ISBLANK(M93), "", M93*VLOOKUP($F93,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P93" s="44"/>
+        <v>5.1000000000000005</v>
+      </c>
+      <c r="P93" s="44" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="94" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B94" s="41">
@@ -5181,30 +6209,50 @@
       </c>
       <c r="C94" s="42" t="str">
         <f>IF(ISBLANK(D94), "", _xlfn.CONCAT("T", TEXT(B94, "0000"), "/", VLOOKUP(D94, Internal!$B$35:C$39, 2, FALSE), IF(OR(D94="QA", D94="Revision"), _xlfn.CONCAT("/", H94), "")))</f>
-        <v/>
-      </c>
-      <c r="D94" s="44"/>
-      <c r="E94" s="43"/>
-      <c r="F94" s="43"/>
-      <c r="G94" s="44"/>
-      <c r="H94" s="43"/>
-      <c r="I94" s="46"/>
-      <c r="J94" s="46"/>
+        <v>T0084/R/T0076/D</v>
+      </c>
+      <c r="D94" s="44" t="s">
+        <v>47</v>
+      </c>
+      <c r="E94" s="43" t="s">
+        <v>60</v>
+      </c>
+      <c r="F94" s="43" t="s">
+        <v>49</v>
+      </c>
+      <c r="G94" s="44" t="s">
+        <v>50</v>
+      </c>
+      <c r="H94" s="43" t="s">
+        <v>133</v>
+      </c>
+      <c r="I94" s="46">
+        <v>46100.486111111109</v>
+      </c>
+      <c r="J94" s="46">
+        <v>46100.534722222219</v>
+      </c>
       <c r="K94" s="45" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-      <c r="L94" s="47"/>
-      <c r="M94" s="47"/>
-      <c r="N94" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L94" s="47">
+        <v>0.5</v>
+      </c>
+      <c r="M94" s="47">
+        <v>1</v>
+      </c>
+      <c r="N94" s="45">
         <f>IF(ISBLANK(L94), "", L94*VLOOKUP($F94,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O94" s="45" t="str">
+        <v>15</v>
+      </c>
+      <c r="O94" s="45">
         <f>IF(ISBLANK(M94), "", M94*VLOOKUP($F94,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P94" s="44"/>
+        <v>30</v>
+      </c>
+      <c r="P94" s="44" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="95" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B95" s="41">
@@ -5212,30 +6260,48 @@
       </c>
       <c r="C95" s="42" t="str">
         <f>IF(ISBLANK(D95), "", _xlfn.CONCAT("T", TEXT(B95, "0000"), "/", VLOOKUP(D95, Internal!$B$35:C$39, 2, FALSE), IF(OR(D95="QA", D95="Revision"), _xlfn.CONCAT("/", H95), "")))</f>
-        <v/>
-      </c>
-      <c r="D95" s="44"/>
-      <c r="E95" s="43"/>
-      <c r="F95" s="43"/>
-      <c r="G95" s="44"/>
+        <v>T0085/M</v>
+      </c>
+      <c r="D95" s="44" t="s">
+        <v>30</v>
+      </c>
+      <c r="E95" s="43" t="s">
+        <v>31</v>
+      </c>
+      <c r="F95" s="43" t="s">
+        <v>32</v>
+      </c>
+      <c r="G95" s="44" t="s">
+        <v>33</v>
+      </c>
       <c r="H95" s="43"/>
-      <c r="I95" s="46"/>
-      <c r="J95" s="46"/>
+      <c r="I95" s="46">
+        <v>46101.645833333336</v>
+      </c>
+      <c r="J95" s="46">
+        <v>46101.649305555555</v>
+      </c>
       <c r="K95" s="45" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-      <c r="L95" s="47"/>
-      <c r="M95" s="47"/>
-      <c r="N95" s="45" t="str">
+        <f ca="1">IF(OR(I95="",J95=""),"",IF(AND(J95&lt;&gt;"",I95&gt;=NOW()),"Planned",IF(AND(J95&lt;&gt;"",J95&lt;NOW()),"Completed","Ongoing")))</f>
+        <v>Planned</v>
+      </c>
+      <c r="L95" s="47">
+        <v>8.3333333333333329E-2</v>
+      </c>
+      <c r="M95" s="47">
+        <v>8.3333333333333329E-2</v>
+      </c>
+      <c r="N95" s="45">
         <f>IF(ISBLANK(L95), "", L95*VLOOKUP($F95,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O95" s="45" t="str">
+        <v>4.1666666666666661</v>
+      </c>
+      <c r="O95" s="45">
         <f>IF(ISBLANK(M95), "", M95*VLOOKUP($F95,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P95" s="44"/>
+        <v>4.1666666666666661</v>
+      </c>
+      <c r="P95" s="44" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="96" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B96" s="41">
@@ -5243,30 +6309,48 @@
       </c>
       <c r="C96" s="42" t="str">
         <f>IF(ISBLANK(D96), "", _xlfn.CONCAT("T", TEXT(B96, "0000"), "/", VLOOKUP(D96, Internal!$B$35:C$39, 2, FALSE), IF(OR(D96="QA", D96="Revision"), _xlfn.CONCAT("/", H96), "")))</f>
-        <v/>
-      </c>
-      <c r="D96" s="44"/>
-      <c r="E96" s="43"/>
-      <c r="F96" s="43"/>
-      <c r="G96" s="44"/>
+        <v>T0086/O</v>
+      </c>
+      <c r="D96" s="44" t="s">
+        <v>134</v>
+      </c>
+      <c r="E96" s="43" t="s">
+        <v>62</v>
+      </c>
+      <c r="F96" s="43" t="s">
+        <v>135</v>
+      </c>
+      <c r="G96" s="44" t="s">
+        <v>136</v>
+      </c>
       <c r="H96" s="43"/>
-      <c r="I96" s="46"/>
-      <c r="J96" s="46"/>
+      <c r="I96" s="46">
+        <v>46101.708333333336</v>
+      </c>
+      <c r="J96" s="46">
+        <v>46101.715277777781</v>
+      </c>
       <c r="K96" s="45" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-      <c r="L96" s="47"/>
-      <c r="M96" s="47"/>
-      <c r="N96" s="45" t="str">
+        <f ca="1">IF(OR(I96="",J96=""),"",IF(AND(J96&lt;&gt;"",I96&gt;=NOW()),"Planned",IF(AND(J96&lt;&gt;"",J96&lt;NOW()),"Completed","Ongoing")))</f>
+        <v>Planned</v>
+      </c>
+      <c r="L96" s="47">
+        <v>0.08</v>
+      </c>
+      <c r="M96" s="47">
+        <v>0.08</v>
+      </c>
+      <c r="N96" s="45">
         <f>IF(ISBLANK(L96), "", L96*VLOOKUP($F96,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O96" s="45" t="str">
+        <v>2.4</v>
+      </c>
+      <c r="O96" s="45">
         <f>IF(ISBLANK(M96), "", M96*VLOOKUP($F96,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P96" s="44"/>
+        <v>2.4</v>
+      </c>
+      <c r="P96" s="44" t="s">
+        <v>137</v>
+      </c>
     </row>
     <row r="97" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B97" s="41">
@@ -5763,6 +6847,37 @@
         <v/>
       </c>
       <c r="P112" s="44"/>
+    </row>
+    <row r="113" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B113" s="41">
+        <v>103</v>
+      </c>
+      <c r="C113" s="42" t="str">
+        <f>IF(ISBLANK(D113), "", _xlfn.CONCAT("T", TEXT(B113, "0000"), "/", VLOOKUP(D113, Internal!$B$35:C$39, 2, FALSE), IF(OR(D113="QA", D113="Revision"), _xlfn.CONCAT("/", H113), "")))</f>
+        <v/>
+      </c>
+      <c r="D113" s="44"/>
+      <c r="E113" s="43"/>
+      <c r="F113" s="43"/>
+      <c r="G113" s="44"/>
+      <c r="H113" s="43"/>
+      <c r="I113" s="46"/>
+      <c r="J113" s="46"/>
+      <c r="K113" s="45" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+      <c r="L113" s="47"/>
+      <c r="M113" s="47"/>
+      <c r="N113" s="45" t="str">
+        <f>IF(ISBLANK(L113), "", L113*VLOOKUP($F113,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v/>
+      </c>
+      <c r="O113" s="45" t="str">
+        <f>IF(ISBLANK(M113), "", M113*VLOOKUP($F113,Internal!$B$26:$C$32,2,FALSE))</f>
+        <v/>
+      </c>
+      <c r="P113" s="44"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -5774,56 +6889,56 @@
     <mergeCell ref="C4:P4"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
-  <conditionalFormatting sqref="H11:H112">
-    <cfRule type="expression" dxfId="5" priority="3">
-      <formula>AND(H11&lt;&gt;"",COUNTIF($C$12:$C$112,H11)=0)</formula>
+  <conditionalFormatting sqref="H11:H113">
+    <cfRule type="expression" dxfId="1" priority="3">
+      <formula>AND(H11&lt;&gt;"",COUNTIF($C$12:$C$113,H11)=0)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J11:J32 J34:J35 J37:J112">
-    <cfRule type="expression" dxfId="4" priority="1">
+  <conditionalFormatting sqref="J11:J32 J34:J35 J37:J39 J52:J59 J61 J63:J71 J73:J91 J93:J113">
+    <cfRule type="expression" dxfId="0" priority="1">
       <formula>AND(I11&lt;&gt;"",J11&lt;&gt;"", I11&gt;J11)</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="9">
+  <dataValidations xWindow="1424" yWindow="1374" count="9">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Description" prompt="Provide a succint description of the task.  If not possible, the provide a link to a document where is is described." sqref="P10" xr:uid="{D0BF2996-BBAB-402C-8777-D22DB1423D76}"/>
-    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Expected workload" prompt="Enter the expected workload in hours or fractions." sqref="L11:L112" xr:uid="{AADDA758-A288-4920-A868-A656B94EE475}">
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Expected workload" prompt="Enter the expected workload in hours or fractions." sqref="M39:M43 M92 M82 M72 M60 L11:L113" xr:uid="{AADDA758-A288-4920-A868-A656B94EE475}">
       <formula1>0</formula1>
       <formula2>1024</formula2>
     </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Actual workload" prompt="Enter the actual workload in hours or fractions._x000a_" sqref="M11:M112" xr:uid="{FFAE3670-28C0-4D44-81DE-0074EF40B001}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Description" prompt="If actually necessary, then write a succint description and/or include a link to a document that provides further information." sqref="K11:K112 P11:P112" xr:uid="{4DDB20BC-C9D1-4AB5-9B81-3F9F25727EAD}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Costs" prompt="The costs are updated automatically.  Don't modify them manually" sqref="N11:O112" xr:uid="{3D1A9EDC-88F9-4796-ACC0-9C5DD1125EFE}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="ID" prompt="The IDs are updated automatically.  Don't modify them manually" sqref="C11:C112" xr:uid="{6C5AA884-EA5C-464F-AE09-58D1C86343FC}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="ORDER" prompt="Order numbers are internal data.  Do not change them._x000a_" sqref="B11:B112" xr:uid="{79B4C829-58F8-4180-8480-F4A0E1F5F1C5}"/>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Activity" prompt="Select the Activity to perfom.  Use &quot;Other&quot; only in truly exceptional cases." sqref="G11:G112" xr:uid="{402079F6-76CA-490B-9F74-CDFB1F7ED8BD}">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Actual workload" prompt="Enter the actual workload in hours or fractions._x000a_" sqref="M11:M38 M44:M59 M83:M91 M73:M81 M61:M71 M93:M113" xr:uid="{FFAE3670-28C0-4D44-81DE-0074EF40B001}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Description" prompt="If actually necessary, then write a succint description and/or include a link to a document that provides further information." sqref="P11:P113 K11:K113" xr:uid="{4DDB20BC-C9D1-4AB5-9B81-3F9F25727EAD}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Costs" prompt="The costs are updated automatically.  Don't modify them manually" sqref="N11:O113" xr:uid="{3D1A9EDC-88F9-4796-ACC0-9C5DD1125EFE}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="ID" prompt="The IDs are updated automatically.  Don't modify them manually" sqref="C11:C113" xr:uid="{6C5AA884-EA5C-464F-AE09-58D1C86343FC}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="ORDER" prompt="Order numbers are internal data.  Do not change them._x000a_" sqref="B11:B113" xr:uid="{79B4C829-58F8-4180-8480-F4A0E1F5F1C5}"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Activity" prompt="Select the Activity to perfom.  Use &quot;Other&quot; only in truly exceptional cases." sqref="G11:G113" xr:uid="{402079F6-76CA-490B-9F74-CDFB1F7ED8BD}">
       <formula1>INDIRECT(F11)</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Parent" prompt="Select the parent task if necessary.  Usually, only &quot;Quality Assurance&quot; and &quot;Revision&quot; tasks have parents." sqref="H11:H112" xr:uid="{D360DC77-273A-412B-AEBB-6D07121D9EA3}">
-      <formula1>$C$12:$C$112</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Parent" prompt="Select the parent task if necessary.  Usually, only &quot;Quality Assurance&quot; and &quot;Revision&quot; tasks have parents." sqref="H11:H113" xr:uid="{D360DC77-273A-412B-AEBB-6D07121D9EA3}">
+      <formula1>$C$12:$C$113</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="5">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xWindow="1424" yWindow="1374" count="5">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Role" prompt="Select a role from the select box.  Use &quot;other&quot; only in truly exceptional cases.  Consult your lecturer in such cases._x000a_" xr:uid="{A1102D1C-503C-44C5-9E57-51358D36832C}">
           <x14:formula1>
             <xm:f>Internal!$B$26:$B$32</xm:f>
           </x14:formula1>
-          <xm:sqref>F11:F112</xm:sqref>
+          <xm:sqref>F11:F113</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Type" prompt="Indicate the type of task." xr:uid="{FB2BBB7B-03FF-45CB-8A89-AFA40F81FC94}">
           <x14:formula1>
             <xm:f>Internal!$B$35:$B$39</xm:f>
           </x14:formula1>
-          <xm:sqref>D11:D112</xm:sqref>
+          <xm:sqref>D11:D113</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Assignee" prompt="Select the workmate the task is assigned to." xr:uid="{9667150F-C763-44E5-A661-FFC8169264CA}">
           <x14:formula1>
             <xm:f>Internal!$B$9:$B$14</xm:f>
           </x14:formula1>
-          <xm:sqref>E11:E112</xm:sqref>
+          <xm:sqref>E11:E113</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Start moment" prompt="Indicate the moment when the assignee starts working on this task.  Use format yy/mm/dd hh:mm." xr:uid="{3E697798-8BF9-4850-9C0F-D14A9C11C1F7}">
           <x14:formula1>
@@ -5832,7 +6947,7 @@
           <x14:formula2>
             <xm:f>Internal!$C$23</xm:f>
           </x14:formula2>
-          <xm:sqref>J33 I11:I112 J36</xm:sqref>
+          <xm:sqref>J33 J40:J51 J36 J62 J72 J92 I11:I113</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="End moment" prompt="Indicate the moment when the assignee finishes working on this task.  Use format yy/mm/dd hh:mm." xr:uid="{AA2B0FBE-439D-4BBE-9231-3859DD87C79A}">
           <x14:formula1>
@@ -5841,7 +6956,7 @@
           <x14:formula2>
             <xm:f>Internal!$C$23</xm:f>
           </x14:formula2>
-          <xm:sqref>J11:J32 J34:J35 J37:J112</xm:sqref>
+          <xm:sqref>J11:J32 J34:J35 J37:J39 J61 J52:J59 J73:J91 J63:J71 J93:J113</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -5852,47 +6967,47 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F28A4DB1-CB48-4778-AC73-C91746932E53}">
   <dimension ref="B2:P110"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="3" max="15" width="18.86328125" customWidth="1"/>
-    <col min="16" max="16" width="64.53125" customWidth="1"/>
+    <col min="16" max="16" width="64.59765625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:16" x14ac:dyDescent="0.45">
-      <c r="C2" s="55" t="s">
-        <v>85</v>
-      </c>
-      <c r="D2" s="55"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="55"/>
-      <c r="G2" s="55"/>
-      <c r="H2" s="55"/>
-      <c r="I2" s="55"/>
-      <c r="J2" s="55"/>
-      <c r="K2" s="55"/>
-      <c r="L2" s="55"/>
-      <c r="M2" s="55"/>
-      <c r="N2" s="55"/>
-      <c r="O2" s="55"/>
-      <c r="P2" s="55"/>
+      <c r="C2" s="56" t="s">
+        <v>138</v>
+      </c>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="56"/>
+      <c r="I2" s="56"/>
+      <c r="J2" s="56"/>
+      <c r="K2" s="56"/>
+      <c r="L2" s="56"/>
+      <c r="M2" s="56"/>
+      <c r="N2" s="56"/>
+      <c r="O2" s="56"/>
+      <c r="P2" s="56"/>
     </row>
     <row r="4" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="C4" s="53" t="s">
-        <v>75</v>
-      </c>
-      <c r="D4" s="53"/>
-      <c r="E4" s="53"/>
-      <c r="F4" s="53"/>
-      <c r="G4" s="53"/>
-      <c r="H4" s="53"/>
-      <c r="I4" s="53"/>
-      <c r="J4" s="53"/>
-      <c r="K4" s="53"/>
-      <c r="L4" s="53"/>
-      <c r="M4" s="53"/>
-      <c r="N4" s="53"/>
-      <c r="O4" s="53"/>
-      <c r="P4" s="53"/>
+      <c r="C4" s="57" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="57"/>
+      <c r="E4" s="57"/>
+      <c r="F4" s="57"/>
+      <c r="G4" s="57"/>
+      <c r="H4" s="57"/>
+      <c r="I4" s="57"/>
+      <c r="J4" s="57"/>
+      <c r="K4" s="57"/>
+      <c r="L4" s="57"/>
+      <c r="M4" s="57"/>
+      <c r="N4" s="57"/>
+      <c r="O4" s="57"/>
+      <c r="P4" s="57"/>
     </row>
     <row r="5" spans="2:16" x14ac:dyDescent="0.45">
       <c r="C5" s="5"/>
@@ -5911,11 +7026,11 @@
       <c r="P5" s="5"/>
     </row>
     <row r="6" spans="2:16" x14ac:dyDescent="0.45">
-      <c r="C6" s="57" t="s">
-        <v>68</v>
+      <c r="C6" s="54" t="s">
+        <v>11</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>69</v>
+        <v>12</v>
       </c>
       <c r="E6" s="35">
         <f>SUM(N11:N110)</f>
@@ -5934,9 +7049,9 @@
       <c r="P6" s="5"/>
     </row>
     <row r="7" spans="2:16" x14ac:dyDescent="0.45">
-      <c r="C7" s="57"/>
+      <c r="C7" s="54"/>
       <c r="D7" s="11" t="s">
-        <v>70</v>
+        <v>13</v>
       </c>
       <c r="E7" s="36">
         <f>SUM(O11:O110)</f>
@@ -5952,66 +7067,66 @@
       <c r="F9" s="7"/>
       <c r="G9" s="7"/>
       <c r="H9" s="7"/>
-      <c r="I9" s="58" t="s">
-        <v>51</v>
-      </c>
-      <c r="J9" s="58"/>
+      <c r="I9" s="55" t="s">
+        <v>14</v>
+      </c>
+      <c r="J9" s="55"/>
       <c r="K9" s="7"/>
-      <c r="L9" s="58" t="s">
-        <v>7</v>
-      </c>
-      <c r="M9" s="58"/>
-      <c r="N9" s="58" t="s">
-        <v>58</v>
-      </c>
-      <c r="O9" s="58"/>
+      <c r="L9" s="55" t="s">
+        <v>15</v>
+      </c>
+      <c r="M9" s="55"/>
+      <c r="N9" s="55" t="s">
+        <v>16</v>
+      </c>
+      <c r="O9" s="55"/>
       <c r="P9" s="7"/>
     </row>
     <row r="10" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B10" s="8" t="s">
-        <v>66</v>
+        <v>17</v>
       </c>
       <c r="C10" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D10" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="D10" s="9" t="s">
-        <v>59</v>
-      </c>
       <c r="E10" s="9" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="F10" s="9" t="s">
         <v>21</v>
       </c>
       <c r="G10" s="9" t="s">
-        <v>76</v>
+        <v>22</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I10" s="38" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="J10" s="38" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="K10" s="9" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="L10" s="38" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="M10" s="38" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="N10" s="38" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="O10" s="38" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="P10" s="9" t="s">
-        <v>67</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
@@ -9124,12 +10239,12 @@
     <mergeCell ref="I9:J9"/>
   </mergeCells>
   <conditionalFormatting sqref="H11:H110">
-    <cfRule type="expression" dxfId="3" priority="2">
+    <cfRule type="expression" dxfId="5" priority="2">
       <formula>AND(H11&lt;&gt;"",COUNTIF($C$11:$C$110,H11)=0)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J11:J110">
-    <cfRule type="expression" dxfId="2" priority="1">
+    <cfRule type="expression" dxfId="4" priority="1">
       <formula>AND(I11&lt;&gt;"",J11&lt;&gt;"", I11&gt;J11)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9201,47 +10316,47 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28A2F053-EB65-4682-A8B4-EF605DDDBF14}">
   <dimension ref="B2:P110"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="3" max="15" width="18.86328125" customWidth="1"/>
-    <col min="16" max="16" width="64.53125" customWidth="1"/>
+    <col min="16" max="16" width="64.59765625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:16" x14ac:dyDescent="0.45">
-      <c r="C2" s="55" t="s">
-        <v>86</v>
-      </c>
-      <c r="D2" s="55"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="55"/>
-      <c r="G2" s="55"/>
-      <c r="H2" s="55"/>
-      <c r="I2" s="55"/>
-      <c r="J2" s="55"/>
-      <c r="K2" s="55"/>
-      <c r="L2" s="55"/>
-      <c r="M2" s="55"/>
-      <c r="N2" s="55"/>
-      <c r="O2" s="55"/>
-      <c r="P2" s="55"/>
+      <c r="C2" s="56" t="s">
+        <v>139</v>
+      </c>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="56"/>
+      <c r="I2" s="56"/>
+      <c r="J2" s="56"/>
+      <c r="K2" s="56"/>
+      <c r="L2" s="56"/>
+      <c r="M2" s="56"/>
+      <c r="N2" s="56"/>
+      <c r="O2" s="56"/>
+      <c r="P2" s="56"/>
     </row>
     <row r="4" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="C4" s="53" t="s">
-        <v>75</v>
-      </c>
-      <c r="D4" s="53"/>
-      <c r="E4" s="53"/>
-      <c r="F4" s="53"/>
-      <c r="G4" s="53"/>
-      <c r="H4" s="53"/>
-      <c r="I4" s="53"/>
-      <c r="J4" s="53"/>
-      <c r="K4" s="53"/>
-      <c r="L4" s="53"/>
-      <c r="M4" s="53"/>
-      <c r="N4" s="53"/>
-      <c r="O4" s="53"/>
-      <c r="P4" s="53"/>
+      <c r="C4" s="57" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="57"/>
+      <c r="E4" s="57"/>
+      <c r="F4" s="57"/>
+      <c r="G4" s="57"/>
+      <c r="H4" s="57"/>
+      <c r="I4" s="57"/>
+      <c r="J4" s="57"/>
+      <c r="K4" s="57"/>
+      <c r="L4" s="57"/>
+      <c r="M4" s="57"/>
+      <c r="N4" s="57"/>
+      <c r="O4" s="57"/>
+      <c r="P4" s="57"/>
     </row>
     <row r="5" spans="2:16" x14ac:dyDescent="0.45">
       <c r="C5" s="5"/>
@@ -9260,11 +10375,11 @@
       <c r="P5" s="5"/>
     </row>
     <row r="6" spans="2:16" x14ac:dyDescent="0.45">
-      <c r="C6" s="57" t="s">
-        <v>68</v>
+      <c r="C6" s="54" t="s">
+        <v>11</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>69</v>
+        <v>12</v>
       </c>
       <c r="E6" s="35">
         <f>SUM(N11:N110)</f>
@@ -9283,9 +10398,9 @@
       <c r="P6" s="5"/>
     </row>
     <row r="7" spans="2:16" x14ac:dyDescent="0.45">
-      <c r="C7" s="57"/>
+      <c r="C7" s="54"/>
       <c r="D7" s="11" t="s">
-        <v>70</v>
+        <v>13</v>
       </c>
       <c r="E7" s="36">
         <f>SUM(O11:O110)</f>
@@ -9301,66 +10416,66 @@
       <c r="F9" s="7"/>
       <c r="G9" s="7"/>
       <c r="H9" s="7"/>
-      <c r="I9" s="58" t="s">
-        <v>51</v>
-      </c>
-      <c r="J9" s="58"/>
+      <c r="I9" s="55" t="s">
+        <v>14</v>
+      </c>
+      <c r="J9" s="55"/>
       <c r="K9" s="7"/>
-      <c r="L9" s="58" t="s">
-        <v>7</v>
-      </c>
-      <c r="M9" s="58"/>
-      <c r="N9" s="58" t="s">
-        <v>58</v>
-      </c>
-      <c r="O9" s="58"/>
+      <c r="L9" s="55" t="s">
+        <v>15</v>
+      </c>
+      <c r="M9" s="55"/>
+      <c r="N9" s="55" t="s">
+        <v>16</v>
+      </c>
+      <c r="O9" s="55"/>
       <c r="P9" s="7"/>
     </row>
     <row r="10" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B10" s="8" t="s">
-        <v>66</v>
+        <v>17</v>
       </c>
       <c r="C10" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D10" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="D10" s="9" t="s">
-        <v>59</v>
-      </c>
       <c r="E10" s="9" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="F10" s="9" t="s">
         <v>21</v>
       </c>
       <c r="G10" s="9" t="s">
-        <v>76</v>
+        <v>22</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I10" s="38" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="J10" s="38" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="K10" s="9" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="L10" s="38" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="M10" s="38" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="N10" s="38" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="O10" s="38" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="P10" s="9" t="s">
-        <v>67</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11" spans="2:16" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
@@ -12473,12 +13588,12 @@
     <mergeCell ref="I9:J9"/>
   </mergeCells>
   <conditionalFormatting sqref="H11:H110">
-    <cfRule type="expression" dxfId="1" priority="2">
+    <cfRule type="expression" dxfId="3" priority="2">
       <formula>AND(H11&lt;&gt;"",COUNTIF($C$11:$C$110,H11)=0)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J11:J110">
-    <cfRule type="expression" dxfId="0" priority="1">
+    <cfRule type="expression" dxfId="2" priority="1">
       <formula>AND(I11&lt;&gt;"",J11&lt;&gt;"", I11&gt;J11)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12550,58 +13665,58 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6230FA8A-EA33-4C76-AA54-C885D607690C}">
   <dimension ref="B2:J39"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="10" width="22" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B2" s="55" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" s="55"/>
-      <c r="D2" s="55"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="55"/>
-      <c r="G2" s="55"/>
-      <c r="H2" s="55"/>
-      <c r="I2" s="55"/>
-      <c r="J2" s="55"/>
+      <c r="B2" s="56" t="s">
+        <v>140</v>
+      </c>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="56"/>
+      <c r="I2" s="56"/>
+      <c r="J2" s="56"/>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B4" s="53" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" s="53"/>
-      <c r="D4" s="53"/>
-      <c r="E4" s="53"/>
-      <c r="F4" s="53"/>
-      <c r="G4" s="53"/>
-      <c r="H4" s="53"/>
-      <c r="I4" s="53"/>
-      <c r="J4" s="53"/>
+      <c r="B4" s="57" t="s">
+        <v>141</v>
+      </c>
+      <c r="C4" s="57"/>
+      <c r="D4" s="57"/>
+      <c r="E4" s="57"/>
+      <c r="F4" s="57"/>
+      <c r="G4" s="57"/>
+      <c r="H4" s="57"/>
+      <c r="I4" s="57"/>
+      <c r="J4" s="57"/>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B5" s="53"/>
-      <c r="C5" s="53"/>
-      <c r="D5" s="53"/>
-      <c r="E5" s="53"/>
-      <c r="F5" s="53"/>
-      <c r="G5" s="53"/>
-      <c r="H5" s="53"/>
-      <c r="I5" s="53"/>
-      <c r="J5" s="53"/>
+      <c r="B5" s="57"/>
+      <c r="C5" s="57"/>
+      <c r="D5" s="57"/>
+      <c r="E5" s="57"/>
+      <c r="F5" s="57"/>
+      <c r="G5" s="57"/>
+      <c r="H5" s="57"/>
+      <c r="I5" s="57"/>
+      <c r="J5" s="57"/>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B6" s="53"/>
-      <c r="C6" s="53"/>
-      <c r="D6" s="53"/>
-      <c r="E6" s="53"/>
-      <c r="F6" s="53"/>
-      <c r="G6" s="53"/>
-      <c r="H6" s="53"/>
-      <c r="I6" s="53"/>
-      <c r="J6" s="53"/>
+      <c r="B6" s="57"/>
+      <c r="C6" s="57"/>
+      <c r="D6" s="57"/>
+      <c r="E6" s="57"/>
+      <c r="F6" s="57"/>
+      <c r="G6" s="57"/>
+      <c r="H6" s="57"/>
+      <c r="I6" s="57"/>
+      <c r="J6" s="57"/>
     </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B7" s="5"/>
@@ -12616,7 +13731,7 @@
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B8" s="25" t="s">
-        <v>12</v>
+        <v>142</v>
       </c>
       <c r="C8" s="12"/>
       <c r="D8" s="12"/>
@@ -12629,7 +13744,7 @@
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B9" s="13" t="s">
-        <v>80</v>
+        <v>31</v>
       </c>
       <c r="C9" s="12"/>
       <c r="D9" s="12"/>
@@ -12642,7 +13757,7 @@
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B10" s="13" t="s">
-        <v>81</v>
+        <v>62</v>
       </c>
       <c r="C10" s="12"/>
       <c r="D10" s="12"/>
@@ -12655,7 +13770,7 @@
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B11" s="13" t="s">
-        <v>82</v>
+        <v>48</v>
       </c>
       <c r="C11" s="12"/>
       <c r="D11" s="12"/>
@@ -12668,7 +13783,7 @@
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B12" s="13" t="s">
-        <v>83</v>
+        <v>58</v>
       </c>
       <c r="C12" s="12"/>
       <c r="D12" s="12"/>
@@ -12681,7 +13796,7 @@
     </row>
     <row r="13" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B13" s="13" t="s">
-        <v>84</v>
+        <v>60</v>
       </c>
       <c r="C13" s="12"/>
       <c r="D13" s="12"/>
@@ -12694,7 +13809,7 @@
     </row>
     <row r="14" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B14" s="14" t="s">
-        <v>77</v>
+        <v>143</v>
       </c>
       <c r="C14" s="12"/>
       <c r="D14" s="12"/>
@@ -12718,7 +13833,7 @@
     </row>
     <row r="16" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B16" s="26" t="s">
-        <v>14</v>
+        <v>144</v>
       </c>
       <c r="C16" s="12"/>
       <c r="D16" s="12"/>
@@ -12731,7 +13846,7 @@
     </row>
     <row r="17" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B17" s="15" t="s">
-        <v>15</v>
+        <v>145</v>
       </c>
       <c r="C17" s="12"/>
       <c r="D17" s="12"/>
@@ -12744,7 +13859,7 @@
     </row>
     <row r="18" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B18" s="15" t="s">
-        <v>16</v>
+        <v>146</v>
       </c>
       <c r="C18" s="12"/>
       <c r="D18" s="12"/>
@@ -12757,7 +13872,7 @@
     </row>
     <row r="19" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B19" s="16" t="s">
-        <v>17</v>
+        <v>147</v>
       </c>
       <c r="C19" s="12"/>
       <c r="D19" s="12"/>
@@ -12781,7 +13896,7 @@
     </row>
     <row r="21" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B21" s="26" t="s">
-        <v>54</v>
+        <v>148</v>
       </c>
       <c r="C21" s="12"/>
       <c r="D21" s="12"/>
@@ -12807,7 +13922,7 @@
     </row>
     <row r="23" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B23" s="18" t="s">
-        <v>55</v>
+        <v>149</v>
       </c>
       <c r="C23" s="12"/>
       <c r="D23" s="12"/>
@@ -12831,13 +13946,13 @@
     </row>
     <row r="25" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B25" s="27" t="s">
-        <v>22</v>
+        <v>150</v>
       </c>
       <c r="C25" s="28" t="s">
-        <v>57</v>
+        <v>151</v>
       </c>
       <c r="D25" s="28" t="s">
-        <v>28</v>
+        <v>152</v>
       </c>
       <c r="E25" s="29"/>
       <c r="F25" s="29"/>
@@ -12848,22 +13963,22 @@
     </row>
     <row r="26" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B26" s="19" t="s">
-        <v>29</v>
+        <v>153</v>
       </c>
       <c r="C26" s="51">
         <v>0</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>30</v>
+        <v>154</v>
       </c>
       <c r="E26" s="12" t="s">
-        <v>31</v>
+        <v>155</v>
       </c>
       <c r="F26" s="12" t="s">
-        <v>50</v>
+        <v>156</v>
       </c>
       <c r="G26" s="12" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="H26" s="12"/>
       <c r="I26" s="12"/>
@@ -12871,148 +13986,148 @@
     </row>
     <row r="27" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B27" s="19" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="C27" s="51">
         <v>50</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="E27" s="12" t="s">
-        <v>33</v>
+        <v>66</v>
       </c>
       <c r="F27" s="12" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G27" s="12" t="s">
+        <v>157</v>
+      </c>
+      <c r="H27" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="H27" s="12" t="s">
-        <v>36</v>
-      </c>
       <c r="I27" s="12" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="J27" s="20"/>
     </row>
     <row r="28" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B28" s="19" t="s">
-        <v>24</v>
+        <v>158</v>
       </c>
       <c r="C28" s="51">
         <v>40</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>37</v>
+        <v>159</v>
       </c>
       <c r="E28" s="12" t="s">
-        <v>38</v>
+        <v>160</v>
       </c>
       <c r="F28" s="12" t="s">
+        <v>161</v>
+      </c>
+      <c r="G28" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="H28" s="12" t="s">
         <v>39</v>
-      </c>
-      <c r="G28" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="H28" s="12" t="s">
-        <v>32</v>
       </c>
       <c r="I28" s="12"/>
       <c r="J28" s="20"/>
     </row>
     <row r="29" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B29" s="19" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="C29" s="51">
         <v>25</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>89</v>
+        <v>43</v>
       </c>
       <c r="E29" s="12" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="F29" s="12" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="G29" s="12" t="s">
-        <v>42</v>
+        <v>162</v>
       </c>
       <c r="H29" s="12" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I29" s="12" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="J29" s="20"/>
     </row>
     <row r="30" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B30" s="19" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="C30" s="51">
         <v>30</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>43</v>
+        <v>163</v>
       </c>
       <c r="E30" s="12" t="s">
-        <v>87</v>
+        <v>50</v>
       </c>
       <c r="F30" s="12" t="s">
-        <v>44</v>
+        <v>164</v>
       </c>
       <c r="G30" s="12" t="s">
-        <v>45</v>
+        <v>165</v>
       </c>
       <c r="H30" s="12" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I30" s="12" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="J30" s="20"/>
     </row>
     <row r="31" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B31" s="21" t="s">
-        <v>27</v>
+        <v>135</v>
       </c>
       <c r="C31" s="51">
         <v>30</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>88</v>
+        <v>166</v>
       </c>
       <c r="E31" s="12" t="s">
-        <v>46</v>
+        <v>136</v>
       </c>
       <c r="F31" s="12" t="s">
-        <v>47</v>
+        <v>167</v>
       </c>
       <c r="G31" s="12" t="s">
-        <v>48</v>
+        <v>168</v>
       </c>
       <c r="H31" s="12" t="s">
-        <v>49</v>
+        <v>169</v>
       </c>
       <c r="I31" s="12" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J31" s="20" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
     </row>
     <row r="32" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B32" s="22" t="s">
-        <v>56</v>
+        <v>134</v>
       </c>
       <c r="C32" s="52">
         <v>10</v>
       </c>
       <c r="D32" s="23" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="E32" s="23"/>
       <c r="F32" s="23"/>
@@ -13034,10 +14149,10 @@
     </row>
     <row r="34" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B34" s="33" t="s">
-        <v>60</v>
+        <v>170</v>
       </c>
       <c r="C34" s="34" t="s">
-        <v>63</v>
+        <v>171</v>
       </c>
       <c r="D34" s="12"/>
       <c r="E34" s="12"/>
@@ -13049,10 +14164,10 @@
     </row>
     <row r="35" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B35" s="21" t="s">
-        <v>64</v>
+        <v>30</v>
       </c>
       <c r="C35" s="31" t="s">
-        <v>74</v>
+        <v>172</v>
       </c>
       <c r="D35" s="12"/>
       <c r="E35" s="12"/>
@@ -13064,10 +14179,10 @@
     </row>
     <row r="36" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B36" s="21" t="s">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="C36" s="20" t="s">
-        <v>72</v>
+        <v>173</v>
       </c>
       <c r="D36" s="12"/>
       <c r="E36" s="12"/>
@@ -13079,10 +14194,10 @@
     </row>
     <row r="37" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B37" s="21" t="s">
-        <v>65</v>
+        <v>174</v>
       </c>
       <c r="C37" s="20" t="s">
-        <v>65</v>
+        <v>174</v>
       </c>
       <c r="D37" s="12"/>
       <c r="E37" s="12"/>
@@ -13094,10 +14209,10 @@
     </row>
     <row r="38" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B38" s="21" t="s">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="C38" s="20" t="s">
-        <v>71</v>
+        <v>175</v>
       </c>
       <c r="D38" s="12"/>
       <c r="E38" s="12"/>
@@ -13109,10 +14224,10 @@
     </row>
     <row r="39" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B39" s="32" t="s">
-        <v>56</v>
+        <v>134</v>
       </c>
       <c r="C39" s="24" t="s">
-        <v>73</v>
+        <v>176</v>
       </c>
       <c r="D39" s="12"/>
       <c r="E39" s="12"/>
